--- a/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
+++ b/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
@@ -21,7 +21,7 @@
     <sheet name="LIMITES CEO" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TAREAS'!$A$4:$F$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TAREAS'!$A$4:$G$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -109,12 +109,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -188,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -222,17 +222,14 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -255,13 +252,13 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -677,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -746,23 +743,23 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"01.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"01.??.??")</f>
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"01.??.??",TAREAS!$E$5:$E$63,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"01.??.??",TAREAS!$E$5:$E$64,"Hecha")</f>
         <v/>
       </c>
       <c r="D4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"01.??.??",TAREAS!$E$5:$E$63,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"01.??.??",TAREAS!$E$5:$E$64,"En curso")</f>
         <v/>
       </c>
       <c r="E4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"01.??.??",TAREAS!$E$5:$E$63,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"01.??.??",TAREAS!$E$5:$E$64,"Pendiente")</f>
         <v/>
       </c>
       <c r="F4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"01.??.??",TAREAS!$E$5:$E$63,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"01.??.??",TAREAS!$E$5:$E$64,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G4" s="6">
@@ -777,23 +774,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"02.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"02.??.??")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"02.??.??",TAREAS!$E$5:$E$63,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"02.??.??",TAREAS!$E$5:$E$64,"Hecha")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"02.??.??",TAREAS!$E$5:$E$63,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"02.??.??",TAREAS!$E$5:$E$64,"En curso")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"02.??.??",TAREAS!$E$5:$E$63,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"02.??.??",TAREAS!$E$5:$E$64,"Pendiente")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"02.??.??",TAREAS!$E$5:$E$63,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"02.??.??",TAREAS!$E$5:$E$64,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G5" s="6">
@@ -808,23 +805,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"03.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"03.??.??")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"03.??.??",TAREAS!$E$5:$E$63,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"03.??.??",TAREAS!$E$5:$E$64,"Hecha")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"03.??.??",TAREAS!$E$5:$E$63,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"03.??.??",TAREAS!$E$5:$E$64,"En curso")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"03.??.??",TAREAS!$E$5:$E$63,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"03.??.??",TAREAS!$E$5:$E$64,"Pendiente")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"03.??.??",TAREAS!$E$5:$E$63,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"03.??.??",TAREAS!$E$5:$E$64,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G6" s="6">
@@ -839,23 +836,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"04.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"04.??.??")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"04.??.??",TAREAS!$E$5:$E$63,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"04.??.??",TAREAS!$E$5:$E$64,"Hecha")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"04.??.??",TAREAS!$E$5:$E$63,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"04.??.??",TAREAS!$E$5:$E$64,"En curso")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"04.??.??",TAREAS!$E$5:$E$63,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"04.??.??",TAREAS!$E$5:$E$64,"Pendiente")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"04.??.??",TAREAS!$E$5:$E$63,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"04.??.??",TAREAS!$E$5:$E$64,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G7" s="6">
@@ -870,23 +867,23 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"05.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"05.??.??")</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"05.??.??",TAREAS!$E$5:$E$63,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"05.??.??",TAREAS!$E$5:$E$64,"Hecha")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"05.??.??",TAREAS!$E$5:$E$63,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"05.??.??",TAREAS!$E$5:$E$64,"En curso")</f>
         <v/>
       </c>
       <c r="E8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"05.??.??",TAREAS!$E$5:$E$63,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"05.??.??",TAREAS!$E$5:$E$64,"Pendiente")</f>
         <v/>
       </c>
       <c r="F8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"05.??.??",TAREAS!$E$5:$E$63,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"05.??.??",TAREAS!$E$5:$E$64,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G8" s="6">
@@ -901,23 +898,23 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"06.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"06.??.??")</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"06.??.??",TAREAS!$E$5:$E$63,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"06.??.??",TAREAS!$E$5:$E$64,"Hecha")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"06.??.??",TAREAS!$E$5:$E$63,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"06.??.??",TAREAS!$E$5:$E$64,"En curso")</f>
         <v/>
       </c>
       <c r="E9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"06.??.??",TAREAS!$E$5:$E$63,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"06.??.??",TAREAS!$E$5:$E$64,"Pendiente")</f>
         <v/>
       </c>
       <c r="F9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"06.??.??",TAREAS!$E$5:$E$63,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"06.??.??",TAREAS!$E$5:$E$64,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G9" s="6">
@@ -932,23 +929,23 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"07.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"07.??.??")</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"07.??.??",TAREAS!$E$5:$E$63,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"07.??.??",TAREAS!$E$5:$E$64,"Hecha")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"07.??.??",TAREAS!$E$5:$E$63,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"07.??.??",TAREAS!$E$5:$E$64,"En curso")</f>
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"07.??.??",TAREAS!$E$5:$E$63,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"07.??.??",TAREAS!$E$5:$E$64,"Pendiente")</f>
         <v/>
       </c>
       <c r="F10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$63,"07.??.??",TAREAS!$E$5:$E$63,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$64,"07.??.??",TAREAS!$E$5:$E$64,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G10" s="6">
@@ -1039,33 +1036,33 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>02.02.02</t>
+          <t>02.03.01</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Coste relativo: coste ÷ movimiento medio, en % (el número clave). Coste de USDJPY corregido a 1,16 pips</t>
+          <t>Revisión independiente de método, fuentes y números</t>
         </is>
       </c>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>Bloqueada</t>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>02.03.01</t>
+          <t>03.01.08</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Revisión independiente de método, fuentes y números</t>
+          <t>Prueba de fuego de las barreras (regla 13): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
         </is>
       </c>
       <c r="C17" s="4" t="n"/>
@@ -1078,87 +1075,109 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>03.01.11</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>PROXIMA PUERTA</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>G1 — elegir mercado y tamaño de vela (criterios en la hoja PUERTAS)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>OBJETIVO DEL MES</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Llegar al 1 de septiembre con respuesta a: ¿existe alguna estrategia que merezca pasar a demo?</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>FUENTE DE VERDAD</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>00-direccion/WBS.md — este Excel se genera de ahi. Si discrepan, manda el texto.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>LEYENDA</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Hecha</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>En curso</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>Bloqueada</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B19:G19"/>
+  <mergeCells count="9">
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B22:G22"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B21:G21"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G11">
     <cfRule type="dataBar" priority="1">
@@ -1459,7 +1478,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="41" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>Lo cierra el equipo, sin consultar</t>
         </is>
@@ -1476,7 +1495,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="41" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>Llega al CEO, en el informe semanal</t>
         </is>
@@ -1489,7 +1508,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="41" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>Llega al CEO como excepción inmediata (se para hasta respuesta)</t>
         </is>
@@ -1504,7 +1523,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Llega al CEO solo en una puerta</t>
         </is>
@@ -1516,14 +1535,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>FORMATO OBLIGATORIO DE FICHA DE DECISION (regla 10)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="100" customHeight="1">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>D[n] — [Qué se decide, una línea]
 A) [opción]   B) [opción]   C) [opción]
@@ -1549,7 +1568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -1565,21 +1584,35 @@
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Horizonte: 1 mes. Evaluación el 1 de septiembre (puerta GM).</t>
+          <t>Horizonte: 1 mes. Evaluación el 1 de septiembre (puerta GM). (D-5)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Tiempo del CEO: 1 hora, lunes.</t>
+          <t>FECHA TOPE: 01/12/2026 (D-12). Si a esa fecha no hay ninguna estrategia en demo, el proyecto se cierra y se escribe el informe de por qué. Antes del 01/08/2026 no existía ninguna fecha de parada.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Dinero real (pendiente de confirmar, ficha D5): capital 1.000-2.000 €, parada dura propuesta en -25%. Nota: el CEO mencionó tolerar caídas del 50-60%, incompatible con parar en -25%; recuperarse de -25% exige +33%, de -50% exige +100% y de -60% exige +150%.</t>
+          <t>Revisión de avance el día 1 de cada mes (D-12): 01/09 (= GM), 01/10 y 01/11. Cada una puede PARAR el proyecto. Pregunta fija: «¿avanza por buen camino?».</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Tiempo del CEO: 1 hora los lunes, como MÍNIMO GARANTIZADO, no como techo (D-4 + D-13). Máximo 5 fichas de decisión por revisión; si hay más, el orquestador prioriza y las sobrantes esperan al lunes siguiente. El CEO sigue el proyecto a diario, lo que NO amplía lo que se le puede preguntar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Dinero real (D-14): capital 1.000-2.000 € (ya es entrada de G1-C6, D-11; cambiarlo obliga a re-verificar G1-C6). AVISO a -25% del capital inicial ingresado, que no para nada: se reporta y decide el CEO. PARADA DURA AUTOMÁTICA a -30% del capital inicial, aplicada por el bot de forma CONTINUA y sin exención activable desde dentro (regla 26). Se mide sobre el capital inicial ingresado, no sobre el máximo alcanzado. Recuperar desde -30% exige +43%.</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1627,86 +1660,86 @@
       <c r="I1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Orden calculado de WBS.md: (1) una tarea entra en la cola cuando TODAS sus dependencias estan hechas; (2) primero lo ya empezado; (3) despues el PRODUCTO antes que el MOTOR (regla 12: el motor no manda); (4) a igualdad, orden de codigo WBS (regla 4). MOTOR = fases 03 y 07 y lo que su texto marque como tal. DESBLOQUEA = tareas vivas que la esperan directamente · EN CADENA = todas las que quedan detras contando el efecto domino.</t>
         </is>
       </c>
-      <c r="B2" s="23" t="n"/>
-      <c r="C2" s="23" t="n"/>
-      <c r="D2" s="23" t="n"/>
-      <c r="E2" s="23" t="n"/>
-      <c r="F2" s="23" t="n"/>
-      <c r="G2" s="23" t="n"/>
-      <c r="H2" s="23" t="n"/>
-      <c r="I2" s="23" t="n"/>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="22" t="n"/>
+      <c r="F2" s="22" t="n"/>
+      <c r="G2" s="22" t="n"/>
+      <c r="H2" s="22" t="n"/>
+      <c r="I2" s="22" t="n"/>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>AHORA — EQUIPO</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>01.02.02 — Trasplante pieza a pieza desde gb2 (D6=B). Una tarea por pieza, cada una con su criterio de aceptación (ver sección Trasplante). Ninguna entra sin pasar su prueba ejecutada</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="26" t="inlineStr">
-        <is>
-          <t>Crítico + Constructores</t>
+      <c r="B4" s="24" t="n"/>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>02.03.01 — Revisión independiente de método, fuentes y números</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="n"/>
+      <c r="E4" s="24" t="n"/>
+      <c r="F4" s="24" t="n"/>
+      <c r="G4" s="24" t="n"/>
+      <c r="H4" s="24" t="n"/>
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>AHORA — CEO</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n"/>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="B5" s="27" t="n"/>
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>01.01.01 — Aprobar plan y reglas</t>
         </is>
       </c>
-      <c r="D5" s="28" t="n"/>
-      <c r="E5" s="28" t="n"/>
-      <c r="F5" s="28" t="n"/>
-      <c r="G5" s="28" t="n"/>
-      <c r="H5" s="28" t="n"/>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="27" t="n"/>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="27" t="n"/>
+      <c r="H5" s="27" t="n"/>
+      <c r="I5" s="28" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>CUELLO DE BOTELLA</t>
         </is>
       </c>
-      <c r="B6" s="31" t="n"/>
-      <c r="C6" s="32" t="inlineStr">
-        <is>
-          <t>01.01.01 — Aprobar plan y reglas. Detras de ella esperan 27 de las 44 tareas vivas.</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="n"/>
-      <c r="E6" s="31" t="n"/>
-      <c r="F6" s="31" t="n"/>
-      <c r="G6" s="31" t="n"/>
-      <c r="H6" s="31" t="n"/>
-      <c r="I6" s="32" t="inlineStr">
-        <is>
-          <t>CEO</t>
+      <c r="B6" s="30" t="n"/>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>02.03.01 — Revisión independiente de método, fuentes y números. Detras de ella esperan 18 de las 38 tareas vivas.</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="n"/>
+      <c r="E6" s="30" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
+      <c r="H6" s="30" t="n"/>
+      <c r="I6" s="31" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
         </is>
       </c>
     </row>
@@ -1758,25 +1791,25 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
-        <is>
-          <t>SE PUEDE TRABAJAR YA — 11 tareas, en este orden</t>
-        </is>
-      </c>
-      <c r="B9" s="33" t="n"/>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="33" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="33" t="n"/>
-      <c r="H9" s="33" t="n"/>
-      <c r="I9" s="33" t="n"/>
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>SE PUEDE TRABAJAR YA — 13 tareas, en este orden</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="n"/>
+      <c r="C9" s="32" t="n"/>
+      <c r="D9" s="32" t="n"/>
+      <c r="E9" s="32" t="n"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="32" t="n"/>
+      <c r="H9" s="32" t="n"/>
+      <c r="I9" s="32" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>01.01.01</t>
         </is>
@@ -1786,7 +1819,7 @@
           <t>Aprobar plan y reglas</t>
         </is>
       </c>
-      <c r="D10" s="29" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
@@ -1801,12 +1834,8 @@
           <t>En curso</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>27</v>
-      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -1817,19 +1846,19 @@
       <c r="A11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>01.02.02</t>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>02.03.01</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Trasplante pieza a pieza desde gb2 (D6=B). Una tarea por pieza, cada una con su criterio de aceptación (ver sección Trasplante). Ninguna entra sin pasar su prueba ejecutada</t>
+          <t>Revisión independiente de método, fuentes y números</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Crítico + Constructores</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1837,13 +1866,17 @@
           <t>PRODUCTO</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>18</v>
+      </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -1854,19 +1887,19 @@
       <c r="A12" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="34" t="inlineStr">
-        <is>
-          <t>04.02.01</t>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>01.02.02</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
+          <t>Trasplante pieza a pieza desde gb2 (D6=B). Una tarea por pieza, cada una con su criterio de aceptación (ver sección Trasplante). Ninguna entra sin pasar su prueba ejecutada</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Crítico + Constructores</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1879,12 +1912,8 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>16</v>
-      </c>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -1895,24 +1924,24 @@
       <c r="A13" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>01.02.03</t>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>02.01.01</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Auditar el catálogo awesome-claude-code y proponer máximo 4 piezas concretas para el motor, con motivo y coste de integración. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="E13" s="35" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
+          <t>Confirmar 8 candidatos: EURUSD, GBPUSD, USDJPY, AUDUSD, USDCHF, XAUUSD, BTC, ETH</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1932,24 +1961,24 @@
       <c r="A14" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="34" t="inlineStr">
-        <is>
-          <t>03.01.03</t>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Ejecución desatendida: arranques programados, permisos AMPLIOS por defecto (git como red de seguridad) y topes de gasto</t>
+          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E14" s="35" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
+          <t>Investigador</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1958,10 +1987,10 @@
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
@@ -1973,22 +2002,22 @@
       <c r="A15" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>03.01.04</t>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>01.02.03</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Plan de respaldo de modelos: si un modelo no está disponible o rechaza, el agente sigue con su respaldo y lo anota</t>
+          <t>Auditar el catálogo awesome-claude-code y proponer máximo 4 piezas concretas para el motor, con motivo y coste de integración. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E15" s="35" t="inlineStr">
+          <t>Investigador</t>
+        </is>
+      </c>
+      <c r="E15" s="34" t="inlineStr">
         <is>
           <t>MOTOR</t>
         </is>
@@ -1998,12 +2027,8 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -2014,22 +2039,22 @@
       <c r="A16" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="34" t="inlineStr">
-        <is>
-          <t>03.01.06</t>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>03.01.03</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Plantilla y automatismo de fichas de decisión: el secretario prepara cada decisión del CEO en el formato obligatorio y la adjunta al informe semanal</t>
+          <t>Ejecución desatendida: arranques programados, permisos AMPLIOS por defecto (git como red de seguridad) y topes de gasto</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
-        </is>
-      </c>
-      <c r="E16" s="35" t="inlineStr">
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E16" s="34" t="inlineStr">
         <is>
           <t>MOTOR</t>
         </is>
@@ -2040,10 +2065,10 @@
         </is>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -2055,14 +2080,14 @@
       <c r="A17" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>03.01.09</t>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>03.01.04</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Enrutado por tipo de tarea y comprobación de que el WBS genera tareas de cada tipo de agente (regla 26)</t>
+          <t>Plan de respaldo de modelos: si un modelo no está disponible o rechaza, el agente sigue con su respaldo y lo anota</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -2070,7 +2095,7 @@
           <t>Constructores</t>
         </is>
       </c>
-      <c r="E17" s="35" t="inlineStr">
+      <c r="E17" s="34" t="inlineStr">
         <is>
           <t>MOTOR</t>
         </is>
@@ -2080,8 +2105,12 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -2092,22 +2121,22 @@
       <c r="A18" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="34" t="inlineStr">
-        <is>
-          <t>03.01.10</t>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>03.01.06</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Testbed sintético de invarianza: resultado de referencia fijo que debe reproducirse tras cualquier cambio del motor</t>
+          <t>Plantilla y automatismo de fichas de decisión: el secretario prepara cada decisión del CEO en el formato obligatorio y la adjunta al informe semanal</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E18" s="35" t="inlineStr">
+          <t>Secretario</t>
+        </is>
+      </c>
+      <c r="E18" s="34" t="inlineStr">
         <is>
           <t>MOTOR</t>
         </is>
@@ -2117,8 +2146,12 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -2129,14 +2162,14 @@
       <c r="A19" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>07.01.01</t>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>03.01.09</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
+          <t>Enrutado por tipo de tarea y comprobación de que el WBS genera tareas de cada tipo de agente (regla 26)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2144,7 +2177,7 @@
           <t>Constructores</t>
         </is>
       </c>
-      <c r="E19" s="35" t="inlineStr">
+      <c r="E19" s="34" t="inlineStr">
         <is>
           <t>MOTOR</t>
         </is>
@@ -2166,14 +2199,14 @@
       <c r="A20" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="34" t="inlineStr">
-        <is>
-          <t>07.01.02</t>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>03.01.10</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
+          <t>Testbed sintético de invarianza: resultado de referencia fijo que debe reproducirse tras cualquier cambio del motor</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -2181,7 +2214,7 @@
           <t>Constructores</t>
         </is>
       </c>
-      <c r="E20" s="35" t="inlineStr">
+      <c r="E20" s="34" t="inlineStr">
         <is>
           <t>MOTOR</t>
         </is>
@@ -2200,44 +2233,64 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="33" t="inlineStr">
-        <is>
-          <t>ESPERANDO A OTRA TAREA — 33 tareas, en orden de codigo WBS</t>
-        </is>
-      </c>
-      <c r="B21" s="33" t="n"/>
-      <c r="C21" s="33" t="n"/>
-      <c r="D21" s="33" t="n"/>
-      <c r="E21" s="33" t="n"/>
-      <c r="F21" s="33" t="n"/>
-      <c r="G21" s="33" t="n"/>
-      <c r="H21" s="33" t="n"/>
-      <c r="I21" s="33" t="n"/>
+      <c r="A21" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>07.01.01</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E21" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>nada: se puede empezar ya</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B22" s="34" t="inlineStr">
-        <is>
-          <t>01.01.02</t>
+      <c r="A22" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>07.01.02</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Aprobar criterios de la puerta G1</t>
-        </is>
-      </c>
-      <c r="D22" s="29" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
+          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E22" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2245,56 +2298,28 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>25</v>
-      </c>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>01.01.01 (en curso, CEO)</t>
+          <t>nada: se puede empezar ya</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B23" s="34" t="inlineStr">
-        <is>
-          <t>01.01.03</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Fijar límites: fecha tope, horas CEO/semana, pérdida máxima futura</t>
-        </is>
-      </c>
-      <c r="D23" s="29" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>01.01.01 (en curso, CEO)</t>
-        </is>
-      </c>
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>ESPERANDO A OTRA TAREA — 25 tareas, en orden de codigo WBS</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="32" t="n"/>
+      <c r="E23" s="32" t="n"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="32" t="n"/>
+      <c r="H23" s="32" t="n"/>
+      <c r="I23" s="32" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2302,19 +2327,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B24" s="34" t="inlineStr">
-        <is>
-          <t>02.01.01</t>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>02.03.02</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Confirmar 8 candidatos: EURUSD, GBPUSD, USDJPY, AUDUSD, USDCHF, XAUUSD, BTC, ETH</t>
-        </is>
-      </c>
-      <c r="D24" s="29" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
+          <t>Informe de decisión: 3-5 mercados poco correlacionados + 1-2 velas</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2328,14 +2353,14 @@
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>01.01.02 (pendiente, CEO)</t>
+          <t>02.03.01 (en curso, Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2345,19 +2370,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B25" s="34" t="inlineStr">
-        <is>
-          <t>02.01.02</t>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>02.03.03</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Costes típicos de operar por mercado (PROVISIONAL hasta 04.01.02)</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Investigador</t>
+          <t>PUERTA G1: el CEO elige</t>
+        </is>
+      </c>
+      <c r="D25" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2374,11 +2399,11 @@
         <v>1</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>02.01.01 (pendiente, CEO + Orquestador)</t>
+          <t>02.03.02 (pendiente, Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2388,24 +2413,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B26" s="34" t="inlineStr">
-        <is>
-          <t>02.02.01</t>
+      <c r="B26" s="33" t="inlineStr">
+        <is>
+          <t>03.01.05</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>CORREGIDA 29/07: descargar precios y CALCULAR el ATR de 15m, 1h y 4h (no buscarlo publicado: no existe). Script atr_local.py</t>
+          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Constructor de datos</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
+          <t>Orquestador</t>
+        </is>
+      </c>
+      <c r="E26" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -2413,15 +2438,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>20</v>
-      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>02.01.01 (pendiente, CEO + Orquestador)</t>
+          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2431,40 +2452,36 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B27" s="34" t="inlineStr">
-        <is>
-          <t>02.02.02</t>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>03.01.07</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Coste relativo: coste ÷ movimiento medio, en % (el número clave). Coste de USDJPY corregido a 1,16 pips</t>
+          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Constructor de datos</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="inlineStr">
-        <is>
-          <t>Bloqueada</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>19</v>
-      </c>
+          <t>Secretario</t>
+        </is>
+      </c>
+      <c r="E27" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>02.01.02 (pendiente, Investigador), 02.02.01 (pendiente, Constructor de datos)</t>
+          <t>03.01.06 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -2474,40 +2491,40 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B28" s="34" t="inlineStr">
-        <is>
-          <t>02.02.03</t>
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>03.01.08</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>CORREGIDA 30/07: CALCULAR la matriz de correlaciones en 3 ventanas (3 meses, 1 año, 2 años) con hora de corte única (22:00 UTC) y en la vela elegida, no solo diaria. No existe publicada de forma homogénea</t>
+          <t>Prueba de fuego de las barreras (regla 13): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Constructor de datos</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>Crítico</t>
+        </is>
+      </c>
+      <c r="E28" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
         </is>
       </c>
       <c r="G28" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>02.01.01 (pendiente, CEO + Orquestador)</t>
+          <t>03.01.03 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2517,40 +2534,36 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B29" s="34" t="inlineStr">
-        <is>
-          <t>02.02.05</t>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>03.01.11</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>NUEVA: coste de mantener posición de un día para otro (swap/financiación) en los 8 instrumentos, 2-3 brokers. En cripto CFD puede superar varias veces al spread</t>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>19</v>
-      </c>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E29" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>02.01.01 (pendiente, CEO + Orquestador)</t>
+          <t>03.01.08 (en curso, Crítico)</t>
         </is>
       </c>
     </row>
@@ -2560,19 +2573,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B30" s="34" t="inlineStr">
-        <is>
-          <t>02.03.01</t>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Revisión independiente de método, fuentes y números</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Orquestador</t>
+          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
+        </is>
+      </c>
+      <c r="D30" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2580,20 +2593,20 @@
           <t>PRODUCTO</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>En curso</t>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>02.02.01 (pendiente, Constructor de datos), 02.02.02 (bloqueada, Constructor de datos), 02.02.03 (pendiente, Constructor de datos), 02.02.05 (pendiente, Investigador)</t>
+          <t>02.03.03 (pendiente, CEO)</t>
         </is>
       </c>
     </row>
@@ -2603,19 +2616,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B31" s="34" t="inlineStr">
-        <is>
-          <t>02.03.02</t>
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>04.01.02</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Informe de decisión: 3-5 mercados poco correlacionados + 1-2 velas</t>
+          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2628,15 +2641,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>17</v>
-      </c>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>02.03.01 (en curso, Orquestador)</t>
+          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2646,19 +2655,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B32" s="34" t="inlineStr">
-        <is>
-          <t>02.03.03</t>
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>04.01.03</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G1: el CEO elige</t>
-        </is>
-      </c>
-      <c r="D32" s="29" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2675,11 +2684,11 @@
         <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>02.03.02 (pendiente, Orquestador)</t>
+          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2689,24 +2698,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B33" s="34" t="inlineStr">
-        <is>
-          <t>03.01.05</t>
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
+          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
-        </is>
-      </c>
-      <c r="E33" s="35" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
+          <t>Investigador</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2714,11 +2723,15 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
+          <t>04.02.01 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -2728,24 +2741,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B34" s="34" t="inlineStr">
-        <is>
-          <t>03.01.07</t>
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
+          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
-        </is>
-      </c>
-      <c r="E34" s="35" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
+          <t>Validador</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2753,11 +2766,15 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>14</v>
+      </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>03.01.06 (pendiente, Secretario)</t>
+          <t>04.02.02 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -2767,24 +2784,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B35" s="34" t="inlineStr">
-        <is>
-          <t>03.01.08</t>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>04.02.04</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego de las barreras (regla 13): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
+          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Crítico</t>
-        </is>
-      </c>
-      <c r="E35" s="35" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
+          <t>Validador</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -2792,11 +2809,15 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>03.01.03 (pendiente, Constructores)</t>
+          <t>04.02.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2806,19 +2827,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B36" s="34" t="inlineStr">
-        <is>
-          <t>04.01.01</t>
+      <c r="B36" s="33" t="inlineStr">
+        <is>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
-        </is>
-      </c>
-      <c r="D36" s="29" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
+          <t>Backtest con costes reales sobre el cajón de construir</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2832,14 +2853,14 @@
         </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>02.03.03 (pendiente, CEO)</t>
+          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2849,19 +2870,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B37" s="34" t="inlineStr">
-        <is>
-          <t>04.01.02</t>
+      <c r="B37" s="33" t="inlineStr">
+        <is>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
+          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2874,11 +2895,15 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr"/>
-      <c r="H37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>11</v>
+      </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
+          <t>04.03.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2888,19 +2913,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B38" s="34" t="inlineStr">
-        <is>
-          <t>04.01.03</t>
+      <c r="B38" s="33" t="inlineStr">
+        <is>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
+          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2917,11 +2942,11 @@
         <v>1</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
+          <t>04.03.02 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2931,19 +2956,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B39" s="34" t="inlineStr">
-        <is>
-          <t>04.02.02</t>
+      <c r="B39" s="33" t="inlineStr">
+        <is>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
+          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2960,11 +2985,11 @@
         <v>1</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>04.02.01 (pendiente, Investigador)</t>
+          <t>04.03.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2974,14 +2999,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B40" s="34" t="inlineStr">
-        <is>
-          <t>04.02.03</t>
+      <c r="B40" s="33" t="inlineStr">
+        <is>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
+          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -3003,11 +3028,11 @@
         <v>1</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>04.02.02 (pendiente, Investigador)</t>
+          <t>04.03.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3017,19 +3042,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B41" s="34" t="inlineStr">
-        <is>
-          <t>04.02.04</t>
+      <c r="B41" s="33" t="inlineStr">
+        <is>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
+          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -3043,14 +3068,14 @@
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>04.02.03 (pendiente, Validador)</t>
+          <t>04.03.05 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3060,19 +3085,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B42" s="34" t="inlineStr">
-        <is>
-          <t>04.03.01</t>
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>04.04.02</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Backtest con costes reales sobre el cajón de construir</t>
+          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -3085,15 +3110,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>12</v>
-      </c>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
+          <t>04.04.01 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -3103,19 +3124,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B43" s="34" t="inlineStr">
-        <is>
-          <t>04.03.02</t>
+      <c r="B43" s="33" t="inlineStr">
+        <is>
+          <t>04.04.03</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
+          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
+        </is>
+      </c>
+      <c r="D43" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -3132,11 +3153,11 @@
         <v>1</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>04.03.01 (pendiente, Constructores)</t>
+          <t>04.04.01 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -3146,19 +3167,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B44" s="34" t="inlineStr">
-        <is>
-          <t>04.03.03</t>
+      <c r="B44" s="33" t="inlineStr">
+        <is>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
+          <t>Bot en demo, solo y con guardias automáticos</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -3175,11 +3196,11 @@
         <v>1</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>04.03.02 (pendiente, Constructores)</t>
+          <t>04.04.03 (pendiente, CEO)</t>
         </is>
       </c>
     </row>
@@ -3189,19 +3210,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B45" s="34" t="inlineStr">
-        <is>
-          <t>04.03.04</t>
+      <c r="B45" s="33" t="inlineStr">
+        <is>
+          <t>05.01.02</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3218,11 +3239,11 @@
         <v>1</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>04.03.03 (pendiente, Validador)</t>
+          <t>05.01.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -3232,19 +3253,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B46" s="34" t="inlineStr">
-        <is>
-          <t>04.03.05</t>
+      <c r="B46" s="33" t="inlineStr">
+        <is>
+          <t>05.01.03</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>Validador</t>
+          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
+        </is>
+      </c>
+      <c r="D46" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3261,11 +3282,11 @@
         <v>1</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>04.03.04 (pendiente, Validador)</t>
+          <t>05.01.02 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -3275,19 +3296,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B47" s="34" t="inlineStr">
-        <is>
-          <t>04.04.01</t>
+      <c r="B47" s="33" t="inlineStr">
+        <is>
+          <t>06.01.01</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
+          <t>Dinero pequeño respetando los límites de 01.01.03</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -3301,14 +3322,14 @@
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>04.03.05 (pendiente, Validador)</t>
+          <t>05.01.03 (pendiente, CEO)</t>
         </is>
       </c>
     </row>
@@ -3318,19 +3339,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B48" s="34" t="inlineStr">
-        <is>
-          <t>04.04.02</t>
+      <c r="B48" s="33" t="inlineStr">
+        <is>
+          <t>06.01.02</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>Orquestador</t>
+          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
+        </is>
+      </c>
+      <c r="D48" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -3347,268 +3368,14 @@
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>04.04.01 (pendiente, Secretario)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B49" s="34" t="inlineStr">
-        <is>
-          <t>04.04.03</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
-        </is>
-      </c>
-      <c r="D49" s="29" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>04.04.01 (pendiente, Secretario)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B50" s="34" t="inlineStr">
-        <is>
-          <t>05.01.01</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Bot en demo, solo y con guardias automáticos</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>04.04.03 (pendiente, CEO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B51" s="34" t="inlineStr">
-        <is>
-          <t>05.01.02</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Secretario</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>05.01.01 (pendiente, Constructores)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B52" s="34" t="inlineStr">
-        <is>
-          <t>05.01.03</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
-        </is>
-      </c>
-      <c r="D52" s="29" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>05.01.02 (pendiente, Secretario)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B53" s="34" t="inlineStr">
-        <is>
-          <t>06.01.01</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Dinero pequeño respetando los límites de 01.01.03</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>05.01.03 (pendiente, CEO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B54" s="34" t="inlineStr">
-        <is>
-          <t>06.01.02</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
-        </is>
-      </c>
-      <c r="D54" s="29" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
           <t>06.01.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="46" customHeight="1">
-      <c r="A56" s="36" t="inlineStr">
-        <is>
-          <t>Aviso de la regla 8 (CLAUDE.md): si la cola de arriba solo tuviera tareas de MOTOR, hay que parar y avisar al CEO; significa que la cola esta mal llena. Ahora mismo la cola tiene 3 de producto y 8 de motor.</t>
+    <row r="50" ht="46" customHeight="1">
+      <c r="A50" s="35" t="inlineStr">
+        <is>
+          <t>Aviso de la regla 8 (CLAUDE.md): si la cola de arriba solo tuviera tareas de MOTOR, hay que parar y avisar al CEO; significa que la cola esta mal llena. Ahora mismo la cola tiene 5 de producto y 8 de motor.</t>
         </is>
       </c>
     </row>
@@ -3620,11 +3387,11 @@
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A56:I56"/>
     <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A50:I50"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A21:I21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3636,15 +3403,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3658,18 +3426,20 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
-        <is>
-          <t>Una fila por tarea. Filtra por ESTADO con la flecha de la cabecera. Verde = hecha · amarillo = en curso · rojo = bloqueada. Las tareas del CEO llevan la columna RESPONSABLE en naranja.</t>
-        </is>
-      </c>
-      <c r="B2" s="23" t="n"/>
-      <c r="C2" s="23" t="n"/>
-      <c r="D2" s="23" t="n"/>
-      <c r="E2" s="23" t="n"/>
-      <c r="F2" s="23" t="n"/>
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Una fila por tarea. Filtra por ESTADO con la flecha de la cabecera. Verde = hecha · amarillo = en curso · rojo = bloqueada. Las tareas del CEO llevan la columna RESPONSABLE en naranja. Los textos largos se cortan y se apunta al WBS: esto es la vista, no la fuente.</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="22" t="n"/>
+      <c r="F2" s="22" t="n"/>
+      <c r="G2" s="22" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -3699,25 +3469,31 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>DETALLE / DONDE ESTA</t>
+          <t>RESULTADO / DONDE ESTA</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>FICHA (LO QUE SE ENCARGO)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>ARRANQUE (PUERTA G0)</t>
         </is>
       </c>
-      <c r="C5" s="38" t="n"/>
-      <c r="D5" s="38" t="n"/>
-      <c r="E5" s="38" t="n"/>
-      <c r="F5" s="38" t="n"/>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="37" t="n"/>
+      <c r="E5" s="37" t="n"/>
+      <c r="F5" s="37" t="n"/>
+      <c r="G5" s="37" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -3730,7 +3506,7 @@
           <t>Aprobar plan y reglas</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
@@ -3746,6 +3522,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
@@ -3758,7 +3535,7 @@
           <t>Aprobar criterios de la puerta G1</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
@@ -3770,10 +3547,15 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>** 01/08 — opción A de la ficha: los 7 criterios G1-C1..G1-C7 aprobados (D-11). Recorrido: constructor-datos, investigador, crítico-código, validador. Propuesta inicial corregida en cuatro puntos por crítico y validador.</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -3786,7 +3568,7 @@
           <t>Fijar límites: fecha tope, horas CEO/semana, pérdida máxima futura</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
@@ -3798,10 +3580,15 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>01/08 — los tres limites firmados como D-12, D-13 y D-14** y escritos en la seccion «Limites del CEO» de este WBS. (1) FECHA TOPE 01/12/2026 + revision de avance el dia 1 de cada mes con poder de parar; GM gana una cuarta salida (parar). (2) 1 h los lunes como MINIMO garantizado, no techo, con tope de 5 fichas por revision. (3) DINERO REAL: aviso a -25% que no para nada, parada dura automatica a -30% del capital inicial ingresado, aplicada por el bot de forma continua (regla 26); genera requisito nuevo en 05.01.01 y 06.01.01. Resuelta la contradiccion que este WBS arrastraba (-25% propuesto frente a tolerancia declarada del 50-60%). No se reabrio el capital: los 1.000-2.000 € ya son entrada […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -3831,9 +3618,10 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>30/07 — INFORME_GB2.md</t>
-        </is>
-      </c>
+          <t>** 30/07 — INFORME_GB2.md</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -3862,6 +3650,7 @@
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -3890,22 +3679,24 @@
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>ELEGIR MERCADO Y TAMAÑO DE VELA (PUERTA G1)</t>
         </is>
       </c>
-      <c r="C12" s="38" t="n"/>
-      <c r="D12" s="38" t="n"/>
-      <c r="E12" s="38" t="n"/>
-      <c r="F12" s="38" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="37" t="n"/>
+      <c r="G12" s="37" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
@@ -3918,7 +3709,7 @@
           <t>Confirmar 8 candidatos: EURUSD, GBPUSD, USDJPY, AUDUSD, USDCHF, XAUUSD, BTC, ETH</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>CEO + Orquestador</t>
         </is>
@@ -3938,6 +3729,7 @@
           <t>los 8 candidatos ya se usan de hecho en 02.02.04 (hecha) y en los briefs A y B; falta ratificación formal del CEO en G1</t>
         </is>
       </c>
+      <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -3962,10 +3754,19 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr"/>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>31/07 — coste_operar.md. Tabla final de coste de entrar y salir, 8 instrumentos, ida y vuelta, con tipo de cuenta declarado (raw/ECN vs spread-only, que no son comparables entre si). CORRECCIONES DE L-002 APLICADAS EN LA TABLA y no en nota al pie: USDJPY 1,16 pips (no 0,90) y USDCHF 0,73 pips (no 0,80). VERIFICADO por el orquestador: aritmetica de las 8 filas recalculada (spread + comision = total, cuadran las 6 con comision); las cifras citadas existen en el origen, localizadas por grep. RECORRIDO: primera entrega DEVUELTA por incumplir la regla 21 (seis citas por numero de linea, que se rompen solas al editar el origen); corregida a referencias por seccion y fila de tabla, verificado que […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (31/07): Alcance: tabla FINAL de coste de entrar y salir (spread + comision) para los 8 instrumentos, en la unidad natural de cada uno, ida y vuelta. Base ya existente: la Entrega 1 del Brief A (entrega_brief_A.md), ACEPTADA por el revisor con fuentes primarias (PDF oficiales de Pepperstone e IC Markets). No se rehace la investigacion: se consolida. Correcciones OBLIGATORIAS, aplicadas EN LA TABLA y no en nota al pie (L-002): USDJPY = 1,16 pips (no 0,90) y USDCHF = 0,73 pips (no 0,80); […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -3990,12 +3791,17 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecha</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>script atr_local.py escrito (142 líneas, en git) pero NUNCA EJECUTADO: 02-datos/bruto/ vacío, no existe atr_real.json. Su ficha debe fijar antes fuente de datos (el script usa Yahoo/yfinance; 02.02.04 concluyó Dukascopy/HistData/TrueFX/Binance/Kraken) y tratamiento del oro (el script usa el futuro GC=F; L-007 dice que no es XAUUSD al contado)</t>
+          <t>31/07 — precios_mercado.py, atr_15m_1h_4h.json, atr_real_15m_1h_4h.md. Tabla de 8 instrumentos x 3 velas, 24/24 celdas calculadas sobre precios descargados, 0 estimadas, 0 duplicados, 0 velas invalidas. Cordura del oro OK: 3.596,64 USD/oz, en miles. RECORRIDO: entregada, RECHAZADA por critico-codigo (bin incompleto contado como completo, en el filtro de ventana y en el primer bin de 4h de los 8 instrumentos), reparada en ronda 1, re-revisada y ACEPTADA. El critico recalculo el ATR desde los datos brutos con su propio codigo y coincide digito a digito con el script (XAUUSD 1h = 14.464676282400184, n=11824); verifico ademas que el descarte de bins de borde NO se come huecos legitimos (801 […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (31/07): Fuente fijada: HistData para EURUSD, GBPUSD, USDJPY, AUDUSD y USDCHF · Dukascopy para XAUUSD al contado (NO el futuro GC=F, ver L-007) · Kraken para BTCUSD y ETHUSD contra dolar real, no contra Tether (L-007). Se jubila Yahoo/yfinance. Alcance: descargar historico suficiente para 2 años completos y calcular ATR(14) en velas de 15m, 1h y 4h para los 8 instrumentos. Corte: 22:00 UTC, unico para todos. Artefacto: un solo script que sirva tambien a 02.02.03 (T2 avisa: en gb2 la […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
@@ -4022,12 +3828,17 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
+          <t>Hecha</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>depende de 02.01.02 (pendiente) y de 02.02.01 (sin ejecutar). El coste de USDJPY corregido a 1,16 pips viene de revision_brief_A.md</t>
+          <t>31/07 — coste_relativo.py, coste_relativo_15m_1h_4h.json, coste_relativo.md. ES EL CRITERIO 1 DE G1. Coste de ida y vuelta ÷ ATR x 100, 8 instrumentos x 3 velas, en CUATRO escenarios: vela media, mediana, tranquila (p10) y agitada (p90). RECORRIDO: entregada, RECHAZADA por critico-codigo (no por error de calculo —reejecuto el script y salio bit-identico— sino por un sesgo de metodo sin declarar), corregida y ACEPTADA. EL SESGO, hallado por el revisor y reproducido por el orquestador: el ATR medio de XAUUSD esta inflado respecto a su mediana (1,28-1,30) mas que el de ningun otro instrumento (0,985-1,144), porque su pausa diaria de 21:00-22:00 UTC genera un salto de rango UNA VEZ AL DIA […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (31/07): Alcance: coste relativo = coste de ida y vuelta ÷ ATR medio de la vela x 100, para los 8 instrumentos x 3 velas (15m, 1h, 4h). Es el criterio 1 de la puerta G1: se exige ≤10-15%. Insumos, ambos ya cerrados y verificados: costes de coste_operar.md (02.01.02) y ATR de 04-resultados/atr_15m_1h_4h.json (02.02.01). No se recalcula ninguno de los dos. TRAMPA PRINCIPAL, declarada de antemano (L-002 y L-004): el JSON guarda el ATR en unidad CRUDA de precio, no en pips. El divisor de pip […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
@@ -4054,12 +3865,17 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecha</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>sin artefacto: no hay matriz calculada ni script. Reutilizará los precios que descargue 02.02.01</t>
+          <t>31/07 — correlaciones_mercado.py, correlaciones_8x8.json, correlaciones_8x8.md. 12 matrices 8x8 (3 ventanas x 4 velas, incluida la diaria) sobre RENDIMIENTOS logaritmicos, corte unico 22:00 UTC. ACEPTADA por critico-codigo sin ronda de reparacion. VERIFICADO POR EJECUCION por el revisor: recalculo 4 celdas con codigo propio y coinciden a 15 decimales; confirmo que correlaciona rendimientos y no precios (XAUUSD/USDJPY da +0,586 en precios frente a -0,060 en rendimientos); demostro que pandas ignora el offset con "1D" y que el codigo usa "24h", con el 100% de las velas diarias ancladas a las 22:00; y SIN REGRESION en precios_mercado.py, cuyo ATR regenerado sale identico digito a digito al […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (31/07): Alcance: matriz de correlaciones 8x8 sobre RENDIMIENTOS logaritmicos (nunca sobre precios), en 3 ventanas (3 meses, 1 año, 2 años) y en LAS TRES VELAS (15m, 1h, 4h), mas la diaria como comprobacion. Por que las tres velas: la ficha original decia "en la vela elegida", pero la vela se elige en G1, que es despues; calcular las tres evita adivinar (regla 6) y deja a la puerta el dato elija la que elija. Corte: 22:00 UTC unico, imprescindible o los rendimientos no coinciden entre […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
@@ -4091,9 +3907,10 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Dukascopy (tick desde 2003, forex y oro al contado), HistData, TrueFX, Binance, Kraken. Todo gratis, muy por encima de los 5 años exigidos</t>
-        </is>
-      </c>
+          <t>** — Dukascopy (tick desde 2003, forex y oro al contado), HistData, TrueFX, Binance, Kraken. Todo gratis, muy por encima de los 5 años exigidos</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
@@ -4118,10 +3935,15 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>** 31/07 — coste_swap.md. Coste de mantener posicion en 8 instrumentos x 3 brokers (OANDA, XTB, Pepperstone), largo y corto por separado, en % anual y $/dia sobre 100.000 USD. VERIFICADO por recalculo independiente: las 30 celdas con % y $/dia cuadran; signos de USDJPY y USDCHF coherentes entre brokers (L-006 comprobada, sin inversion de convencion). HALLAZGO PARA G1: mantener cripto cuesta -33,6% anual (OANDA) y -22,5% (Pepperstone), entre 20 y 30 veces mas que entrar y salir; el oro -6,6%/-8,2%; y USDCHF y USDJPY en largo PAGAN (+2,6% y +1,6%). Implicacion: si entra cripto en el portafolio, la estrategia no puede aguantar posiciones de un dia para otro. HUECO DECLARADO: ETHUSD queda con […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
@@ -4151,9 +3973,10 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>revisados Brief A (revision_brief_A.md, 29/07) y Brief B (revision_brief_B.md, 30/07). No se cierra hasta que 02.02.* entreguen números. ("parcial" no era un estado legal)</t>
-        </is>
-      </c>
+          <t>RECHAZA 31/07. Revision transversal ejecutada sobre los 5 entregables (no repite las revisiones por tarea: busca contradicciones ENTRE documentos). ARITMETICA LIMPIA: coste, ATR y correlaciones coinciden digito a digito entre los .md y los JSON; 0 citas D-NN inventadas; 0 referencias por numero de linea. MOTIVOS DEL RECHAZO: (1) dos criterios de G1 llegan SIN DATO — "cientos de operaciones posibles" (señalado ya el dia 1 en los puntos ciegos del Brief A y nunca cerrado; el orquestador calculo hoy la cota: ~1.615 velas/año a 4h y ~6.235 a 1h en forex) y "operable sin nadie delante" (es Fase 03, abierta). (2) Los criterios de G1 NO estan numerados en el WBS: cada documento se invento su […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
@@ -4182,6 +4005,7 @@
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -4194,7 +4018,7 @@
           <t>PUERTA G1: el CEO elige</t>
         </is>
       </c>
-      <c r="C22" s="29" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
@@ -4210,22 +4034,24 @@
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>MONTAR LA CASA (CLAUDE CODE) — EN PARALELO CON LA FASE 02</t>
         </is>
       </c>
-      <c r="C23" s="38" t="n"/>
-      <c r="D23" s="38" t="n"/>
-      <c r="E23" s="38" t="n"/>
-      <c r="F23" s="38" t="n"/>
+      <c r="C23" s="37" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="37" t="n"/>
+      <c r="F23" s="37" t="n"/>
+      <c r="G23" s="37" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -4255,9 +4081,10 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>30/07 — repo completo: carpetas, WBS, CLAUDE.md, DECISIONES.md, LECCIONES.md, plantillas y .gitignore (42 ficheros en git). AVISO regla 24 NO VERIFICADA: la prueba de inyección de datos no se ha ejecutado; 02-datos/ está vacío. Se ejecuta al bajar los primeros precios en 02.02.01</t>
-        </is>
-      </c>
+          <t>30/07 — repo completo: carpetas, WBS, CLAUDE.md, DECISIONES.md, LECCIONES.md, plantillas y .gitignore (42 ficheros en git). AVISO regla 24 NO VERIFICADA**: la prueba de inyección de datos no se ha ejecutado; 02-datos/ está vacío. Se ejecuta al bajar los primeros precios en 02.02.01</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
@@ -4287,9 +4114,10 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>30/07 — 8 agentes en .claude/agents/, cada uno con identificador exacto de modelo y respaldo. Prueba de activación ejecutada 30/07: los 8 respondieron y leyeron un fichero real, ningún fantasma. LÍMITE: la prueba no demuestra que el modelo enrutado sea el de la ficha; se verifica en 03.01.04, con atención a claude-fable-5 (validador y arquitecto)</t>
-        </is>
-      </c>
+          <t>** 30/07 — 8 agentes en .claude/agents/, cada uno con identificador exacto de modelo y respaldo. Prueba de activación ejecutada 30/07: los 8 respondieron y leyeron un fichero real, ningún fantasma. LÍMITE: la prueba no demuestra que el modelo enrutado sea el de la ficha; se verifica en 03.01.04, con atención a claude-fable-5 (validador y arquitecto)</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
@@ -4318,6 +4146,7 @@
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
@@ -4346,6 +4175,7 @@
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -4374,6 +4204,7 @@
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -4402,6 +4233,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -4430,6 +4262,7 @@
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
@@ -4454,10 +4287,15 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr"/>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>ejecutada la primera pasada 31/07 con verificar_barreras.py: 4 barreras de 5 VERIFICADAS por ejecucion (hooks instalados, datos rechazados en commit, .gitignore ignora 02-datos, mensaje exige codigo WBS). 1 NO VERIFICADA: el cajon reservado era un filtro de texto sobre el comando. Se remedia en 03.01.11 (D-10). No se cierra hasta repetir la pasada con 03.01.11 terminada</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -4486,6 +4324,7 @@
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
@@ -4514,86 +4353,94 @@
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="37" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>03.01.11</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>03.01.08</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>script escrito y probado por ejecucion 31/07: 6 de 6 casos prohibidos bloqueados (contraseña por tuberia, abrir sin declarar variante, lectura a pelo del fichero cifrado, contraseña incorrecta, y ninguna orden de terminal vuelca datos en claro). FALTA: que el CEO ejecute sellar en una terminal real para fijar la contraseña</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="B34" s="38" t="inlineStr">
+      <c r="B35" s="37" t="inlineStr">
         <is>
           <t>HIPÓTESIS Y VALIDACIÓN (PUERTA G2)</t>
         </is>
       </c>
-      <c r="C34" s="38" t="n"/>
-      <c r="D34" s="38" t="n"/>
-      <c r="E34" s="38" t="n"/>
-      <c r="F34" s="38" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="39" t="inlineStr">
+      <c r="C35" s="37" t="n"/>
+      <c r="D35" s="37" t="n"/>
+      <c r="E35" s="37" t="n"/>
+      <c r="F35" s="37" t="n"/>
+      <c r="G35" s="37" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="38" t="inlineStr">
         <is>
           <t>04.01</t>
         </is>
       </c>
-      <c r="B35" s="40" t="inlineStr">
+      <c r="B36" s="39" t="inlineStr">
         <is>
           <t>Broker y cajones de datos</t>
         </is>
       </c>
-      <c r="C35" s="40" t="n"/>
-      <c r="D35" s="40" t="n"/>
-      <c r="E35" s="40" t="n"/>
-      <c r="F35" s="40" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>04.01.01</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
-        </is>
-      </c>
-      <c r="C36" s="29" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>02.03.03</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="C36" s="39" t="n"/>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="39" t="n"/>
+      <c r="F36" s="39" t="n"/>
+      <c r="G36" s="39" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>04.01.02</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Constructor datos</t>
+          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>02.03.03</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -4602,88 +4449,92 @@
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
+          <t>04.01.02</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Constructor datos</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>04.01.01</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
           <t>04.01.03</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Constructor datos</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>04.01.01</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="39" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="38" t="inlineStr">
         <is>
           <t>04.02</t>
         </is>
       </c>
-      <c r="B39" s="40" t="inlineStr">
+      <c r="B40" s="39" t="inlineStr">
         <is>
           <t>Investigación de hipótesis</t>
         </is>
       </c>
-      <c r="C39" s="40" t="n"/>
-      <c r="D39" s="40" t="n"/>
-      <c r="E39" s="40" t="n"/>
-      <c r="F39" s="40" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>04.02.01</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>03.01.02</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="C40" s="39" t="n"/>
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="39" t="n"/>
+      <c r="F40" s="39" t="n"/>
+      <c r="G40" s="39" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
+          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -4693,7 +4544,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>04.02.01</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -4702,26 +4553,27 @@
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
+          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -4730,88 +4582,92 @@
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
+          <t>04.02.03</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Validador</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>04.02.02</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
           <t>04.02.04</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>Validador</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>04.02.03</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="39" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="38" t="inlineStr">
         <is>
           <t>04.03</t>
         </is>
       </c>
-      <c r="B44" s="40" t="inlineStr">
+      <c r="B45" s="39" t="inlineStr">
         <is>
           <t>Laboratorio de pruebas (por hipótesis y variante)</t>
         </is>
       </c>
-      <c r="C44" s="40" t="n"/>
-      <c r="D44" s="40" t="n"/>
-      <c r="E44" s="40" t="n"/>
-      <c r="F44" s="40" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="13" t="inlineStr">
-        <is>
-          <t>04.03.01</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Backtest con costes reales sobre el cajón de construir</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>04.01.03, 04.02.04</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr"/>
+      <c r="C45" s="39" t="n"/>
+      <c r="D45" s="39" t="n"/>
+      <c r="E45" s="39" t="n"/>
+      <c r="F45" s="39" t="n"/>
+      <c r="G45" s="39" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
+          <t>Backtest con costes reales sobre el cajón de construir</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -4821,7 +4677,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.01.03, 04.02.04</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -4830,26 +4686,27 @@
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
+          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4858,16 +4715,17 @@
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4877,7 +4735,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -4886,98 +4744,102 @@
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
+          <t>04.03.04</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Validador</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>04.03.03</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
           <t>04.03.05</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Validador</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>04.03.04</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="39" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="38" t="inlineStr">
         <is>
           <t>04.04</t>
         </is>
       </c>
-      <c r="B50" s="40" t="inlineStr">
+      <c r="B51" s="39" t="inlineStr">
         <is>
           <t>Decisión y bucle</t>
         </is>
       </c>
-      <c r="C50" s="40" t="n"/>
-      <c r="D50" s="40" t="n"/>
-      <c r="E50" s="40" t="n"/>
-      <c r="F50" s="40" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="13" t="inlineStr">
-        <is>
-          <t>04.04.01</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Secretario</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>04.03.05</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr"/>
+      <c r="C51" s="39" t="n"/>
+      <c r="D51" s="39" t="n"/>
+      <c r="E51" s="39" t="n"/>
+      <c r="F51" s="39" t="n"/>
+      <c r="G51" s="39" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>04.04.02</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
+          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -4986,98 +4848,102 @@
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
+          <t>04.04.02</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>04.04.01</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
           <t>04.04.03</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>PUERTA G2: el CEO decide qué pasa a demo</t>
         </is>
       </c>
-      <c r="C53" s="29" t="inlineStr">
+      <c r="C54" s="28" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>04.04.01</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="37" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="36" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="B54" s="38" t="inlineStr">
+      <c r="B55" s="37" t="inlineStr">
         <is>
           <t>DEMO (PUERTA G3) — SE DETALLA AL CERRAR G2</t>
         </is>
       </c>
-      <c r="C54" s="38" t="n"/>
-      <c r="D54" s="38" t="n"/>
-      <c r="E54" s="38" t="n"/>
-      <c r="F54" s="38" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>05.01.01</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Bot en demo, solo y con guardias automáticos</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>04.04.03</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr"/>
+      <c r="C55" s="37" t="n"/>
+      <c r="D55" s="37" t="n"/>
+      <c r="E55" s="37" t="n"/>
+      <c r="F55" s="37" t="n"/>
+      <c r="G55" s="37" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>05.01.02</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
+          <t>Bot en demo, solo y con guardias automáticos</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>04.04.03</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -5085,187 +4951,232 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>REQUISITO AÑADIDO POR D-14 (01/08): el guardia de parada dura (-30% del capital inicial) lo aplica el BOT de forma CONTINUA, no una revision periodica; comprobado solo una vez al mes, un -30% puede ser un -45% cuando alguien mire. Se verifica por inyeccion antes de declararlo activo (regla 25).</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
+          <t>05.01.02</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Secretario</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>05.01.01</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
           <t>05.01.03</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
         </is>
       </c>
-      <c r="C57" s="29" t="inlineStr">
+      <c r="C58" s="28" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>05.01.02</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr"/>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="37" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="36" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
-      <c r="B58" s="38" t="inlineStr">
+      <c r="B59" s="37" t="inlineStr">
         <is>
           <t>REAL (PUERTA G4) — SE DETALLA AL CERRAR G3</t>
         </is>
       </c>
-      <c r="C58" s="38" t="n"/>
-      <c r="D58" s="38" t="n"/>
-      <c r="E58" s="38" t="n"/>
-      <c r="F58" s="38" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="13" t="inlineStr">
-        <is>
-          <t>06.01.01</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Dinero pequeño respetando los límites de 01.01.03</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>05.01.03</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr"/>
+      <c r="C59" s="37" t="n"/>
+      <c r="D59" s="37" t="n"/>
+      <c r="E59" s="37" t="n"/>
+      <c r="F59" s="37" t="n"/>
+      <c r="G59" s="37" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
+          <t>06.01.01</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Dinero pequeño respetando los límites de 01.01.03</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>05.01.03</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>limites ya escritos y firmados (D-14, 01/08): capital 1.000-2.000 €, AVISO a -25% del capital inicial que no para nada, PARADA DURA AUTOMATICA a -30% aplicada por el bot de forma continua y sin exencion activable desde dentro (regla 26).</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
           <t>06.01.02</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
         </is>
       </c>
-      <c r="C60" s="29" t="inlineStr">
+      <c r="C61" s="28" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>06.01.01</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="37" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="36" t="inlineStr">
         <is>
           <t>07</t>
         </is>
       </c>
-      <c r="B61" s="38" t="inlineStr">
+      <c r="B62" s="37" t="inlineStr">
         <is>
           <t>MOTOR Y ORDEN (PARALELA; MÁX. 20% DEL ESFUERZO SEMANAL)</t>
         </is>
       </c>
-      <c r="C61" s="38" t="n"/>
-      <c r="D61" s="38" t="n"/>
-      <c r="E61" s="38" t="n"/>
-      <c r="F61" s="38" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="13" t="inlineStr">
-        <is>
-          <t>07.01.01</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>03.01.01</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr"/>
+      <c r="C62" s="37" t="n"/>
+      <c r="D62" s="37" t="n"/>
+      <c r="E62" s="37" t="n"/>
+      <c r="F62" s="37" t="n"/>
+      <c r="G62" s="37" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
+          <t>07.01.01</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>03.01.01</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
           <t>07.01.02</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>Constructores</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>03.01.02</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F63"/>
+  <autoFilter ref="A4:G64"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E63">
+  <conditionalFormatting sqref="E5:E64">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecha"</formula>
     </cfRule>
@@ -5277,7 +5188,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,Hecha,Bloqueada"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5313,15 +5224,15 @@
       <c r="E1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Objetivo del mes: NO es tener el bot en demo. Es llegar al 1 de septiembre con respuesta a "¿existe alguna estrategia que merezca pasar a demo?".</t>
         </is>
       </c>
-      <c r="B2" s="23" t="n"/>
-      <c r="C2" s="23" t="n"/>
-      <c r="D2" s="23" t="n"/>
-      <c r="E2" s="23" t="n"/>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="22" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -5486,34 +5397,34 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>GM</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>1 sept</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>Puerta del mes con el CEO</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>Arrancar demo / otra vuelta / replantear</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>Mar 1: la reunión</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>Lo que NO cabe en el mes: la demo (8-12 semanas de mercado real, reloj no acelerable) · las 3 vueltas del bucle (cabe una y media) · el dinero real.</t>
         </is>
@@ -5551,12 +5462,12 @@
       <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Criterios tal y como estan escritos en WBS.md (G1 corregida el 30/07/2026).</t>
         </is>
       </c>
-      <c r="B2" s="23" t="n"/>
+      <c r="B2" s="22" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -5571,7 +5482,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="41" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>G0</t>
         </is>
@@ -5583,19 +5494,19 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="41" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>(criterios corregidos 30/07): coste de entrar y salir ≤10-15% del movimiento medio de vela y coste de mantener posición medido aparte · cientos de operaciones posibles · datos suficientes (deja de discriminar: hay 20+ años gratis para todos) · correlación que no supere 0,7 en ninguna de las tres ventanas (3 meses, 1 año, 2 años), medida en la vela elegida y con hora de corte única · operable sin nadie delante. Aviso: parte de la correlación entre pares de divisas es aritmética por compartir el dólar (EURUSD/USDCHF: -0,97), así que 5 pares de forex no son 5 apuestas.</t>
+          <t>(CRITERIOS APROBADOS 01/08/2026, D-11): siete criterios numerados</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
@@ -5607,7 +5518,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="41" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
@@ -5619,26 +5530,26 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="41" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>(mensual): si pierde más de lo escrito en 01.01.03, se para.</t>
+          <t>(mensual): si toca la parada dura de -30% del capital inicial (D-14), se para sin discusión. El aviso de -25% NO para: se reporta y decide el CEO. La parada la aplica el bot de forma continua, no esta revisión mensual.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>GM</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>(1 de septiembre de 2026): puerta de evaluación del primer mes. Decisión: arrancar demo, dar otra vuelta al bucle o replantear.</t>
+          <t>(1 de septiembre de 2026): puerta de evaluación del primer mes. Decisión: arrancar demo, dar otra vuelta al bucle, replantear o PARAR (cuarta salida añadida en D-12). Es la primera de las revisiones mensuales de avance; las siguientes, 01/10 y 01/11.</t>
         </is>
       </c>
     </row>
@@ -5679,15 +5590,15 @@
       <c r="E1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Regla 29: identificador exacto del modelo, nunca un alias, y ningun agente sin modelo.</t>
         </is>
       </c>
-      <c r="B2" s="23" t="n"/>
-      <c r="C2" s="23" t="n"/>
-      <c r="D2" s="23" t="n"/>
-      <c r="E2" s="23" t="n"/>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="22" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -5933,14 +5844,14 @@
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>Precios oficiales por millón de tokens (platform.claude.com, consultado 29/07/2026): Fable 5 (claude-fable-5) 10 $/50 $ · Opus 5 (claude-opus-5) 5 $/25 $ · Sonnet 5 (claude-sonnet-5) 3 $/15 $, con 2 $/10 $ hasta el 31/08/2026 · Haiku 4.5 (claude-haiku-4-5-20251001) 1 $/5 $. Contexto de 1M tokens salvo Haiku (200k).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>Aviso Fable 5: estuvo suspendido en junio de 2026 por controles de exportación y volvió el 1 de julio; además puede rechazar peticiones por sus filtros. Respaldo obligatorio (tarea 03.01.04).</t>
         </is>
@@ -6804,14 +6715,14 @@
       <c r="D1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Ninguna pieza entra por ser buena en gb2: entra si pasa su prueba, ejecutada aqui.</t>
         </is>
       </c>
-      <c r="B2" s="23" t="n"/>
-      <c r="C2" s="23" t="n"/>
-      <c r="D2" s="23" t="n"/>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -6946,7 +6857,7 @@
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>NO se trae: la configuración de agentes, la cola de tareas, el historial de git, los ficheros de estado, los encadenadores de sesión ni ninguna documentación de gb2 como norma. Las lecciones ya están extraídas en las reglas 12 a 26.</t>
         </is>

--- a/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
+++ b/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
@@ -21,7 +21,7 @@
     <sheet name="LIMITES CEO" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TAREAS'!$A$4:$G$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TAREAS'!$A$4:$G$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -743,23 +743,23 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"01.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"01.??.??")</f>
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"01.??.??",TAREAS!$E$5:$E$64,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"01.??.??",TAREAS!$E$5:$E$69,"Hecha")</f>
         <v/>
       </c>
       <c r="D4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"01.??.??",TAREAS!$E$5:$E$64,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"01.??.??",TAREAS!$E$5:$E$69,"En curso")</f>
         <v/>
       </c>
       <c r="E4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"01.??.??",TAREAS!$E$5:$E$64,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"01.??.??",TAREAS!$E$5:$E$69,"Pendiente")</f>
         <v/>
       </c>
       <c r="F4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"01.??.??",TAREAS!$E$5:$E$64,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"01.??.??",TAREAS!$E$5:$E$69,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G4" s="6">
@@ -774,23 +774,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"02.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"02.??.??")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"02.??.??",TAREAS!$E$5:$E$64,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"02.??.??",TAREAS!$E$5:$E$69,"Hecha")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"02.??.??",TAREAS!$E$5:$E$64,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"02.??.??",TAREAS!$E$5:$E$69,"En curso")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"02.??.??",TAREAS!$E$5:$E$64,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"02.??.??",TAREAS!$E$5:$E$69,"Pendiente")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"02.??.??",TAREAS!$E$5:$E$64,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"02.??.??",TAREAS!$E$5:$E$69,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G5" s="6">
@@ -805,23 +805,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"03.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"03.??.??")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"03.??.??",TAREAS!$E$5:$E$64,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"03.??.??",TAREAS!$E$5:$E$69,"Hecha")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"03.??.??",TAREAS!$E$5:$E$64,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"03.??.??",TAREAS!$E$5:$E$69,"En curso")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"03.??.??",TAREAS!$E$5:$E$64,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"03.??.??",TAREAS!$E$5:$E$69,"Pendiente")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"03.??.??",TAREAS!$E$5:$E$64,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"03.??.??",TAREAS!$E$5:$E$69,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G6" s="6">
@@ -836,23 +836,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"04.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"04.??.??")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"04.??.??",TAREAS!$E$5:$E$64,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"04.??.??",TAREAS!$E$5:$E$69,"Hecha")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"04.??.??",TAREAS!$E$5:$E$64,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"04.??.??",TAREAS!$E$5:$E$69,"En curso")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"04.??.??",TAREAS!$E$5:$E$64,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"04.??.??",TAREAS!$E$5:$E$69,"Pendiente")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"04.??.??",TAREAS!$E$5:$E$64,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"04.??.??",TAREAS!$E$5:$E$69,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G7" s="6">
@@ -867,23 +867,23 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"05.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"05.??.??")</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"05.??.??",TAREAS!$E$5:$E$64,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"05.??.??",TAREAS!$E$5:$E$69,"Hecha")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"05.??.??",TAREAS!$E$5:$E$64,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"05.??.??",TAREAS!$E$5:$E$69,"En curso")</f>
         <v/>
       </c>
       <c r="E8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"05.??.??",TAREAS!$E$5:$E$64,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"05.??.??",TAREAS!$E$5:$E$69,"Pendiente")</f>
         <v/>
       </c>
       <c r="F8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"05.??.??",TAREAS!$E$5:$E$64,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"05.??.??",TAREAS!$E$5:$E$69,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G8" s="6">
@@ -898,23 +898,23 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"06.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"06.??.??")</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"06.??.??",TAREAS!$E$5:$E$64,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"06.??.??",TAREAS!$E$5:$E$69,"Hecha")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"06.??.??",TAREAS!$E$5:$E$64,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"06.??.??",TAREAS!$E$5:$E$69,"En curso")</f>
         <v/>
       </c>
       <c r="E9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"06.??.??",TAREAS!$E$5:$E$64,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"06.??.??",TAREAS!$E$5:$E$69,"Pendiente")</f>
         <v/>
       </c>
       <c r="F9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"06.??.??",TAREAS!$E$5:$E$64,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"06.??.??",TAREAS!$E$5:$E$69,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G9" s="6">
@@ -929,23 +929,23 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"07.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"07.??.??")</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"07.??.??",TAREAS!$E$5:$E$64,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"07.??.??",TAREAS!$E$5:$E$69,"Hecha")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"07.??.??",TAREAS!$E$5:$E$64,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"07.??.??",TAREAS!$E$5:$E$69,"En curso")</f>
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"07.??.??",TAREAS!$E$5:$E$64,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"07.??.??",TAREAS!$E$5:$E$69,"Pendiente")</f>
         <v/>
       </c>
       <c r="F10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$64,"07.??.??",TAREAS!$E$5:$E$64,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$69,"07.??.??",TAREAS!$E$5:$E$69,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G10" s="6">
@@ -1036,12 +1036,12 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>02.03.01</t>
+          <t>01.02.03</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Revisión independiente de método, fuentes y números</t>
+          <t>Auditar el catálogo awesome-claude-code y, por ampliación del CEO (01/08), las fuentes oficiales de Anthropic y los mecanismos nativos de Claude Code; proponer máximo 4 piezas concretas para el motor, con motivo y coste de integración. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
         </is>
       </c>
       <c r="C16" s="4" t="n"/>
@@ -1057,12 +1057,12 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>03.01.08</t>
+          <t>01.02.04</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego de las barreras (regla 13): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
+          <t>NUEVA 01/08 (petición del CEO): evaluar si merece la pena añadir servidores MCP al proyecto, con veredicto por servidor y regla de admisión escrita para el futuro. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
         </is>
       </c>
       <c r="C17" s="4" t="n"/>
@@ -1078,12 +1078,12 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>03.01.11</t>
+          <t>02.03.01</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
+          <t>Revisión independiente de método, fuentes y números</t>
         </is>
       </c>
       <c r="C18" s="4" t="n"/>
@@ -1096,86 +1096,130 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>03.01.08</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>PROXIMA PUERTA</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>G1 — elegir mercado y tamaño de vela (criterios en la hoja PUERTAS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>OBJETIVO DEL MES</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Llegar al 1 de septiembre con respuesta a: ¿existe alguna estrategia que merezca pasar a demo?</t>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>03.01.11</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
+          <t>PROXIMA PUERTA</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>G1 — elegir mercado y tamaño de vela (criterios en la hoja PUERTAS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>OBJETIVO DEL MES</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Llegar al 1 de septiembre con respuesta a: ¿existe alguna estrategia que merezca pasar a demo?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
           <t>FUENTE DE VERDAD</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>00-direccion/WBS.md — este Excel se genera de ahi. Si discrepan, manda el texto.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>LEYENDA</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Hecha</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>En curso</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Bloqueada</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B20:G20"/>
+  <mergeCells count="11">
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B19:F19"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B21:G21"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
   </mergeCells>
@@ -1198,7 +1242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1433,6 +1477,108 @@
       <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Auditoría gb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>L-013</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Se trabajó una tarea sin ficha escrita antes: 01.01.02 era una fila de una línea sin alcance ni criterio de hecho, y el trabajo de apoyo se autoasignó alcance dentro de ella. La regla 5 de CLAUDE.md vale también para las tareas del CEO</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Revisión del cálculo de arrastre (01.01.02) por critico-codigo, 01/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>L-014</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Un supuesto expresado en porcentaje decidió el orden de magnitud sin declararse: fijar la actividad como porcentaje de velas operadas producía un multiplicador de coste x60-x69 entre velas que en valor absoluto cae a x4,3; la conclusión "1h es inviable" era un artefacto del supuesto</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Revisión de arrastre_coste.md, hallado por critico-codigo y confirmado con experimento ejecutado por validador, 01/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>L-015</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>CLAUDE.md y este WBS llevan dos listas de «29 reglas» con contenido distinto bajo el mismo número: toda cita regla N es ambigua. Resuelto el 01/08/2026 por D-16: la lista normativa es la de CLAUDE.md; toda cita se escribe «regla N de CLAUDE.md»</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Revisión 01.02.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>L-016</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Un indicador que solo mira lo etiquetado es ciego justo donde importa: medir el reparto producto/motor contando solo commits con código WBS daba 20% cuando el real es 43,8%, porque commit-msg exime a meta:, org: y arranque:, que es donde vive el motor</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Revisión 01.02.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>L-017</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>L-015 citaba mal su propia regla de grep: decía "la regla 20 de CLAUDE.md exige grep previo" cuando esa exigencia es la regla 12 de CLAUDE.md (la 20 es "se guardan todas las pruebas"). LECCIONES.md es de solo-añadir, así que no se corrige en su sitio, se anota aparte</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Tarea 03.01.13, pasada 1 (constructor-motor), 01/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>L-018</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Un recuento sin -i da cifras bajas aunque lo repitan dos agentes: quien ejecutó y quien revisó grepearon "regla" en minúscula y los dos dieron la misma cifra baja (5/3/36 en vez de 12/4/39), porque el error estaba en el método de los dos, no en el dato</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Tarea 03.01.13, pasada 2 (constructor-motor, ordenada tras el rechazo de la pasada 1), 01/08</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1758,7 @@
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Dinero real (D-14): capital 1.000-2.000 € (ya es entrada de G1-C6, D-11; cambiarlo obliga a re-verificar G1-C6). AVISO a -25% del capital inicial ingresado, que no para nada: se reporta y decide el CEO. PARADA DURA AUTOMÁTICA a -30% del capital inicial, aplicada por el bot de forma CONTINUA y sin exención activable desde dentro (regla 26). Se mide sobre el capital inicial ingresado, no sobre el máximo alcanzado. Recuperar desde -30% exige +43%.</t>
+          <t>Dinero real (D-14): capital 1.000-2.000 € (ya es entrada de G1-C6, D-11; cambiarlo obliga a re-verificar G1-C6). AVISO a -25% del capital inicial ingresado, que no para nada: se reporta y decide el CEO. PARADA DURA AUTOMÁTICA a -30% del capital inicial, aplicada por el bot de forma CONTINUA y sin exención activable desde dentro (regla 26 de CLAUDE.md). Se mide sobre el capital inicial ingresado, no sobre el máximo alcanzado. Recuperar desde -30% exige +43%.</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1729,7 +1875,7 @@
       <c r="B6" s="30" t="n"/>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>02.03.01 — Revisión independiente de método, fuentes y números. Detras de ella esperan 18 de las 38 tareas vivas.</t>
+          <t>02.03.01 — Revisión independiente de método, fuentes y números. Detras de ella esperan 18 de las 42 tareas vivas.</t>
         </is>
       </c>
       <c r="D6" s="30" t="n"/>
@@ -1793,7 +1939,7 @@
     <row r="9">
       <c r="A9" s="32" t="inlineStr">
         <is>
-          <t>SE PUEDE TRABAJAR YA — 13 tareas, en este orden</t>
+          <t>SE PUEDE TRABAJAR YA — 17 tareas, en este orden</t>
         </is>
       </c>
       <c r="B9" s="32" t="n"/>
@@ -1889,27 +2035,27 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>01.02.02</t>
+          <t>01.02.03</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Trasplante pieza a pieza desde gb2 (D6=B). Una tarea por pieza, cada una con su criterio de aceptación (ver sección Trasplante). Ninguna entra sin pasar su prueba ejecutada</t>
+          <t>Auditar el catálogo awesome-claude-code y, por ampliación del CEO (01/08), las fuentes oficiales de Anthropic y los mecanismos nativos de Claude Code; proponer máximo 4 piezas concretas para el motor, con motivo y coste de integración. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Crítico + Constructores</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>Investigador</t>
+        </is>
+      </c>
+      <c r="E12" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -1926,27 +2072,27 @@
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>02.01.01</t>
+          <t>01.02.04</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Confirmar 8 candidatos: EURUSD, GBPUSD, USDJPY, AUDUSD, USDCHF, XAUUSD, BTC, ETH</t>
-        </is>
-      </c>
-      <c r="D13" s="28" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>NUEVA 01/08 (petición del CEO): evaluar si merece la pena añadir servidores MCP al proyecto, con veredicto por servidor y regla de admisión escrita para el futuro. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Investigador</t>
+        </is>
+      </c>
+      <c r="E13" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -1963,17 +2109,17 @@
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>04.02.01</t>
+          <t>01.02.02</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
+          <t>Trasplante pieza a pieza desde gb2 (D6=B). Una tarea por pieza, cada una con su criterio de aceptación (ver sección Trasplante). Ninguna entra sin pasar su prueba ejecutada</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Crítico + Constructores</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1986,12 +2132,8 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>16</v>
-      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -2004,22 +2146,22 @@
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>01.02.03</t>
+          <t>02.01.01</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Auditar el catálogo awesome-claude-code y proponer máximo 4 piezas concretas para el motor, con motivo y coste de integración. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="E15" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
+          <t>Confirmar 8 candidatos: EURUSD, GBPUSD, USDJPY, AUDUSD, USDCHF, XAUUSD, BTC, ETH</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -2041,22 +2183,22 @@
       </c>
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>03.01.03</t>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Ejecución desatendida: arranques programados, permisos AMPLIOS por defecto (git como red de seguridad) y topes de gasto</t>
+          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E16" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
+          <t>Investigador</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2065,10 +2207,10 @@
         </is>
       </c>
       <c r="G16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -2082,12 +2224,12 @@
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>03.01.04</t>
+          <t>03.01.03</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Plan de respaldo de modelos: si un modelo no está disponible o rechaza, el agente sigue con su respaldo y lo anota</t>
+          <t>Ejecución desatendida: arranques programados, permisos AMPLIOS por defecto (git como red de seguridad) y topes de gasto</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -2106,10 +2248,10 @@
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -2123,17 +2265,17 @@
       </c>
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>03.01.06</t>
+          <t>03.01.04</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Plantilla y automatismo de fichas de decisión: el secretario prepara cada decisión del CEO en el formato obligatorio y la adjunta al informe semanal</t>
+          <t>Plan de respaldo de modelos: si un modelo no está disponible o rechaza, el agente sigue con su respaldo y lo anota</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E18" s="34" t="inlineStr">
@@ -2164,17 +2306,17 @@
       </c>
       <c r="B19" s="33" t="inlineStr">
         <is>
-          <t>03.01.09</t>
+          <t>03.01.06</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Enrutado por tipo de tarea y comprobación de que el WBS genera tareas de cada tipo de agente (regla 26)</t>
+          <t>Plantilla y automatismo de fichas de decisión: el secretario prepara cada decisión del CEO en el formato obligatorio y la adjunta al informe semanal</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E19" s="34" t="inlineStr">
@@ -2187,8 +2329,12 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -2201,12 +2347,12 @@
       </c>
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>03.01.10</t>
+          <t>03.01.09</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Testbed sintético de invarianza: resultado de referencia fijo que debe reproducirse tras cualquier cambio del motor</t>
+          <t>Enrutado por tipo de tarea y comprobación de que el WBS genera tareas de cada tipo de agente (ver L-010 de LECCIONES.md; sin número propio en CLAUDE.md)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -2238,12 +2384,12 @@
       </c>
       <c r="B21" s="33" t="inlineStr">
         <is>
-          <t>07.01.01</t>
+          <t>03.01.10</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
+          <t>Testbed sintético de invarianza: resultado de referencia fijo que debe reproducirse tras cualquier cambio del motor</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2275,12 +2421,12 @@
       </c>
       <c r="B22" s="33" t="inlineStr">
         <is>
-          <t>07.01.02</t>
+          <t>03.01.12</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
+          <t>NUEVA 01/08 (petición del CEO): fijar la estrategia de ramas de git. Criterio del CEO, literal: que dé agilidad, no complejidad</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -2307,44 +2453,64 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="inlineStr">
-        <is>
-          <t>ESPERANDO A OTRA TAREA — 25 tareas, en orden de codigo WBS</t>
-        </is>
-      </c>
-      <c r="B23" s="32" t="n"/>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="32" t="n"/>
-      <c r="E23" s="32" t="n"/>
-      <c r="F23" s="32" t="n"/>
-      <c r="G23" s="32" t="n"/>
-      <c r="H23" s="32" t="n"/>
-      <c r="I23" s="32" t="n"/>
+      <c r="A23" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>03.01.14</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 01/08 (deuda detectada al cerrar 03.01.13): la hoja REGLAS del Excel del CEO la construye 05-vista-ceo/generar_excel.py leyendo las líneas numeradas de la sección de reglas del WBS, que tras D-16 ya no existen: la hoja saldría vacía bajo el título «LAS 29 REGLAS», y verificar_excel.py no comprueba esa hoja, así que sus 8 pruebas pasarían igual (L-016). Hay que leer las reglas de CLAUDE.md y añadir una prueba que falle si la hoja sale vacía. Deuda de motor: no se ejecuta sin permiso del CEO.</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E23" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>nada: se puede empezar ya</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="A24" s="5" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>02.03.02</t>
+          <t>03.01.15</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Informe de decisión: 3-5 mercados poco correlacionados + 1-2 velas</t>
+          <t>Herramientas del secretario: puede escribir los registros que solo admiten añadir pero no puede verificarlos</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E24" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2352,80 +2518,68 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="5" t="n">
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>nada: se puede empezar ya</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>07.01.01</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>nada: se puede empezar ya</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>02.03.01 (en curso, Orquestador)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>02.03.03</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>PUERTA G1: el CEO elige</t>
-        </is>
-      </c>
-      <c r="D25" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>02.03.02 (pendiente, Orquestador)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="B26" s="33" t="inlineStr">
         <is>
-          <t>03.01.05</t>
+          <t>07.01.02</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
+          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E26" s="34" t="inlineStr">
@@ -2442,48 +2596,24 @@
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
+          <t>nada: se puede empezar ya</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B27" s="33" t="inlineStr">
-        <is>
-          <t>03.01.07</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Secretario</t>
-        </is>
-      </c>
-      <c r="E27" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>03.01.06 (pendiente, Secretario)</t>
-        </is>
-      </c>
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>ESPERANDO A OTRA TAREA — 25 tareas, en orden de codigo WBS</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="n"/>
+      <c r="C27" s="32" t="n"/>
+      <c r="D27" s="32" t="n"/>
+      <c r="E27" s="32" t="n"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="32" t="n"/>
+      <c r="H27" s="32" t="n"/>
+      <c r="I27" s="32" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2493,38 +2623,38 @@
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>03.01.08</t>
+          <t>02.03.02</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego de las barreras (regla 13): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
+          <t>Informe de decisión: 3-5 mercados poco correlacionados + 1-2 velas</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Crítico</t>
-        </is>
-      </c>
-      <c r="E28" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>En curso</t>
+          <t>Orquestador</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G28" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>03.01.03 (pendiente, Constructores)</t>
+          <t>02.03.01 (en curso, Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2536,34 +2666,38 @@
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>03.01.11</t>
+          <t>02.03.03</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E29" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
+          <t>PUERTA G1: el CEO elige</t>
+        </is>
+      </c>
+      <c r="D29" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>16</v>
+      </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>03.01.08 (en curso, Crítico)</t>
+          <t>02.03.02 (pendiente, Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2575,22 +2709,22 @@
       </c>
       <c r="B30" s="33" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>03.01.05</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
-        </is>
-      </c>
-      <c r="D30" s="28" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
+          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
+        </is>
+      </c>
+      <c r="E30" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2598,15 +2732,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G30" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>15</v>
-      </c>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>02.03.03 (pendiente, CEO)</t>
+          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2618,22 +2748,22 @@
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>04.01.02</t>
+          <t>03.01.07</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
+          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
+          <t>Secretario</t>
+        </is>
+      </c>
+      <c r="E31" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2645,7 +2775,7 @@
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
+          <t>03.01.06 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -2657,38 +2787,38 @@
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>04.01.03</t>
+          <t>03.01.08</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
+          <t>Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>Crítico</t>
+        </is>
+      </c>
+      <c r="E32" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
         </is>
       </c>
       <c r="G32" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
+          <t>03.01.03 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2700,38 +2830,34 @@
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>03.01.11</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>15</v>
-      </c>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E33" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>04.02.01 (pendiente, Investigador)</t>
+          <t>03.01.08 (en curso, Crítico)</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2869,17 @@
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Validador</t>
+          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
+        </is>
+      </c>
+      <c r="D34" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2767,14 +2893,14 @@
         </is>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>04.02.02 (pendiente, Investigador)</t>
+          <t>02.03.03 (pendiente, CEO)</t>
         </is>
       </c>
     </row>
@@ -2786,17 +2912,17 @@
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>04.02.04</t>
+          <t>04.01.02</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
+          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2809,15 +2935,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>13</v>
-      </c>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>04.02.03 (pendiente, Validador)</t>
+          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2829,17 +2951,17 @@
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.01.03</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Backtest con costes reales sobre el cajón de construir</t>
+          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2856,11 +2978,11 @@
         <v>1</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
+          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2872,17 +2994,17 @@
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
+          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2899,11 +3021,11 @@
         <v>1</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>04.03.01 (pendiente, Constructores)</t>
+          <t>04.02.01 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -2915,12 +3037,12 @@
       </c>
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
+          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2942,11 +3064,11 @@
         <v>1</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>04.03.02 (pendiente, Constructores)</t>
+          <t>04.02.02 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -2958,12 +3080,12 @@
       </c>
       <c r="B39" s="33" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>04.02.04</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2985,11 +3107,11 @@
         <v>1</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>04.03.03 (pendiente, Validador)</t>
+          <t>04.02.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3001,17 +3123,17 @@
       </c>
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>04.03.05</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
+          <t>Backtest con costes reales sobre el cajón de construir</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3028,11 +3150,11 @@
         <v>1</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>04.03.04 (pendiente, Validador)</t>
+          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3044,17 +3166,17 @@
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
+          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -3068,14 +3190,14 @@
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>04.03.05 (pendiente, Validador)</t>
+          <t>04.03.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -3087,17 +3209,17 @@
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>04.04.02</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
+          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -3110,11 +3232,15 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>04.04.01 (pendiente, Secretario)</t>
+          <t>04.03.02 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -3126,17 +3252,17 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>04.04.03</t>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
-        </is>
-      </c>
-      <c r="D43" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -3153,11 +3279,11 @@
         <v>1</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>04.04.01 (pendiente, Secretario)</t>
+          <t>04.03.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3169,17 +3295,17 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Bot en demo, solo y con guardias automáticos</t>
+          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -3196,11 +3322,11 @@
         <v>1</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>04.04.03 (pendiente, CEO)</t>
+          <t>04.03.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3212,12 +3338,12 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>05.01.02</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
+          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3236,14 +3362,14 @@
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>05.01.01 (pendiente, Constructores)</t>
+          <t>04.03.05 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3255,17 +3381,17 @@
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>05.01.03</t>
+          <t>04.04.02</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
-        </is>
-      </c>
-      <c r="D46" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3278,15 +3404,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>05.01.02 (pendiente, Secretario)</t>
+          <t>04.04.01 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -3298,17 +3420,17 @@
       </c>
       <c r="B47" s="33" t="inlineStr">
         <is>
-          <t>06.01.01</t>
+          <t>04.04.03</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Dinero pequeño respetando los límites de 01.01.03</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
+          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
+        </is>
+      </c>
+      <c r="D47" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -3325,11 +3447,11 @@
         <v>1</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>05.01.03 (pendiente, CEO)</t>
+          <t>04.04.01 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -3341,41 +3463,213 @@
       </c>
       <c r="B48" s="33" t="inlineStr">
         <is>
+          <t>05.01.01</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Bot en demo, solo y con guardias automáticos</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>04.04.03 (pendiente, CEO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B49" s="33" t="inlineStr">
+        <is>
+          <t>05.01.02</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Secretario</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>05.01.01 (pendiente, Constructores)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B50" s="33" t="inlineStr">
+        <is>
+          <t>05.01.03</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
+        </is>
+      </c>
+      <c r="D50" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>05.01.02 (pendiente, Secretario)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B51" s="33" t="inlineStr">
+        <is>
+          <t>06.01.01</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Dinero pequeño respetando los límites de 01.01.03</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>05.01.03 (pendiente, CEO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B52" s="33" t="inlineStr">
+        <is>
           <t>06.01.02</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
         </is>
       </c>
-      <c r="D48" s="28" t="inlineStr">
+      <c r="D52" s="28" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>PRODUCTO</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>06.01.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="46" customHeight="1">
-      <c r="A50" s="35" t="inlineStr">
-        <is>
-          <t>Aviso de la regla 8 (CLAUDE.md): si la cola de arriba solo tuviera tareas de MOTOR, hay que parar y avisar al CEO; significa que la cola esta mal llena. Ahora mismo la cola tiene 5 de producto y 8 de motor.</t>
+    <row r="54" ht="46" customHeight="1">
+      <c r="A54" s="35" t="inlineStr">
+        <is>
+          <t>Aviso de la regla 8 (CLAUDE.md): si la cola de arriba solo tuviera tareas de MOTOR, hay que parar y avisar al CEO; significa que la cola esta mal llena. Ahora mismo la cola tiene 5 de producto y 12 de motor.</t>
         </is>
       </c>
     </row>
@@ -3387,11 +3681,11 @@
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A50:I50"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3403,7 +3697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3552,7 +3846,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>** 01/08 — opción A de la ficha: los 7 criterios G1-C1..G1-C7 aprobados (D-11). Recorrido: constructor-datos, investigador, crítico-código, validador. Propuesta inicial corregida en cuatro puntos por crítico y validador.</t>
+          <t>** 01/08 — opción A de la ficha: los 7 criterios G1-C1..G1-C7 aprobados (D-11). Recorrido: constructor-datos, investigador, crítico-código, validador. Propuesta inicial corregida en cuatro puntos por crítico y validador. FICHAS DE APOYO (localizadas en 07.01.01(c), 02/08): 01-investigacion/mercados/evidencia_umbrales_g1.md (investigador, evidencia externa; se autodeclara «Apoya a: 01.01.02») y 04-resultados/veredictos/veredicto_criterios_g1.md (validador, contraataque a la propuesta C1-C7; título propio «tarea 01.01.02»).</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -3585,7 +3879,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>01/08 — los tres limites firmados como D-12, D-13 y D-14** y escritos en la seccion «Limites del CEO» de este WBS. (1) FECHA TOPE 01/12/2026 + revision de avance el dia 1 de cada mes con poder de parar; GM gana una cuarta salida (parar). (2) 1 h los lunes como MINIMO garantizado, no techo, con tope de 5 fichas por revision. (3) DINERO REAL: aviso a -25% que no para nada, parada dura automatica a -30% del capital inicial ingresado, aplicada por el bot de forma continua (regla 26); genera requisito nuevo en 05.01.01 y 06.01.01. Resuelta la contradiccion que este WBS arrastraba (-25% propuesto frente a tolerancia declarada del 50-60%). No se reabrio el capital: los 1.000-2.000 € ya son entrada […] texto completo en 00-direccion/WBS.md</t>
+          <t>01/08 — los tres limites firmados como D-12, D-13 y D-14** y escritos en la seccion «Limites del CEO» de este WBS. (1) FECHA TOPE 01/12/2026 + revision de avance el dia 1 de cada mes con poder de parar; GM gana una cuarta salida (parar). (2) 1 h los lunes como MINIMO garantizado, no techo, con tope de 5 fichas por revision. (3) DINERO REAL: aviso a -25% que no para nada, parada dura automatica a -30% del capital inicial ingresado, aplicada por el bot de forma continua (regla 26 de CLAUDE.md); genera requisito nuevo en 05.01.01 y 06.01.01. Resuelta la contradiccion que este WBS arrastraba (-25% propuesto frente a tolerancia declarada del 50-60%). No se reabrio el capital: los 1.000-2.000 € […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -3618,7 +3912,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>** 30/07 — INFORME_GB2.md</t>
+          <t>** 30/07 — INFORME_GB2.md. FICHA DE APOYO (localizada en 07.01.01(c), 02/08): 01-investigacion/herencia-gb2/HERENCIA_GB2.md, que se autodeclara en su primera línea «Tarea 01.02.01 cerrada. Fuente: INFORME_GB2.md» y contiene la ficha D6 del trasplante.</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -3660,7 +3954,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Auditar el catálogo awesome-claude-code y proponer máximo 4 piezas concretas para el motor, con motivo y coste de integración. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
+          <t>Auditar el catálogo awesome-claude-code y, por ampliación del CEO (01/08), las fuentes oficiales de Anthropic y los mecanismos nativos de Claude Code; proponer máximo 4 piezas concretas para el motor, con motivo y coste de integración. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -3675,113 +3969,121 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>01/08: informe entregado. Lo escribió el ORQUESTADOR en sesión principal, no el investigador, porque la sesión arrancó con la invocación de subagentes restringida; el CEO lo señaló y el reparto se corrigió en la misma tirada. Conclusión del informe: CERO piezas del catálogo, las 4 propuestas son mecanismos nativos (contador mecánico producto/motor, registro de autoría contra la auto-revisión, detección de fallo o rechazo de modelo, ejecución desatendida por cron). Hallazgo con consecuencia para 03.01.03: Claude Code no ofrece ningún tope de gasto que el proyecto pueda elegir; solo /usage (mirar, no bloquear), límites de workspace en la Console con clave de API, y OpenTelemetry. Matización […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (01/08): Aviso de proceso, dicho sin adornos: la ficha se escribe DESPUÉS del barrido, no antes, incumpliendo la regla 5 de CLAUDE.md. Motivo: el CEO pidió la investigación y la ampliación de alcance en la misma orden, en sesión. Queda anotado en vez de disimulado. Alcance ampliado: además del catálogo, fuentes oficiales de Anthropic (anthropics/*, documentación de code.claude.com) y mecanismos nativos ya instalados y sin usar (hooks, reglas con ámbito de ruta, worktrees, subagentes […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>01.02.04</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 01/08 (petición del CEO): evaluar si merece la pena añadir servidores MCP al proyecto, con veredicto por servidor y regla de admisión escrita para el futuro. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Investigador</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>03.01.02</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (01/08): Motivo de la tarea: el CEO pregunta si los MCP salen a cuenta aquí; no estaba medido en el WBS. Alcance: veredicto uno por uno sobre los servidores de referencia oficiales (filesystem, git, memory, sequential-thinking, fetch, time, everything, y sqlite, que está archivado upstream), sobre github, sobre los de datos de mercado (yfinance, TradingView, QuantConnect, ccxt), sobre los de broker (Kraken, Alpaca, IBKR) y sobre los de navegador (Playwright, Chrome DevTools). Filtros […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>ELEGIR MERCADO Y TAMAÑO DE VELA (PUERTA G1)</t>
         </is>
       </c>
-      <c r="C12" s="37" t="n"/>
-      <c r="D12" s="37" t="n"/>
-      <c r="E12" s="37" t="n"/>
-      <c r="F12" s="37" t="n"/>
-      <c r="G12" s="37" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>02.01.01</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Confirmar 8 candidatos: EURUSD, GBPUSD, USDJPY, AUDUSD, USDCHF, XAUUSD, BTC, ETH</t>
-        </is>
-      </c>
-      <c r="C13" s="28" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>01.01.02</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>los 8 candidatos ya se usan de hecho en 02.02.04 (hecha) y en los briefs A y B; falta ratificación formal del CEO en G1</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>02.01.02</t>
+          <t>02.01.01</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Costes típicos de operar por mercado (PROVISIONAL hasta 04.01.02)</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Investigador</t>
+          <t>Confirmar 8 candidatos: EURUSD, GBPUSD, USDJPY, AUDUSD, USDCHF, XAUUSD, BTC, ETH</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>02.01.01</t>
+          <t>01.01.02</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>31/07 — coste_operar.md. Tabla final de coste de entrar y salir, 8 instrumentos, ida y vuelta, con tipo de cuenta declarado (raw/ECN vs spread-only, que no son comparables entre si). CORRECCIONES DE L-002 APLICADAS EN LA TABLA y no en nota al pie: USDJPY 1,16 pips (no 0,90) y USDCHF 0,73 pips (no 0,80). VERIFICADO por el orquestador: aritmetica de las 8 filas recalculada (spread + comision = total, cuadran las 6 con comision); las cifras citadas existen en el origen, localizadas por grep. RECORRIDO: primera entrega DEVUELTA por incumplir la regla 21 (seis citas por numero de linea, que se rompen solas al editar el origen); corregida a referencias por seccion y fila de tabla, verificado que […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (31/07): Alcance: tabla FINAL de coste de entrar y salir (spread + comision) para los 8 instrumentos, en la unidad natural de cada uno, ida y vuelta. Base ya existente: la Entrega 1 del Brief A (entrega_brief_A.md), ACEPTADA por el revisor con fuentes primarias (PDF oficiales de Pepperstone e IC Markets). No se rehace la investigacion: se consolida. Correcciones OBLIGATORIAS, aplicadas EN LA TABLA y no en nota al pie (L-002): USDJPY = 1,16 pips (no 0,90) y USDCHF = 0,73 pips (no 0,80); […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
+          <t>los 8 candidatos ya se usan de hecho en 02.02.04 (hecha) y en los briefs A y B; falta ratificación formal del CEO en G1</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>02.02.01</t>
+          <t>02.01.02</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CORREGIDA 29/07: descargar precios y CALCULAR el ATR de 15m, 1h y 4h (no buscarlo publicado: no existe). Script atr_local.py</t>
+          <t>Costes típicos de operar por mercado (PROVISIONAL hasta 04.01.02)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Constructor de datos</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -3796,24 +4098,24 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>31/07 — precios_mercado.py, atr_15m_1h_4h.json, atr_real_15m_1h_4h.md. Tabla de 8 instrumentos x 3 velas, 24/24 celdas calculadas sobre precios descargados, 0 estimadas, 0 duplicados, 0 velas invalidas. Cordura del oro OK: 3.596,64 USD/oz, en miles. RECORRIDO: entregada, RECHAZADA por critico-codigo (bin incompleto contado como completo, en el filtro de ventana y en el primer bin de 4h de los 8 instrumentos), reparada en ronda 1, re-revisada y ACEPTADA. El critico recalculo el ATR desde los datos brutos con su propio codigo y coincide digito a digito con el script (XAUUSD 1h = 14.464676282400184, n=11824); verifico ademas que el descarte de bins de borde NO se come huecos legitimos (801 […] texto completo en 00-direccion/WBS.md</t>
+          <t>31/07 — coste_operar.md. Tabla final de coste de entrar y salir, 8 instrumentos, ida y vuelta, con tipo de cuenta declarado (raw/ECN vs spread-only, que no son comparables entre si). CORRECCIONES DE L-002 APLICADAS EN LA TABLA y no en nota al pie: USDJPY 1,16 pips (no 0,90) y USDCHF 0,73 pips (no 0,80). VERIFICADO por el orquestador: aritmetica de las 8 filas recalculada (spread + comision = total, cuadran las 6 con comision); las cifras citadas existen en el origen, localizadas por grep. RECORRIDO: primera entrega DEVUELTA por incumplir la regla 13 de CLAUDE.md (seis citas por numero de linea, que se rompen solas al editar el origen); corregida a referencias por seccion y fila de tabla, […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>FICHA (31/07): Fuente fijada: HistData para EURUSD, GBPUSD, USDJPY, AUDUSD y USDCHF · Dukascopy para XAUUSD al contado (NO el futuro GC=F, ver L-007) · Kraken para BTCUSD y ETHUSD contra dolar real, no contra Tether (L-007). Se jubila Yahoo/yfinance. Alcance: descargar historico suficiente para 2 años completos y calcular ATR(14) en velas de 15m, 1h y 4h para los 8 instrumentos. Corte: 22:00 UTC, unico para todos. Artefacto: un solo script que sirva tambien a 02.02.03 (T2 avisa: en gb2 la […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (31/07): Alcance: tabla FINAL de coste de entrar y salir (spread + comision) para los 8 instrumentos, en la unidad natural de cada uno, ida y vuelta. Base ya existente: la Entrega 1 del Brief A (entrega_brief_A.md), ACEPTADA por el revisor con fuentes primarias (PDF oficiales de Pepperstone e IC Markets). No se rehace la investigacion: se consolida. Correcciones OBLIGATORIAS, aplicadas EN LA TABLA y no en nota al pie (L-002): USDJPY = 1,16 pips (no 0,90) y USDCHF = 0,73 pips (no 0,80); […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>02.02.02</t>
+          <t>02.02.01</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Coste relativo: coste ÷ movimiento medio, en % (el número clave). Coste de USDJPY corregido a 1,16 pips</t>
+          <t>CORREGIDA 29/07: descargar precios y CALCULAR el ATR de 15m, 1h y 4h (no buscarlo publicado: no existe). Script atr_local.py</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3823,7 +4125,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>02.01.02, 02.02.01</t>
+          <t>02.01.01</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -3833,24 +4135,24 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>31/07 — coste_relativo.py, coste_relativo_15m_1h_4h.json, coste_relativo.md. ES EL CRITERIO 1 DE G1. Coste de ida y vuelta ÷ ATR x 100, 8 instrumentos x 3 velas, en CUATRO escenarios: vela media, mediana, tranquila (p10) y agitada (p90). RECORRIDO: entregada, RECHAZADA por critico-codigo (no por error de calculo —reejecuto el script y salio bit-identico— sino por un sesgo de metodo sin declarar), corregida y ACEPTADA. EL SESGO, hallado por el revisor y reproducido por el orquestador: el ATR medio de XAUUSD esta inflado respecto a su mediana (1,28-1,30) mas que el de ningun otro instrumento (0,985-1,144), porque su pausa diaria de 21:00-22:00 UTC genera un salto de rango UNA VEZ AL DIA […] texto completo en 00-direccion/WBS.md</t>
+          <t>31/07 — precios_mercado.py, atr_15m_1h_4h.json, atr_real_15m_1h_4h.md. Tabla de 8 instrumentos x 3 velas, 24/24 celdas calculadas sobre precios descargados, 0 estimadas, 0 duplicados, 0 velas invalidas. Cordura del oro OK: 3.596,64 USD/oz, en miles. RECORRIDO: entregada, RECHAZADA por critico-codigo (bin incompleto contado como completo, en el filtro de ventana y en el primer bin de 4h de los 8 instrumentos), reparada en ronda 1, re-revisada y ACEPTADA. El critico recalculo el ATR desde los datos brutos con su propio codigo y coincide digito a digito con el script (XAUUSD 1h = 14.464676282400184, n=11824); verifico ademas que el descarte de bins de borde NO se come huecos legitimos (801 […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>FICHA (31/07): Alcance: coste relativo = coste de ida y vuelta ÷ ATR medio de la vela x 100, para los 8 instrumentos x 3 velas (15m, 1h, 4h). Es el criterio 1 de la puerta G1: se exige ≤10-15%. Insumos, ambos ya cerrados y verificados: costes de coste_operar.md (02.01.02) y ATR de 04-resultados/atr_15m_1h_4h.json (02.02.01). No se recalcula ninguno de los dos. TRAMPA PRINCIPAL, declarada de antemano (L-002 y L-004): el JSON guarda el ATR en unidad CRUDA de precio, no en pips. El divisor de pip […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (31/07): Fuente fijada: HistData para EURUSD, GBPUSD, USDJPY, AUDUSD y USDCHF · Dukascopy para XAUUSD al contado (NO el futuro GC=F, ver L-007) · Kraken para BTCUSD y ETHUSD contra dolar real, no contra Tether (L-007). Se jubila Yahoo/yfinance. Alcance: descargar historico suficiente para 2 años completos y calcular ATR(14) en velas de 15m, 1h y 4h para los 8 instrumentos. Corte: 22:00 UTC, unico para todos. Artefacto: un solo script que sirva tambien a 02.02.03 (T2 avisa: en gb2 la […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>02.02.03</t>
+          <t>02.02.02</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CORREGIDA 30/07: CALCULAR la matriz de correlaciones en 3 ventanas (3 meses, 1 año, 2 años) con hora de corte única (22:00 UTC) y en la vela elegida, no solo diaria. No existe publicada de forma homogénea</t>
+          <t>Coste relativo: coste ÷ movimiento medio, en % (el número clave). Coste de USDJPY corregido a 1,16 pips</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -3860,7 +4162,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>02.01.01</t>
+          <t>02.01.02, 02.02.01</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -3870,29 +4172,29 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>31/07 — correlaciones_mercado.py, correlaciones_8x8.json, correlaciones_8x8.md. 12 matrices 8x8 (3 ventanas x 4 velas, incluida la diaria) sobre RENDIMIENTOS logaritmicos, corte unico 22:00 UTC. ACEPTADA por critico-codigo sin ronda de reparacion. VERIFICADO POR EJECUCION por el revisor: recalculo 4 celdas con codigo propio y coinciden a 15 decimales; confirmo que correlaciona rendimientos y no precios (XAUUSD/USDJPY da +0,586 en precios frente a -0,060 en rendimientos); demostro que pandas ignora el offset con "1D" y que el codigo usa "24h", con el 100% de las velas diarias ancladas a las 22:00; y SIN REGRESION en precios_mercado.py, cuyo ATR regenerado sale identico digito a digito al […] texto completo en 00-direccion/WBS.md</t>
+          <t>31/07 — coste_relativo.py, coste_relativo_15m_1h_4h.json, coste_relativo.md. ES EL CRITERIO 1 DE G1. Coste de ida y vuelta ÷ ATR x 100, 8 instrumentos x 3 velas, en CUATRO escenarios: vela media, mediana, tranquila (p10) y agitada (p90). RECORRIDO: entregada, RECHAZADA por critico-codigo (no por error de calculo —reejecuto el script y salio bit-identico— sino por un sesgo de metodo sin declarar), corregida y ACEPTADA. EL SESGO, hallado por el revisor y reproducido por el orquestador: el ATR medio de XAUUSD esta inflado respecto a su mediana (1,28-1,30) mas que el de ningun otro instrumento (0,985-1,144), porque su pausa diaria de 21:00-22:00 UTC genera un salto de rango UNA VEZ AL DIA […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>FICHA (31/07): Alcance: matriz de correlaciones 8x8 sobre RENDIMIENTOS logaritmicos (nunca sobre precios), en 3 ventanas (3 meses, 1 año, 2 años) y en LAS TRES VELAS (15m, 1h, 4h), mas la diaria como comprobacion. Por que las tres velas: la ficha original decia "en la vela elegida", pero la vela se elige en G1, que es despues; calcular las tres evita adivinar (regla 6) y deja a la puerta el dato elija la que elija. Corte: 22:00 UTC unico, imprescindible o los rendimientos no coinciden entre […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (31/07): Alcance: coste relativo = coste de ida y vuelta ÷ ATR medio de la vela x 100, para los 8 instrumentos x 3 velas (15m, 1h, 4h). Es el criterio 1 de la puerta G1: se exige ≤10-15%. Insumos, ambos ya cerrados y verificados: costes de coste_operar.md (02.01.02) y ATR de 04-resultados/atr_15m_1h_4h.json (02.02.01). No se recalcula ninguno de los dos. TRAMPA PRINCIPAL, declarada de antemano (L-002 y L-004): el JSON guarda el ATR en unidad CRUDA de precio, no en pips. El divisor de pip […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>02.02.04</t>
+          <t>02.02.03</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Historial disponible: años, fuente, coste</t>
+          <t>CORREGIDA 30/07: CALCULAR la matriz de correlaciones en 3 ventanas (3 meses, 1 año, 2 años) con hora de corte única (22:00 UTC) y en la vela elegida, no solo diaria. No existe publicada de forma homogénea</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Constructor de datos</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -3907,20 +4209,24 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>** — Dukascopy (tick desde 2003, forex y oro al contado), HistData, TrueFX, Binance, Kraken. Todo gratis, muy por encima de los 5 años exigidos</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
+          <t>31/07 — correlaciones_mercado.py, correlaciones_8x8.json, correlaciones_8x8.md. 12 matrices 8x8 (3 ventanas x 4 velas, incluida la diaria) sobre RENDIMIENTOS logaritmicos, corte unico 22:00 UTC. ACEPTADA por critico-codigo sin ronda de reparacion. VERIFICADO POR EJECUCION por el revisor: recalculo 4 celdas con codigo propio y coinciden a 15 decimales; confirmo que correlaciona rendimientos y no precios (XAUUSD/USDJPY da +0,586 en precios frente a -0,060 en rendimientos); demostro que pandas ignora el offset con "1D" y que el codigo usa "24h", con el 100% de las velas diarias ancladas a las 22:00; y SIN REGRESION en precios_mercado.py, cuyo ATR regenerado sale identico digito a digito al […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (31/07): Alcance: matriz de correlaciones 8x8 sobre RENDIMIENTOS logaritmicos (nunca sobre precios), en 3 ventanas (3 meses, 1 año, 2 años) y en LAS TRES VELAS (15m, 1h, 4h), mas la diaria como comprobacion. Por que las tres velas: la ficha original decia "en la vela elegida", pero la vela se elige en G1, que es despues; calcular las tres evita adivinar (regla 6 de CLAUDE.md) y deja a la puerta el dato elija la que elija. Corte: 22:00 UTC unico, imprescindible o los rendimientos no […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>02.02.05</t>
+          <t>02.02.04</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>NUEVA: coste de mantener posición de un día para otro (swap/financiación) en los 8 instrumentos, 2-3 brokers. En cripto CFD puede superar varias veces al spread</t>
+          <t>Historial disponible: años, fuente, coste</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -3940,7 +4246,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>** 31/07 — coste_swap.md. Coste de mantener posicion en 8 instrumentos x 3 brokers (OANDA, XTB, Pepperstone), largo y corto por separado, en % anual y $/dia sobre 100.000 USD. VERIFICADO por recalculo independiente: las 30 celdas con % y $/dia cuadran; signos de USDJPY y USDCHF coherentes entre brokers (L-006 comprobada, sin inversion de convencion). HALLAZGO PARA G1: mantener cripto cuesta -33,6% anual (OANDA) y -22,5% (Pepperstone), entre 20 y 30 veces mas que entrar y salir; el oro -6,6%/-8,2%; y USDCHF y USDJPY en largo PAGAN (+2,6% y +1,6%). Implicacion: si entra cripto en el portafolio, la estrategia no puede aguantar posiciones de un dia para otro. HUECO DECLARADO: ETHUSD queda con […] texto completo en 00-direccion/WBS.md</t>
+          <t>** — Dukascopy (tick desde 2003, forex y oro al contado), HistData, TrueFX, Binance, Kraken. Todo gratis, muy por encima de los 5 años exigidos</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
@@ -3948,32 +4254,32 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>02.03.01</t>
+          <t>02.02.05</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Revisión independiente de método, fuentes y números</t>
+          <t>NUEVA: coste de mantener posición de un día para otro (swap/financiación) en los 8 instrumentos, 2-3 brokers. En cripto CFD puede superar varias veces al spread</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>02.02.*</t>
+          <t>02.01.01</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecha</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>RECHAZA 31/07. Revision transversal ejecutada sobre los 5 entregables (no repite las revisiones por tarea: busca contradicciones ENTRE documentos). ARITMETICA LIMPIA: coste, ATR y correlaciones coinciden digito a digito entre los .md y los JSON; 0 citas D-NN inventadas; 0 referencias por numero de linea. MOTIVOS DEL RECHAZO: (1) dos criterios de G1 llegan SIN DATO — "cientos de operaciones posibles" (señalado ya el dia 1 en los puntos ciegos del Brief A y nunca cerrado; el orquestador calculo hoy la cota: ~1.615 velas/año a 4h y ~6.235 a 1h en forex) y "operable sin nadie delante" (es Fase 03, abierta). (2) Los criterios de G1 NO estan numerados en el WBS: cada documento se invento su […] texto completo en 00-direccion/WBS.md</t>
+          <t>** 31/07 — coste_swap.md. Coste de mantener posicion en 8 instrumentos x 3 brokers (OANDA, XTB, Pepperstone), largo y corto por separado, en % anual y $/dia sobre 100.000 USD. VERIFICADO por recalculo independiente: las 30 celdas con % y $/dia cuadran; signos de USDJPY y USDCHF coherentes entre brokers (L-006 comprobada, sin inversion de convencion). HALLAZGO PARA G1: mantener cripto cuesta -33,6% anual (OANDA) y -22,5% (Pepperstone), entre 20 y 30 veces mas que entrar y salir; el oro -6,6%/-8,2%; y USDCHF y USDJPY en largo PAGAN (+2,6% y +1,6%). Implicacion: si entra cripto en el portafolio, la estrategia no puede aguantar posiciones de un dia para otro. HUECO DECLARADO: ETHUSD queda con […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
@@ -3981,12 +4287,12 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>02.03.02</t>
+          <t>02.03.01</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Informe de decisión: 3-5 mercados poco correlacionados + 1-2 velas</t>
+          <t>Revisión independiente de método, fuentes y números</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3996,36 +4302,40 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>02.03.01</t>
+          <t>02.02.*</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>FICHA SEGUNDA PASADA (02/08): PUNTO DE PARTIDA: la primera pasada dio RECHAZA el 31/07 con 7 motivos, y ese veredicto solo existe dentro de esta celda del WBS: no hay artefacto en disco. Entremedias el CEO aprobó los siete criterios de G1 en D-11 (00-direccion/DECISIONES.md), que dice resolver parte de esos motivos. ALCANCE — un veredicto por cada uno de los 7 motivos, con la etiqueta CERRADO o ABIERTO y la prueba al lado: (1) Dos criterios de G1 sin dato («cientos de operaciones posibles» y […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>02.03.03</t>
+          <t>02.03.02</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G1: el CEO elige</t>
-        </is>
-      </c>
-      <c r="C22" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Informe de decisión: 3-5 mercados poco correlacionados + 1-2 velas</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>02.03.02</t>
+          <t>02.03.01</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -4036,65 +4346,61 @@
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr"/>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="36" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>02.03.03</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>PUERTA G1: el CEO elige</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>02.03.02</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>MONTAR LA CASA (CLAUDE CODE) — EN PARALELO CON LA FASE 02</t>
         </is>
       </c>
-      <c r="C23" s="37" t="n"/>
-      <c r="D23" s="37" t="n"/>
-      <c r="E23" s="37" t="n"/>
-      <c r="F23" s="37" t="n"/>
-      <c r="G23" s="37" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>03.01.01</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Repositorio: carpetas, WBS texto, CLAUDE.md, DECISIONES.md, LECCIONES.md</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>01.01.01</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Hecha</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>30/07 — repo completo: carpetas, WBS, CLAUDE.md, DECISIONES.md, LECCIONES.md, plantillas y .gitignore (42 ficheros en git). AVISO regla 24 NO VERIFICADA**: la prueba de inyección de datos no se ha ejecutado; 02-datos/ está vacío. Se ejecuta al bajar los primeros precios en 02.02.01</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr"/>
+      <c r="C24" s="37" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="E24" s="37" t="n"/>
+      <c r="F24" s="37" t="n"/>
+      <c r="G24" s="37" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>03.01.02</t>
+          <t>03.01.01</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Crear TODOS los agentes del Equipo, cada uno con su modelo y descripción sin ambigüedad; prueba de activación de todos (ningún agente fantasma)</t>
+          <t>Repositorio: carpetas, WBS texto, CLAUDE.md, DECISIONES.md, LECCIONES.md</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -4104,7 +4410,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>03.01.01, 01.02.01</t>
+          <t>01.01.01</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -4114,7 +4420,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>** 30/07 — 8 agentes en .claude/agents/, cada uno con identificador exacto de modelo y respaldo. Prueba de activación ejecutada 30/07: los 8 respondieron y leyeron un fichero real, ningún fantasma. LÍMITE: la prueba no demuestra que el modelo enrutado sea el de la ficha; se verifica en 03.01.04, con atención a claude-fable-5 (validador y arquitecto)</t>
+          <t>30/07 — repo completo: carpetas, WBS, CLAUDE.md, DECISIONES.md, LECCIONES.md, plantillas y .gitignore (42 ficheros en git). AVISO regla 27 de CLAUDE.md NO VERIFICADA**: la prueba de inyección de datos no se ha ejecutado; 02-datos/ está vacío. Se ejecuta al bajar los primeros precios en 02.02.01</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
@@ -4122,12 +4428,12 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>03.01.03</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Ejecución desatendida: arranques programados, permisos AMPLIOS por defecto (git como red de seguridad) y topes de gasto</t>
+          <t>Crear TODOS los agentes del Equipo, cada uno con su modelo y descripción sin ambigüedad; prueba de activación de todos (ningún agente fantasma)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -4137,26 +4443,30 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>03.01.02</t>
+          <t>03.01.01, 01.02.01</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>** 30/07 — 8 agentes en .claude/agents/, cada uno con identificador exacto de modelo y respaldo. Prueba de activación ejecutada 30/07: los 8 respondieron y leyeron un fichero real, ningún fantasma. LÍMITE: la prueba no demuestra que el modelo enrutado sea el de la ficha; se verifica en 03.01.04, con atención a claude-fable-5 (validador y arquitecto)</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>03.01.04</t>
+          <t>03.01.03</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Plan de respaldo de modelos: si un modelo no está disponible o rechaza, el agente sigue con su respaldo y lo anota</t>
+          <t>Ejecución desatendida: arranques programados, permisos AMPLIOS por defecto (git como red de seguridad) y topes de gasto</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -4180,22 +4490,22 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>03.01.05</t>
+          <t>03.01.04</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
+          <t>Plan de respaldo de modelos: si un modelo no está disponible o rechaza, el agente sigue con su respaldo y lo anota</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>03.01.03, 03.01.04</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -4209,22 +4519,22 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>03.01.06</t>
+          <t>03.01.05</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Plantilla y automatismo de fichas de decisión: el secretario prepara cada decisión del CEO en el formato obligatorio y la adjunta al informe semanal</t>
+          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>03.01.02</t>
+          <t>03.01.03, 03.01.04</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -4238,12 +4548,12 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>03.01.07</t>
+          <t>03.01.06</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
+          <t>Plantilla y automatismo de fichas de decisión: el secretario prepara cada decisión del CEO en el formato obligatorio y la adjunta al informe semanal</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -4253,7 +4563,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>03.01.06</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -4267,74 +4577,74 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>03.01.08</t>
+          <t>03.01.07</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego de las barreras (regla 13): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
+          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Crítico</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>03.01.03</t>
+          <t>03.01.06</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>ejecutada la primera pasada 31/07 con verificar_barreras.py: 4 barreras de 5 VERIFICADAS por ejecucion (hooks instalados, datos rechazados en commit, .gitignore ignora 02-datos, mensaje exige codigo WBS). 1 NO VERIFICADA: el cajon reservado era un filtro de texto sobre el comando. Se remedia en 03.01.11 (D-10). No se cierra hasta repetir la pasada con 03.01.11 terminada</t>
-        </is>
-      </c>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>03.01.09</t>
+          <t>03.01.08</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Enrutado por tipo de tarea y comprobación de que el WBS genera tareas de cada tipo de agente (regla 26)</t>
+          <t>Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Crítico</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>03.01.02</t>
+          <t>03.01.03</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>ejecutada la primera pasada 31/07 con verificar_barreras.py: 4 barreras de 5 VERIFICADAS por ejecucion (hooks instalados, datos rechazados en commit, .gitignore ignora 02-datos, mensaje exige codigo WBS). 1 NO VERIFICADA: el cajon reservado era un filtro de texto sobre el comando. Se remedia en 03.01.11 (D-10). No se cierra hasta repetir la pasada con 03.01.11 terminada</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>03.01.10</t>
+          <t>03.01.09</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Testbed sintético de invarianza: resultado de referencia fijo que debe reproducirse tras cualquier cambio del motor</t>
+          <t>Enrutado por tipo de tarea y comprobación de que el WBS genera tareas de cada tipo de agente (ver L-010 de LECCIONES.md; sin número propio en CLAUDE.md)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -4344,7 +4654,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>03.01.01</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -4358,12 +4668,12 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>03.01.11</t>
+          <t>03.01.10</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
+          <t>Testbed sintético de invarianza: resultado de referencia fijo que debe reproducirse tras cualquier cambio del motor</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -4373,103 +4683,135 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>03.01.08</t>
+          <t>03.01.01</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>script escrito y probado por ejecucion 31/07: 6 de 6 casos prohibidos bloqueados (contraseña por tuberia, abrir sin declarar variante, lectura a pelo del fichero cifrado, contraseña incorrecta, y ninguna orden de terminal vuelca datos en claro). FALTA: que el CEO ejecute sellar en una terminal real para fijar la contraseña</t>
-        </is>
-      </c>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr"/>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="36" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="B35" s="37" t="inlineStr">
-        <is>
-          <t>HIPÓTESIS Y VALIDACIÓN (PUERTA G2)</t>
-        </is>
-      </c>
-      <c r="C35" s="37" t="n"/>
-      <c r="D35" s="37" t="n"/>
-      <c r="E35" s="37" t="n"/>
-      <c r="F35" s="37" t="n"/>
-      <c r="G35" s="37" t="n"/>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>03.01.13</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 01/08 (L-015): una sola lista de reglas. Hoy CLAUDE.md y este WBS llevan cada uno una lista de «29 reglas» con contenido distinto bajo el mismo número, así que toda cita regla N del proyecto es ambigua</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="inlineStr">
+        <is>
+          <t>Constructores + CEO</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (01/08): Hallazgo, comprobado por grep sobre los dos ficheros el 01/08: regla 16 = «nadie valida su propio trabajo» (CLAUDE.md) frente a «test de compuerta» (WBS) · regla 23 = «dos niveles de barrera» frente a «un fallo reportado no es un fallo verificado» · regla 25 = «toda barrera se verifica por ejecución» frente a «cada agente lleva el identificador exacto de su modelo». Por qué importa: la regla 12 de CLAUDE.md exige que toda cita se localice con grep antes de entrar en un informe; […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="38" t="inlineStr">
-        <is>
-          <t>04.01</t>
-        </is>
-      </c>
-      <c r="B36" s="39" t="inlineStr">
-        <is>
-          <t>Broker y cajones de datos</t>
-        </is>
-      </c>
-      <c r="C36" s="39" t="n"/>
-      <c r="D36" s="39" t="n"/>
-      <c r="E36" s="39" t="n"/>
-      <c r="F36" s="39" t="n"/>
-      <c r="G36" s="39" t="n"/>
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>03.01.12</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 01/08 (petición del CEO): fijar la estrategia de ramas de git. Criterio del CEO, literal: que dé agilidad, no complejidad</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>03.01.01</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (01/08): Estado de partida, comprobado por ejecución el 01/08: git branch -a → una sola rama, main · git remote -v → vacío, no hay remoto · 16 commits · un solo humano. Alcance: decidir y dejar escrito (a) cuándo se trabaja en main y cuándo no, (b) si se usan worktrees y para qué, (c) qué NO se hace. Lo que ya se sabe y no hay que volver a investigar: Claude Code 2.1.220 trae worktrees nativos (claude --worktree &lt;nombre&gt;, y isolation: worktree en la ficha de un subagente) · los worktrees […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>03.01.11</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
-        </is>
-      </c>
-      <c r="C37" s="28" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>02.03.03</t>
+          <t>03.01.08</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr"/>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>script escrito y probado por ejecucion 31/07: 6 de 6 casos prohibidos bloqueados (contraseña por tuberia, abrir sin declarar variante, lectura a pelo del fichero cifrado, contraseña incorrecta, y ninguna orden de terminal vuelca datos en claro). FALTA: que el CEO ejecute sellar en una terminal real para fijar la contraseña. ARTEFACTO (localizado en 07.01.01(c), 02/08): 04-resultados/registro-cajon.md, escrito por 03-motor/scripts/cajon_reservado.py y citado en D-10; ya tiene una entrada SELLAR del 31/07.</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>04.01.02</t>
+          <t>03.01.14</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
+          <t>NUEVA 01/08 (deuda detectada al cerrar 03.01.13): la hoja REGLAS del Excel del CEO la construye 05-vista-ceo/generar_excel.py leyendo las líneas numeradas de la sección de reglas del WBS, que tras D-16 ya no existen: la hoja saldría vacía bajo el título «LAS 29 REGLAS», y verificar_excel.py no comprueba esa hoja, así que sus 8 pruebas pasarían igual (L-016). Hay que leer las reglas de CLAUDE.md y añadir una prueba que falle si la hoja sale vacía. Deuda de motor: no se ejecuta sin permiso del CEO.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>03.01.13</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -4477,28 +4819,32 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>04.01.03</t>
+          <t>03.01.15</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
+          <t>Herramientas del secretario: puede escribir los registros que solo admiten añadir pero no puede verificarlos</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -4507,73 +4853,65 @@
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="38" t="inlineStr">
-        <is>
-          <t>04.02</t>
-        </is>
-      </c>
-      <c r="B40" s="39" t="inlineStr">
-        <is>
-          <t>Investigación de hipótesis</t>
-        </is>
-      </c>
-      <c r="C40" s="39" t="n"/>
-      <c r="D40" s="39" t="n"/>
-      <c r="E40" s="39" t="n"/>
-      <c r="F40" s="39" t="n"/>
-      <c r="G40" s="39" t="n"/>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 02/08 (tres incidentes reales el 02/08): secretario mantiene los tres registros que solo admiten añadir y todas las fichas del CEO, y no tiene Bash: no puede comprobar por ejecución ninguna de las reglas que gobiernan su trabajo. El 02/08 falló tres veces por lo mismo — no pudo verificar el pegado en tabla, ni el append-only, ni el ancho de su ficha — y las tres las descubrió otro agente, que es la regla 15 de CLAUDE.md rota por diseño, no por descuido. Decidir entre dos salidas, y NO se […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="36" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B40" s="37" t="inlineStr">
+        <is>
+          <t>HIPÓTESIS Y VALIDACIÓN (PUERTA G2)</t>
+        </is>
+      </c>
+      <c r="C40" s="37" t="n"/>
+      <c r="D40" s="37" t="n"/>
+      <c r="E40" s="37" t="n"/>
+      <c r="F40" s="37" t="n"/>
+      <c r="G40" s="37" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>04.02.01</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>03.01.02</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr"/>
+      <c r="A41" s="38" t="inlineStr">
+        <is>
+          <t>04.01</t>
+        </is>
+      </c>
+      <c r="B41" s="39" t="inlineStr">
+        <is>
+          <t>Broker y cajones de datos</t>
+        </is>
+      </c>
+      <c r="C41" s="39" t="n"/>
+      <c r="D41" s="39" t="n"/>
+      <c r="E41" s="39" t="n"/>
+      <c r="F41" s="39" t="n"/>
+      <c r="G41" s="39" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Investigador</t>
+          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>04.02.01</t>
+          <t>02.03.03</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -4587,22 +4925,22 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.01.02</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
+          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -4616,22 +4954,22 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>04.02.04</t>
+          <t>04.01.03</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
+          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -4645,12 +4983,12 @@
     <row r="45">
       <c r="A45" s="38" t="inlineStr">
         <is>
-          <t>04.03</t>
+          <t>04.02</t>
         </is>
       </c>
       <c r="B45" s="39" t="inlineStr">
         <is>
-          <t>Laboratorio de pruebas (por hipótesis y variante)</t>
+          <t>Investigación de hipótesis</t>
         </is>
       </c>
       <c r="C45" s="39" t="n"/>
@@ -4662,22 +5000,22 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Backtest con costes reales sobre el cajón de construir</t>
+          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>04.01.03, 04.02.04</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -4691,22 +5029,22 @@
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
+          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4720,12 +5058,12 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
+          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4735,7 +5073,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -4749,12 +5087,12 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>04.02.04</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4764,7 +5102,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4776,70 +5114,70 @@
       <c r="G49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>04.03.05</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Validador</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>04.03.04</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr"/>
+      <c r="A50" s="38" t="inlineStr">
+        <is>
+          <t>04.03</t>
+        </is>
+      </c>
+      <c r="B50" s="39" t="inlineStr">
+        <is>
+          <t>Laboratorio de pruebas (por hipótesis y variante)</t>
+        </is>
+      </c>
+      <c r="C50" s="39" t="n"/>
+      <c r="D50" s="39" t="n"/>
+      <c r="E50" s="39" t="n"/>
+      <c r="F50" s="39" t="n"/>
+      <c r="G50" s="39" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="38" t="inlineStr">
-        <is>
-          <t>04.04</t>
-        </is>
-      </c>
-      <c r="B51" s="39" t="inlineStr">
-        <is>
-          <t>Decisión y bucle</t>
-        </is>
-      </c>
-      <c r="C51" s="39" t="n"/>
-      <c r="D51" s="39" t="n"/>
-      <c r="E51" s="39" t="n"/>
-      <c r="F51" s="39" t="n"/>
-      <c r="G51" s="39" t="n"/>
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>04.03.01</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Backtest con costes reales sobre el cajón de construir</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>04.01.03, 04.02.04</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
+          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>04.03.05</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -4853,22 +5191,22 @@
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>04.04.02</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
+          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -4882,22 +5220,22 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>04.04.03</t>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
-        </is>
-      </c>
-      <c r="C54" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Validador</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -4908,65 +5246,61 @@
       <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="inlineStr"/>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="36" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="B55" s="37" t="inlineStr">
-        <is>
-          <t>DEMO (PUERTA G3) — SE DETALLA AL CERRAR G2</t>
-        </is>
-      </c>
-      <c r="C55" s="37" t="n"/>
-      <c r="D55" s="37" t="n"/>
-      <c r="E55" s="37" t="n"/>
-      <c r="F55" s="37" t="n"/>
-      <c r="G55" s="37" t="n"/>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>04.03.05</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Validador</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>04.03.04</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>05.01.01</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Bot en demo, solo y con guardias automáticos</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>04.04.03</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>REQUISITO AÑADIDO POR D-14 (01/08): el guardia de parada dura (-30% del capital inicial) lo aplica el BOT de forma CONTINUA, no una revision periodica; comprobado solo una vez al mes, un -30% puede ser un -45% cuando alguien mire. Se verifica por inyeccion antes de declararlo activo (regla 25).</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr"/>
+      <c r="A56" s="38" t="inlineStr">
+        <is>
+          <t>04.04</t>
+        </is>
+      </c>
+      <c r="B56" s="39" t="inlineStr">
+        <is>
+          <t>Decisión y bucle</t>
+        </is>
+      </c>
+      <c r="C56" s="39" t="n"/>
+      <c r="D56" s="39" t="n"/>
+      <c r="E56" s="39" t="n"/>
+      <c r="F56" s="39" t="n"/>
+      <c r="G56" s="39" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>05.01.02</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
+          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -4976,7 +5310,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -4990,22 +5324,22 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>05.01.03</t>
+          <t>04.04.02</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
-        </is>
-      </c>
-      <c r="C58" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>05.01.02</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -5016,75 +5350,71 @@
       <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="inlineStr"/>
     </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="36" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="B59" s="37" t="inlineStr">
-        <is>
-          <t>REAL (PUERTA G4) — SE DETALLA AL CERRAR G3</t>
-        </is>
-      </c>
-      <c r="C59" s="37" t="n"/>
-      <c r="D59" s="37" t="n"/>
-      <c r="E59" s="37" t="n"/>
-      <c r="F59" s="37" t="n"/>
-      <c r="G59" s="37" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="13" t="inlineStr">
-        <is>
-          <t>06.01.01</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Dinero pequeño respetando los límites de 01.01.03</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>05.01.03</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>limites ya escritos y firmados (D-14, 01/08): capital 1.000-2.000 €, AVISO a -25% del capital inicial que no para nada, PARADA DURA AUTOMATICA a -30% aplicada por el bot de forma continua y sin exencion activable desde dentro (regla 26).</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr"/>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>04.04.03</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
+        </is>
+      </c>
+      <c r="C59" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>04.04.01</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="36" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B60" s="37" t="inlineStr">
+        <is>
+          <t>DEMO (PUERTA G3) — SE DETALLA AL CERRAR G2</t>
+        </is>
+      </c>
+      <c r="C60" s="37" t="n"/>
+      <c r="D60" s="37" t="n"/>
+      <c r="E60" s="37" t="n"/>
+      <c r="F60" s="37" t="n"/>
+      <c r="G60" s="37" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>06.01.02</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
-        </is>
-      </c>
-      <c r="C61" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Bot en demo, solo y con guardias automáticos</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>06.01.01</t>
+          <t>04.04.03</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -5092,45 +5422,61 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>REQUISITO AÑADIDO POR D-14 (01/08): el guardia de parada dura (-30% del capital inicial) lo aplica el BOT de forma CONTINUA, no una revision periodica; comprobado solo una vez al mes, un -30% puede ser un -45% cuando alguien mire. Se verifica por inyeccion antes de declararlo activo (regla 25 de CLAUDE.md).</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="inlineStr"/>
     </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="36" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="B62" s="37" t="inlineStr">
-        <is>
-          <t>MOTOR Y ORDEN (PARALELA; MÁX. 20% DEL ESFUERZO SEMANAL)</t>
-        </is>
-      </c>
-      <c r="C62" s="37" t="n"/>
-      <c r="D62" s="37" t="n"/>
-      <c r="E62" s="37" t="n"/>
-      <c r="F62" s="37" t="n"/>
-      <c r="G62" s="37" t="n"/>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>05.01.02</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Secretario</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>05.01.01</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>07.01.01</t>
+          <t>05.01.03</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
+          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
+        </is>
+      </c>
+      <c r="C63" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>03.01.01</t>
+          <t>05.01.02</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -5141,42 +5487,171 @@
       <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="inlineStr"/>
     </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="36" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B64" s="37" t="inlineStr">
+        <is>
+          <t>REAL (PUERTA G4) — SE DETALLA AL CERRAR G3</t>
+        </is>
+      </c>
+      <c r="C64" s="37" t="n"/>
+      <c r="D64" s="37" t="n"/>
+      <c r="E64" s="37" t="n"/>
+      <c r="F64" s="37" t="n"/>
+      <c r="G64" s="37" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>06.01.01</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Dinero pequeño respetando los límites de 01.01.03</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>05.01.03</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>limites ya escritos y firmados (D-14, 01/08): capital 1.000-2.000 €, AVISO a -25% del capital inicial que no para nada, PARADA DURA AUTOMATICA a -30% aplicada por el bot de forma continua y sin exencion activable desde dentro (regla 26 de CLAUDE.md).</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>06.01.02</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
+        </is>
+      </c>
+      <c r="C66" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>06.01.01</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="36" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B67" s="37" t="inlineStr">
+        <is>
+          <t>MOTOR Y ORDEN (PARALELA; MÁX. 20% DEL ESFUERZO SEMANAL)</t>
+        </is>
+      </c>
+      <c r="C67" s="37" t="n"/>
+      <c r="D67" s="37" t="n"/>
+      <c r="E67" s="37" t="n"/>
+      <c r="F67" s="37" t="n"/>
+      <c r="G67" s="37" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>07.01.01</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>03.01.01</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (02/08): ALCANCE — cuatro arreglos de documento, NINGUNO toca código: (a) Las celdas ESTADO de 01.02.04 y 03.01.12 declaran en negrita un estado del vocabulario pendiente / en_curso / hecha / bloqueada, como exige la sección «Estados y cadencia de este WBS». Valores ya decididos por el orquestador, no se deducen: 01.02.04 pasa a en_curso (entregado INFORME_MCP_2.md, RECHAZADO por critico-codigo, sin reparar); 03.01.12 pasa a pendiente (nadie la ha trabajado). En 01.02.04 la marca actual […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
         <is>
           <t>07.01.02</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>Constructores</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>03.01.02</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr"/>
-      <c r="G64" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G64"/>
+  <autoFilter ref="A4:G69"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E64">
+  <conditionalFormatting sqref="E5:E69">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecha"</formula>
     </cfRule>
@@ -5188,7 +5663,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,Hecha,Bloqueada"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5874,7 +6349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5898,296 +6373,6 @@
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>REGLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Toda tarea se ejecuta y se anuncia por su código WBS. Prohibidos identificadores opacos (t55).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>No se inventan tareas: trabajo nuevo = primero se añade aquí con código y motivo. Subtareas dentro de alcance las crea el orquestador; tareas nuevas de primer nivel, solo en revisión semanal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Los códigos son estables: una tarea empezada no se renumera jamás.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Se va en orden salvo tareas marcadas paralelas. Una tarea no se cierra sin cumplir su criterio de "hecho".</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Nadie valida su propio trabajo. Los veredictos de estrategia los firma el Validador, no quien construyó.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Regla de no-ambigüedad: toda tarea debe poder ejecutarse sin adivinar nada. Si un agente tiene que suponer, la tarea vuelve al orquestador para reescribirse.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Pre-registro: ninguna variante de estrategia se prueba sin estar registrada antes. Se guardan TODAS las pruebas, también las fallidas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Cada agente usa el modelo asignado en la sección Equipo, y su respaldo si ese modelo falla o rechaza la petición.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Restricción justificada, en dos niveles. Lo REVERSIBLE (archivos, carpetas, código, pruebas) empieza con permisos amplios: git lo deshace todo, y una restricción solo se añade tras un incidente real, anotada junto al incidente y revisada cada mes. Lo IRREVERSIBLE (dinero real, órdenes al broker, borrar el cajón de datos reservado, gastar dinero nuevo) lleva barrera desde el minuto uno y no se negocia. Manga ancha con lo que se puede deshacer, cero manga con lo que no.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Ficha de decisión del CEO: nada llega al CEO como "opina sobre esto". Toda decisión llega con: 1 línea de qué se decide · 2-4 opciones cerradas · la recomendada marcada con su motivo · qué pasa con cada opción · respuesta de una letra o un número. Ninguna ficha puede pedirle redactar, buscar o calcular nada. Si no cabe en media pantalla de móvil, vuelve atrás.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Cadencia de entregables: el WBS en texto se actualiza SIEMPRE que cambie algo (no es negociable). El Excel de vista del CEO se regenera solo para la revisión de los lunes y para las puertas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Cada tirada autónoma cierra al menos una tarea que avanza el producto. La infraestructura que no desbloquee mecánicamente una tarea de producto se registra como deuda y no se ejecuta sin permiso del CEO. (gb2: 70% del esfuerzo al motor, 1 de 13 hipótesis probada, motor congelado dos veces sin frenarlo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Toda barrera se verifica por ejecución —inyectando el caso prohibido y comprobando que se bloquea— antes de documentarla como activa. Sin prueba, se marca "no verificada". Un guardia nunca se da por bueno por estar presente en el código. (gb2: el aislamiento del sistema nunca funcionó y nadie lo comprobó en meses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Los guardias bloquean por defecto (todo prohibido salvo lista explícita). La condición que activa una exención debe ser un hecho impuesto por el sistema, nunca un dato que elija el vigilado. (gb2: bastaba escribir "merge:" en el mensaje para saltarse el muro)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Éxito = código fiel a la especificación, NO estrategia rentable. Un backtest con mal resultado y código correcto es un éxito registrable. (vacuna contra tocar parámetros hasta que salga bonito)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Test de compuerta: si la justificación de un cambio no se sostiene sin citar métricas de resultado, se deniega.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Registros que solo permiten añadir: el registro de pruebas y el de decisiones nunca se reescriben; una corrección es una entrada nueva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Todo dato numérico se calcula sobre datos brutos, salvo que exista una fuente primaria homogénea demostrable. (confirmado dos veces: ni el ATR intradía ni la matriz de correlaciones existen publicados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>La ficha de una tarea se escribe en la cola ANTES de trabajarla, nunca al cerrarla. Sin ficha, no hay tarea.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Ninguna referencia a una decisión entra en código o informe sin un grep previo que la localice. Solo se cita lo firmado y guardado. (gb2: 4 citas inventadas dentro del código de producción)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Se referencia por nombre de símbolo, nunca por número de línea.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Quien implementa ejecuta y lee su artefacto completo antes de entregar. Las puertas confirman, no descubren.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Un fallo reportado por un agente no es un fallo verificado: antes de encolar o reparar, se lee el componente y se reproduce el fallo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Los datos nunca entran en git. Se descargan con script y se ignoran de verdad, comprobándolo el día 1. (gb2: 50.089 ficheros de datos versionados contra su propio .gitignore, 1,4 GB por clon)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Cada agente lleva el identificador exacto de su modelo, nunca un alias, y ningún agente sin modelo. (gb2: 7 de 13 con alias y el firmante sin modelo, contra su propia política)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Antes de crear un agente se comprueba que el WBS contiene tareas de su tipo. El reparto enruta por tipo de tarea. Un agente sin tareas durante dos semanas se elimina o se justifica en la revisión del lunes. (gb2: 3 agentes nunca invocados porque la cola nunca tuvo tareas de su tipo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Jerarquía de la prueba (contra el "una IA decide y se equivoca"). Ninguna afirmación se acepta por consenso entre agentes. El orden de fuerza es: (1) prueba ejecutada — el fallo se reproduce, el guardia se dispara, el número se recalcula: esto cierra el asunto; (2) verificación documental — grep que localiza la cita por fichero y línea; (3) contraste entre dos agentes con papeles opuestos — solo cuando (1) y (2) no son posibles, y el resultado se marca como no probado. Dos agentes de acuerdo no son una prueba: en gb2 hubo tres diagnósticos consecutivos del mismo componente, dos de ellos falsos, y lo que los corrigió no fue debatir más, fue leer el código y reproducir el fallo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Quien discrepa aporta el experimento que zanjaría la discusión, no otro argumento. Si no existe experimento posible, la decisión sube al CEO marcada como no probada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Estados: pendiente | en_curso | hecha | bloqueada.</t>
         </is>
       </c>
     </row>
@@ -6205,7 +6390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6519,7 +6704,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Formato obligatorio de ficha de decisión del CEO (regla 10 + plantilla)</t>
+          <t>Formato obligatorio de ficha de decisión del CEO (sección «Qué llega al CEO y qué no» de CLAUDE.md + plantilla)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -6677,7 +6862,75 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Aplicación de la regla 12 a una petición del propio CEO</t>
+          <t>Aplicación de la regla 8 de CLAUDE.md a una petición del propio CEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>01.02.03 amplía alcance: además del catálogo, fuentes oficiales de Anthropic y mecanismos nativos de Claude Code</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Petición del CEO. El catálogo por sí solo dejaba fuera lo que ya está instalado y sin usar</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Se añade 01.02.04: evaluar MCP con veredicto por servidor y regla de admisión escrita</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Petición del CEO; no estaba medido en el WBS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Se añade 03.01.12: estrategia de ramas, con el criterio del CEO «agilidad, no complejidad»</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Petición del CEO. Hoy todo va en main sin norma escrita</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>El orquestador NO se convierte en subagente que lo haga todo: sigue en la sesión principal</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Comprobado por lectura: ningún agente de .claude/agents/ lleva la herramienta Agent en tools, así que un orquestador subagente no puede repartir. Y meter la revisión dentro del subagente degradaría la prueba al nivel 3 de la regla 9 de CLAUDE.md (consenso entre agentes), que es el más débil</t>
         </is>
       </c>
     </row>
@@ -6764,7 +7017,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Todo lo que esté versionado en git: los datos se descargan, no se clonan (regla 24)</t>
+          <t>Todo lo que esté versionado en git: los datos se descargan, no se clonan (regla 27 de CLAUDE.md)</t>
         </is>
       </c>
     </row>
@@ -6825,7 +7078,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Se intenta leer el cajón reservado por tres vías distintas (agente, script, terminal) y las tres deben bloquearse (regla 13). En gb2 estos sí mordían</t>
+          <t>Se intenta leer el cajón reservado por tres vías distintas (agente, script, terminal) y las tres deben bloquearse (regla 25 de CLAUDE.md). En gb2 estos sí mordían</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -6859,7 +7112,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>NO se trae: la configuración de agentes, la cola de tareas, el historial de git, los ficheros de estado, los encadenadores de sesión ni ninguna documentación de gb2 como norma. Las lecciones ya están extraídas en las reglas 12 a 26.</t>
+          <t>NO se trae: la configuración de agentes, la cola de tareas, el historial de git, los ficheros de estado, los encadenadores de sesión ni ninguna documentación de gb2 como norma. Las lecciones ya están extraídas en las reglas 5, 7, 11, 12, 13, 14, 15, 17, 18, 21, 25, 26, 27 y 29 de CLAUDE.md (el contenido de la antigua regla 26 del WBS —"antes de crear un agente se comprueba que el WBS tiene tareas de su tipo"— no tiene número propio en CLAUDE.md; ver L-010 de LECCIONES.md).</t>
         </is>
       </c>
     </row>

--- a/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
+++ b/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1078,12 +1078,12 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>02.03.01</t>
+          <t>03.01.08</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Revisión independiente de método, fuentes y números</t>
+          <t>Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
         </is>
       </c>
       <c r="C18" s="4" t="n"/>
@@ -1099,12 +1099,12 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>03.01.08</t>
+          <t>03.01.11</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
         </is>
       </c>
       <c r="C19" s="4" t="n"/>
@@ -1117,109 +1117,87 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>03.01.11</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>En curso</t>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>PROXIMA PUERTA</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>G1 — elegir mercado y tamaño de vela (criterios en la hoja PUERTAS)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>PROXIMA PUERTA</t>
+          <t>OBJETIVO DEL MES</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>G1 — elegir mercado y tamaño de vela (criterios en la hoja PUERTAS)</t>
+          <t>Llegar al 1 de septiembre con respuesta a: ¿existe alguna estrategia que merezca pasar a demo?</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>OBJETIVO DEL MES</t>
+          <t>FUENTE DE VERDAD</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>Llegar al 1 de septiembre con respuesta a: ¿existe alguna estrategia que merezca pasar a demo?</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>FUENTE DE VERDAD</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
           <t>00-direccion/WBS.md — este Excel se genera de ahi. Si discrepan, manda el texto.</t>
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>LEYENDA</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>LEYENDA</t>
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Hecha</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Hecha</t>
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>En curso</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>En curso</t>
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Bloqueada</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B24:G24"/>
+  <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B22:G22"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B22:G22"/>
     <mergeCell ref="B23:G23"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
   </mergeCells>
@@ -1776,7 +1754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1829,7 +1807,7 @@
       <c r="B4" s="24" t="n"/>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t>02.03.01 — Revisión independiente de método, fuentes y números</t>
+          <t>01.02.03 — Auditar el catálogo awesome-claude-code y, por ampliación del CEO (01/08), las fuentes oficiales de Anthropic y los mecanismos nativos de Claude Code; proponer máximo 4 piezas concretas para el motor, con motivo y coste de integración. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
         </is>
       </c>
       <c r="D4" s="24" t="n"/>
@@ -1839,7 +1817,7 @@
       <c r="H4" s="24" t="n"/>
       <c r="I4" s="25" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Investigador</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1853,7 @@
       <c r="B6" s="30" t="n"/>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>02.03.01 — Revisión independiente de método, fuentes y números. Detras de ella esperan 18 de las 42 tareas vivas.</t>
+          <t>02.03.02 — Informe de decisión: 3-5 mercados poco correlacionados + 1-2 velas. Detras de ella esperan 17 de las 41 tareas vivas.</t>
         </is>
       </c>
       <c r="D6" s="30" t="n"/>
@@ -1994,22 +1972,22 @@
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
-          <t>02.03.01</t>
+          <t>01.02.03</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Revisión independiente de método, fuentes y números</t>
+          <t>Auditar el catálogo awesome-claude-code y, por ampliación del CEO (01/08), las fuentes oficiales de Anthropic y los mecanismos nativos de Claude Code; proponer máximo 4 piezas concretas para el motor, con motivo y coste de integración. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
+          <t>Investigador</t>
+        </is>
+      </c>
+      <c r="E11" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
@@ -2017,12 +1995,8 @@
           <t>En curso</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>18</v>
-      </c>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -2035,12 +2009,12 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>01.02.03</t>
+          <t>01.02.04</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Auditar el catálogo awesome-claude-code y, por ampliación del CEO (01/08), las fuentes oficiales de Anthropic y los mecanismos nativos de Claude Code; proponer máximo 4 piezas concretas para el motor, con motivo y coste de integración. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
+          <t>NUEVA 01/08 (petición del CEO): evaluar si merece la pena añadir servidores MCP al proyecto, con veredicto por servidor y regla de admisión escrita para el futuro. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -2072,27 +2046,27 @@
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>01.02.04</t>
+          <t>01.02.02</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 01/08 (petición del CEO): evaluar si merece la pena añadir servidores MCP al proyecto, con veredicto por servidor y regla de admisión escrita para el futuro. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
+          <t>Trasplante pieza a pieza desde gb2 (D6=B). Una tarea por pieza, cada una con su criterio de aceptación (ver sección Trasplante). Ninguna entra sin pasar su prueba ejecutada</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="E13" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>En curso</t>
+          <t>Crítico + Constructores</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -2109,17 +2083,17 @@
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>01.02.02</t>
+          <t>02.01.01</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Trasplante pieza a pieza desde gb2 (D6=B). Una tarea por pieza, cada una con su criterio de aceptación (ver sección Trasplante). Ninguna entra sin pasar su prueba ejecutada</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Crítico + Constructores</t>
+          <t>Confirmar 8 candidatos: EURUSD, GBPUSD, USDJPY, AUDUSD, USDCHF, XAUUSD, BTC, ETH</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2146,17 +2120,17 @@
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>02.01.01</t>
+          <t>02.03.02</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Confirmar 8 candidatos: EURUSD, GBPUSD, USDJPY, AUDUSD, USDCHF, XAUUSD, BTC, ETH</t>
-        </is>
-      </c>
-      <c r="D15" s="28" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
+          <t>Informe de decisión: 3-5 mercados poco correlacionados + 1-2 velas</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2169,8 +2143,12 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>17</v>
+      </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -2603,7 +2581,7 @@
     <row r="27">
       <c r="A27" s="32" t="inlineStr">
         <is>
-          <t>ESPERANDO A OTRA TAREA — 25 tareas, en orden de codigo WBS</t>
+          <t>ESPERANDO A OTRA TAREA — 24 tareas, en orden de codigo WBS</t>
         </is>
       </c>
       <c r="B27" s="32" t="n"/>
@@ -2623,17 +2601,17 @@
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>02.03.02</t>
+          <t>02.03.03</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Informe de decisión: 3-5 mercados poco correlacionados + 1-2 velas</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Orquestador</t>
+          <t>PUERTA G1: el CEO elige</t>
+        </is>
+      </c>
+      <c r="D28" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2650,11 +2628,11 @@
         <v>1</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>02.03.01 (en curso, Orquestador)</t>
+          <t>02.03.02 (pendiente, Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2666,22 +2644,22 @@
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>02.03.03</t>
+          <t>03.01.05</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G1: el CEO elige</t>
-        </is>
-      </c>
-      <c r="D29" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
+          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
+        </is>
+      </c>
+      <c r="E29" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2689,15 +2667,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>16</v>
-      </c>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>02.03.02 (pendiente, Orquestador)</t>
+          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2709,17 +2683,17 @@
       </c>
       <c r="B30" s="33" t="inlineStr">
         <is>
-          <t>03.01.05</t>
+          <t>03.01.07</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
+          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E30" s="34" t="inlineStr">
@@ -2736,7 +2710,7 @@
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
+          <t>03.01.06 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -2748,17 +2722,17 @@
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>03.01.07</t>
+          <t>03.01.08</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
+          <t>Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Crítico</t>
         </is>
       </c>
       <c r="E31" s="34" t="inlineStr">
@@ -2766,16 +2740,20 @@
           <t>MOTOR</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>03.01.06 (pendiente, Secretario)</t>
+          <t>03.01.03 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2787,17 +2765,17 @@
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>03.01.08</t>
+          <t>03.01.11</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Crítico</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E32" s="34" t="inlineStr">
@@ -2810,15 +2788,11 @@
           <t>En curso</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>03.01.03 (pendiente, Constructores)</t>
+          <t>03.01.08 (en curso, Crítico)</t>
         </is>
       </c>
     </row>
@@ -2830,34 +2804,38 @@
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>03.01.11</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E33" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr"/>
+          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
+        </is>
+      </c>
+      <c r="D33" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>03.01.08 (en curso, Crítico)</t>
+          <t>02.03.03 (pendiente, CEO)</t>
         </is>
       </c>
     </row>
@@ -2869,17 +2847,17 @@
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>04.01.02</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
-        </is>
-      </c>
-      <c r="D34" s="28" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
+          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2892,15 +2870,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G34" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>15</v>
-      </c>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>02.03.03 (pendiente, CEO)</t>
+          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2912,12 +2886,12 @@
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>04.01.02</t>
+          <t>04.01.03</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
+          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2935,8 +2909,12 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
           <t>04.01.01 (pendiente, CEO + Orquestador)</t>
@@ -2951,17 +2929,17 @@
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>04.01.03</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
+          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2978,11 +2956,11 @@
         <v>1</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
+          <t>04.02.01 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -2994,17 +2972,17 @@
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
+          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -3021,11 +2999,11 @@
         <v>1</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>04.02.01 (pendiente, Investigador)</t>
+          <t>04.02.02 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3015,12 @@
       </c>
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.02.04</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
+          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -3064,11 +3042,11 @@
         <v>1</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>04.02.02 (pendiente, Investigador)</t>
+          <t>04.02.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3080,17 +3058,17 @@
       </c>
       <c r="B39" s="33" t="inlineStr">
         <is>
-          <t>04.02.04</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
+          <t>Backtest con costes reales sobre el cajón de construir</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -3107,11 +3085,11 @@
         <v>1</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>04.02.03 (pendiente, Validador)</t>
+          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3101,12 @@
       </c>
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Backtest con costes reales sobre el cajón de construir</t>
+          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -3150,11 +3128,11 @@
         <v>1</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
+          <t>04.03.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -3166,17 +3144,17 @@
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
+          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -3193,11 +3171,11 @@
         <v>1</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>04.03.01 (pendiente, Constructores)</t>
+          <t>04.03.02 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -3209,12 +3187,12 @@
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
+          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -3236,11 +3214,11 @@
         <v>1</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>04.03.02 (pendiente, Constructores)</t>
+          <t>04.03.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3252,12 +3230,12 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -3279,11 +3257,11 @@
         <v>1</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>04.03.03 (pendiente, Validador)</t>
+          <t>04.03.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3295,17 +3273,17 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>04.03.05</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
+          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -3319,14 +3297,14 @@
         </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>04.03.04 (pendiente, Validador)</t>
+          <t>04.03.05 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3316,17 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.04.02</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
+          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3361,15 +3339,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>7</v>
-      </c>
+      <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>04.03.05 (pendiente, Validador)</t>
+          <t>04.04.01 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -3381,17 +3355,17 @@
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>04.04.02</t>
+          <t>04.04.03</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>Orquestador</t>
+          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
+        </is>
+      </c>
+      <c r="D46" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3404,8 +3378,12 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
           <t>04.04.01 (pendiente, Secretario)</t>
@@ -3420,17 +3398,17 @@
       </c>
       <c r="B47" s="33" t="inlineStr">
         <is>
-          <t>04.04.03</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
-        </is>
-      </c>
-      <c r="D47" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Bot en demo, solo y con guardias automáticos</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -3447,11 +3425,11 @@
         <v>1</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>04.04.01 (pendiente, Secretario)</t>
+          <t>04.04.03 (pendiente, CEO)</t>
         </is>
       </c>
     </row>
@@ -3463,17 +3441,17 @@
       </c>
       <c r="B48" s="33" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>05.01.02</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Bot en demo, solo y con guardias automáticos</t>
+          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -3490,11 +3468,11 @@
         <v>1</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>04.04.03 (pendiente, CEO)</t>
+          <t>05.01.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -3506,17 +3484,17 @@
       </c>
       <c r="B49" s="33" t="inlineStr">
         <is>
-          <t>05.01.02</t>
+          <t>05.01.03</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Secretario</t>
+          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
+        </is>
+      </c>
+      <c r="D49" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -3533,11 +3511,11 @@
         <v>1</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>05.01.01 (pendiente, Constructores)</t>
+          <t>05.01.02 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -3549,17 +3527,17 @@
       </c>
       <c r="B50" s="33" t="inlineStr">
         <is>
-          <t>05.01.03</t>
+          <t>06.01.01</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
-        </is>
-      </c>
-      <c r="D50" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Dinero pequeño respetando los límites de 01.01.03</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -3576,11 +3554,11 @@
         <v>1</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>05.01.02 (pendiente, Secretario)</t>
+          <t>05.01.03 (pendiente, CEO)</t>
         </is>
       </c>
     </row>
@@ -3592,17 +3570,17 @@
       </c>
       <c r="B51" s="33" t="inlineStr">
         <is>
-          <t>06.01.01</t>
+          <t>06.01.02</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Dinero pequeño respetando los límites de 01.01.03</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
+          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
+        </is>
+      </c>
+      <c r="D51" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -3615,59 +3593,16 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>05.01.03 (pendiente, CEO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B52" s="33" t="inlineStr">
-        <is>
-          <t>06.01.02</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
-        </is>
-      </c>
-      <c r="D52" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
           <t>06.01.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="46" customHeight="1">
-      <c r="A54" s="35" t="inlineStr">
+    <row r="53" ht="46" customHeight="1">
+      <c r="A53" s="35" t="inlineStr">
         <is>
           <t>Aviso de la regla 8 (CLAUDE.md): si la cola de arriba solo tuviera tareas de MOTOR, hay que parar y avisar al CEO; significa que la cola esta mal llena. Ahora mismo la cola tiene 5 de producto y 12 de motor.</t>
         </is>
@@ -3684,8 +3619,8 @@
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="A27:I27"/>
     <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A53:I53"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4307,15 +4242,15 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>FICHA SEGUNDA PASADA (02/08): PUNTO DE PARTIDA: la primera pasada dio RECHAZA el 31/07 con 7 motivos, y ese veredicto solo existe dentro de esta celda del WBS: no hay artefacto en disco. Entremedias el CEO aprobó los siete criterios de G1 en D-11 (00-direccion/DECISIONES.md), que dice resolver parte de esos motivos. ALCANCE — un veredicto por cada uno de los 7 motivos, con la etiqueta CERRADO o ABIERTO y la prueba al lado: (1) Dos criterios de G1 sin dato («cientos de operaciones posibles» y […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>02/08 — 04-resultados/veredictos/veredicto_fase_02.md y 03-motor/scripts/deriva_oro.py. Segunda pasada del RECHAZA del 31/07. ACEPTA CON HUECOS DECLARADOS, válido SOLO si el defecto del motivo 5 llega declarado al CEO en la ficha de G1; si se omite, decae y rige el RECHAZA. Balance: 4 cerrados (1, 3, 6, 7), 3 abiertos (2, 4, 5), el 5 escalado. Motivo 3 zanjado por ejecución: XAUUSD a 4h pasa de 2,32% a 4,22% y 5,43%, bajo el umbral del 10%, así que la deriva del coste del oro NO cambia el veredicto a 4h; sí lo rompe a 1h (11,01%) y a 15m (19,80-25,46%). Motivo 5 confirmado uno a uno: 7 de 8 instrumentos** mezclan broker o tipo de cuenta; solo BTCUSD comparte fuente. RECORRIDO: validador […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">

--- a/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
+++ b/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
@@ -15,13 +15,12 @@
     <sheet name="EQUIPO" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="REGLAS" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="DECISIONES" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="TRASPLANTE gb2" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="LECCIONES" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="AUTONOMIA" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="LIMITES CEO" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="LECCIONES" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="AUTONOMIA" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="LIMITES CEO" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TAREAS'!$A$4:$G$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TAREAS'!$A$4:$G$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -674,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -743,23 +742,23 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"01.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"01.??.??")</f>
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"01.??.??",TAREAS!$E$5:$E$69,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"01.??.??",TAREAS!$E$5:$E$73,"Hecha")</f>
         <v/>
       </c>
       <c r="D4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"01.??.??",TAREAS!$E$5:$E$69,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"01.??.??",TAREAS!$E$5:$E$73,"En curso")</f>
         <v/>
       </c>
       <c r="E4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"01.??.??",TAREAS!$E$5:$E$69,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"01.??.??",TAREAS!$E$5:$E$73,"Pendiente")</f>
         <v/>
       </c>
       <c r="F4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"01.??.??",TAREAS!$E$5:$E$69,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"01.??.??",TAREAS!$E$5:$E$73,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G4" s="6">
@@ -774,23 +773,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"02.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"02.??.??")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"02.??.??",TAREAS!$E$5:$E$69,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"02.??.??",TAREAS!$E$5:$E$73,"Hecha")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"02.??.??",TAREAS!$E$5:$E$69,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"02.??.??",TAREAS!$E$5:$E$73,"En curso")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"02.??.??",TAREAS!$E$5:$E$69,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"02.??.??",TAREAS!$E$5:$E$73,"Pendiente")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"02.??.??",TAREAS!$E$5:$E$69,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"02.??.??",TAREAS!$E$5:$E$73,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G5" s="6">
@@ -805,23 +804,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"03.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"03.??.??")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"03.??.??",TAREAS!$E$5:$E$69,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"03.??.??",TAREAS!$E$5:$E$73,"Hecha")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"03.??.??",TAREAS!$E$5:$E$69,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"03.??.??",TAREAS!$E$5:$E$73,"En curso")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"03.??.??",TAREAS!$E$5:$E$69,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"03.??.??",TAREAS!$E$5:$E$73,"Pendiente")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"03.??.??",TAREAS!$E$5:$E$69,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"03.??.??",TAREAS!$E$5:$E$73,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G6" s="6">
@@ -836,23 +835,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"04.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"04.??.??")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"04.??.??",TAREAS!$E$5:$E$69,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"04.??.??",TAREAS!$E$5:$E$73,"Hecha")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"04.??.??",TAREAS!$E$5:$E$69,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"04.??.??",TAREAS!$E$5:$E$73,"En curso")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"04.??.??",TAREAS!$E$5:$E$69,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"04.??.??",TAREAS!$E$5:$E$73,"Pendiente")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"04.??.??",TAREAS!$E$5:$E$69,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"04.??.??",TAREAS!$E$5:$E$73,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G7" s="6">
@@ -867,23 +866,23 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"05.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"05.??.??")</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"05.??.??",TAREAS!$E$5:$E$69,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"05.??.??",TAREAS!$E$5:$E$73,"Hecha")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"05.??.??",TAREAS!$E$5:$E$69,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"05.??.??",TAREAS!$E$5:$E$73,"En curso")</f>
         <v/>
       </c>
       <c r="E8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"05.??.??",TAREAS!$E$5:$E$69,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"05.??.??",TAREAS!$E$5:$E$73,"Pendiente")</f>
         <v/>
       </c>
       <c r="F8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"05.??.??",TAREAS!$E$5:$E$69,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"05.??.??",TAREAS!$E$5:$E$73,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G8" s="6">
@@ -898,23 +897,23 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"06.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"06.??.??")</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"06.??.??",TAREAS!$E$5:$E$69,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"06.??.??",TAREAS!$E$5:$E$73,"Hecha")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"06.??.??",TAREAS!$E$5:$E$69,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"06.??.??",TAREAS!$E$5:$E$73,"En curso")</f>
         <v/>
       </c>
       <c r="E9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"06.??.??",TAREAS!$E$5:$E$69,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"06.??.??",TAREAS!$E$5:$E$73,"Pendiente")</f>
         <v/>
       </c>
       <c r="F9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"06.??.??",TAREAS!$E$5:$E$69,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"06.??.??",TAREAS!$E$5:$E$73,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G9" s="6">
@@ -929,23 +928,23 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"07.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"07.??.??")</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"07.??.??",TAREAS!$E$5:$E$69,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"07.??.??",TAREAS!$E$5:$E$73,"Hecha")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"07.??.??",TAREAS!$E$5:$E$69,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"07.??.??",TAREAS!$E$5:$E$73,"En curso")</f>
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"07.??.??",TAREAS!$E$5:$E$69,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"07.??.??",TAREAS!$E$5:$E$73,"Pendiente")</f>
         <v/>
       </c>
       <c r="F10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$69,"07.??.??",TAREAS!$E$5:$E$69,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$73,"07.??.??",TAREAS!$E$5:$E$73,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G10" s="6">
@@ -1015,12 +1014,12 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>01.01.01</t>
+          <t>03.01.08</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Aprobar plan y reglas</t>
+          <t>Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
         </is>
       </c>
       <c r="C15" s="4" t="n"/>
@@ -1036,12 +1035,12 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>01.02.03</t>
+          <t>03.01.11</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Auditar el catálogo awesome-claude-code y, por ampliación del CEO (01/08), las fuentes oficiales de Anthropic y los mecanismos nativos de Claude Code; proponer máximo 4 piezas concretas para el motor, con motivo y coste de integración. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
         </is>
       </c>
       <c r="C16" s="4" t="n"/>
@@ -1057,12 +1056,12 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>01.02.04</t>
+          <t>07.01.03</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 01/08 (petición del CEO): evaluar si merece la pena añadir servidores MCP al proyecto, con veredicto por servidor y regla de admisión escrita para el futuro. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
+          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
         </is>
       </c>
       <c r="C17" s="4" t="n"/>
@@ -1075,131 +1074,87 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>03.01.08</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>En curso</t>
-        </is>
-      </c>
-    </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>03.01.11</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>En curso</t>
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>PROXIMA PUERTA</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>G1 — elegir mercado y tamaño de vela (criterios en la hoja PUERTAS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>OBJETIVO DEL MES</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Llegar al 1 de septiembre con respuesta a: ¿existe alguna estrategia que merezca pasar a demo?</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>PROXIMA PUERTA</t>
+          <t>FUENTE DE VERDAD</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>G1 — elegir mercado y tamaño de vela (criterios en la hoja PUERTAS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>OBJETIVO DEL MES</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>Llegar al 1 de septiembre con respuesta a: ¿existe alguna estrategia que merezca pasar a demo?</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>FUENTE DE VERDAD</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
           <t>00-direccion/WBS.md — este Excel se genera de ahi. Si discrepan, manda el texto.</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>LEYENDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>Hecha</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>LEYENDA</t>
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>En curso</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Hecha</t>
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>En curso</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Bloqueada</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="8">
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B22:G22"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B19:F19"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B21:G21"/>
     <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G11">
     <cfRule type="dataBar" priority="1">
@@ -1220,349 +1175,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LECCIONES APRENDIDAS</t>
+          <t>AUTONOMIA — que llega al CEO y que no</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>CUANDO</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Lección</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Origen</t>
+          <t>QUE PASA</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>L-001</t>
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>Lo cierra el equipo, sin consultar</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Si un dato se puede calcular a partir de datos brutos disponibles, se calcula. Buscar el dato ya masticado pierde tiempo y devuelve fuentes flojas</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Revisión 02.03.01</t>
+          <t>cerrar tareas que cumplen su criterio
+· orden de tareas ya aprobadas
+· subtareas dentro de alcance
+· descartar hipótesis o variantes que no pasan el filtro
+· reescribir tareas ambiguas
+· mover, corregir o borrar archivos para mantener el orden (git deshace).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>L-002</t>
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>Llega al CEO, en el informe semanal</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Toda conversión de unidades se aplica en la tabla final, no solo se explica en una nota al pie</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Revisión 02.03.01</t>
+          <t>mejoras del motor no previstas (sin aprobación, no se hacen)
+· tareas nuevas de primer nivel.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>L-003</t>
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>Llega al CEO como excepción inmediata (se para hasta respuesta)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Medir el coste de entrar y salir sin medir el de mantener da una foto incompleta</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Revisión 02.03.01</t>
+          <t>gasto nuevo (datos de pago, VPS, broker, créditos extra)
+· cualquier cosa con dinero real
+· bloqueo de más de 24 h
+· 3 vueltas del bucle de hipótesis sin éxito.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>L-004</t>
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>Llega al CEO solo en una puerta</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Los valores absolutos no se comparan entre activos distintos: se normalizan antes</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Revisión 02.03.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>L-005</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>El modelo no aprende: acumula notas escritas. Si nadie escribe bien las notas, no mejora nada</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Análisis del vídeo, 29/07</t>
+          <t>cambiar de mercado, de tamaño de vela o de planteamiento.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>L-006</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Si dos fuentes usan convenciones distintas (yen y franco invertidos), sus números tienen el signo cambiado. Verificar la convención antes de comparar</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Revisión Brief B</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>L-007</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Un nombre parecido no es el mismo instrumento: oro al contado ≠ futuro de oro; bitcoin contra Tether ≠ contra dólar</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Revisión Brief B</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>L-008</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Un umbral sobre una magnitud inestable necesita varias ventanas, no una</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Revisión Brief B</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>L-009</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Un guardia verificado por presencia y no por ejecución da falsa seguridad, que es peor que no tenerlo</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Auditoría gb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>L-010</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Los agentes no se activan solos porque tengan buena descripción: se activan si la cola contiene tareas de su tipo y el reparto enruta por tipo</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Auditoría gb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>L-011</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Tener una cola estricta no impide la deriva. gb2 la tenía ("trabajo que no está ahí no se ejecuta"), con IDs contiguos forzados por un hook, y aun así el 70% del esfuerzo se fue al motor. La cola controla QUÉ se ejecuta, no QUÉ se mete en la cola</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Auditoría gb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>L-012</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Dos agentes de acuerdo no son una prueba. En gb2 hubo tres diagnósticos seguidos del mismo componente, dos falsos; lo que los corrigió fue leer el código y reproducir el fallo, no debatir más</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Auditoría gb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>L-013</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Se trabajó una tarea sin ficha escrita antes: 01.01.02 era una fila de una línea sin alcance ni criterio de hecho, y el trabajo de apoyo se autoasignó alcance dentro de ella. La regla 5 de CLAUDE.md vale también para las tareas del CEO</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Revisión del cálculo de arrastre (01.01.02) por critico-codigo, 01/08</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>L-014</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Un supuesto expresado en porcentaje decidió el orden de magnitud sin declararse: fijar la actividad como porcentaje de velas operadas producía un multiplicador de coste x60-x69 entre velas que en valor absoluto cae a x4,3; la conclusión "1h es inviable" era un artefacto del supuesto</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Revisión de arrastre_coste.md, hallado por critico-codigo y confirmado con experimento ejecutado por validador, 01/08</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>L-015</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>CLAUDE.md y este WBS llevan dos listas de «29 reglas» con contenido distinto bajo el mismo número: toda cita regla N es ambigua. Resuelto el 01/08/2026 por D-16: la lista normativa es la de CLAUDE.md; toda cita se escribe «regla N de CLAUDE.md»</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Revisión 01.02.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>L-016</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Un indicador que solo mira lo etiquetado es ciego justo donde importa: medir el reparto producto/motor contando solo commits con código WBS daba 20% cuando el real es 43,8%, porque commit-msg exime a meta:, org: y arranque:, que es donde vive el motor</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Revisión 01.02.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>L-017</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>L-015 citaba mal su propia regla de grep: decía "la regla 20 de CLAUDE.md exige grep previo" cuando esa exigencia es la regla 12 de CLAUDE.md (la 20 es "se guardan todas las pruebas"). LECCIONES.md es de solo-añadir, así que no se corrige en su sitio, se anota aparte</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Tarea 03.01.13, pasada 1 (constructor-motor), 01/08</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>L-018</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Un recuento sin -i da cifras bajas aunque lo repitan dos agentes: quien ejecutó y quien revisó grepearon "regla" en minúscula y los dos dieron la misma cifra baja (5/3/36 en vez de 12/4/39), porque el error estaba en el método de los dos, no en el dato</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Tarea 03.01.13, pasada 2 (constructor-motor, ordenada tras el rechazo de la pasada 1), 01/08</t>
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>FORMATO OBLIGATORIO DE FICHA DE DECISION (regla 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="100" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>D[n] — [Qué se decide, una línea]
+A) [opción]   B) [opción]   C) [opción]
+RECOMENDADA: [letra] — [motivo en una línea]
+SI ELIGES OTRA: [consecuencia de cada una, una línea]
+BLOQUEA: [qué tareas no pueden avanzar hasta que respondas]
+RESPUESTA: [una letra]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1574,125 +1293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>AUTONOMIA — que llega al CEO y que no</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>CUANDO</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>QUE PASA</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="40" t="inlineStr">
-        <is>
-          <t>Lo cierra el equipo, sin consultar</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>cerrar tareas que cumplen su criterio
-· orden de tareas ya aprobadas
-· subtareas dentro de alcance
-· descartar hipótesis o variantes que no pasan el filtro
-· reescribir tareas ambiguas
-· mover, corregir o borrar archivos para mantener el orden (git deshace).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="40" t="inlineStr">
-        <is>
-          <t>Llega al CEO, en el informe semanal</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>mejoras del motor no previstas (sin aprobación, no se hacen)
-· tareas nuevas de primer nivel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="40" t="inlineStr">
-        <is>
-          <t>Llega al CEO como excepción inmediata (se para hasta respuesta)</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>gasto nuevo (datos de pago, VPS, broker, créditos extra)
-· cualquier cosa con dinero real
-· bloqueo de más de 24 h
-· 3 vueltas del bucle de hipótesis sin éxito.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="40" t="inlineStr">
-        <is>
-          <t>Llega al CEO solo en una puerta</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>cambiar de mercado, de tamaño de vela o de planteamiento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>FORMATO OBLIGATORIO DE FICHA DE DECISION (regla 10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="100" customHeight="1">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t>D[n] — [Qué se decide, una línea]
-A) [opción]   B) [opción]   C) [opción]
-RECOMENDADA: [letra] — [motivo en una línea]
-SI ELIGES OTRA: [consecuencia de cada una, una línea]
-BLOQUEA: [qué tareas no pueden avanzar hasta que respondas]
-RESPUESTA: [una letra]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -1729,7 +1330,7 @@
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Tiempo del CEO: 1 hora los lunes, como MÍNIMO GARANTIZADO, no como techo (D-4 + D-13). Máximo 5 fichas de decisión por revisión; si hay más, el orquestador prioriza y las sobrantes esperan al lunes siguiente. El CEO sigue el proyecto a diario, lo que NO amplía lo que se le puede preguntar.</t>
+          <t>Tiempo del CEO: 1 hora los lunes, como MÍNIMO GARANTIZADO, no como techo (D-4 + D-13 + D-18). Lo que esté listo le llega el día que esté listo, sin tope de número; el CEO marca el final del día cuando no puede seguir, lo que quede acumula al día siguiente. Máximo 5 fichas de decisión en el checkpoint del lunes; si hay más, el orquestador prioriza y las sobrantes esperan al lunes siguiente. Lo que protege es que cada ficha llegue en formato obligatorio (sección «Qué llega al CEO y qué no» de CLAUDE.md): masticada, opciones cerradas, recomendada con motivo, respuesta de una letra. El CEO sigue el proyecto a diario, lo que NO amplía lo que se le puede preguntar.</t>
         </is>
       </c>
     </row>
@@ -1737,6 +1338,13 @@
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Dinero real (D-14): capital 1.000-2.000 € (ya es entrada de G1-C6, D-11; cambiarlo obliga a re-verificar G1-C6). AVISO a -25% del capital inicial ingresado, que no para nada: se reporta y decide el CEO. PARADA DURA AUTOMÁTICA a -30% del capital inicial, aplicada por el bot de forma CONTINUA y sin exención activable desde dentro (regla 26 de CLAUDE.md). Se mide sobre el capital inicial ingresado, no sobre el máximo alcanzado. Recuperar desde -30% exige +43%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Techo del 20% de motor (regla 8 de CLAUDE.md) SUSPENDIDO (D-17): El 03/08/2026 el techo de motor quedó SUSPENDIDO hasta que 03.01.05 esté hecha O llegue el 01/09/2026, lo que ocurra PRIMERO. Mientras esté en vigor la suspensión, el equipo puede dedicar más del 20% a motor en una tirada si es necesario para desbloquear producto. La regla 8 no se elimina; se suspende con disparador que impone el sistema (regla 26 de CLAUDE.md).</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1807,7 +1415,7 @@
       <c r="B4" s="24" t="n"/>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t>01.02.03 — Auditar el catálogo awesome-claude-code y, por ampliación del CEO (01/08), las fuentes oficiales de Anthropic y los mecanismos nativos de Claude Code; proponer máximo 4 piezas concretas para el motor, con motivo y coste de integración. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
+          <t>03.01.08 — Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
         </is>
       </c>
       <c r="D4" s="24" t="n"/>
@@ -1817,7 +1425,7 @@
       <c r="H4" s="24" t="n"/>
       <c r="I4" s="25" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Crítico</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1438,7 @@
       <c r="B5" s="27" t="n"/>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>01.01.01 — Aprobar plan y reglas</t>
+          <t>04.01.01 — Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
         </is>
       </c>
       <c r="D5" s="27" t="n"/>
@@ -1840,7 +1448,7 @@
       <c r="H5" s="27" t="n"/>
       <c r="I5" s="28" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>CEO + Orquestador</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1461,7 @@
       <c r="B6" s="30" t="n"/>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>02.03.02 — Informe de decisión: 3-5 mercados poco correlacionados + 1-2 velas. Detras de ella esperan 17 de las 41 tareas vivas.</t>
+          <t>04.02.01 — Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente. Detras de ella esperan 16 de las 39 tareas vivas.</t>
         </is>
       </c>
       <c r="D6" s="30" t="n"/>
@@ -1863,7 +1471,7 @@
       <c r="H6" s="30" t="n"/>
       <c r="I6" s="31" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Investigador</t>
         </is>
       </c>
     </row>
@@ -1935,22 +1543,22 @@
       </c>
       <c r="B10" s="33" t="inlineStr">
         <is>
-          <t>01.01.01</t>
+          <t>03.01.08</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Aprobar plan y reglas</t>
-        </is>
-      </c>
-      <c r="D10" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
+          <t>Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+      <c r="E10" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -1958,8 +1566,12 @@
           <t>En curso</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -1972,17 +1584,17 @@
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
-          <t>01.02.03</t>
+          <t>07.01.03</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Auditar el catálogo awesome-claude-code y, por ampliación del CEO (01/08), las fuentes oficiales de Anthropic y los mecanismos nativos de Claude Code; proponer máximo 4 piezas concretas para el motor, con motivo y coste de integración. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
+          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="E11" s="34" t="inlineStr">
@@ -2009,31 +1621,35 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>01.02.04</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 01/08 (petición del CEO): evaluar si merece la pena añadir servidores MCP al proyecto, con veredicto por servidor y regla de admisión escrita para el futuro. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="E12" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
+          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -2046,17 +1662,17 @@
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>01.02.02</t>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Trasplante pieza a pieza desde gb2 (D6=B). Una tarea por pieza, cada una con su criterio de aceptación (ver sección Trasplante). Ninguna entra sin pasar su prueba ejecutada</t>
+          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Crítico + Constructores</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2069,8 +1685,12 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>16</v>
+      </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -2083,22 +1703,22 @@
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>02.01.01</t>
+          <t>03.01.03</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Confirmar 8 candidatos: EURUSD, GBPUSD, USDJPY, AUDUSD, USDCHF, XAUUSD, BTC, ETH</t>
-        </is>
-      </c>
-      <c r="D14" s="28" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
+          <t>Ejecución desatendida: arranques programados, permisos AMPLIOS por defecto (git como red de seguridad) y topes de gasto</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E14" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -2106,8 +1726,12 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -2120,22 +1744,22 @@
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>02.03.02</t>
+          <t>03.01.04</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Informe de decisión: 3-5 mercados poco correlacionados + 1-2 velas</t>
+          <t>Plan de respaldo de modelos: si un modelo no está disponible o rechaza, el agente sigue con su respaldo y lo anota</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E15" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -2147,7 +1771,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -2161,22 +1785,22 @@
       </c>
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>04.02.01</t>
+          <t>03.01.06</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
+          <t>Plantilla y automatismo de fichas de decisión: el secretario prepara cada decisión del CEO en el formato obligatorio y la adjunta al informe semanal</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
+          <t>Secretario</t>
+        </is>
+      </c>
+      <c r="E16" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2188,7 +1812,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -2202,12 +1826,12 @@
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>03.01.03</t>
+          <t>03.01.09</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Ejecución desatendida: arranques programados, permisos AMPLIOS por defecto (git como red de seguridad) y topes de gasto</t>
+          <t>Enrutado por tipo de tarea y comprobación de que el WBS genera tareas de cada tipo de agente (ver L-010 de LECCIONES.md; sin número propio en CLAUDE.md)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -2225,12 +1849,8 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>3</v>
-      </c>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -2243,12 +1863,12 @@
       </c>
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>03.01.04</t>
+          <t>03.01.10</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Plan de respaldo de modelos: si un modelo no está disponible o rechaza, el agente sigue con su respaldo y lo anota</t>
+          <t>Testbed sintético de invarianza: resultado de referencia fijo que debe reproducirse tras cualquier cambio del motor</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -2266,12 +1886,8 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -2284,17 +1900,17 @@
       </c>
       <c r="B19" s="33" t="inlineStr">
         <is>
-          <t>03.01.06</t>
+          <t>03.01.12</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Plantilla y automatismo de fichas de decisión: el secretario prepara cada decisión del CEO en el formato obligatorio y la adjunta al informe semanal</t>
+          <t>NUEVA 01/08 (petición del CEO): fijar la estrategia de ramas de git. Criterio del CEO, literal: que dé agilidad, no complejidad</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E19" s="34" t="inlineStr">
@@ -2307,12 +1923,8 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -2325,12 +1937,12 @@
       </c>
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>03.01.09</t>
+          <t>03.01.14</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Enrutado por tipo de tarea y comprobación de que el WBS genera tareas de cada tipo de agente (ver L-010 de LECCIONES.md; sin número propio en CLAUDE.md)</t>
+          <t>NUEVA 01/08 (deuda detectada al cerrar 03.01.13): la hoja REGLAS del Excel del CEO la construye 05-vista-ceo/generar_excel.py leyendo las líneas numeradas de la sección de reglas del WBS, que tras D-16 ya no existen: la hoja saldría vacía bajo el título «LAS 29 REGLAS», y verificar_excel.py no comprueba esa hoja, así que sus 8 pruebas pasarían igual (L-016). Hay que leer las reglas de CLAUDE.md y añadir una prueba que falle si la hoja sale vacía. Deuda de motor: no se ejecuta sin permiso del CEO.</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -2348,8 +1960,12 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -2362,12 +1978,12 @@
       </c>
       <c r="B21" s="33" t="inlineStr">
         <is>
-          <t>03.01.10</t>
+          <t>03.01.15</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Testbed sintético de invarianza: resultado de referencia fijo que debe reproducirse tras cualquier cambio del motor</t>
+          <t>Herramientas del secretario: puede escribir los registros que solo admiten añadir pero no puede verificarlos</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2399,17 +2015,17 @@
       </c>
       <c r="B22" s="33" t="inlineStr">
         <is>
-          <t>03.01.12</t>
+          <t>03.01.17</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 01/08 (petición del CEO): fijar la estrategia de ramas de git. Criterio del CEO, literal: que dé agilidad, no complejidad</t>
+          <t>Reparar la prueba 7 de verificar_excel.py (entregables de las tareas hechas)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Constructor de motor</t>
         </is>
       </c>
       <c r="E22" s="34" t="inlineStr">
@@ -2436,12 +2052,12 @@
       </c>
       <c r="B23" s="33" t="inlineStr">
         <is>
-          <t>03.01.14</t>
+          <t>03.01.18</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 01/08 (deuda detectada al cerrar 03.01.13): la hoja REGLAS del Excel del CEO la construye 05-vista-ceo/generar_excel.py leyendo las líneas numeradas de la sección de reglas del WBS, que tras D-16 ya no existen: la hoja saldría vacía bajo el título «LAS 29 REGLAS», y verificar_excel.py no comprueba esa hoja, así que sus 8 pruebas pasarían igual (L-016). Hay que leer las reglas de CLAUDE.md y añadir una prueba que falle si la hoja sale vacía. Deuda de motor: no se ejecuta sin permiso del CEO.</t>
+          <t>NUEVA 03/08 (D-20, idea 1 de las auditorías): contador mecánico del reparto producto/motor, inyectado en el contexto al arrancar cada tirada</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2473,12 +2089,12 @@
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>03.01.15</t>
+          <t>03.01.19</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Herramientas del secretario: puede escribir los registros que solo admiten añadir pero no puede verificarlos</t>
+          <t>NUEVA 03/08 (D-20, idea 2 de las auditorías): registro mecánico de autoría, para que «nadie valida su propio trabajo» deje de ser solo prosa</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -2581,7 +2197,7 @@
     <row r="27">
       <c r="A27" s="32" t="inlineStr">
         <is>
-          <t>ESPERANDO A OTRA TAREA — 24 tareas, en orden de codigo WBS</t>
+          <t>ESPERANDO A OTRA TAREA — 22 tareas, en orden de codigo WBS</t>
         </is>
       </c>
       <c r="B27" s="32" t="n"/>
@@ -2601,22 +2217,22 @@
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>02.03.03</t>
+          <t>03.01.05</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G1: el CEO elige</t>
-        </is>
-      </c>
-      <c r="D28" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
+          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
+        </is>
+      </c>
+      <c r="E28" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2624,15 +2240,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>16</v>
-      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>02.03.02 (pendiente, Orquestador)</t>
+          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2644,17 +2256,17 @@
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>03.01.05</t>
+          <t>03.01.07</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
+          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E29" s="34" t="inlineStr">
@@ -2671,7 +2283,7 @@
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
+          <t>03.01.06 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -2683,17 +2295,17 @@
       </c>
       <c r="B30" s="33" t="inlineStr">
         <is>
-          <t>03.01.07</t>
+          <t>03.01.11</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E30" s="34" t="inlineStr">
@@ -2701,16 +2313,16 @@
           <t>MOTOR</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>03.01.06 (pendiente, Secretario)</t>
+          <t>03.01.08 (en curso, Crítico)</t>
         </is>
       </c>
     </row>
@@ -2722,17 +2334,17 @@
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>03.01.08</t>
+          <t>03.01.16</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
+          <t>Las hojas del Excel se construyen de sus fuentes primarias, no de copias</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Crítico</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E31" s="34" t="inlineStr">
@@ -2740,20 +2352,16 @@
           <t>MOTOR</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>03.01.03 (pendiente, Constructores)</t>
+          <t>03.01.14 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2765,34 +2373,34 @@
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>03.01.11</t>
+          <t>04.01.02</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
+          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E32" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>En curso</t>
+          <t>Constructor datos</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>03.01.08 (en curso, Crítico)</t>
+          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2804,17 +2412,17 @@
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>04.01.03</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
-        </is>
-      </c>
-      <c r="D33" s="28" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
+          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2828,14 +2436,14 @@
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>02.03.03 (pendiente, CEO)</t>
+          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2847,17 +2455,17 @@
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>04.01.02</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
+          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2870,11 +2478,15 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
+          <t>04.02.01 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -2886,17 +2498,17 @@
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>04.01.03</t>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
+          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2913,11 +2525,11 @@
         <v>1</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
+          <t>04.02.02 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -2929,17 +2541,17 @@
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>04.02.04</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
+          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2956,11 +2568,11 @@
         <v>1</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>04.02.01 (pendiente, Investigador)</t>
+          <t>04.02.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2972,17 +2584,17 @@
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
+          <t>Backtest con costes reales sobre el cajón de construir</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2999,11 +2611,11 @@
         <v>1</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>04.02.02 (pendiente, Investigador)</t>
+          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3015,17 +2627,17 @@
       </c>
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>04.02.04</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
+          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -3042,11 +2654,11 @@
         <v>1</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>04.02.03 (pendiente, Validador)</t>
+          <t>04.03.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -3058,17 +2670,17 @@
       </c>
       <c r="B39" s="33" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Backtest con costes reales sobre el cajón de construir</t>
+          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -3085,11 +2697,11 @@
         <v>1</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
+          <t>04.03.02 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -3101,17 +2713,17 @@
       </c>
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
+          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3128,11 +2740,11 @@
         <v>1</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>04.03.01 (pendiente, Constructores)</t>
+          <t>04.03.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3144,12 +2756,12 @@
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
+          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -3171,11 +2783,11 @@
         <v>1</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>04.03.02 (pendiente, Constructores)</t>
+          <t>04.03.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3187,17 +2799,17 @@
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -3211,14 +2823,14 @@
         </is>
       </c>
       <c r="G42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>04.03.03 (pendiente, Validador)</t>
+          <t>04.03.05 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -3230,17 +2842,17 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>04.03.05</t>
+          <t>04.04.02</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
+          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -3253,15 +2865,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>8</v>
-      </c>
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>04.03.04 (pendiente, Validador)</t>
+          <t>04.04.01 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -3273,17 +2881,17 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.04.03</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Secretario</t>
+          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
+        </is>
+      </c>
+      <c r="D44" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -3297,14 +2905,14 @@
         </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>04.03.05 (pendiente, Validador)</t>
+          <t>04.04.01 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -3316,17 +2924,17 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>04.04.02</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
+          <t>Bot en demo, solo y con guardias automáticos</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3339,11 +2947,15 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>04.04.01 (pendiente, Secretario)</t>
+          <t>04.04.03 (pendiente, CEO)</t>
         </is>
       </c>
     </row>
@@ -3355,17 +2967,17 @@
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>04.04.03</t>
+          <t>05.01.02</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
-        </is>
-      </c>
-      <c r="D46" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3382,11 +2994,11 @@
         <v>1</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>04.04.01 (pendiente, Secretario)</t>
+          <t>05.01.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -3398,17 +3010,17 @@
       </c>
       <c r="B47" s="33" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>05.01.03</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Bot en demo, solo y con guardias automáticos</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
+          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
+        </is>
+      </c>
+      <c r="D47" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -3425,11 +3037,11 @@
         <v>1</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>04.04.03 (pendiente, CEO)</t>
+          <t>05.01.02 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -3441,17 +3053,17 @@
       </c>
       <c r="B48" s="33" t="inlineStr">
         <is>
-          <t>05.01.02</t>
+          <t>06.01.01</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
+          <t>Dinero pequeño respetando los límites de 01.01.03</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -3468,11 +3080,11 @@
         <v>1</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>05.01.01 (pendiente, Constructores)</t>
+          <t>05.01.03 (pendiente, CEO)</t>
         </is>
       </c>
     </row>
@@ -3484,12 +3096,12 @@
       </c>
       <c r="B49" s="33" t="inlineStr">
         <is>
-          <t>05.01.03</t>
+          <t>06.01.02</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
+          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
         </is>
       </c>
       <c r="D49" s="28" t="inlineStr">
@@ -3507,104 +3119,18 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>05.01.02 (pendiente, Secretario)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B50" s="33" t="inlineStr">
-        <is>
-          <t>06.01.01</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Dinero pequeño respetando los límites de 01.01.03</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>05.01.03 (pendiente, CEO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B51" s="33" t="inlineStr">
-        <is>
-          <t>06.01.02</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
-        </is>
-      </c>
-      <c r="D51" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
           <t>06.01.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="46" customHeight="1">
-      <c r="A53" s="35" t="inlineStr">
-        <is>
-          <t>Aviso de la regla 8 (CLAUDE.md): si la cola de arriba solo tuviera tareas de MOTOR, hay que parar y avisar al CEO; significa que la cola esta mal llena. Ahora mismo la cola tiene 5 de producto y 12 de motor.</t>
+    <row r="51" ht="46" customHeight="1">
+      <c r="A51" s="35" t="inlineStr">
+        <is>
+          <t>Aviso de la regla 8 (CLAUDE.md): si la cola de arriba solo tuviera tareas de MOTOR, hay que parar y avisar al CEO; significa que la cola esta mal llena. Ahora mismo la cola tiene 2 de producto y 15 de motor.</t>
         </is>
       </c>
     </row>
@@ -3613,13 +3139,13 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A51:I51"/>
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="A27:I27"/>
     <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A53:I53"/>
     <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3632,7 +3158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3747,10 +3273,14 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>** 03/08 — FICHA (incumplimiento de regla 5 de CLAUDE.md declarado: se trabajó sin ficha previa): aprobación del WBS v0.7 (29/07/2026), que antecede a CLAUDE.md. El 01/08/2026 se aprobaron las decisiones D-1 a D-16, que ratificaban el WBS vigente más CLAUDE.md. El 03/08/2026 se aprobó D-17, que suspende la regla 8 de CLAUDE.md hasta que 03.01.05 esté hecha o llegue el 01/09/2026, lo que ocurra primero. CRITERIO DE HECHO: aprobación declarada en las decisiones del 01/08 (D-1 a D-16) y la del 03/08 (D-17) en 00-direccion/DECISIONES.md. RESUELTO: lo que el CEO aprobó el 29/07 (WBS v0.7 anterior a CLAUDE.md) se ratifica ahora por D-1 a D-16, que fijan la lista completa de valores, límites y […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
@@ -3855,41 +3385,45 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>01.02.02</t>
+          <t>01.02.03</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Trasplante pieza a pieza desde gb2 (D6=B). Una tarea por pieza, cada una con su criterio de aceptación (ver sección Trasplante). Ninguna entra sin pasar su prueba ejecutada</t>
+          <t>Auditar el catálogo awesome-claude-code y, por ampliación del CEO (01/08), las fuentes oficiales de Anthropic y los mecanismos nativos de Claude Code; proponer máximo 4 piezas concretas para el motor, con motivo y coste de integración. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Crítico + Constructores</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>03.01.01</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecha</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (01/08): Aviso de proceso, dicho sin adornos: la ficha se escribe DESPUÉS del barrido, no antes, incumpliendo la regla 5 de CLAUDE.md. Motivo: el CEO pidió la investigación y la ampliación de alcance en la misma orden, en sesión. Queda anotado en vez de disimulado. Alcance ampliado: además del catálogo, fuentes oficiales de Anthropic (anthropics/, documentación de code.claude.com) y mecanismos nativos ya instalados y sin usar (hooks, reglas con ámbito de ruta, worktrees, subagentes […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>01.02.03</t>
+          <t>01.02.04</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Auditar el catálogo awesome-claude-code y, por ampliación del CEO (01/08), las fuentes oficiales de Anthropic y los mecanismos nativos de Claude Code; proponer máximo 4 piezas concretas para el motor, con motivo y coste de integración. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
+          <t>NUEVA 01/08 (petición del CEO): evaluar si merece la pena añadir servidores MCP al proyecto, con veredicto por servidor y regla de admisión escrita para el futuro. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -3904,121 +3438,117 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>01/08: informe entregado. Lo escribió el ORQUESTADOR en sesión principal, no el investigador, porque la sesión arrancó con la invocación de subagentes restringida; el CEO lo señaló y el reparto se corrigió en la misma tirada. Conclusión del informe: CERO piezas del catálogo, las 4 propuestas son mecanismos nativos (contador mecánico producto/motor, registro de autoría contra la auto-revisión, detección de fallo o rechazo de modelo, ejecución desatendida por cron). Hallazgo con consecuencia para 03.01.03: Claude Code no ofrece ningún tope de gasto que el proyecto pueda elegir; solo /usage (mirar, no bloquear), límites de workspace en la Console con clave de API, y OpenTelemetry. Matización […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>FICHA (01/08): Aviso de proceso, dicho sin adornos: la ficha se escribe DESPUÉS del barrido, no antes, incumpliendo la regla 5 de CLAUDE.md. Motivo: el CEO pidió la investigación y la ampliación de alcance en la misma orden, en sesión. Queda anotado en vez de disimulado. Alcance ampliado: además del catálogo, fuentes oficiales de Anthropic (anthropics/*, documentación de code.claude.com) y mecanismos nativos ya instalados y sin usar (hooks, reglas con ámbito de ruta, worktrees, subagentes […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>01.02.04</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>NUEVA 01/08 (petición del CEO): evaluar si merece la pena añadir servidores MCP al proyecto, con veredicto por servidor y regla de admisión escrita para el futuro. Carril de motor: cuenta contra el 20% y se limita a 1 tirada</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>03.01.02</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
           <t>FICHA (01/08): Motivo de la tarea: el CEO pregunta si los MCP salen a cuenta aquí; no estaba medido en el WBS. Alcance: veredicto uno por uno sobre los servidores de referencia oficiales (filesystem, git, memory, sequential-thinking, fetch, time, everything, y sqlite, que está archivado upstream), sobre github, sobre los de datos de mercado (yfinance, TradingView, QuantConnect, ccxt), sobre los de broker (Kraken, Alpaca, IBKR) y sobre los de navegador (Playwright, Chrome DevTools). Filtros […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="36" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>ELEGIR MERCADO Y TAMAÑO DE VELA (PUERTA G1)</t>
         </is>
       </c>
-      <c r="C13" s="37" t="n"/>
-      <c r="D13" s="37" t="n"/>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="37" t="n"/>
-      <c r="G13" s="37" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="37" t="n"/>
+      <c r="G12" s="37" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>02.01.01</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Confirmar 8 candidatos: EURUSD, GBPUSD, USDJPY, AUDUSD, USDCHF, XAUUSD, BTC, ETH</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>01.01.02</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>03/08 — ratificado por la vía de los hechos: D-19** elige XAUUSD, y elegir un miembro del censo ratifica el censo del que sale. Los 8 se usaron en toda la Fase 02 (ATR, costes, correlaciones, arrastre). No queda ratificación formal pendiente.</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
+          <t>02.01.02</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Costes típicos de operar por mercado (PROVISIONAL hasta 04.01.02)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Investigador</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
           <t>02.01.01</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Confirmar 8 candidatos: EURUSD, GBPUSD, USDJPY, AUDUSD, USDCHF, XAUUSD, BTC, ETH</t>
-        </is>
-      </c>
-      <c r="C14" s="28" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>01.01.02</t>
-        </is>
-      </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecha</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>los 8 candidatos ya se usan de hecho en 02.02.04 (hecha) y en los briefs A y B; falta ratificación formal del CEO en G1</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
+          <t>31/07 — coste_operar.md. Tabla final de coste de entrar y salir, 8 instrumentos, ida y vuelta, con tipo de cuenta declarado (raw/ECN vs spread-only, que no son comparables entre si). CORRECCIONES DE L-002 APLICADAS EN LA TABLA y no en nota al pie: USDJPY 1,16 pips (no 0,90) y USDCHF 0,73 pips (no 0,80). VERIFICADO por el orquestador: aritmetica de las 8 filas recalculada (spread + comision = total, cuadran las 6 con comision); las cifras citadas existen en el origen, localizadas por grep. RECORRIDO: primera entrega DEVUELTA por incumplir la regla 13 de CLAUDE.md (seis citas por numero de linea, que se rompen solas al editar el origen); corregida a referencias por seccion y fila de tabla, […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (31/07): Alcance: tabla FINAL de coste de entrar y salir (spread + comision) para los 8 instrumentos, en la unidad natural de cada uno, ida y vuelta. Base ya existente: la Entrega 1 del Brief A (entrega_brief_A.md), ACEPTADA por el revisor con fuentes primarias (PDF oficiales de Pepperstone e IC Markets). No se rehace la investigacion: se consolida. Correcciones OBLIGATORIAS, aplicadas EN LA TABLA y no en nota al pie (L-002): USDJPY = 1,16 pips (no 0,90) y USDCHF = 0,73 pips (no 0,80); […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>02.01.02</t>
+          <t>02.02.01</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Costes típicos de operar por mercado (PROVISIONAL hasta 04.01.02)</t>
+          <t>CORREGIDA 29/07: descargar precios y CALCULAR el ATR de 15m, 1h y 4h (no buscarlo publicado: no existe). Script atr_local.py</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Constructor de datos</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -4033,24 +3563,24 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>31/07 — coste_operar.md. Tabla final de coste de entrar y salir, 8 instrumentos, ida y vuelta, con tipo de cuenta declarado (raw/ECN vs spread-only, que no son comparables entre si). CORRECCIONES DE L-002 APLICADAS EN LA TABLA y no en nota al pie: USDJPY 1,16 pips (no 0,90) y USDCHF 0,73 pips (no 0,80). VERIFICADO por el orquestador: aritmetica de las 8 filas recalculada (spread + comision = total, cuadran las 6 con comision); las cifras citadas existen en el origen, localizadas por grep. RECORRIDO: primera entrega DEVUELTA por incumplir la regla 13 de CLAUDE.md (seis citas por numero de linea, que se rompen solas al editar el origen); corregida a referencias por seccion y fila de tabla, […] texto completo en 00-direccion/WBS.md</t>
+          <t>31/07 — precios_mercado.py, atr_15m_1h_4h.json, atr_real_15m_1h_4h.md. Tabla de 8 instrumentos x 3 velas, 24/24 celdas calculadas sobre precios descargados, 0 estimadas, 0 duplicados, 0 velas invalidas. Cordura del oro OK: 3.596,64 USD/oz, en miles. RECORRIDO: entregada, RECHAZADA por critico-codigo (bin incompleto contado como completo, en el filtro de ventana y en el primer bin de 4h de los 8 instrumentos), reparada en ronda 1, re-revisada y ACEPTADA. El critico recalculo el ATR desde los datos brutos con su propio codigo y coincide digito a digito con el script (XAUUSD 1h = 14.464676282400184, n=11824); verifico ademas que el descarte de bins de borde NO se come huecos legitimos (801 […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>FICHA (31/07): Alcance: tabla FINAL de coste de entrar y salir (spread + comision) para los 8 instrumentos, en la unidad natural de cada uno, ida y vuelta. Base ya existente: la Entrega 1 del Brief A (entrega_brief_A.md), ACEPTADA por el revisor con fuentes primarias (PDF oficiales de Pepperstone e IC Markets). No se rehace la investigacion: se consolida. Correcciones OBLIGATORIAS, aplicadas EN LA TABLA y no en nota al pie (L-002): USDJPY = 1,16 pips (no 0,90) y USDCHF = 0,73 pips (no 0,80); […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (31/07): Fuente fijada: HistData para EURUSD, GBPUSD, USDJPY, AUDUSD y USDCHF · Dukascopy para XAUUSD al contado (NO el futuro GC=F, ver L-007) · Kraken para BTCUSD y ETHUSD contra dolar real, no contra Tether (L-007). Se jubila Yahoo/yfinance. Alcance: descargar historico suficiente para 2 años completos y calcular ATR(14) en velas de 15m, 1h y 4h para los 8 instrumentos. Corte: 22:00 UTC, unico para todos. Artefacto: un solo script que sirva tambien a 02.02.03 (T2 avisa: en gb2 la […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>02.02.01</t>
+          <t>02.02.02</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CORREGIDA 29/07: descargar precios y CALCULAR el ATR de 15m, 1h y 4h (no buscarlo publicado: no existe). Script atr_local.py</t>
+          <t>Coste relativo: coste ÷ movimiento medio, en % (el número clave). Coste de USDJPY corregido a 1,16 pips</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4060,7 +3590,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>02.01.01</t>
+          <t>02.01.02, 02.02.01</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -4070,24 +3600,24 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>31/07 — precios_mercado.py, atr_15m_1h_4h.json, atr_real_15m_1h_4h.md. Tabla de 8 instrumentos x 3 velas, 24/24 celdas calculadas sobre precios descargados, 0 estimadas, 0 duplicados, 0 velas invalidas. Cordura del oro OK: 3.596,64 USD/oz, en miles. RECORRIDO: entregada, RECHAZADA por critico-codigo (bin incompleto contado como completo, en el filtro de ventana y en el primer bin de 4h de los 8 instrumentos), reparada en ronda 1, re-revisada y ACEPTADA. El critico recalculo el ATR desde los datos brutos con su propio codigo y coincide digito a digito con el script (XAUUSD 1h = 14.464676282400184, n=11824); verifico ademas que el descarte de bins de borde NO se come huecos legitimos (801 […] texto completo en 00-direccion/WBS.md</t>
+          <t>31/07 — coste_relativo.py, coste_relativo_15m_1h_4h.json, coste_relativo.md. ES EL CRITERIO 1 DE G1. Coste de ida y vuelta ÷ ATR x 100, 8 instrumentos x 3 velas, en CUATRO escenarios: vela media, mediana, tranquila (p10) y agitada (p90). RECORRIDO: entregada, RECHAZADA por critico-codigo (no por error de calculo —reejecuto el script y salio bit-identico— sino por un sesgo de metodo sin declarar), corregida y ACEPTADA. EL SESGO, hallado por el revisor y reproducido por el orquestador: el ATR medio de XAUUSD esta inflado respecto a su mediana (1,28-1,30) mas que el de ningun otro instrumento (0,985-1,144), porque su pausa diaria de 21:00-22:00 UTC genera un salto de rango UNA VEZ AL DIA […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>FICHA (31/07): Fuente fijada: HistData para EURUSD, GBPUSD, USDJPY, AUDUSD y USDCHF · Dukascopy para XAUUSD al contado (NO el futuro GC=F, ver L-007) · Kraken para BTCUSD y ETHUSD contra dolar real, no contra Tether (L-007). Se jubila Yahoo/yfinance. Alcance: descargar historico suficiente para 2 años completos y calcular ATR(14) en velas de 15m, 1h y 4h para los 8 instrumentos. Corte: 22:00 UTC, unico para todos. Artefacto: un solo script que sirva tambien a 02.02.03 (T2 avisa: en gb2 la […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (31/07): Alcance: coste relativo = coste de ida y vuelta ÷ ATR medio de la vela x 100, para los 8 instrumentos x 3 velas (15m, 1h, 4h). Es el criterio 1 de la puerta G1: se exige ≤10-15%. Insumos, ambos ya cerrados y verificados: costes de coste_operar.md (02.01.02) y ATR de 04-resultados/atr_15m_1h_4h.json (02.02.01). No se recalcula ninguno de los dos. TRAMPA PRINCIPAL, declarada de antemano (L-002 y L-004): el JSON guarda el ATR en unidad CRUDA de precio, no en pips. El divisor de pip […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>02.02.02</t>
+          <t>02.02.03</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Coste relativo: coste ÷ movimiento medio, en % (el número clave). Coste de USDJPY corregido a 1,16 pips</t>
+          <t>CORREGIDA 30/07: CALCULAR la matriz de correlaciones en 3 ventanas (3 meses, 1 año, 2 años) con hora de corte única (22:00 UTC) y en la vela elegida, no solo diaria. No existe publicada de forma homogénea</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -4097,7 +3627,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>02.01.02, 02.02.01</t>
+          <t>02.01.01</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -4107,29 +3637,29 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>31/07 — coste_relativo.py, coste_relativo_15m_1h_4h.json, coste_relativo.md. ES EL CRITERIO 1 DE G1. Coste de ida y vuelta ÷ ATR x 100, 8 instrumentos x 3 velas, en CUATRO escenarios: vela media, mediana, tranquila (p10) y agitada (p90). RECORRIDO: entregada, RECHAZADA por critico-codigo (no por error de calculo —reejecuto el script y salio bit-identico— sino por un sesgo de metodo sin declarar), corregida y ACEPTADA. EL SESGO, hallado por el revisor y reproducido por el orquestador: el ATR medio de XAUUSD esta inflado respecto a su mediana (1,28-1,30) mas que el de ningun otro instrumento (0,985-1,144), porque su pausa diaria de 21:00-22:00 UTC genera un salto de rango UNA VEZ AL DIA […] texto completo en 00-direccion/WBS.md</t>
+          <t>31/07 — correlaciones_mercado.py, correlaciones_8x8.json, correlaciones_8x8.md. 12 matrices 8x8 (3 ventanas x 4 velas, incluida la diaria) sobre RENDIMIENTOS logaritmicos, corte unico 22:00 UTC. ACEPTADA por critico-codigo sin ronda de reparacion. VERIFICADO POR EJECUCION por el revisor: recalculo 4 celdas con codigo propio y coinciden a 15 decimales; confirmo que correlaciona rendimientos y no precios (XAUUSD/USDJPY da +0,586 en precios frente a -0,060 en rendimientos); demostro que pandas ignora el offset con "1D" y que el codigo usa "24h", con el 100% de las velas diarias ancladas a las 22:00; y SIN REGRESION en precios_mercado.py, cuyo ATR regenerado sale identico digito a digito al […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>FICHA (31/07): Alcance: coste relativo = coste de ida y vuelta ÷ ATR medio de la vela x 100, para los 8 instrumentos x 3 velas (15m, 1h, 4h). Es el criterio 1 de la puerta G1: se exige ≤10-15%. Insumos, ambos ya cerrados y verificados: costes de coste_operar.md (02.01.02) y ATR de 04-resultados/atr_15m_1h_4h.json (02.02.01). No se recalcula ninguno de los dos. TRAMPA PRINCIPAL, declarada de antemano (L-002 y L-004): el JSON guarda el ATR en unidad CRUDA de precio, no en pips. El divisor de pip […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (31/07): Alcance: matriz de correlaciones 8x8 sobre RENDIMIENTOS logaritmicos (nunca sobre precios), en 3 ventanas (3 meses, 1 año, 2 años) y en LAS TRES VELAS (15m, 1h, 4h), mas la diaria como comprobacion. Por que las tres velas: la ficha original decia "en la vela elegida", pero la vela se elige en G1, que es despues; calcular las tres evita adivinar (regla 6 de CLAUDE.md) y deja a la puerta el dato elija la que elija. Corte: 22:00 UTC unico, imprescindible o los rendimientos no […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>02.02.03</t>
+          <t>02.02.04</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CORREGIDA 30/07: CALCULAR la matriz de correlaciones en 3 ventanas (3 meses, 1 año, 2 años) con hora de corte única (22:00 UTC) y en la vela elegida, no solo diaria. No existe publicada de forma homogénea</t>
+          <t>Historial disponible: años, fuente, coste</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Constructor de datos</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -4144,24 +3674,20 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>31/07 — correlaciones_mercado.py, correlaciones_8x8.json, correlaciones_8x8.md. 12 matrices 8x8 (3 ventanas x 4 velas, incluida la diaria) sobre RENDIMIENTOS logaritmicos, corte unico 22:00 UTC. ACEPTADA por critico-codigo sin ronda de reparacion. VERIFICADO POR EJECUCION por el revisor: recalculo 4 celdas con codigo propio y coinciden a 15 decimales; confirmo que correlaciona rendimientos y no precios (XAUUSD/USDJPY da +0,586 en precios frente a -0,060 en rendimientos); demostro que pandas ignora el offset con "1D" y que el codigo usa "24h", con el 100% de las velas diarias ancladas a las 22:00; y SIN REGRESION en precios_mercado.py, cuyo ATR regenerado sale identico digito a digito al […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (31/07): Alcance: matriz de correlaciones 8x8 sobre RENDIMIENTOS logaritmicos (nunca sobre precios), en 3 ventanas (3 meses, 1 año, 2 años) y en LAS TRES VELAS (15m, 1h, 4h), mas la diaria como comprobacion. Por que las tres velas: la ficha original decia "en la vela elegida", pero la vela se elige en G1, que es despues; calcular las tres evita adivinar (regla 6 de CLAUDE.md) y deja a la puerta el dato elija la que elija. Corte: 22:00 UTC unico, imprescindible o los rendimientos no […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
+          <t>** — Dukascopy (tick desde 2003, forex y oro al contado), HistData, TrueFX, Binance, Kraken. Todo gratis, muy por encima de los 5 años exigidos</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>02.02.04</t>
+          <t>02.02.05</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Historial disponible: años, fuente, coste</t>
+          <t>NUEVA: coste de mantener posición de un día para otro (swap/financiación) en los 8 instrumentos, 2-3 brokers. En cripto CFD puede superar varias veces al spread</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -4181,7 +3707,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>** — Dukascopy (tick desde 2003, forex y oro al contado), HistData, TrueFX, Binance, Kraken. Todo gratis, muy por encima de los 5 años exigidos</t>
+          <t>** 31/07 — coste_swap.md. Coste de mantener posicion en 8 instrumentos x 3 brokers (OANDA, XTB, Pepperstone), largo y corto por separado, en % anual y $/dia sobre 100.000 USD. VERIFICADO por recalculo independiente: las 30 celdas con % y $/dia cuadran; signos de USDJPY y USDCHF coherentes entre brokers (L-006 comprobada, sin inversion de convencion). HALLAZGO PARA G1: mantener cripto cuesta -33,6% anual (OANDA) y -22,5% (Pepperstone), entre 20 y 30 veces mas que entrar y salir; el oro -6,6%/-8,2%; y USDCHF y USDJPY en largo PAGAN (+2,6% y +1,6%). Implicacion: si entra cripto en el portafolio, la estrategia no puede aguantar posiciones de un dia para otro. HUECO DECLARADO: ETHUSD queda con […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
@@ -4189,22 +3715,22 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>02.02.05</t>
+          <t>02.03.01</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>NUEVA: coste de mantener posición de un día para otro (swap/financiación) en los 8 instrumentos, 2-3 brokers. En cripto CFD puede superar varias veces al spread</t>
+          <t>Revisión independiente de método, fuentes y números</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>02.01.01</t>
+          <t>02.02.*</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -4214,7 +3740,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>** 31/07 — coste_swap.md. Coste de mantener posicion en 8 instrumentos x 3 brokers (OANDA, XTB, Pepperstone), largo y corto por separado, en % anual y $/dia sobre 100.000 USD. VERIFICADO por recalculo independiente: las 30 celdas con % y $/dia cuadran; signos de USDJPY y USDCHF coherentes entre brokers (L-006 comprobada, sin inversion de convencion). HALLAZGO PARA G1: mantener cripto cuesta -33,6% anual (OANDA) y -22,5% (Pepperstone), entre 20 y 30 veces mas que entrar y salir; el oro -6,6%/-8,2%; y USDCHF y USDJPY en largo PAGAN (+2,6% y +1,6%). Implicacion: si entra cripto en el portafolio, la estrategia no puede aguantar posiciones de un dia para otro. HUECO DECLARADO: ETHUSD queda con […] texto completo en 00-direccion/WBS.md</t>
+          <t>02/08 — 04-resultados/veredictos/veredicto_fase_02.md y 03-motor/scripts/deriva_oro.py. Segunda pasada del RECHAZA del 31/07. ACEPTA CON HUECOS DECLARADOS, válido SOLO si el defecto del motivo 5 llega declarado al CEO en la ficha de G1; si se omite, decae y rige el RECHAZA. Balance: 4 cerrados (1, 3, 6, 7), 3 abiertos (2, 4, 5), el 5 escalado. Motivo 3 zanjado por ejecución: XAUUSD a 4h pasa de 2,32% a 4,22% y 5,43%, bajo el umbral del 10%, así que la deriva del coste del oro NO cambia el veredicto a 4h; sí lo rompe a 1h (11,01%) y a 15m (19,80-25,46%). Motivo 5 confirmado uno a uno: 7 de 8 instrumentos** mezclan broker o tipo de cuenta; solo BTCUSD comparte fuente. RECORRIDO: validador […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
@@ -4222,24 +3748,24 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
+          <t>02.03.02</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Informe de decisión: mercado y vela. El alcance original decía 3-5 mercados poco correlacionados y 1-2 velas, alcance que D-19 sustituye por un solo mercado</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
           <t>02.03.01</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Revisión independiente de método, fuentes y números</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Orquestador</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>02.02.*</t>
-        </is>
-      </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Hecha</t>
@@ -4247,7 +3773,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>02/08 — 04-resultados/veredictos/veredicto_fase_02.md y 03-motor/scripts/deriva_oro.py. Segunda pasada del RECHAZA del 31/07. ACEPTA CON HUECOS DECLARADOS, válido SOLO si el defecto del motivo 5 llega declarado al CEO en la ficha de G1; si se omite, decae y rige el RECHAZA. Balance: 4 cerrados (1, 3, 6, 7), 3 abiertos (2, 4, 5), el 5 escalado. Motivo 3 zanjado por ejecución: XAUUSD a 4h pasa de 2,32% a 4,22% y 5,43%, bajo el umbral del 10%, así que la deriva del coste del oro NO cambia el veredicto a 4h; sí lo rompe a 1h (11,01%) y a 15m (19,80-25,46%). Motivo 5 confirmado uno a uno: 7 de 8 instrumentos** mezclan broker o tipo de cuenta; solo BTCUSD comparte fuente. RECORRIDO: validador […] texto completo en 00-direccion/WBS.md</t>
+          <t>03/08 — 01-investigacion/mercados/INFORME_DECISION_G1.md y 03-motor/scripts/cestas_g1.py. Escrito por el validador, RECHAZADO por critico-codigo en ronda 1 por tres motivos (la ficha colisionaba con D-18, ya firmada ese día; el máximo medido de 5,05x quedaba fuera de la ficha que lee el CEO, que decía 4,5x; ficha de 1.566 caracteres) y ACEPTADO en ronda 2 tras reparación del propio validador. Medido por ejecución y reproducido después por Claude Code: a 4h no existe ninguna cesta admisible de 4 ni de 5 instrumentos, existen exactamente 4 de 3**, y XAUUSD está en las cuatro. La condición del ACEPTA de 02.03.01 queda cumplida: el defecto del motivo 5 llegó declarado al CEO como AVISO 1.</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
@@ -4255,87 +3781,95 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
+          <t>02.03.03</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>PUERTA G1: el CEO elige</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
           <t>02.03.02</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Informe de decisión: 3-5 mercados poco correlacionados + 1-2 velas</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Orquestador</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>02.03.01</t>
-        </is>
-      </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>03/08 — D-19: XAUUSD (oro al contado), vela de 4h, UN SOLO MERCADO. Opción propia del CEO, fuera de las cuatro presentadas. Deroga D-2** (portafolio de 3-5 mercados). La ampliación a un segundo mercado queda condicionada a que una hipótesis demuestre ganar dinero de verdad. Consecuencias registradas en D-19: G1-C5 queda sin objeto mientras haya un solo mercado, y los cinco huecos declarados del oro pasan a ser el riesgo entero del proyecto.</t>
+        </is>
+      </c>
       <c r="G22" s="4" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>02.03.03</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>PUERTA G1: el CEO elige</t>
-        </is>
-      </c>
-      <c r="C23" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>02.03.02</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="36" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="B24" s="37" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>MONTAR LA CASA (CLAUDE CODE) — EN PARALELO CON LA FASE 02</t>
         </is>
       </c>
-      <c r="C24" s="37" t="n"/>
-      <c r="D24" s="37" t="n"/>
-      <c r="E24" s="37" t="n"/>
-      <c r="F24" s="37" t="n"/>
-      <c r="G24" s="37" t="n"/>
+      <c r="C23" s="37" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="37" t="n"/>
+      <c r="F23" s="37" t="n"/>
+      <c r="G23" s="37" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>03.01.01</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Repositorio: carpetas, WBS texto, CLAUDE.md, DECISIONES.md, LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>01.01.01</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>30/07 — repo completo: carpetas, WBS, CLAUDE.md, DECISIONES.md, LECCIONES.md, plantillas y .gitignore (42 ficheros en git). AVISO regla 27 de CLAUDE.md NO VERIFICADA**: la prueba de inyección de datos no se ha ejecutado; 02-datos/ está vacío. Se ejecuta al bajar los primeros precios en 02.02.01</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>03.01.01</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Repositorio: carpetas, WBS texto, CLAUDE.md, DECISIONES.md, LECCIONES.md</t>
+          <t>Crear TODOS los agentes del Equipo, cada uno con su modelo y descripción sin ambigüedad; prueba de activación de todos (ningún agente fantasma)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -4345,7 +3879,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>01.01.01</t>
+          <t>03.01.01, 01.02.01</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -4355,7 +3889,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>30/07 — repo completo: carpetas, WBS, CLAUDE.md, DECISIONES.md, LECCIONES.md, plantillas y .gitignore (42 ficheros en git). AVISO regla 27 de CLAUDE.md NO VERIFICADA**: la prueba de inyección de datos no se ha ejecutado; 02-datos/ está vacío. Se ejecuta al bajar los primeros precios en 02.02.01</t>
+          <t>** 30/07 — 8 agentes en .claude/agents/, cada uno con identificador exacto de modelo y respaldo. Prueba de activación ejecutada 30/07: los 8 respondieron y leyeron un fichero real, ningún fantasma. LÍMITE: la prueba no demuestra que el modelo enrutado sea el de la ficha; se verifica en 03.01.04, con atención a claude-fable-5 (validador y arquitecto)</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
@@ -4363,45 +3897,45 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
+          <t>03.01.03</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Ejecución desatendida: arranques programados, permisos AMPLIOS por defecto (git como red de seguridad) y topes de gasto</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
           <t>03.01.02</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Crear TODOS los agentes del Equipo, cada uno con su modelo y descripción sin ambigüedad; prueba de activación de todos (ningún agente fantasma)</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>03.01.01, 01.02.01</t>
-        </is>
-      </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Hecha</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>** 30/07 — 8 agentes en .claude/agents/, cada uno con identificador exacto de modelo y respaldo. Prueba de activación ejecutada 30/07: los 8 respondieron y leyeron un fichero real, ningún fantasma. LÍMITE: la prueba no demuestra que el modelo enrutado sea el de la ficha; se verifica en 03.01.04, con atención a claude-fable-5 (validador y arquitecto)</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (03/08, D-20): Cómo se arranca: claude -p en modo no interactivo lanzado desde el cron del sistema. Los arranques programados son dos líneas de crontab y no requieren ninguna pieza externa. Cómo se avisa al humano sin instalar nada, idea 5 de las auditorías: hook nativo de tipo http, que hace el POST él mismo sin script intermedio, con los eventos StopFailure (admite matcher por tipo de error), Notification con matchers idle_prompt y permission_prompt —que detectan la tirada parada […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>03.01.03</t>
+          <t>03.01.04</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Ejecución desatendida: arranques programados, permisos AMPLIOS por defecto (git como red de seguridad) y topes de gasto</t>
+          <t>Plan de respaldo de modelos: si un modelo no está disponible o rechaza, el agente sigue con su respaldo y lo anota</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -4420,27 +3954,31 @@
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (03/08, D-20) — CORRECCIÓN DE ALCANCE, dicha sin adornos: esta tarea prometía que el agente «sigue con su respaldo», y eso no se puede automatizar entero: un hook no puede cambiar el modelo. Lo que sí se puede: el evento StopFailure admite matcher por tipo de error (rate_limit, overloaded, authentication_failed, server_error, entre otros) y SubagentStop avisa del fin de un subagente. Con ellos, un fallo silencioso pasa a ser un fallo registrado. Esta tarea entrega esa mitad mecánica. El […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>03.01.04</t>
+          <t>03.01.05</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Plan de respaldo de modelos: si un modelo no está disponible o rechaza, el agente sigue con su respaldo y lo anota</t>
+          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>03.01.02</t>
+          <t>03.01.03, 03.01.04</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -4454,22 +3992,22 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>03.01.05</t>
+          <t>03.01.06</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
+          <t>Plantilla y automatismo de fichas de decisión: el secretario prepara cada decisión del CEO en el formato obligatorio y la adjunta al informe semanal</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>03.01.03, 03.01.04</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -4483,22 +4021,22 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
+          <t>03.01.07</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Secretario</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
           <t>03.01.06</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Plantilla y automatismo de fichas de decisión: el secretario prepara cada decisión del CEO en el formato obligatorio y la adjunta al informe semanal</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Secretario</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>03.01.02</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -4512,74 +4050,74 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>03.01.07</t>
+          <t>03.01.08</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
+          <t>Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Crítico</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>03.01.06</t>
+          <t>03.01.01, 03.01.02</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr"/>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>ejecutada la primera pasada 31/07 con verificar_barreras.py: 4 barreras de 5 VERIFICADAS por ejecucion (hooks instalados, datos rechazados en commit, .gitignore ignora 02-datos, mensaje exige codigo WBS). 1 NO VERIFICADA: el cajon reservado era un filtro de texto sobre el comando. CORRECCIÓN DE DEPENDENCIA (03/08/2026): la dependencia de 03.01.03 fue falsa desde el inicio — verificar_barreras.py ejecutada el 31/07 sin que 03.01.03 existiera ya. Las barreras probadas (hooks, .gitignore, commit-msg, cifrado) dependen de 03.01.01 (repo con WBS y reglas) y 03.01.02 (ocho agentes creados). Se remedia en 03.01.11 (D-10). No se cierra hasta repetir la pasada con 03.01.11 terminada</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>03.01.08</t>
+          <t>03.01.09</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
+          <t>Enrutado por tipo de tarea y comprobación de que el WBS genera tareas de cada tipo de agente (ver L-010 de LECCIONES.md; sin número propio en CLAUDE.md)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Crítico</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>03.01.03</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>ejecutada la primera pasada 31/07 con verificar_barreras.py: 4 barreras de 5 VERIFICADAS por ejecucion (hooks instalados, datos rechazados en commit, .gitignore ignora 02-datos, mensaje exige codigo WBS). 1 NO VERIFICADA: el cajon reservado era un filtro de texto sobre el comando. Se remedia en 03.01.11 (D-10). No se cierra hasta repetir la pasada con 03.01.11 terminada</t>
-        </is>
-      </c>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>03.01.09</t>
+          <t>03.01.10</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Enrutado por tipo de tarea y comprobación de que el WBS genera tareas de cada tipo de agente (ver L-010 de LECCIONES.md; sin número propio en CLAUDE.md)</t>
+          <t>Testbed sintético de invarianza: resultado de referencia fijo que debe reproducirse tras cualquier cambio del motor</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -4589,7 +4127,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>03.01.02</t>
+          <t>03.01.01</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -4603,74 +4141,78 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>03.01.10</t>
+          <t>03.01.13</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Testbed sintético de invarianza: resultado de referencia fijo que debe reproducirse tras cualquier cambio del motor</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
+          <t>NUEVA 01/08 (L-015): una sola lista de reglas. Hoy CLAUDE.md y este WBS llevan cada uno una lista de «29 reglas» con contenido distinto bajo el mismo número, así que toda cita regla N del proyecto es ambigua</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="inlineStr">
+        <is>
+          <t>Constructores + CEO</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>03.01.01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecha</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (01/08): Hallazgo, comprobado por grep sobre los dos ficheros el 01/08: regla 16 = «nadie valida su propio trabajo» (CLAUDE.md) frente a «test de compuerta» (WBS) · regla 23 = «dos niveles de barrera» frente a «un fallo reportado no es un fallo verificado» · regla 25 = «toda barrera se verifica por ejecución» frente a «cada agente lleva el identificador exacto de su modelo». Por qué importa: la regla 12 de CLAUDE.md exige que toda cita se localice con grep antes de entrar en un informe; […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>03.01.13</t>
+          <t>03.01.12</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 01/08 (L-015): una sola lista de reglas. Hoy CLAUDE.md y este WBS llevan cada uno una lista de «29 reglas» con contenido distinto bajo el mismo número, así que toda cita regla N del proyecto es ambigua</t>
-        </is>
-      </c>
-      <c r="C35" s="28" t="inlineStr">
-        <is>
-          <t>Constructores + CEO</t>
+          <t>NUEVA 01/08 (petición del CEO): fijar la estrategia de ramas de git. Criterio del CEO, literal: que dé agilidad, no complejidad</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>03.01.01</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>FICHA (01/08): Hallazgo, comprobado por grep sobre los dos ficheros el 01/08: regla 16 = «nadie valida su propio trabajo» (CLAUDE.md) frente a «test de compuerta» (WBS) · regla 23 = «dos niveles de barrera» frente a «un fallo reportado no es un fallo verificado» · regla 25 = «toda barrera se verifica por ejecución» frente a «cada agente lleva el identificador exacto de su modelo». Por qué importa: la regla 12 de CLAUDE.md exige que toda cita se localice con grep antes de entrar en un informe; […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (01/08): Estado de partida, comprobado por ejecución el 01/08: git branch -a → una sola rama, main · git remote -v → vacío, no hay remoto · 16 commits · un solo humano. Alcance: decidir y dejar escrito (a) cuándo se trabaja en main y cuándo no, (b) si se usan worktrees y para qué, (c) qué NO se hace. Lo que ya se sabe y no hay que volver a investigar: Claude Code 2.1.220 trae worktrees nativos (claude --worktree &lt;nombre&gt;, y isolation: worktree en la ficha de un subagente) · los worktrees […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>03.01.12</t>
+          <t>03.01.11</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 01/08 (petición del CEO): fijar la estrategia de ramas de git. Criterio del CEO, literal: que dé agilidad, no complejidad</t>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -4680,30 +4222,30 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>03.01.01</t>
+          <t>03.01.08</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (01/08): Estado de partida, comprobado por ejecución el 01/08: git branch -a → una sola rama, main · git remote -v → vacío, no hay remoto · 16 commits · un solo humano. Alcance: decidir y dejar escrito (a) cuándo se trabaja en main y cuándo no, (b) si se usan worktrees y para qué, (c) qué NO se hace. Lo que ya se sabe y no hay que volver a investigar: Claude Code 2.1.220 trae worktrees nativos (claude --worktree &lt;nombre&gt;, y isolation: worktree en la ficha de un subagente) · los worktrees […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>script escrito y probado por ejecucion 31/07: 6 de 6 casos prohibidos bloqueados (contraseña por tuberia, abrir sin declarar variante, lectura a pelo del fichero cifrado, contraseña incorrecta, y ninguna orden de terminal vuelca datos en claro). VERIFICADO POR EJECUCION (03/08/2026): 04-resultados/registro-cajon.md registra una entrada SELLAR del 31/07 a las 18:31:29 UTC con resultado sellado. La funcion sellar() en cajon_reservado.py aborta con mensaje «El cajon ya esta sellado» si se intenta llamar una segunda vez. El CEO confirmo el 03/08/2026 que la contraseña la tecleo en una terminal real del sistema (nunca mediante el prefijo de ejecucion rapida de la sesion de Claude Code), porque […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>03.01.11</t>
+          <t>03.01.14</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
+          <t>NUEVA 01/08 (deuda detectada al cerrar 03.01.13): la hoja REGLAS del Excel del CEO la construye 05-vista-ceo/generar_excel.py leyendo las líneas numeradas de la sección de reglas del WBS, que tras D-16 ya no existen: la hoja saldría vacía bajo el título «LAS 29 REGLAS», y verificar_excel.py no comprueba esa hoja, así que sus 8 pruebas pasarían igual (L-016). Hay que leer las reglas de CLAUDE.md y añadir una prueba que falle si la hoja sale vacía. Deuda de motor: no se ejecuta sin permiso del CEO.</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -4713,17 +4255,17 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>03.01.08</t>
+          <t>03.01.13</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>script escrito y probado por ejecucion 31/07: 6 de 6 casos prohibidos bloqueados (contraseña por tuberia, abrir sin declarar variante, lectura a pelo del fichero cifrado, contraseña incorrecta, y ninguna orden de terminal vuelca datos en claro). FALTA: que el CEO ejecute sellar en una terminal real para fijar la contraseña. ARTEFACTO (localizado en 07.01.01(c), 02/08): 04-resultados/registro-cajon.md, escrito por 03-motor/scripts/cajon_reservado.py y citado en D-10; ya tiene una entrada SELLAR del 31/07.</t>
+          <t>**</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
@@ -4731,12 +4273,12 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>03.01.14</t>
+          <t>03.01.15</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 01/08 (deuda detectada al cerrar 03.01.13): la hoja REGLAS del Excel del CEO la construye 05-vista-ceo/generar_excel.py leyendo las líneas numeradas de la sección de reglas del WBS, que tras D-16 ya no existen: la hoja saldría vacía bajo el título «LAS 29 REGLAS», y verificar_excel.py no comprueba esa hoja, así que sus 8 pruebas pasarían igual (L-016). Hay que leer las reglas de CLAUDE.md y añadir una prueba que falle si la hoja sale vacía. Deuda de motor: no se ejecuta sin permiso del CEO.</t>
+          <t>Herramientas del secretario: puede escribir los registros que solo admiten añadir pero no puede verificarlos</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -4746,7 +4288,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>03.01.13</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -4754,22 +4296,22 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 02/08 (tres incidentes reales el 02/08): secretario mantiene los tres registros que solo admiten añadir y todas las fichas del CEO, y no tiene Bash: no puede comprobar por ejecución ninguna de las reglas que gobiernan su trabajo. El 02/08 falló tres veces por lo mismo — no pudo verificar el pegado en tabla, ni el append-only, ni el ancho de su ficha — y las tres las descubrió otro agente, que es la regla 15 de CLAUDE.md rota por diseño, no por descuido. Decidir entre dos salidas, y NO se […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>03.01.15</t>
+          <t>03.01.16</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Herramientas del secretario: puede escribir los registros que solo admiten añadir pero no puede verificarlos</t>
+          <t>Las hojas del Excel se construyen de sus fuentes primarias, no de copias</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -4779,7 +4321,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>03.01.02</t>
+          <t>03.01.13, 03.01.14</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -4790,167 +4332,191 @@
       <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 02/08 (tres incidentes reales el 02/08): secretario mantiene los tres registros que solo admiten añadir y todas las fichas del CEO, y no tiene Bash: no puede comprobar por ejecución ninguna de las reglas que gobiernan su trabajo. El 02/08 falló tres veces por lo mismo — no pudo verificar el pegado en tabla, ni el append-only, ni el ancho de su ficha — y las tres las descubrió otro agente, que es la regla 15 de CLAUDE.md rota por diseño, no por descuido. Decidir entre dos salidas, y NO se […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="36" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="B40" s="37" t="inlineStr">
-        <is>
-          <t>HIPÓTESIS Y VALIDACIÓN (PUERTA G2)</t>
-        </is>
-      </c>
-      <c r="C40" s="37" t="n"/>
-      <c r="D40" s="37" t="n"/>
-      <c r="E40" s="37" t="n"/>
-      <c r="F40" s="37" t="n"/>
-      <c r="G40" s="37" t="n"/>
+          <t>FICHA (03/08): Problema verificado hoy: 05-vista-ceo/generar_excel.py construye las hojas REGLAS, LECCIONES y DECISIONES, pero lo hace leyendo tablas espejo en el WBS, no de las fuentes primarias. Consecuencia: (1) hoja REGLAS sale vacía tras D-16 (las reglas ya no están numeradas en el WBS); (2) hoja LECCIONES muestra 18 cuando 00-direccion/LECCIONES.md tiene 23 (L-016); (3) hoja DECISIONES muestra 0 cuando 00-direccion/DECISIONES.md tiene 16 — el CEO no ve ninguna de sus propias decisiones […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>03.01.17</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Reparar la prueba 7 de verificar_excel.py (entregables de las tareas hechas)</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Constructor de motor</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>03.01.13</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (03/08): Problema reproducido hoy: la prueba 7 localiza entregables citados en las celdas de tarea, pero corta cada celda por el primer hecha y solo examina lo que va después. En 03.01.13 ese marcador es el último carácter de la celda, así que examina cero ficheros y no caza que esa tarea, marcada hecha, cita 00-direccion/PENDIENTE-03.01.13-lista-de-reglas.md, que no existe en disco ni ha existido nunca en git. Dos defectos más: busca por nombre de fichero en CUALQUIER parte del […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="38" t="inlineStr">
-        <is>
-          <t>04.01</t>
-        </is>
-      </c>
-      <c r="B41" s="39" t="inlineStr">
-        <is>
-          <t>Broker y cajones de datos</t>
-        </is>
-      </c>
-      <c r="C41" s="39" t="n"/>
-      <c r="D41" s="39" t="n"/>
-      <c r="E41" s="39" t="n"/>
-      <c r="F41" s="39" t="n"/>
-      <c r="G41" s="39" t="n"/>
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>03.01.18</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 03/08 (D-20, idea 1 de las auditorías): contador mecánico del reparto producto/motor, inyectado en el contexto al arrancar cada tirada</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>03.01.01</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (03/08): Problema, medido y no supuesto: el techo del 20% de motor de la regla 8 de CLAUDE.md es prosa y nadie lo mide. La primera vez que se midió, el 01/08, el reparto real era 7 de 16 commits, 43,8%, más del doble del techo, y el proyecto llevaba desde el arranque sin saberlo. Qué se construye: un hook SessionStart que calcula el reparto desde git log y lo inyecta en el contexto con hookSpecificOutput.additionalContext, de forma que cada tirada empiece con el número delante en vez de […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
+          <t>03.01.19</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 03/08 (D-20, idea 2 de las auditorías): registro mecánico de autoría, para que «nadie valida su propio trabajo» deje de ser solo prosa</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>03.01.02</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (03/08): Problema: la regla 16 de CLAUDE.md y C2 no tienen muro. Hoy dependen de que el orquestador reparta bien y de que nadie se equivoque; no hay forma de comprobar a posteriori quién escribió qué. Nivel 1, que es lo que ESTA tarea entrega: un hook PostToolUse con matcher de escritura anota en 04-resultados/autoria.jsonl qué fichero se tocó y qué tipo de agente lo tocó. El campo del tipo de agente viaja en la entrada JSON de todo hook que corre dentro de un subagente. Con eso la regla […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="36" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B43" s="37" t="inlineStr">
+        <is>
+          <t>HIPÓTESIS Y VALIDACIÓN (PUERTA G2)</t>
+        </is>
+      </c>
+      <c r="C43" s="37" t="n"/>
+      <c r="D43" s="37" t="n"/>
+      <c r="E43" s="37" t="n"/>
+      <c r="F43" s="37" t="n"/>
+      <c r="G43" s="37" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t>04.01</t>
+        </is>
+      </c>
+      <c r="B44" s="39" t="inlineStr">
+        <is>
+          <t>Broker y cajones de datos</t>
+        </is>
+      </c>
+      <c r="C44" s="39" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="39" t="n"/>
+      <c r="F44" s="39" t="n"/>
+      <c r="G44" s="39" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
           <t>04.01.01</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
         </is>
       </c>
-      <c r="C42" s="28" t="inlineStr">
+      <c r="C45" s="28" t="inlineStr">
         <is>
           <t>CEO + Orquestador</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>02.03.03</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>04.01.02</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Constructor datos</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>04.01.01</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>04.01.03</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Constructor datos</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>04.01.01</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="4" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="38" t="inlineStr">
-        <is>
-          <t>04.02</t>
-        </is>
-      </c>
-      <c r="B45" s="39" t="inlineStr">
-        <is>
-          <t>Investigación de hipótesis</t>
-        </is>
-      </c>
-      <c r="C45" s="39" t="n"/>
-      <c r="D45" s="39" t="n"/>
-      <c r="E45" s="39" t="n"/>
-      <c r="F45" s="39" t="n"/>
-      <c r="G45" s="39" t="n"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>04.02.01</t>
+          <t>04.01.02</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
+          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>03.01.02</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -4964,22 +4530,22 @@
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>04.01.03</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
+          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>04.02.01</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4991,53 +4557,41 @@
       <c r="G47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>04.02.03</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Validador</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>04.02.02</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="4" t="inlineStr"/>
+      <c r="A48" s="38" t="inlineStr">
+        <is>
+          <t>04.02</t>
+        </is>
+      </c>
+      <c r="B48" s="39" t="inlineStr">
+        <is>
+          <t>Investigación de hipótesis</t>
+        </is>
+      </c>
+      <c r="C48" s="39" t="n"/>
+      <c r="D48" s="39" t="n"/>
+      <c r="E48" s="39" t="n"/>
+      <c r="F48" s="39" t="n"/>
+      <c r="G48" s="39" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>04.02.04</t>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
+          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -5049,41 +4603,53 @@
       <c r="G49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="38" t="inlineStr">
-        <is>
-          <t>04.03</t>
-        </is>
-      </c>
-      <c r="B50" s="39" t="inlineStr">
-        <is>
-          <t>Laboratorio de pruebas (por hipótesis y variante)</t>
-        </is>
-      </c>
-      <c r="C50" s="39" t="n"/>
-      <c r="D50" s="39" t="n"/>
-      <c r="E50" s="39" t="n"/>
-      <c r="F50" s="39" t="n"/>
-      <c r="G50" s="39" t="n"/>
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>04.02.02</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Investigador</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>04.02.01</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Backtest con costes reales sobre el cajón de construir</t>
+          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>04.01.03, 04.02.04</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -5097,22 +4663,22 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.02.04</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
+          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -5124,53 +4690,41 @@
       <c r="G52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="inlineStr">
-        <is>
-          <t>04.03.03</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Validador</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>04.03.02</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="4" t="inlineStr"/>
+      <c r="A53" s="38" t="inlineStr">
+        <is>
+          <t>04.03</t>
+        </is>
+      </c>
+      <c r="B53" s="39" t="inlineStr">
+        <is>
+          <t>Laboratorio de pruebas (por hipótesis y variante)</t>
+        </is>
+      </c>
+      <c r="C53" s="39" t="n"/>
+      <c r="D53" s="39" t="n"/>
+      <c r="E53" s="39" t="n"/>
+      <c r="F53" s="39" t="n"/>
+      <c r="G53" s="39" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+          <t>Backtest con costes reales sobre el cajón de construir</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.01.03, 04.02.04</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -5184,22 +4738,22 @@
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>04.03.05</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
+          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -5211,41 +4765,53 @@
       <c r="G55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="38" t="inlineStr">
-        <is>
-          <t>04.04</t>
-        </is>
-      </c>
-      <c r="B56" s="39" t="inlineStr">
-        <is>
-          <t>Decisión y bucle</t>
-        </is>
-      </c>
-      <c r="C56" s="39" t="n"/>
-      <c r="D56" s="39" t="n"/>
-      <c r="E56" s="39" t="n"/>
-      <c r="F56" s="39" t="n"/>
-      <c r="G56" s="39" t="n"/>
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>04.03.03</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Validador</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>04.03.02</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
+          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>04.03.05</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -5259,22 +4825,22 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>04.04.02</t>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
+          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -5286,70 +4852,70 @@
       <c r="G58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
-        <is>
-          <t>04.04.03</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
-        </is>
-      </c>
-      <c r="C59" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="A59" s="38" t="inlineStr">
+        <is>
+          <t>04.04</t>
+        </is>
+      </c>
+      <c r="B59" s="39" t="inlineStr">
+        <is>
+          <t>Decisión y bucle</t>
+        </is>
+      </c>
+      <c r="C59" s="39" t="n"/>
+      <c r="D59" s="39" t="n"/>
+      <c r="E59" s="39" t="n"/>
+      <c r="F59" s="39" t="n"/>
+      <c r="G59" s="39" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>04.04.01</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr"/>
-      <c r="G59" s="4" t="inlineStr"/>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="36" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="B60" s="37" t="inlineStr">
-        <is>
-          <t>DEMO (PUERTA G3) — SE DETALLA AL CERRAR G2</t>
-        </is>
-      </c>
-      <c r="C60" s="37" t="n"/>
-      <c r="D60" s="37" t="n"/>
-      <c r="E60" s="37" t="n"/>
-      <c r="F60" s="37" t="n"/>
-      <c r="G60" s="37" t="n"/>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Secretario</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>04.03.05</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>04.04.02</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Bot en demo, solo y con guardias automáticos</t>
+          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>04.04.03</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -5357,32 +4923,28 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>REQUISITO AÑADIDO POR D-14 (01/08): el guardia de parada dura (-30% del capital inicial) lo aplica el BOT de forma CONTINUA, no una revision periodica; comprobado solo una vez al mes, un -30% puede ser un -45% cuando alguien mire. Se verifica por inyeccion antes de declararlo activo (regla 25 de CLAUDE.md).</t>
-        </is>
-      </c>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>05.01.02</t>
+          <t>04.04.03</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>Secretario</t>
+          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
+        </is>
+      </c>
+      <c r="C62" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -5393,71 +4955,75 @@
       <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="inlineStr"/>
     </row>
-    <row r="63">
-      <c r="A63" s="13" t="inlineStr">
-        <is>
-          <t>05.01.03</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
-        </is>
-      </c>
-      <c r="C63" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>05.01.02</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr"/>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="36" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="B64" s="37" t="inlineStr">
-        <is>
-          <t>REAL (PUERTA G4) — SE DETALLA AL CERRAR G3</t>
-        </is>
-      </c>
-      <c r="C64" s="37" t="n"/>
-      <c r="D64" s="37" t="n"/>
-      <c r="E64" s="37" t="n"/>
-      <c r="F64" s="37" t="n"/>
-      <c r="G64" s="37" t="n"/>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="36" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B63" s="37" t="inlineStr">
+        <is>
+          <t>DEMO (PUERTA G3) — SE DETALLA AL CERRAR G2</t>
+        </is>
+      </c>
+      <c r="C63" s="37" t="n"/>
+      <c r="D63" s="37" t="n"/>
+      <c r="E63" s="37" t="n"/>
+      <c r="F63" s="37" t="n"/>
+      <c r="G63" s="37" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>05.01.01</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Bot en demo, solo y con guardias automáticos</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>04.04.03</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>REQUISITO AÑADIDO POR D-14 (01/08): el guardia de parada dura (-30% del capital inicial) lo aplica el BOT de forma CONTINUA, no una revision periodica; comprobado solo una vez al mes, un -30% puede ser un -45% cuando alguien mire. Se verifica por inyeccion antes de declararlo activo (regla 25 de CLAUDE.md).</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>06.01.01</t>
+          <t>05.01.02</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Dinero pequeño respetando los límites de 01.01.03</t>
+          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>05.01.03</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -5465,22 +5031,18 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>limites ya escritos y firmados (D-14, 01/08): capital 1.000-2.000 €, AVISO a -25% del capital inicial que no para nada, PARADA DURA AUTOMATICA a -30% aplicada por el bot de forma continua y sin exencion activable desde dentro (regla 26 de CLAUDE.md).</t>
-        </is>
-      </c>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>06.01.02</t>
+          <t>05.01.03</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
+          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
@@ -5490,7 +5052,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>06.01.01</t>
+          <t>05.01.02</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -5504,12 +5066,12 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="36" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="B67" s="37" t="inlineStr">
         <is>
-          <t>MOTOR Y ORDEN (PARALELA; MÁX. 20% DEL ESFUERZO SEMANAL)</t>
+          <t>REAL (PUERTA G4) — SE DETALLA AL CERRAR G3</t>
         </is>
       </c>
       <c r="C67" s="37" t="n"/>
@@ -5521,12 +5083,12 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>07.01.01</t>
+          <t>06.01.01</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
+          <t>Dinero pequeño respetando los límites de 01.01.03</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -5536,7 +5098,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>03.01.01</t>
+          <t>05.01.03</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -5544,32 +5106,32 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr"/>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (02/08): ALCANCE — cuatro arreglos de documento, NINGUNO toca código: (a) Las celdas ESTADO de 01.02.04 y 03.01.12 declaran en negrita un estado del vocabulario pendiente / en_curso / hecha / bloqueada, como exige la sección «Estados y cadencia de este WBS». Valores ya decididos por el orquestador, no se deducen: 01.02.04 pasa a en_curso (entregado INFORME_MCP_2.md, RECHAZADO por critico-codigo, sin reparar); 03.01.12 pasa a pendiente (nadie la ha trabajado). En 01.02.04 la marca actual […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>limites ya escritos y firmados (D-14, 01/08): capital 1.000-2.000 €, AVISO a -25% del capital inicial que no para nada, PARADA DURA AUTOMATICA a -30% aplicada por el bot de forma continua y sin exencion activable desde dentro (regla 26 de CLAUDE.md).</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>07.01.02</t>
+          <t>06.01.02</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
+          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
+        </is>
+      </c>
+      <c r="C69" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>03.01.02</t>
+          <t>06.01.01</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -5580,13 +5142,125 @@
       <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="inlineStr"/>
     </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="36" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B70" s="37" t="inlineStr">
+        <is>
+          <t>MOTOR Y ORDEN (PARALELA; MÁX. 20% DEL ESFUERZO SEMANAL)</t>
+        </is>
+      </c>
+      <c r="C70" s="37" t="n"/>
+      <c r="D70" s="37" t="n"/>
+      <c r="E70" s="37" t="n"/>
+      <c r="F70" s="37" t="n"/>
+      <c r="G70" s="37" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>07.01.01</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>03.01.01</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (02/08): ALCANCE — cuatro arreglos de documento, NINGUNO toca código: (a) Las celdas ESTADO de 01.02.04 y 03.01.12 declaran en negrita un estado del vocabulario pendiente / en_curso / hecha / bloqueada, como exige la sección «Estados y cadencia de este WBS». Valores ya decididos por el orquestador, no se deducen: 01.02.04 pasa a en_curso (entregado INFORME_MCP_2.md, RECHAZADO por critico-codigo, sin reparar); 03.01.12 pasa a pendiente (nadie la ha trabajado). En 01.02.04 la marca actual […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>07.01.03</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (03/08, dictada por el orquestador): Qué pasó, medido y no supuesto: tras un /compact a las 21:29, la sesión recibió una orden del CEO a las 21:44 y trabajó sola hasta las 21:58 sin invocar a un solo subagente. Escribió D-19, D-20 y D-21 en un registro de solo-añadir, L-024 a L-027, cirugía estructural sobre el WBS, y dos scripts del Excel del CEO. Nadie lo revisó (regla 16 de CLAUDE.md y C2 rotas). Alcance: tres lotes con veredicto propio — (d) procedencia del motor de backtest, (b y c) […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>07.01.02</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>03.01.02</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr"/>
+      <c r="G73" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G69"/>
+  <autoFilter ref="A4:G73"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E69">
+  <conditionalFormatting sqref="E5:E73">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecha"</formula>
     </cfRule>
@@ -5598,7 +5272,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,Hecha,Bloqueada"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5612,7 +5286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5636,7 +5310,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Objetivo del mes: NO es tener el bot en demo. Es llegar al 1 de septiembre con respuesta a "¿existe alguna estrategia que merezca pasar a demo?".</t>
+          <t>Objetivo del mes: NO es tener el bot en demo. Es llegar al 1 de septiembre con respuesta a "¿existe alguna estrategia que merezca pasar a demo?". Holgura de calendario: cero. G1 se cierra 04-05/08; broker se firma 10/08 (NO RETORNO). Nota crítica: 04.03.03 (prueba OOS) es una sola pasada por variante sobre el cajón reservado — no se puede repetir ni acelerar.</t>
         </is>
       </c>
       <c r="B2" s="22" t="n"/>
@@ -5647,7 +5321,7 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Período</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -5657,17 +5331,22 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Tareas</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Qué se hace</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Hecho al final</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Lunes del CEO (1 h)</t>
+          <t>Fin previsto</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Checkpoint</t>
         </is>
       </c>
     </row>
@@ -5679,22 +5358,27 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>29 jul – 4 ago</t>
+          <t>03 – 05 ago</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Fase 02 completa + 01.02.01 (gb2) + 03.01.01 (repo), en paralelo</t>
+          <t>02.03.02, 02.03.03</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Mercado y vela elegidos (G1)</t>
+          <t>Informe de G1 + puerta (el CEO elige mercados)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Lun 3: leer informe G1 y elegir</t>
+          <t>Mercados y vela</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Mié 4-Jue 5: decisión del CEO</t>
         </is>
       </c>
     </row>
@@ -5706,22 +5390,27 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>5 – 11 ago</t>
+          <t>06 – 10 ago</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>03.01.02 a 03.01.06 + 04.01.01 (broker)</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Motor solo 24 h sin caerse + broker</t>
+          <t>Elegir broker, abrir demo</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Lun 10: firmar broker</t>
+          <t>Broker firmado</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Viernes 10 ago: NO RETORNO</t>
         </is>
       </c>
     </row>
@@ -5733,22 +5422,27 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>12 – 18 ago</t>
+          <t>11 – 14 ago</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>04.01.02, 04.01.03 + 04.02.01 a 04.02.04</t>
+          <t>04.01.02, 04.01.03</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>3-5 hipótesis con variantes pre-registradas</t>
+          <t>Costes reales del broker + tres cajones (train, validación, OOS)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Lun 17: ver hipótesis</t>
+          <t>Cajones listos</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Lun 12-Jue 14: preparando OOS</t>
         </is>
       </c>
     </row>
@@ -5760,22 +5454,27 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>19 – 25 ago</t>
+          <t>15 – 20 ago</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04.03.01, 04.03.02</t>
+          <t>04.02.01 a 04.02.04</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Variantes supervivientes tras ajuste</t>
+          <t>Barrido de hipótesis + filtro de sentido + pre-registro de variantes</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Lun 24: cuántas siguen vivas</t>
+          <t>3-5 hipótesis con variantes registradas</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Lun 19-Jue 20: qué entra al backtest</t>
         </is>
       </c>
     </row>
@@ -5787,64 +5486,170 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>26 ago – 1 sept</t>
+          <t>21 – 25 ago</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04.03.03 a 04.03.05 + 04.04.01</t>
+          <t>04.03.01, 04.03.02</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>Backtest sobre train + ajuste sobre validación</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Variantes supervivientes tras ajuste</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Lun 24-Jue 25: cuántas avanzan</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>26 – 30 ago</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>04.03.03 a 04.03.05</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>OOS sobre cajón reservado (UNA sola pasada) + Monte Carlo + walk-forward + veredicto</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
           <t>Veredicto pasa/no pasa por variante</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Lun 31: preparar evaluación</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Lun 26: OOS listo (irreversible)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>31 ago</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>04.04.01</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Informe de la vuelta</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Informe guardado, métricas listas</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Lun 31: preparar GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>GM</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>1 sept</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
-        <is>
-          <t>Puerta del mes con el CEO</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="inlineStr">
-        <is>
-          <t>Arrancar demo / otra vuelta / replantear</t>
-        </is>
-      </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>Mar 1: la reunión</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>Lo que NO cabe en el mes: la demo (8-12 semanas de mercado real, reloj no acelerable) · las 3 vueltas del bucle (cabe una y media) · el dinero real.</t>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>Puerta del mes: arrancar demo / otra vuelta / replantear / PARAR</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>Decisión del CEO</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Mar 1: reunión presencial</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>07 ago</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>03.01.05</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Fin bloque de motor: Fase 03 (03.01.02 a 03.01.06) lista en 24 h continuas de trabajo desatendido</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Motor probado</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>Lo que NO cabe en el mes: la demo (8-12 semanas de mercado real, reloj no acelerable) · más de una vuelta del bucle (cabe una) · el dinero real.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6325,7 +6130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6866,6 +6671,91 @@
       <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Comprobado por lectura: ningún agente de .claude/agents/ lleva la herramienta Agent en tools, así que un orquestador subagente no puede repartir. Y meter la revisión dentro del subagente degradaría la prueba al nivel 3 de la regla 9 de CLAUDE.md (consenso entre agentes), que es el más débil</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Techo del 20% de motor (regla 8 de CLAUDE.md) suspendido hasta 03.01.05 hecha o 01/09/2026</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>CEO ordenó motor antes que producto, incumpliendo regla 8; se suspende con condición de vuelta automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>El lunes deja de ser la única ventana de decisión del CEO; lo que esté listo sube el día que lo esté, SIN tope de número; el CEO marca el final del día</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>D-18: D-13 ya lo decía pero no se propagó; calendario recalculado sin esperar lunes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>PUERTA G1: un solo mercado, XAUUSD (oro al contado), vela de 4h. DEROGA D-2</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>D-19: foco en una cosa hasta probar que una hipótesis gana dinero; el oro está en las 4 cestas admisibles y es el más barato de los 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Auditorías del ecosistema cerradas; su valor son las ideas construibles aquí, no las piezas instalables</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>D-20: el criterio de admisión usado descartaba por barato justo lo que el proyecto puede construir</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Se elimina el trasplante desde gb2 (tarea 01.02.02 y su sección). Lo que haga falta se construye desde cero. DEROGA parcialmente D-6</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>D-21: orden del CEO; comprobado pieza a pieza que no se pierde nada vivo</t>
         </is>
       </c>
     </row>
@@ -6883,179 +6773,349 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TRASPLANTE DESDE gb2 (D6 = B, 30/07/2026)</t>
+          <t>LECCIONES APRENDIDAS</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>Ninguna pieza entra por ser buena en gb2: entra si pasa su prueba, ejecutada aqui.</t>
-        </is>
-      </c>
-      <c r="B2" s="22" t="n"/>
-      <c r="C2" s="22" t="n"/>
-      <c r="D2" s="22" t="n"/>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Pieza</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Qué se trae</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Criterio de aceptación (prueba ejecutada)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Qué se descarta de ella</t>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Lección</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Origen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>L-001</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Si un dato se puede calcular a partir de datos brutos disponibles, se calcula. Buscar el dato ya masticado pierde tiempo y devuelve fuentes flojas</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Revisión 02.03.01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>T1 — Dataset histórico</t>
+          <t>L-002</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Precios validados 2015-2022</t>
+          <t>Toda conversión de unidades se aplica en la tabla final, no solo se explica en una nota al pie</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Se recalcula la cobertura, los duplicados y los spreads negativos AQUÍ, sin fiarse del informe. Prueba de cordura de precio: el oro debe estar en cientos/miles, no en decenas (en gb2 un divisor mal puesto lo puso a 17 $/onza)</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Todo lo que esté versionado en git: los datos se descargan, no se clonan (regla 27 de CLAUDE.md)</t>
+          <t>Revisión 02.03.01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>T2 — Motor de backtest</t>
+          <t>L-003</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Costes reales nativos: entrada al precio de compra y salida al de venta, stops sin mejora de precio, financiación asimétrica con triple miércoles, dimensionado</t>
+          <t>Medir el coste de entrar y salir sin medir el de mantener da una foto incompleta</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Se ejecuta con un caso hecho a mano cuyo resultado se calcula con lápiz y papel; si no coincide, no entra. Además se prueba que un stop nunca ejecuta a mejor precio del disparado</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Los drivers duplicados (scripts/backtest_f03*.py): en gb2 la lógica vivía en dos sitios con riesgo de divergencia</t>
+          <t>Revisión 02.03.01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>T3 — Testbed de invarianza</t>
+          <t>L-004</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Prueba sintética con resultado de referencia fijo</t>
+          <t>Los valores absolutos no se comparan entre activos distintos: se normalizan antes</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Se corre dos veces y da el mismo número; se altera el motor a propósito y debe cambiar. Un testbed que no detecta un cambio inducido no sirve</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>El número de referencia de gb2: se genera uno nuevo aquí</t>
+          <t>Revisión 02.03.01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>T4 — Guardias de datos reservados</t>
+          <t>L-005</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Bloqueo de acceso al cajón OOS</t>
+          <t>El modelo no aprende: acumula notas escritas. Si nadie escribe bien las notas, no mejora nada</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Se intenta leer el cajón reservado por tres vías distintas (agente, script, terminal) y las tres deben bloquearse (regla 25 de CLAUDE.md). En gb2 estos sí mordían</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Los guardias que el propio informe señala como muertos o mal cableados</t>
+          <t>Análisis del vídeo, 29/07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>T5 — Especificaciones e informes de las 13 hipótesis</t>
+          <t>L-006</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Material de partida para la fase 04</t>
+          <t>Si dos fuentes usan convenciones distintas (yen y franco invertidos), sus números tienen el signo cambiado. Verificar la convención antes de comparar</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Ninguno: es material de lectura, no código. Advertencia obligatoria: 12 de las 13 nunca se probaron. Entran como hipótesis candidatas, no como conocimiento validado</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Cualquier conclusión sobre su calidad: no la hay</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>NO se trae: la configuración de agentes, la cola de tareas, el historial de git, los ficheros de estado, los encadenadores de sesión ni ninguna documentación de gb2 como norma. Las lecciones ya están extraídas en las reglas 5, 7, 11, 12, 13, 14, 15, 17, 18, 21, 25, 26, 27 y 29 de CLAUDE.md (el contenido de la antigua regla 26 del WBS —"antes de crear un agente se comprueba que el WBS tiene tareas de su tipo"— no tiene número propio en CLAUDE.md; ver L-010 de LECCIONES.md).</t>
+          <t>Revisión Brief B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>L-007</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Un nombre parecido no es el mismo instrumento: oro al contado ≠ futuro de oro; bitcoin contra Tether ≠ contra dólar</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Revisión Brief B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>L-008</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Un umbral sobre una magnitud inestable necesita varias ventanas, no una</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Revisión Brief B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>L-009</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Un guardia verificado por presencia y no por ejecución da falsa seguridad, que es peor que no tenerlo</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Auditoría gb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>L-010</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Los agentes no se activan solos porque tengan buena descripción: se activan si la cola contiene tareas de su tipo y el reparto enruta por tipo</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Auditoría gb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>L-011</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Tener una cola estricta no impide la deriva. gb2 la tenía ("trabajo que no está ahí no se ejecuta"), con IDs contiguos forzados por un hook, y aun así el 70% del esfuerzo se fue al motor. La cola controla QUÉ se ejecuta, no QUÉ se mete en la cola</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Auditoría gb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>L-012</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Dos agentes de acuerdo no son una prueba. En gb2 hubo tres diagnósticos seguidos del mismo componente, dos falsos; lo que los corrigió fue leer el código y reproducir el fallo, no debatir más</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Auditoría gb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>L-013</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Se trabajó una tarea sin ficha escrita antes: 01.01.02 era una fila de una línea sin alcance ni criterio de hecho, y el trabajo de apoyo se autoasignó alcance dentro de ella. La regla 5 de CLAUDE.md vale también para las tareas del CEO</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Revisión del cálculo de arrastre (01.01.02) por critico-codigo, 01/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>L-014</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Un supuesto expresado en porcentaje decidió el orden de magnitud sin declararse: fijar la actividad como porcentaje de velas operadas producía un multiplicador de coste x60-x69 entre velas que en valor absoluto cae a x4,3; la conclusión "1h es inviable" era un artefacto del supuesto</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Revisión de arrastre_coste.md, hallado por critico-codigo y confirmado con experimento ejecutado por validador, 01/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>L-015</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>CLAUDE.md y este WBS llevan dos listas de «29 reglas» con contenido distinto bajo el mismo número: toda cita regla N es ambigua. Resuelto el 01/08/2026 por D-16: la lista normativa es la de CLAUDE.md; toda cita se escribe «regla N de CLAUDE.md»</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Revisión 01.02.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>L-016</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Un indicador que solo mira lo etiquetado es ciego justo donde importa: medir el reparto producto/motor contando solo commits con código WBS daba 20% cuando el real es 43,8%, porque commit-msg exime a meta:, org: y arranque:, que es donde vive el motor</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Revisión 01.02.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>L-017</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>L-015 citaba mal su propia regla de grep: decía "la regla 20 de CLAUDE.md exige grep previo" cuando esa exigencia es la regla 12 de CLAUDE.md (la 20 es "se guardan todas las pruebas"). LECCIONES.md es de solo-añadir, así que no se corrige en su sitio, se anota aparte</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Tarea 03.01.13, pasada 1 (constructor-motor), 01/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>L-018</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Un recuento sin -i da cifras bajas aunque lo repitan dos agentes: quien ejecutó y quien revisó grepearon "regla" en minúscula y los dos dieron la misma cifra baja (5/3/36 en vez de 12/4/39), porque el error estaba en el método de los dos, no en el dato</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Tarea 03.01.13, pasada 2 (constructor-motor, ordenada tras el rechazo de la pasada 1), 01/08</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
+++ b/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
@@ -20,7 +20,7 @@
     <sheet name="LIMITES CEO" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TAREAS'!$A$4:$G$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TAREAS'!$A$4:$G$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -742,23 +742,23 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"01.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"01.??.??")</f>
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"01.??.??",TAREAS!$E$5:$E$73,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"01.??.??",TAREAS!$E$5:$E$81,"Hecha")</f>
         <v/>
       </c>
       <c r="D4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"01.??.??",TAREAS!$E$5:$E$73,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"01.??.??",TAREAS!$E$5:$E$81,"En curso")</f>
         <v/>
       </c>
       <c r="E4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"01.??.??",TAREAS!$E$5:$E$73,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"01.??.??",TAREAS!$E$5:$E$81,"Pendiente")</f>
         <v/>
       </c>
       <c r="F4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"01.??.??",TAREAS!$E$5:$E$73,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"01.??.??",TAREAS!$E$5:$E$81,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G4" s="6">
@@ -773,23 +773,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"02.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"02.??.??")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"02.??.??",TAREAS!$E$5:$E$73,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"02.??.??",TAREAS!$E$5:$E$81,"Hecha")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"02.??.??",TAREAS!$E$5:$E$73,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"02.??.??",TAREAS!$E$5:$E$81,"En curso")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"02.??.??",TAREAS!$E$5:$E$73,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"02.??.??",TAREAS!$E$5:$E$81,"Pendiente")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"02.??.??",TAREAS!$E$5:$E$73,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"02.??.??",TAREAS!$E$5:$E$81,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G5" s="6">
@@ -804,23 +804,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"03.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"03.??.??")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"03.??.??",TAREAS!$E$5:$E$73,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"03.??.??",TAREAS!$E$5:$E$81,"Hecha")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"03.??.??",TAREAS!$E$5:$E$73,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"03.??.??",TAREAS!$E$5:$E$81,"En curso")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"03.??.??",TAREAS!$E$5:$E$73,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"03.??.??",TAREAS!$E$5:$E$81,"Pendiente")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"03.??.??",TAREAS!$E$5:$E$73,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"03.??.??",TAREAS!$E$5:$E$81,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G6" s="6">
@@ -835,23 +835,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"04.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"04.??.??")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"04.??.??",TAREAS!$E$5:$E$73,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"04.??.??",TAREAS!$E$5:$E$81,"Hecha")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"04.??.??",TAREAS!$E$5:$E$73,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"04.??.??",TAREAS!$E$5:$E$81,"En curso")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"04.??.??",TAREAS!$E$5:$E$73,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"04.??.??",TAREAS!$E$5:$E$81,"Pendiente")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"04.??.??",TAREAS!$E$5:$E$73,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"04.??.??",TAREAS!$E$5:$E$81,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G7" s="6">
@@ -866,23 +866,23 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"05.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"05.??.??")</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"05.??.??",TAREAS!$E$5:$E$73,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"05.??.??",TAREAS!$E$5:$E$81,"Hecha")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"05.??.??",TAREAS!$E$5:$E$73,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"05.??.??",TAREAS!$E$5:$E$81,"En curso")</f>
         <v/>
       </c>
       <c r="E8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"05.??.??",TAREAS!$E$5:$E$73,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"05.??.??",TAREAS!$E$5:$E$81,"Pendiente")</f>
         <v/>
       </c>
       <c r="F8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"05.??.??",TAREAS!$E$5:$E$73,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"05.??.??",TAREAS!$E$5:$E$81,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G8" s="6">
@@ -897,23 +897,23 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"06.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"06.??.??")</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"06.??.??",TAREAS!$E$5:$E$73,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"06.??.??",TAREAS!$E$5:$E$81,"Hecha")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"06.??.??",TAREAS!$E$5:$E$73,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"06.??.??",TAREAS!$E$5:$E$81,"En curso")</f>
         <v/>
       </c>
       <c r="E9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"06.??.??",TAREAS!$E$5:$E$73,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"06.??.??",TAREAS!$E$5:$E$81,"Pendiente")</f>
         <v/>
       </c>
       <c r="F9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"06.??.??",TAREAS!$E$5:$E$73,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"06.??.??",TAREAS!$E$5:$E$81,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G9" s="6">
@@ -928,23 +928,23 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"07.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"07.??.??")</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"07.??.??",TAREAS!$E$5:$E$73,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"07.??.??",TAREAS!$E$5:$E$81,"Hecha")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"07.??.??",TAREAS!$E$5:$E$73,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"07.??.??",TAREAS!$E$5:$E$81,"En curso")</f>
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"07.??.??",TAREAS!$E$5:$E$73,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"07.??.??",TAREAS!$E$5:$E$81,"Pendiente")</f>
         <v/>
       </c>
       <c r="F10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$73,"07.??.??",TAREAS!$E$5:$E$73,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$81,"07.??.??",TAREAS!$E$5:$E$81,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G10" s="6">
@@ -1056,12 +1056,12 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>07.01.03</t>
+          <t>03.01.23</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
+          <t>Encadenador de trabajo desatendido: una conversación por tarea</t>
         </is>
       </c>
       <c r="C17" s="4" t="n"/>
@@ -1074,87 +1074,109 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>PROXIMA PUERTA</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>G1 — elegir mercado y tamaño de vela (criterios en la hoja PUERTAS)</t>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>07.01.03</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>OBJETIVO DEL MES</t>
+          <t>PROXIMA PUERTA</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>Llegar al 1 de septiembre con respuesta a: ¿existe alguna estrategia que merezca pasar a demo?</t>
+          <t>G1 — elegir mercado y tamaño de vela (criterios en la hoja PUERTAS)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
+          <t>OBJETIVO DEL MES</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Llegar al 1 de septiembre con respuesta a: ¿existe alguna estrategia que merezca pasar a demo?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
           <t>FUENTE DE VERDAD</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>00-direccion/WBS.md — este Excel se genera de ahi. Si discrepan, manda el texto.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>LEYENDA</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Hecha</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>En curso</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>Bloqueada</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B19:G19"/>
+  <mergeCells count="9">
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B22:G22"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B21:G21"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G11">
     <cfRule type="dataBar" priority="1">
@@ -1362,7 +1384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1461,7 +1483,7 @@
       <c r="B6" s="30" t="n"/>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>04.02.01 — Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente. Detras de ella esperan 16 de las 39 tareas vivas.</t>
+          <t>04.02.01 — Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente. Detras de ella esperan 16 de las 42 tareas vivas.</t>
         </is>
       </c>
       <c r="D6" s="30" t="n"/>
@@ -1525,7 +1547,7 @@
     <row r="9">
       <c r="A9" s="32" t="inlineStr">
         <is>
-          <t>SE PUEDE TRABAJAR YA — 17 tareas, en este orden</t>
+          <t>SE PUEDE TRABAJAR YA — 20 tareas, en este orden</t>
         </is>
       </c>
       <c r="B9" s="32" t="n"/>
@@ -1567,10 +1589,10 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
@@ -1584,17 +1606,17 @@
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
-          <t>07.01.03</t>
+          <t>03.01.23</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
+          <t>Encadenador de trabajo desatendido: una conversación por tarea</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Constructor de motor</t>
         </is>
       </c>
       <c r="E11" s="34" t="inlineStr">
@@ -1621,35 +1643,31 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>07.01.03</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
-        </is>
-      </c>
-      <c r="D12" s="28" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>15</v>
-      </c>
+          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
+        </is>
+      </c>
+      <c r="E12" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -1662,17 +1680,17 @@
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>04.02.01</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Investigador</t>
+          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1686,10 +1704,10 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
@@ -1703,22 +1721,22 @@
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>03.01.03</t>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Ejecución desatendida: arranques programados, permisos AMPLIOS por defecto (git como red de seguridad) y topes de gasto</t>
+          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E14" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
+          <t>Investigador</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1730,7 +1748,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
@@ -1744,12 +1762,12 @@
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>03.01.04</t>
+          <t>03.01.03</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Plan de respaldo de modelos: si un modelo no está disponible o rechaza, el agente sigue con su respaldo y lo anota</t>
+          <t>Ejecución desatendida: arranques programados, permisos AMPLIOS por defecto (git como red de seguridad) y topes de gasto</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1785,17 +1803,17 @@
       </c>
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>03.01.06</t>
+          <t>03.01.04</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Plantilla y automatismo de fichas de decisión: el secretario prepara cada decisión del CEO en el formato obligatorio y la adjunta al informe semanal</t>
+          <t>Plan de respaldo de modelos: si un modelo no está disponible o rechaza, el agente sigue con su respaldo y lo anota</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E16" s="34" t="inlineStr">
@@ -1826,17 +1844,17 @@
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>03.01.09</t>
+          <t>03.01.06</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Enrutado por tipo de tarea y comprobación de que el WBS genera tareas de cada tipo de agente (ver L-010 de LECCIONES.md; sin número propio en CLAUDE.md)</t>
+          <t>Plantilla y automatismo de fichas de decisión: el secretario prepara cada decisión del CEO en el formato obligatorio y la adjunta al informe semanal</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E17" s="34" t="inlineStr">
@@ -1849,8 +1867,12 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -1863,12 +1885,12 @@
       </c>
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>03.01.10</t>
+          <t>03.01.09</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Testbed sintético de invarianza: resultado de referencia fijo que debe reproducirse tras cualquier cambio del motor</t>
+          <t>Enrutado por tipo de tarea y comprobación de que el WBS genera tareas de cada tipo de agente (ver L-010 de LECCIONES.md; sin número propio en CLAUDE.md)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1900,12 +1922,12 @@
       </c>
       <c r="B19" s="33" t="inlineStr">
         <is>
-          <t>03.01.12</t>
+          <t>03.01.10</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 01/08 (petición del CEO): fijar la estrategia de ramas de git. Criterio del CEO, literal: que dé agilidad, no complejidad</t>
+          <t>Testbed sintético de invarianza: resultado de referencia fijo que debe reproducirse tras cualquier cambio del motor</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1937,12 +1959,12 @@
       </c>
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>03.01.14</t>
+          <t>03.01.12</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 01/08 (deuda detectada al cerrar 03.01.13): la hoja REGLAS del Excel del CEO la construye 05-vista-ceo/generar_excel.py leyendo las líneas numeradas de la sección de reglas del WBS, que tras D-16 ya no existen: la hoja saldría vacía bajo el título «LAS 29 REGLAS», y verificar_excel.py no comprueba esa hoja, así que sus 8 pruebas pasarían igual (L-016). Hay que leer las reglas de CLAUDE.md y añadir una prueba que falle si la hoja sale vacía. Deuda de motor: no se ejecuta sin permiso del CEO.</t>
+          <t>NUEVA 01/08 (petición del CEO): fijar la estrategia de ramas de git. Criterio del CEO, literal: que dé agilidad, no complejidad</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1960,12 +1982,8 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -1978,12 +1996,12 @@
       </c>
       <c r="B21" s="33" t="inlineStr">
         <is>
-          <t>03.01.15</t>
+          <t>03.01.14</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Herramientas del secretario: puede escribir los registros que solo admiten añadir pero no puede verificarlos</t>
+          <t>NUEVA 01/08 (deuda detectada al cerrar 03.01.13): la hoja REGLAS del Excel del CEO la construye 05-vista-ceo/generar_excel.py leyendo las líneas numeradas de la sección de reglas del WBS, que tras D-16 ya no existen: la hoja saldría vacía bajo el título «LAS 29 REGLAS», y verificar_excel.py no comprueba esa hoja, así que sus 8 pruebas pasarían igual (L-016). Hay que leer las reglas de CLAUDE.md y añadir una prueba que falle si la hoja sale vacía. Deuda de motor: no se ejecuta sin permiso del CEO.</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2015,17 +2033,17 @@
       </c>
       <c r="B22" s="33" t="inlineStr">
         <is>
-          <t>03.01.17</t>
+          <t>03.01.15</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Reparar la prueba 7 de verificar_excel.py (entregables de las tareas hechas)</t>
+          <t>Herramientas del secretario: puede escribir los registros que solo admiten añadir pero no puede verificarlos</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Constructor de motor</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E22" s="34" t="inlineStr">
@@ -2052,17 +2070,17 @@
       </c>
       <c r="B23" s="33" t="inlineStr">
         <is>
-          <t>03.01.18</t>
+          <t>03.01.17</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (D-20, idea 1 de las auditorías): contador mecánico del reparto producto/motor, inyectado en el contexto al arrancar cada tirada</t>
+          <t>Reparar la prueba 7 de verificar_excel.py (entregables de las tareas hechas)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Constructor de motor</t>
         </is>
       </c>
       <c r="E23" s="34" t="inlineStr">
@@ -2089,12 +2107,12 @@
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>03.01.19</t>
+          <t>03.01.18</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (D-20, idea 2 de las auditorías): registro mecánico de autoría, para que «nadie valida su propio trabajo» deje de ser solo prosa</t>
+          <t>NUEVA 03/08 (D-20, idea 1 de las auditorías): contador mecánico del reparto producto/motor, inyectado en el contexto al arrancar cada tirada</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -2126,12 +2144,12 @@
       </c>
       <c r="B25" s="33" t="inlineStr">
         <is>
-          <t>07.01.01</t>
+          <t>03.01.19</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
+          <t>NUEVA 03/08 (D-20, idea 2 de las auditorías): registro mecánico de autoría, para que «nadie valida su propio trabajo» deje de ser solo prosa</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2163,12 +2181,12 @@
       </c>
       <c r="B26" s="33" t="inlineStr">
         <is>
-          <t>07.01.02</t>
+          <t>03.01.20</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
+          <t>NUEVA 04/08 (incidente del 03/08): muro para que una sesión no siga trabajando sola después de un /compact</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -2195,39 +2213,59 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="inlineStr">
-        <is>
-          <t>ESPERANDO A OTRA TAREA — 22 tareas, en orden de codigo WBS</t>
-        </is>
-      </c>
-      <c r="B27" s="32" t="n"/>
-      <c r="C27" s="32" t="n"/>
-      <c r="D27" s="32" t="n"/>
-      <c r="E27" s="32" t="n"/>
-      <c r="F27" s="32" t="n"/>
-      <c r="G27" s="32" t="n"/>
-      <c r="H27" s="32" t="n"/>
-      <c r="I27" s="32" t="n"/>
+      <c r="A27" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>03.01.25</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 05/08 (nace del incidente de este mismo día): guardia en .githooks/pre-commit que ejecuta la métrica de L-027 de 00-direccion/LECCIONES.md sobre 00-direccion/WBS.md y rechaza el commit si alguna fila de tarea no da 7 campos al partirla por la barra vertical. Motivo: hoy la métrica existe, está escrita como normativa en este WBS, y no la ejecuta nadie automáticamente; 05-vista-ceo/verificar_excel.py no la cubre. Es el muro que le falta a la única fuente de verdad del proyecto. Regla 24 de CLAUDE.md: nace de un incidente real y medido — el 05/08 cuatro filas quedaron partidas y ningún guardia se enteró. Regla 25 de CLAUDE.md: se verifica por inyección de una fila rota ANTES de documentarse como activo. AVISO PARA QUIEN LA EJECUTE, medido el mismo día: el propio texto de esta fila no puede contener el comando literal, porque la barra vertical que lleva dentro rompe la fila que describe; el guardia tiene que tolerar esa cita cuando aparezca en prosa fuera de una tabla.</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Constructor de motor</t>
+        </is>
+      </c>
+      <c r="E27" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>nada: se puede empezar ya</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="A28" s="5" t="n">
+        <v>19</v>
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>03.01.05</t>
+          <t>07.01.01</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
+          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E28" s="34" t="inlineStr">
@@ -2244,29 +2282,27 @@
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
+          <t>nada: se puede empezar ya</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="A29" s="5" t="n">
+        <v>20</v>
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>03.01.07</t>
+          <t>07.01.02</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
+          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E29" s="34" t="inlineStr">
@@ -2283,48 +2319,24 @@
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>03.01.06 (pendiente, Secretario)</t>
+          <t>nada: se puede empezar ya</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>03.01.11</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E30" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>03.01.08 (en curso, Crítico)</t>
-        </is>
-      </c>
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>ESPERANDO A OTRA TAREA — 22 tareas, en orden de codigo WBS</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="n"/>
+      <c r="C30" s="32" t="n"/>
+      <c r="D30" s="32" t="n"/>
+      <c r="E30" s="32" t="n"/>
+      <c r="F30" s="32" t="n"/>
+      <c r="G30" s="32" t="n"/>
+      <c r="H30" s="32" t="n"/>
+      <c r="I30" s="32" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -2334,17 +2346,17 @@
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>03.01.16</t>
+          <t>03.01.05</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Las hojas del Excel se construyen de sus fuentes primarias, no de copias</t>
+          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="E31" s="34" t="inlineStr">
@@ -2361,7 +2373,7 @@
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>03.01.14 (pendiente, Constructores)</t>
+          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2373,22 +2385,22 @@
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>04.01.02</t>
+          <t>03.01.07</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
+          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
+          <t>Secretario</t>
+        </is>
+      </c>
+      <c r="E32" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2400,7 +2412,7 @@
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
+          <t>03.01.06 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -2412,38 +2424,34 @@
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>04.01.03</t>
+          <t>03.01.11</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>13</v>
-      </c>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E33" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
+          <t>03.01.08 (en curso, Crítico)</t>
         </is>
       </c>
     </row>
@@ -2455,22 +2463,22 @@
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>03.01.24</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
+          <t>NUEVA 05/08 (nace de los huecos medidos por ejecución en 03.01.08): las tres barreras que hoy NO existen. (a) El patrón Bash( 02-datos/reservado) de .claude/settings.json exige un espacio literal y no cubre la ruta pegada a una comilla, así que una línea de python lo esquiva: sustituirlo por un patrón que cubra cualquier verbo y cualquier forma de escribir la ruta, y probarlo con las TRES formas. (b) Nada impide rm -rf dentro de 02-datos/, y los datos no están en git (regla 27 de CLAUDE.md): no se rehacen deshaciendo un commit, se rehacen volviendo a descargarlos. (c) No hay ninguna barrera de gasto, ni en código ni en configuración; D-26 de 00-direccion/DECISIONES.md deja escrito que --max-budget-usd existe. Regla 24 de CLAUDE.md: las tres nacen de una inyección ejecutada con su salida guardada, no de una sospecha, y ninguna causó daño. Regla 25 de CLAUDE.md: cada barrera nueva se verifica por inyección ANTES de documentarse como activa.</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E34" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2478,15 +2486,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>15</v>
-      </c>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>04.02.01 (pendiente, Investigador)</t>
+          <t>03.01.08 (en curso, Crítico)</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2502,17 @@
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.01.02</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
+          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02) REQUISITO AÑADIDO 04/08: al recalcular con precios reales se comprueba que la entidad que publica la tarifa es la misma con la que se opera. Si no coinciden, la cifra vieja no se hereda: se vuelve a medir.</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2521,15 +2525,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>14</v>
-      </c>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>04.02.02 (pendiente, Investigador)</t>
+          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2541,17 +2541,17 @@
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>04.02.04</t>
+          <t>04.01.03</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
+          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>04.02.03 (pendiente, Validador)</t>
+          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2584,17 +2584,17 @@
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Backtest con costes reales sobre el cajón de construir</t>
+          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2611,11 +2611,11 @@
         <v>1</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
+          <t>04.02.01 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -2627,17 +2627,17 @@
       </c>
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
+          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2654,11 +2654,11 @@
         <v>1</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>04.03.01 (pendiente, Constructores)</t>
+          <t>04.02.02 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="B39" s="33" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.02.04</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
+          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2697,11 +2697,11 @@
         <v>1</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>04.03.02 (pendiente, Constructores)</t>
+          <t>04.02.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2713,17 +2713,17 @@
       </c>
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+          <t>Backtest con costes reales sobre el cajón de construir</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2740,11 +2740,11 @@
         <v>1</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>04.03.03 (pendiente, Validador)</t>
+          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2756,17 +2756,17 @@
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>04.03.05</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
+          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -2783,11 +2783,11 @@
         <v>1</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>04.03.04 (pendiente, Validador)</t>
+          <t>04.03.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2799,17 +2799,17 @@
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
+          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -2823,14 +2823,14 @@
         </is>
       </c>
       <c r="G42" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>04.03.05 (pendiente, Validador)</t>
+          <t>04.03.02 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2842,17 +2842,17 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>04.04.02</t>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
+          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -2865,11 +2865,15 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr"/>
-      <c r="H43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>04.04.01 (pendiente, Secretario)</t>
+          <t>04.03.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2881,17 +2885,17 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>04.04.03</t>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
-        </is>
-      </c>
-      <c r="D44" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -2908,11 +2912,11 @@
         <v>1</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>04.04.01 (pendiente, Secretario)</t>
+          <t>04.03.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2924,17 +2928,17 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Bot en demo, solo y con guardias automáticos</t>
+          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -2948,14 +2952,14 @@
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>04.04.03 (pendiente, CEO)</t>
+          <t>04.03.05 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2971,17 @@
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>05.01.02</t>
+          <t>04.04.02</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
+          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -2990,15 +2994,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>3</v>
-      </c>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>05.01.01 (pendiente, Constructores)</t>
+          <t>04.04.01 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="B47" s="33" t="inlineStr">
         <is>
-          <t>05.01.03</t>
+          <t>04.04.03</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
+          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
         </is>
       </c>
       <c r="D47" s="28" t="inlineStr">
@@ -3037,11 +3037,11 @@
         <v>1</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>05.01.02 (pendiente, Secretario)</t>
+          <t>04.04.01 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -3053,12 +3053,12 @@
       </c>
       <c r="B48" s="33" t="inlineStr">
         <is>
-          <t>06.01.01</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Dinero pequeño respetando los límites de 01.01.03</t>
+          <t>Bot en demo, solo y con guardias automáticos</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3080,11 +3080,11 @@
         <v>1</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>05.01.03 (pendiente, CEO)</t>
+          <t>04.04.03 (pendiente, CEO)</t>
         </is>
       </c>
     </row>
@@ -3096,41 +3096,170 @@
       </c>
       <c r="B49" s="33" t="inlineStr">
         <is>
+          <t>05.01.02</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Secretario</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>05.01.01 (pendiente, Constructores)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B50" s="33" t="inlineStr">
+        <is>
+          <t>05.01.03</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
+        </is>
+      </c>
+      <c r="D50" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>05.01.02 (pendiente, Secretario)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B51" s="33" t="inlineStr">
+        <is>
+          <t>06.01.01</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Dinero pequeño respetando los límites de 01.01.03</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>05.01.03 (pendiente, CEO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B52" s="33" t="inlineStr">
+        <is>
           <t>06.01.02</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
         </is>
       </c>
-      <c r="D49" s="28" t="inlineStr">
+      <c r="D52" s="28" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>PRODUCTO</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>06.01.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="46" customHeight="1">
-      <c r="A51" s="35" t="inlineStr">
-        <is>
-          <t>Aviso de la regla 8 (CLAUDE.md): si la cola de arriba solo tuviera tareas de MOTOR, hay que parar y avisar al CEO; significa que la cola esta mal llena. Ahora mismo la cola tiene 2 de producto y 15 de motor.</t>
+    <row r="54" ht="46" customHeight="1">
+      <c r="A54" s="35" t="inlineStr">
+        <is>
+          <t>Aviso de la regla 8 (CLAUDE.md): si la cola de arriba solo tuviera tareas de MOTOR, hay que parar y avisar al CEO; significa que la cola esta mal llena. Ahora mismo la cola tiene 2 de producto y 18 de motor.</t>
         </is>
       </c>
     </row>
@@ -3139,14 +3268,14 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A51:I51"/>
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A27:I27"/>
     <mergeCell ref="C4:H4"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3158,7 +3287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3956,7 +4085,7 @@
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>FICHA (03/08, D-20) — CORRECCIÓN DE ALCANCE, dicha sin adornos: esta tarea prometía que el agente «sigue con su respaldo», y eso no se puede automatizar entero: un hook no puede cambiar el modelo. Lo que sí se puede: el evento StopFailure admite matcher por tipo de error (rate_limit, overloaded, authentication_failed, server_error, entre otros) y SubagentStop avisa del fin de un subagente. Con ellos, un fallo silencioso pasa a ser un fallo registrado. Esta tarea entrega esa mitad mecánica. El […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (03/08, D-20) — CORRECCIÓN DE ALCANCE, dicha sin adornos: esta tarea prometía que el agente «sigue con su respaldo», y eso no se puede automatizar entero: un hook no puede cambiar el modelo (CORRECCIÓN DE ALCANCE (04/08, reproducida por el orquestador): cierto que un hook no cambia de modelo, pero existe --fallback-model &lt;model&gt; — "Enable automatic fallback to specified model(s) when the default model is overloaded or not available. Accepts a comma-separated list to try each in order. […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4204,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>ejecutada la primera pasada 31/07 con verificar_barreras.py: 4 barreras de 5 VERIFICADAS por ejecucion (hooks instalados, datos rechazados en commit, .gitignore ignora 02-datos, mensaje exige codigo WBS). 1 NO VERIFICADA: el cajon reservado era un filtro de texto sobre el comando. CORRECCIÓN DE DEPENDENCIA (03/08/2026): la dependencia de 03.01.03 fue falsa desde el inicio — verificar_barreras.py ejecutada el 31/07 sin que 03.01.03 existiera ya. Las barreras probadas (hooks, .gitignore, commit-msg, cifrado) dependen de 03.01.01 (repo con WBS y reglas) y 03.01.02 (ocho agentes creados). Se remedia en 03.01.11 (D-10). No se cierra hasta repetir la pasada con 03.01.11 terminada</t>
+          <t>ejecutada la primera pasada 31/07 con verificar_barreras.py: 4 barreras de 5 VERIFICADAS por ejecucion (hooks instalados, datos rechazados en commit, .gitignore ignora 02-datos, mensaje exige codigo WBS). 1 NO VERIFICADA: el cajon reservado era un filtro de texto sobre el comando. CORRECCIÓN DE DEPENDENCIA (03/08/2026): la dependencia de 03.01.03 fue falsa desde el inicio — verificar_barreras.py ejecutada el 31/07 sin que 03.01.03 existiera ya. Las barreras probadas (hooks, .gitignore, commit-msg, cifrado) dependen de 03.01.01 (repo con WBS y reglas) y 03.01.02 (ocho agentes creados). Se remedia en 03.01.11 (D-10). No se cierra hasta repetir la pasada con 03.01.11 terminada SEGUNDA PASADA […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
@@ -4326,13 +4455,17 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr"/>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>el 03/08», que llevaba la marca sin guion delante) que se detectó y reparó antes de terminar. Las dos demostradas por inyección en 05-vista-ceo/prueba_inyeccion.sh, casos 6 y 7 nuevos (función probar_argv, con el mismo guardia FIXTURE de L-026): el caso 6 añade una lección a una copia de LECCIONES.md sin tocar el Excel y hace caer la prueba de recuento; el caso 7 inserta una marca pendiente sin guion delante 40 caracteres antes del cierre real de una celda y hace caer solo la prueba de posición, sin falsear el ESTADO leído (igual que describe el mecanismo del bug). bash 05-vista-ceo/prueba_inyeccion.sh caza los 7 casos salvo el 3, que ya fallaba ANTES de esta tarea: usa el código 07.01.03 […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>FICHA (03/08): Problema verificado hoy: 05-vista-ceo/generar_excel.py construye las hojas REGLAS, LECCIONES y DECISIONES, pero lo hace leyendo tablas espejo en el WBS, no de las fuentes primarias. Consecuencia: (1) hoja REGLAS sale vacía tras D-16 (las reglas ya no están numeradas en el WBS); (2) hoja LECCIONES muestra 18 cuando 00-direccion/LECCIONES.md tiene 23 (L-016); (3) hoja DECISIONES muestra 0 cuando 00-direccion/DECISIONES.md tiene 16 — el CEO no ve ninguna de sus propias decisiones […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (03/08): Problema verificado hoy: 05-vista-ceo/generar_excel.py construye las hojas REGLAS, LECCIONES y DECISIONES, pero lo hace leyendo tablas espejo en el WBS, no de las fuentes primarias. Consecuencia, medida el 03/08 y ya caducada en sus cifras concretas —de ahí la reescritura del 04/08 más abajo, la fuente sigue viva y crece cada día—: (1) hoja REGLAS sale vacía tras D-16 (las reglas ya no están numeradas en el WBS); (2) hoja LECCIONES muestra 18 cuando 00-direccion/LECCIONES.md […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
@@ -4435,117 +4568,161 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="36" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="B43" s="37" t="inlineStr">
-        <is>
-          <t>HIPÓTESIS Y VALIDACIÓN (PUERTA G2)</t>
-        </is>
-      </c>
-      <c r="C43" s="37" t="n"/>
-      <c r="D43" s="37" t="n"/>
-      <c r="E43" s="37" t="n"/>
-      <c r="F43" s="37" t="n"/>
-      <c r="G43" s="37" t="n"/>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>03.01.20</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 04/08 (incidente del 03/08): muro para que una sesión no siga trabajando sola después de un /compact</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>03.01.02</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (04/08, dictada por el orquestador): Incidente que la origina, verificado (regla 24 de CLAUDE.md): el 03/08/2026, tras un /compact a las 21:29, la sesión recibió una orden del CEO a las 21:44 y trabajó sin invocar a un solo subagente hasta las 21:58 — escribió tres decisiones y cuatro lecciones en registros de solo-añadir, hizo cirugía estructural sobre el WBS y tocó dos scripts del Excel del CEO. Nadie lo revisó. El detalle está en la tarea 07.01.03. NO ES EL «Nivel 2» DE 03.01.19 y no […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="38" t="inlineStr">
-        <is>
-          <t>04.01</t>
-        </is>
-      </c>
-      <c r="B44" s="39" t="inlineStr">
-        <is>
-          <t>Broker y cajones de datos</t>
-        </is>
-      </c>
-      <c r="C44" s="39" t="n"/>
-      <c r="D44" s="39" t="n"/>
-      <c r="E44" s="39" t="n"/>
-      <c r="F44" s="39" t="n"/>
-      <c r="G44" s="39" t="n"/>
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>03.01.21</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Diagnóstico medido del consumo de tokens del motor de agentes</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Secretario</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>03.01.01</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>04/08 — medición sobre el transcript en disco de la sesión del 03-04/08 (/home/server/.claude/projects/-home-server-projects-bot-trading/1d064480-a2c4-42fd-a199-5fd72ce78fd9.jsonl y su carpeta subagents/). Hilo principal: 207 peticiones, 94,9 M de tokens leídos de cache, contexto pico 794.459, contexto medio ~452.000. 75 subagentes: 1.293 peticiones, 114,8 M leídos, 11,5 M escritos. Total ~209,7 M en una sola sesión. Causa identificada: el coste crece con el cuadrado de los pasos dados dentro de una misma conversación, sobre un suelo fijo de ~85.000 tokens por conversación. Correcciones aplicadas al propio diagnóstico tras revisión de critico-codigo: el ahorro estimado bajó de "5x" y de un […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>03.01.22</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
-        </is>
-      </c>
-      <c r="C45" s="28" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
+          <t>Inventario por ejecución de los mecanismos de trabajo desatendido en esta máquina</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Constructor de motor</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>02.03.03</t>
+          <t>03.01.01</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr"/>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>04/08 — ejecutado por constructor-motor, revisado por critico-codigo. Probado por ejecución: tmux 3.4 presente · cron corriendo (PID 156, activo bajo systemd, persiste tras reinicio) · systemd real en esta WSL2 · flock y jq presentes · screen, at, notify-send, mail y sendmail NO instalados · claude 2.1.221. Hallazgos: --max-budget-usd existe (solo con --print) · --max-turns existe pero oculto, no sale en claude --help · --fallback-model existe · en modo -p un permiso no se queda colgado: se resuelve solo. HUECOS:** no hay forma de avisar al CEO fuera de la máquina sin webhook, porque no hay notify-send ni correo. Pendiente de decisión del CEO. Que --max-budget-usd corte de verdad no está […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
       <c r="G45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>04.01.02</t>
+          <t>03.01.23</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02)</t>
+          <t>Encadenador de trabajo desatendido: una conversación por tarea</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
+          <t>Constructor de motor</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr"/>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>. No se enciende: depende de una tirada real supervisada y de 03.01.08. CRITERIO DE HECHO (no cambia): una tirada que arranque sola sin nadie delante, y la tabla muro/prosa con cada línea "muro" disparada por inyección. (Tabla muro/prosa en 03-motor/desatendido/LEEME.md, líneas 62-81; 13 mecanismos: 12 MURO verificados por ejecución, 1 NO verificado.)</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>REDUCCIÓN ORDENADA POR EL CEO (04/08): la pieza se había crecido con gobernanza que él nunca pidió. Se borraron: lista-verde.txt (y toda su barrera de autorización) · los topes en dólares (MAX_BUDGET_USD_SESION, MAX_BUDGET_USD_DIARIO, gasto-.tsv) · crontab.propuesto.txt (arranques programados) · hook-notificacion.ejemplo.json (aviso al móvil) · cola.txt, progreso.tsv y --disallowedTools. Petición literal del CEO: "en vez de enlazar tantas tareas seguidas se parará antes para no consumir tokens […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>04.01.03</t>
+          <t>03.01.24</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
+          <t>NUEVA 05/08 (nace de los huecos medidos por ejecución en 03.01.08): las tres barreras que hoy NO existen. (a) El patrón Bash( 02-datos/reservado) de .claude/settings.json exige un espacio literal y no cubre la ruta pegada a una comilla, así que una línea de python lo esquiva: sustituirlo por un patrón que cubra cualquier verbo y cualquier forma de escribir la ruta, y probarlo con las TRES formas. (b) Nada impide rm -rf dentro de 02-datos/, y los datos no están en git (regla 27 de CLAUDE.md): no se rehacen deshaciendo un commit, se rehacen volviendo a descargarlos. (c) No hay ninguna barrera de gasto, ni en código ni en configuración; D-26 de 00-direccion/DECISIONES.md deja escrito que --max-budget-usd existe. Regla 24 de CLAUDE.md: las tres nacen de una inyección ejecutada con su salida guardada, no de una sospecha, y ninguna causó daño. Regla 25 de CLAUDE.md: cada barrera nueva se verifica por inyección ANTES de documentarse como activa.</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>03.01.08</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4553,103 +4730,99 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>** — DEUDA DE MOTOR: no se ejecuta sin permiso expreso del CEO (regla 7 de CLAUDE.md). Ficha de decisión preparada para el 06/08</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="38" t="inlineStr">
-        <is>
-          <t>04.02</t>
-        </is>
-      </c>
-      <c r="B48" s="39" t="inlineStr">
-        <is>
-          <t>Investigación de hipótesis</t>
-        </is>
-      </c>
-      <c r="C48" s="39" t="n"/>
-      <c r="D48" s="39" t="n"/>
-      <c r="E48" s="39" t="n"/>
-      <c r="F48" s="39" t="n"/>
-      <c r="G48" s="39" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>04.02.01</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>03.01.02</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>03.01.25</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 05/08 (nace del incidente de este mismo día): guardia en .githooks/pre-commit que ejecuta la métrica de L-027 de 00-direccion/LECCIONES.md sobre 00-direccion/WBS.md y rechaza el commit si alguna fila de tarea no da 7 campos al partirla por la barra vertical. Motivo: hoy la métrica existe, está escrita como normativa en este WBS, y no la ejecuta nadie automáticamente; 05-vista-ceo/verificar_excel.py no la cubre. Es el muro que le falta a la única fuente de verdad del proyecto. Regla 24 de CLAUDE.md: nace de un incidente real y medido — el 05/08 cuatro filas quedaron partidas y ningún guardia se enteró. Regla 25 de CLAUDE.md: se verifica por inyección de una fila rota ANTES de documentarse como activo. AVISO PARA QUIEN LA EJECUTE, medido el mismo día: el propio texto de esta fila no puede contener el comando literal, porque la barra vertical que lleva dentro rompe la fila que describe; el guardia tiene que tolerar esa cita cuando aparezca en prosa fuera de una tabla.</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Constructor de motor</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>03.01.01</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>** — DEUDA DE MOTOR: no se ejecuta sin permiso expreso del CEO (regla 7 de CLAUDE.md). Entra como cuarto punto de la ficha D-29 del 06/08</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="36" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B49" s="37" t="inlineStr">
+        <is>
+          <t>HIPÓTESIS Y VALIDACIÓN (PUERTA G2)</t>
+        </is>
+      </c>
+      <c r="C49" s="37" t="n"/>
+      <c r="D49" s="37" t="n"/>
+      <c r="E49" s="37" t="n"/>
+      <c r="F49" s="37" t="n"/>
+      <c r="G49" s="37" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>04.02.02</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>04.02.01</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr"/>
+      <c r="A50" s="38" t="inlineStr">
+        <is>
+          <t>04.01</t>
+        </is>
+      </c>
+      <c r="B50" s="39" t="inlineStr">
+        <is>
+          <t>Broker y cajones de datos</t>
+        </is>
+      </c>
+      <c r="C50" s="39" t="n"/>
+      <c r="D50" s="39" t="n"/>
+      <c r="E50" s="39" t="n"/>
+      <c r="F50" s="39" t="n"/>
+      <c r="G50" s="39" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Validador</t>
+          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>02.03.03</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -4658,27 +4831,31 @@
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr"/>
-      <c r="G51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (04/08, dictada por el orquestador): Por qué ahora: 02.03.03 cerró el 03/08 con D-19 y esta tarea quedó desbloqueada; es la única con plazo duro —10/08, sin retorno— y quedan 6 días. Alcance: comparar 3 o 4 brokers que ofrezcan XAUUSD al contado y entregar la tabla para que el CEO firme. PROHIBIDO ELEGIR: la elección es del CEO. Criterios obligatorios, uno por columna: (1) lote mínimo, y si admite fraccionado de 0,1 onzas —es eliminatorio de hecho: el lote entero son unos 1.962 € contra […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>04.02.04</t>
+          <t>04.01.02</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
+          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02) REQUISITO AÑADIDO 04/08: al recalcular con precios reales se comprueba que la entidad que publica la tarifa es la misma con la que se opera. Si no coinciden, la cifra vieja no se hereda: se vuelve a medir.</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -4690,70 +4867,70 @@
       <c r="G52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="38" t="inlineStr">
-        <is>
-          <t>04.03</t>
-        </is>
-      </c>
-      <c r="B53" s="39" t="inlineStr">
-        <is>
-          <t>Laboratorio de pruebas (por hipótesis y variante)</t>
-        </is>
-      </c>
-      <c r="C53" s="39" t="n"/>
-      <c r="D53" s="39" t="n"/>
-      <c r="E53" s="39" t="n"/>
-      <c r="F53" s="39" t="n"/>
-      <c r="G53" s="39" t="n"/>
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>04.01.03</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Constructor datos</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>04.01.01</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>04.03.01</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Backtest con costes reales sobre el cajón de construir</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>04.01.03, 04.02.04</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="4" t="inlineStr"/>
+      <c r="A54" s="38" t="inlineStr">
+        <is>
+          <t>04.02</t>
+        </is>
+      </c>
+      <c r="B54" s="39" t="inlineStr">
+        <is>
+          <t>Investigación de hipótesis</t>
+        </is>
+      </c>
+      <c r="C54" s="39" t="n"/>
+      <c r="D54" s="39" t="n"/>
+      <c r="E54" s="39" t="n"/>
+      <c r="F54" s="39" t="n"/>
+      <c r="G54" s="39" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
+          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -4767,22 +4944,22 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
+          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -4796,12 +4973,12 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -4811,7 +4988,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -4825,12 +5002,12 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>04.03.05</t>
+          <t>04.02.04</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
+          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -4840,7 +5017,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -4854,12 +5031,12 @@
     <row r="59">
       <c r="A59" s="38" t="inlineStr">
         <is>
-          <t>04.04</t>
+          <t>04.03</t>
         </is>
       </c>
       <c r="B59" s="39" t="inlineStr">
         <is>
-          <t>Decisión y bucle</t>
+          <t>Laboratorio de pruebas (por hipótesis y variante)</t>
         </is>
       </c>
       <c r="C59" s="39" t="n"/>
@@ -4871,22 +5048,22 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
+          <t>Backtest con costes reales sobre el cajón de construir</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>04.03.05</t>
+          <t>04.01.03, 04.02.04, 04.03.07</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -4900,22 +5077,22 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>04.04.02</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
+          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -4929,22 +5106,22 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>04.04.03</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
-        </is>
-      </c>
-      <c r="C62" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Validador</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -4955,42 +5132,54 @@
       <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="inlineStr"/>
     </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="36" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="B63" s="37" t="inlineStr">
-        <is>
-          <t>DEMO (PUERTA G3) — SE DETALLA AL CERRAR G2</t>
-        </is>
-      </c>
-      <c r="C63" s="37" t="n"/>
-      <c r="D63" s="37" t="n"/>
-      <c r="E63" s="37" t="n"/>
-      <c r="F63" s="37" t="n"/>
-      <c r="G63" s="37" t="n"/>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>04.03.04</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Validador</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>04.03.03</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Bot en demo, solo y con guardias automáticos</t>
+          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>04.04.03</t>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -4998,107 +5187,119 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>REQUISITO AÑADIDO POR D-14 (01/08): el guardia de parada dura (-30% del capital inicial) lo aplica el BOT de forma CONTINUA, no una revision periodica; comprobado solo una vez al mes, un -30% puede ser un -45% cuando alguien mire. Se verifica por inyeccion antes de declararlo activo (regla 25 de CLAUDE.md).</t>
-        </is>
-      </c>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>05.01.02</t>
+          <t>04.03.06</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
+          <t>NUEVA 03/08 (decisión del CEO, opción B): especificación del motor de backtest propio, escrita para una construcción desde cero y no para un trasplante</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Arquitecto</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>02.03.03</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr"/>
-      <c r="G65" s="4" t="inlineStr"/>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>04/08 — 03-motor/ESPECIFICACION_MOTOR_BACKTEST.md. 16 requisitos, cada uno con su prueba de aceptación ejecutable; 8 casos calculados a mano; 8 exclusiones motivadas y 7 huecos declarados. RECORRIDO: escrita por arquitecto a ciegas —declara no haber abierto 03-motor/backtester/, ni el commit 0c35959, ni /home/server/projects/gold-bot-2, y la prohibición se comprobó pidiéndole la lista de ficheros leídos—; RECHAZADA en ronda 1 por constructor-datos porque R-06(c) era una revisión a ojo y no una prueba ejecutable, más una atribución de fuente desajustada en R-13(b); el orquestador añadió un tercer defecto que la revisión no cazó: tres citas por número de línea en la sección 10, ya caducadas […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (03/08, dictada por el orquestador): Por qué se rehace y no se rescata: el criterio de aceptación anterior vivía en la sección «Trasplante desde gb2 — criterios de aceptación», que la cirugía de D-21 borró y hoy solo existe en el historial de git. Nació describiendo qué se traía y qué se descartaba de otro proyecto, y se escribió el 30/07, antes de D-19 y antes de las mediciones de la Fase 02, así que no dice nada del oro, ni de la vela de 4h, ni del lote mínimo. Insumos obligatorios: los […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>05.01.03</t>
+          <t>04.03.07</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
-        </is>
-      </c>
-      <c r="C66" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>NUEVA 03/08 (decisión del CEO, opción B): construir el motor de backtest desde cero contra la especificación de 04.03.06, tras retirar el anterior</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Constructor de motor</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>05.01.02</t>
+          <t>04.03.06, 07.01.03</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr"/>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="36" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="B67" s="37" t="inlineStr">
-        <is>
-          <t>REAL (PUERTA G4) — SE DETALLA AL CERRAR G3</t>
-        </is>
-      </c>
-      <c r="C67" s="37" t="n"/>
-      <c r="D67" s="37" t="n"/>
-      <c r="E67" s="37" t="n"/>
-      <c r="F67" s="37" t="n"/>
-      <c r="G67" s="37" t="n"/>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>04/08 — 03-motor/backtester/. Motor de backtest construido desde cero contra la especificación de 04.03.06. PROCEDENCIA, que era la pregunta que originó esta tarea: INDEPENDIENTE de las dos fuentes. Medido con el procedimiento pre-registrado del lote (d) de 07.01.03, bajo la segunda lectura de gb2 que autorizó el CEO en D-25: 0% de intersección de símbolos contra gb2 y contra el commit retirado 0c35959, con coincidencias de línea de 5,2-12,9% que son boilerplate (import pandas as pd, @dataclass, else:) y ninguna constante de calibración heredada. Contraste: 0c35959 disparaba 66,7% y 100% en ese mismo criterio. Reproducido de forma independiente por el orquestador. ADAPTACIÓN DEL […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (03/08, dictada por el orquestador): PASO 0, que se ejecuta antes que nada: retirar del árbol de trabajo el motor anterior con git revert, sin reescribir historia, para que quien construya no lo tenga delante. El código sigue existiendo en el commit 0c35959 para siempre, y con él sus 44 funciones de prueba —13 en test_costs.py, 20 en test_execution.py y 11 en test_sizing.py, contadas sobre el commit— que la regla 20 de CLAUDE.md obliga a conservar aunque no se usen. Verificado antes de […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="38" t="inlineStr">
+        <is>
+          <t>04.04</t>
+        </is>
+      </c>
+      <c r="B67" s="39" t="inlineStr">
+        <is>
+          <t>Decisión y bucle</t>
+        </is>
+      </c>
+      <c r="C67" s="39" t="n"/>
+      <c r="D67" s="39" t="n"/>
+      <c r="E67" s="39" t="n"/>
+      <c r="F67" s="39" t="n"/>
+      <c r="G67" s="39" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>06.01.01</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Dinero pequeño respetando los límites de 01.01.03</t>
+          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>05.01.03</t>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -5106,32 +5307,28 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>limites ya escritos y firmados (D-14, 01/08): capital 1.000-2.000 €, AVISO a -25% del capital inicial que no para nada, PARADA DURA AUTOMATICA a -30% aplicada por el bot de forma continua y sin exencion activable desde dentro (regla 26 de CLAUDE.md).</t>
-        </is>
-      </c>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>06.01.02</t>
+          <t>04.04.02</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
-        </is>
-      </c>
-      <c r="C69" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>06.01.01</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -5142,108 +5339,104 @@
       <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="inlineStr"/>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="36" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="B70" s="37" t="inlineStr">
-        <is>
-          <t>MOTOR Y ORDEN (PARALELA; MÁX. 20% DEL ESFUERZO SEMANAL)</t>
-        </is>
-      </c>
-      <c r="C70" s="37" t="n"/>
-      <c r="D70" s="37" t="n"/>
-      <c r="E70" s="37" t="n"/>
-      <c r="F70" s="37" t="n"/>
-      <c r="G70" s="37" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="13" t="inlineStr">
-        <is>
-          <t>07.01.01</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>03.01.01</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>04.04.03</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
+        </is>
+      </c>
+      <c r="C70" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>04.04.01</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr"/>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (02/08): ALCANCE — cuatro arreglos de documento, NINGUNO toca código: (a) Las celdas ESTADO de 01.02.04 y 03.01.12 declaran en negrita un estado del vocabulario pendiente / en_curso / hecha / bloqueada, como exige la sección «Estados y cadencia de este WBS». Valores ya decididos por el orquestador, no se deducen: 01.02.04 pasa a en_curso (entregado INFORME_MCP_2.md, RECHAZADO por critico-codigo, sin reparar); 03.01.12 pasa a pendiente (nadie la ha trabajado). En 01.02.04 la marca actual […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="36" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B71" s="37" t="inlineStr">
+        <is>
+          <t>DEMO (PUERTA G3) — SE DETALLA AL CERRAR G2</t>
+        </is>
+      </c>
+      <c r="C71" s="37" t="n"/>
+      <c r="D71" s="37" t="n"/>
+      <c r="E71" s="37" t="n"/>
+      <c r="F71" s="37" t="n"/>
+      <c r="G71" s="37" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>07.01.03</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
+          <t>Bot en demo, solo y con guardias automáticos</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>04.04.03</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr"/>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (03/08, dictada por el orquestador): Qué pasó, medido y no supuesto: tras un /compact a las 21:29, la sesión recibió una orden del CEO a las 21:44 y trabajó sola hasta las 21:58 sin invocar a un solo subagente. Escribió D-19, D-20 y D-21 en un registro de solo-añadir, L-024 a L-027, cirugía estructural sobre el WBS, y dos scripts del Excel del CEO. Nadie lo revisó (regla 16 de CLAUDE.md y C2 rotas). Alcance: tres lotes con veredicto propio — (d) procedencia del motor de backtest, (b y c) […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>REQUISITO AÑADIDO POR D-14 (01/08): el guardia de parada dura (-30% del capital inicial) lo aplica el BOT de forma CONTINUA, no una revision periodica; comprobado solo una vez al mes, un -30% puede ser un -45% cuando alguien mire. Se verifica por inyeccion antes de declararlo activo (regla 25 de CLAUDE.md).</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>07.01.02</t>
+          <t>05.01.02</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
+          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>03.01.02</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -5254,13 +5447,237 @@
       <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>05.01.03</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
+        </is>
+      </c>
+      <c r="C74" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>05.01.02</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="36" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B75" s="37" t="inlineStr">
+        <is>
+          <t>REAL (PUERTA G4) — SE DETALLA AL CERRAR G3</t>
+        </is>
+      </c>
+      <c r="C75" s="37" t="n"/>
+      <c r="D75" s="37" t="n"/>
+      <c r="E75" s="37" t="n"/>
+      <c r="F75" s="37" t="n"/>
+      <c r="G75" s="37" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>06.01.01</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Dinero pequeño respetando los límites de 01.01.03</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>05.01.03</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>limites ya escritos y firmados (D-14, 01/08): capital 1.000-2.000 €, AVISO a -25% del capital inicial que no para nada, PARADA DURA AUTOMATICA a -30% aplicada por el bot de forma continua y sin exencion activable desde dentro (regla 26 de CLAUDE.md).</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>06.01.02</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
+        </is>
+      </c>
+      <c r="C77" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>06.01.01</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr"/>
+      <c r="G77" s="4" t="inlineStr"/>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="36" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B78" s="37" t="inlineStr">
+        <is>
+          <t>MOTOR Y ORDEN (PARALELA; MÁX. 20% DEL ESFUERZO SEMANAL)</t>
+        </is>
+      </c>
+      <c r="C78" s="37" t="n"/>
+      <c r="D78" s="37" t="n"/>
+      <c r="E78" s="37" t="n"/>
+      <c r="F78" s="37" t="n"/>
+      <c r="G78" s="37" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>07.01.01</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>03.01.01</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (02/08): ALCANCE — cuatro arreglos de documento, NINGUNO toca código: (a) Las celdas ESTADO de 01.02.04 y 03.01.12 declaran en negrita un estado del vocabulario pendiente / en_curso / hecha / bloqueada, como exige la sección «Estados y cadencia de este WBS». Valores ya decididos por el orquestador, no se deducen: 01.02.04 pasa a en_curso (entregado INFORME_MCP_2.md, RECHAZADO por critico-codigo, sin reparar); 03.01.12 pasa a pendiente (nadie la ha trabajado). En 01.02.04 la marca actual […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>07.01.03</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>2ª AMPLIACIÓN 03/08, decisión del CEO — opción B: el motor de backtest se tira y se construye de cero. Consecuencias sobre esta tarea: los lotes (e1) y (e2) de aptitud QUEDAN CANCELADOS — juzgar si sirve un código que se borra es gastar la verificación en un cadáver. No se pierde su contenido: su eje A3, que no juzgaba al motor viejo sino que describía qué debe hacer cualquier motor para servir a D-19, migra íntegro a la especificación nueva (tarea 04.03.06). El lote (d) SE MANTIENE, recortado a la medición mecánica, por tres motivos: D-21 afirma en un registro de solo-añadir que no se copió una sola línea de gb2 y esa mitad sigue sin comprobar; la autorización de una sola apertura que dio […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (03/08, dictada por el orquestador): Qué pasó, medido y no supuesto: tras un /compact a las 21:29, la sesión recibió una orden del CEO a las 21:44 y trabajó sola hasta las 21:58 sin invocar a un solo subagente. Escribió D-19, D-20 y D-21 en un registro de solo-añadir, L-024 a L-027, cirugía estructural sobre el WBS, y dos scripts del Excel del CEO. Nadie lo revisó (regla 16 de CLAUDE.md y C2 rotas). Alcance: tres lotes con veredicto propio — (d) procedencia del motor de backtest, (b y c) […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>07.01.02</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>03.01.02</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G73"/>
+  <autoFilter ref="A4:G81"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E73">
+  <conditionalFormatting sqref="E5:E81">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecha"</formula>
     </cfRule>
@@ -5272,7 +5689,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,Hecha,Bloqueada"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6089,7 +6506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6104,20 +6521,319 @@
       </c>
       <c r="B1" s="2" t="n"/>
     </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Leidas de CLAUDE.md, seccion «## Las N reglas» (D-16: unica lista normativa). No se lee la tabla espejo que tenia el WBS: quedo derogada y vacia.</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="n"/>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>REGLA</t>
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Toda tarea se ejecuta y se anuncia por su código WBS ("Ejecutando 02.02.01"). Prohibidos los identificadores opacos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>No se inventan tareas. Trabajo nuevo = primero se añade al WBS con código y motivo. Subtareas dentro del alcance las crea el orquestador; tareas nuevas de primer nivel, solo en la revisión del lunes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Los códigos son estables: una tarea empezada no se renumera jamás.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Se va en orden salvo las marcadas paralelas. Una tarea no se cierra sin cumplir su criterio de "hecho".</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>La ficha de una tarea se escribe en la cola ANTES de trabajarla, nunca al cerrarla. Sin ficha, no hay tarea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Regla de no-ambigüedad: toda tarea debe poder ejecutarse sin adivinar nada. Si tienes que suponer algo, devuelve la tarea al orquestador para que la reescriba. No supongas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Cada tirada autónoma cierra al menos una tarea que avanza el PRODUCTO. La infraestructura que no desbloquee mecánicamente una tarea de producto se registra como deuda y no se ejecuta sin permiso del CEO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>El trabajo de motor y orden tiene un techo del 20% del esfuerzo semanal. Si en una tirada solo hay tareas de motor disponibles, para y avisa: es señal de que la cola está mal llena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Jerarquía de la prueba. Ninguna afirmación se acepta por consenso entre agentes:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Quien discrepa aporta el experimento que zanjaría la discusión, no otro argumento. Si no hay experimento posible, sube al CEO marcado como no probado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Un fallo reportado por un agente no es un fallo verificado. Antes de encolar o reparar: lee el componente y reproduce el fallo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Ninguna referencia a una decisión entra en código o informe sin un grep previo que la localice por fichero y línea. Solo se cita lo firmado y guardado, nunca en pasado ni antes de existir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Se referencia por nombre de símbolo, nunca por número de línea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Todo dato numérico se calcula sobre datos brutos, salvo que exista una fuente primaria homogénea demostrable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Quien implementa ejecuta y lee su artefacto completo antes de entregar. Las puertas confirman, no descubren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Nadie valida su propio trabajo. Quien construye no revisa; quien produce las métricas no firma el veredicto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Éxito = código fiel a la especificación, NO estrategia rentable. Un backtest con mal resultado y código correcto es un éxito registrable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Test de compuerta: si la justificación de un cambio no se sostiene sin citar métricas de resultado, se deniega.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Pre-registro: ninguna variante se prueba sin estar registrada antes (máx. 5-7 por hipótesis). Lo no registrado no se prueba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Se guardan TODAS las pruebas, también las fallidas. Saber cuántas cosas se probaron es lo que permite juzgar si la ganadora es real o casualidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Registros que solo permiten añadir: 04-resultados/registro-pruebas.md y 00-direccion/DECISIONES.md nunca se reescriben. Una corrección es una entrada nueva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>El cajón 02-datos/reservado/ no se abre. Solo el CEO puede autorizar su uso, una vez por variante. Ningún agente, ningún debate, ninguna urgencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Dos niveles. Lo REVERSIBLE (archivos, código, pruebas) tiene permisos amplios: git lo deshace. Lo IRREVERSIBLE (dinero real, órdenes al broker, borrar el cajón reservado, gastar dinero nuevo) lleva barrera desde el minuto uno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Una restricción solo se añade tras un incidente real, anotada junto al incidente, y se revisa cada mes. La que no tenga incidente vivo detrás, se quita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Toda barrera se verifica por ejecución —inyectando el caso prohibido— antes de documentarla como activa. Sin prueba: "no verificada". Un guardia presente en el código no es un guardia probado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Los guardias bloquean por defecto. La condición que activa una exención debe ser un hecho impuesto por el sistema, nunca un dato que elija el vigilado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Los datos nunca entran en git. Se descargan con script. Comprobar el día 1 que .gitignore funciona de verdad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Una sola fuente de verdad por tema. Documento que se sustituye, se borra: git guarda el historial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Cada agente lleva el identificador exacto de su modelo, nunca un alias, y ningún agente sin modelo.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6130,638 +6846,736 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REGISTRO DE DECISIONES — solo se añade, nunca se reescribe (regla 21)</t>
+          <t>REGISTRO DE DECISIONES (27) — solo se añade, nunca se reescribe (regla 21 de CLAUDE.md)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Decisión</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Motivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Leido de 00-direccion/DECISIONES.md, una fila por cada 'D-N'. No se lee la tabla espejo del WBS.</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>DECISIÓN</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>DETALLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Producto antes que motor; motor máx. 20% en paralelo</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Evitar la deriva de gb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Producto antes que motor; el motor en paralelo con techo del 20%</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: en el proyecto anterior el 70% del esfuerzo se fue al motor y se probo 1 de 13 hipotesis.
+Decide: CEO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>D-2</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Portafolio 3-5 mercados poco correlacionados</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Riesgo repartido + muestra</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Portafolio de 3-5 mercados poco correlacionados, no un solo par</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: repartir riesgo y ganar muestra de operaciones.
+Decide: CEO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>D-3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Mercado y vela se deciden en G1 con datos</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Evitar corazonadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Mercado y tamaño de vela se deciden en la puerta G1 con datos, no de antemano</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: evitar decisiones por corazonada.
+Decide: CEO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>CEO: revisión semanal + puertas, sin firmas por tarea</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Dirección por excepción</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>El CEO revisa una hora los lunes y decide en las puertas; no firma tareas</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: direccion por excepcion.
+Decide: CEO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>D-5</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Broker después de G1; costes provisionales mientras</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Búsqueda enfocada</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>WBS texto = fuente de verdad; Excel = vista del CEO</t>
-        </is>
-      </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Agentes leen texto</t>
+          <t>Horizonte de 1 mes con evaluacion el 1 de septiembre de 2026 (puerta GM)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: obligar a mirar los numeros pronto. NO es fecha de demo: el objetivo del mes es tener
+veredicto sobre si existe una estrategia que merezca ir a demo.
+Decide: CEO.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>D-6</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Cada agente con su modelo según tarea (tabla Equipo); confirmar con análisis gb2</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Replicar lo bueno de gb2 con criterio</t>
+          <t>Repositorio nuevo con trasplante de 5 piezas verificadas de gb2</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: reescribir motor y datos desde cero se comeria el mes sin acercar la respuesta. Lo que
+fallaba en gb2 no era el motor, era la capa de gestion, que no se hereda.
+Decide: CEO. Condicion: cada pieza pasa su criterio de aceptacion, ejecutado aqui.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>D-7</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>gb2 se analiza como información, no como copia (01.02.01)</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Lecciones sin contaminación</t>
+          <t>Jerarquia de la prueba: ejecucion &gt; verificacion documental &gt; contraste entre agentes</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: el consenso entre agentes no es prueba. En gb2 hubo tres diagnosticos seguidos del mismo
+componente, dos falsos; los corrigio leer el codigo y reproducir el fallo, no debatir mas.
+Decide: CEO.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>D-8</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Validación: 3 cajones (train/validación/OOS) + Monte Carlo + walk-forward, con pre-registro de variantes (máx. 5-7) y registro de fallidas</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Cuantas más variantes, más fácil que una gane por suerte; esto lo controla</t>
+          <t>Cada agente lleva identificador exacto de modelo; ningun alias, ningun agente sin modelo</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: en gb2, 7 de 13 agentes usaban alias contra su propia politica, y el agente que firmaba
+decisiones no tenia modelo asignado.
+Decide: direccion tecnica.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>D-9</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Bucle de investigación si nada pasa; a la 3ª vuelta sin éxito, revisión con el CEO</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Bucle sano, no infinito</t>
+          <t>Los datos nunca entran en git</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: gb2 versiono 50.089 ficheros de datos (1,4 GB por clon) contra su propio .gitignore.
+Decide: direccion tecnica.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>D-10</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Regla de no-ambigüedad: tarea que obliga a adivinar vuelve al orquestador</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>La ambigüedad fue causa del caos en gb2</t>
+          <t>El cajon reservado se protege cifrandolo con una contraseña que solo tiene el CEO</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: el 31/07 verificar_barreras.py demostro POR EJECUCION que el guardia anterior era un filtro sobre el TEXTO del comando: un comando que nombraba la ruta se bloqueaba, pero un programa que la construia por dentro entraba sin obstaculo. La condicion que activaba la exencion la elegia el vigilado, que es justo lo que prohibe la regla 26. Cifrar convierte el bloqueo en un hecho matematico que no depende de la buena voluntad de ningun agente.
+Decide: CEO. Condicion: la contraseña no se guarda en ningun sitio (ni fichero, ni variable de entorno, ni sesion); cada operacion la vuelve a pedir; nada se descifra a disco; el cajon se queda dentro del proyecto. Toda apertura queda anotada en 04-resultados/registro-cajon.md.
+Que bloqueaba: 04.01.03 (partir el historico en tres cajones) y, detras, toda la puerta G2.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>D-11</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Restricción justificada: permisos amplios + git; restricciones solo tras incidente real, revisadas cada mes</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>En gb2 se restringió de más sobre el papel y hubo que ir quitando</t>
+          <t>Siete criterios de G1 aprobados (G1-C1 a G1-C7)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: definicion de la barra de elegibilidad de mercados y vela. G1-C1 presupuesto de coste TOTAL al año ≤5% del capital, formula compuesta, con el coste de mantener DENTRO de ese mismo 5% (no aparte); anclado en la regla publicada de Robert Carver ("no gastar mas de un tercio del retorno esperado en costes") con retorno objetivo del 15% anual, que ES UN SUPUESTO ELEGIDO POR EL ORQUESTADOR Y APROBADO POR EL CEO, NO UN DATO MEDIDO. G1-C2 coste de ida y vuelta ÷ ATR de la vela tranquila (percentil 10) ≤10%. G1-C3 coste de mantener, sin umbral propio, suma dentro de G1-C1. G1-C4 minimo 1.000 velas/año en la vela elegida, sin minimo de operaciones (ninguna fuente primaria lo respalda). G1-C5 correlacion ≤0,7 entre los elegidos en las tres ventanas (3 meses, 1 año, 2 años), filtra la CESTA y no instrumentos sueltos. G1-C6 tamaño minimo operable con capital de 1.000-2.000 €, medido con ATR […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>D-12</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Modelos por puesto: Fable 5 en validación y arquitectura, Opus 5 en orquestación, Sonnet 5 en construcción e investigación, Haiku 4.5 en secretaría</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Fuentes oficiales consultadas 29/07/2026; el modelo caro solo donde un error cuesta dinero</t>
+          <t>Fecha tope el 01/12/2026, con revision de avance el dia 1 de cada mes</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: D-5 fijaba la evaluacion GM del 01/09/2026 pero NO fijaba ninguna fecha de parada, y las
+tres salidas de GM (arrancar demo, dar otra vuelta, replantear) tampoco cerraban el proyecto: no
+existia fecha tope en ningun documento. Sin fecha de parada el proyecto puede derivar
+indefinidamente, que es lo que ocurrio en gb2.
+Forma operativa: revision de avance el dia 1 de cada mes (01/09 = GM, 01/10, 01/11), cada una
+con poder explicito de PARAR el proyecto ademas de las tres salidas que GM ya tenia. La pregunta de
+cada revision la fija el CEO: "¿avanza por buen camino?". El 01/12/2026 es fecha tope dura: si a esa
+fecha no hay ninguna estrategia en demo, el proyecto se cierra y se escribe el informe de por que.
+Decide: CEO (opcion B de la ficha, con el seguimiento mensual añadido por el CEO).
+Que bloqueaba: cierre de 01.01.03 y puerta G0.
+Consecuencia: GM gana una cuarta salida […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>D-13</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Respaldo obligatorio para todo agente con Fable 5</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Fable 5 estuvo suspendido en junio de 2026 y puede rechazar peticiones</t>
+          <t>Tope de 5 fichas por revision del lunes; la hora es minimo garantizado, no techo</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: D-4 fija 1 h los lunes, pero lo que se desborda no es el tiempo sino el numero de
+decisiones acumuladas: cerrar solo la tarea 01.01.03 genero 3 fichas en un dia.
+Forma operativa: maximo 5 fichas de decision por revision del lunes; si hay mas, el orquestador
+prioriza y las sobrantes esperan al lunes siguiente. El CEO declara que ademas sigue el proyecto dia
+a dia y que pasar de la hora no le supone problema: la hora del lunes es un MINIMO GARANTIZADO, no
+un techo.
+Decide: CEO (opcion B de la ficha, con la aclaracion del CEO de que la hora no es techo).
+Que bloqueaba: cierre de 01.01.03 y puerta G0.
+Aviso registrado: el modelo de autonomia de CLAUDE.md esta construido sobre un CEO escaso. Con
+un CEO disponible a diario el riesgo deja de ser su tiempo y pasa a ser que el equipo consulte en
+vez de decidir. Se mantiene SIN CAMBIO la lista de lo que el equipo cierra sin consultar: que […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>D-14</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>La Fase 03 no se cierra sin un día entero de trabajo desatendido real (03.01.05)</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Evitar el motor perfecto en papel de gb2</t>
+          <t>Dinero real: aviso a -25% y parada dura automatica a -30% del capital inicial</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: el WBS registraba una contradiccion viva sin resolver — parada dura propuesta en -25%
+frente a una tolerancia del 50-60% mencionada por el CEO. El CEO fija el nivel entre el 25% y el 30%
+y pide explicitamente que no se pare solo, porque una estrategia puede bajar y recuperar. Eso obliga
+a DOS niveles, no a uno.
+Forma operativa: (1) AVISO a -25% del capital inicial ingresado: NO para nada, se reporta al CEO
+y decide el CEO. (2) PARADA DURA a -30% del capital inicial: el bot deja de abrir posiciones,
+automaticamente y sin exencion activable desde dentro (regla 26). Se mide sobre el CAPITAL INICIAL
+INGRESADO, no sobre el maximo alcanzado. Recuperar desde -30% exige +43%.
+Decide: CEO (opcion A de la ficha refinada). SIN recomendacion del equipo:
+.claude/commands/ficha.md prohibe recomendar en decisiones de tolerancia al riesgo.
+Que bloqueaba: cierre de 01.01.03 y puerta G0. Da […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>D-15</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Escalado definido (sección Autonomía): el CEO solo interviene en puertas y excepciones</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>El CEO no firma tareas</t>
+          <t>Flujo obligatorio de cuatro capas: CEO → Claude Code → orquestador → agentes</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: medido sobre los transcripts de sesion, de 39 invocaciones de subagente el orquestador
+tenia UNA, y era la prueba de activacion del 30/07: cero trabajo real. La causa: los comandos
+suplantaban a los agentes en vez de invocarlos (/autonomo empezaba con "Eres el ORQUESTADOR" y
+/informe con "Eres el SECRETARIO"), asi que el rol se ejercia desde la sesion principal y el agente
+no hacia falta nunca. Consecuencia real: el 01/08 un barrido del catalogo awesome-claude-code
+devolvio 3 hallazgos, nadie lo cuestiono y tuvo que ser el CEO quien dijera que era imposible. Con el
+flujo de capas, esa implausibilidad la caza el orquestador al juzgar, y si se le escapa la caza
+Claude Code en el filtro final. El CEO no deberia ser el primer control de calidad.
+Forma operativa: ver la seccion "Como se trabaja: las cuatro capas" de CLAUDE.md. En corto:
+el CEO pide · Claude Code entiende y llama al […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>D-16</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Formato obligatorio de ficha de decisión del CEO (sección «Qué llega al CEO y qué no» de CLAUDE.md + plantilla)</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Reducir al mínimo el tiempo del CEO: ni redactar, ni buscar, ni calcular</t>
+          <t>CLAUDE.md es la unica lista de reglas normativa; la del WBS se sustituye por un puntero</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: el proyecto tenia DOS listas de "29 reglas" con contenido distinto bajo el mismo numero. Verificado por ejecucion: una en CLAUDE.md bajo "## Las 29 reglas" y otra en 00-direccion/WBS.md bajo "## Reglas (sin ambiguedad posible)". Medido con grep -inoE 'regla[s]? [0-9]+' sobre el repositorio: 24 de las 29 reglas divergen; solo coinciden en sustancia la 1, 2, 3, 4 y 6. Ejemplos: "los datos nunca entran en git" es la regla 27 en CLAUDE.md y la 24 en el WBS; la regla 25 es "toda barrera se verifica por ejecucion" en CLAUDE.md y "cada agente lleva el identificador exacto de su modelo" en el WBS; la regla 26 es "los guardias bloquean por defecto" frente a "antes de crear un agente se comprueba que el WBS contiene tareas de su tipo". Consecuencia: ninguna cita "regla N" del proyecto era verificable por la regla 12 de CLAUDE.md (ninguna referencia entra sin un grep que la localice […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>D-17</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>D1 resuelta: se fija AHORA qué se mide (misma vara para los 8) y se calibran los umbrales en G1 con los números delante</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>El CEO no quiere cortes a ciegas; sin vara común, cada mercado se mediría distinto</t>
+          <t>Techo del 20% de motor (regla 8 de CLAUDE.md) suspendido hasta que 03.01.05 esté hecha o 01/09/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: el CEO ordenó el 03/08 construir el motor antes que el producto, lo que incumple la regla 8 de CLAUDE.md (cada tirada autónoma cierra al menos una tarea que avanza el PRODUCTO). B lo pone por escrito con condición de vuelta automática en vez de saltarse la regla en silencio cada semana. La regla 8 NO se elimina —tiene incidente vivo detrás: el proyecto anterior murió al 70% de motor— se suspende con disparador que impone el sistema, no el vigilado (regla 26 de CLAUDE.md).
+Forma operativa: la suspensión es por DOS condiciones, ambas deben cumplirse para levantar la suspensión: (1) la tarea 03.01.05 esté hecha, O (2) llegue la fecha 01/09/2026, lo que ocurra PRIMERO. Si llega el 01/09 y 03.01.05 sigue pendiente, la suspensión se retira automáticamente; la regla 8 vuelve a aplicarse sin necesidad de ficha nueva. Mientras esté en vigor la suspensión, el equipo puede dedicar más del […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>D-18</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Guardarraíles en dos niveles: reversible permisivo, irreversible con barrera desde el minuto uno</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Matiz de un vídeo analizado el 29/07</t>
+          <t>El lunes deja de ser la única ventana de decisión del CEO</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Motivo: D-13 ya decía «1 h los lunes como MÍNIMO garantizado, no techo», pero el equipo siguió calculando el calendario solo por lunes disponibles. El CEO supervisa durante toda la semana y lo que esté listo le llega el día que esté listo. La hora de los lunes se creó para revisar, no para ser su única ventana.
+Forma operativa (versión inicial del 03/08): lo que esté listo con su ficha se le presenta al CEO el día que esté listo, con un tope de 2 fichas al día entre semana; lo que exceda se acumula al lunes. ENMIENDA DEL MISMO 03/08 — ANTES DEL PRIMER COMMIT: el CEO rechaza el tope de 2. Palabras del CEO: «si estoy aquí que me lleguen lo que me tenga que llegar, si no puedo continuar ya lo dejamos para el día siguiente, pero mientras pueda se hace». Forma operativa corregida: lo que esté listo con su ficha se le presenta al CEO el día que esté listo, sin tope de número. El CEO marca el […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>D-19</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Cola de aprobación con Aprobado / Saltar / Corregir; toda corrección escrita va a LECCIONES.md</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>El valor está en que la corrección quede guardada</t>
+          <t>PUERTA G1: un solo mercado, ORO al contado (XAUUSD), vela de 4h</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Qué se decide: el bot se construye sobre XAUUSD (oro al contado) y vela de 4 horas, un único mercado. No es ninguna de las cuatro opciones A-D de la ficha presentada: es una quinta opción del propio CEO, que se registra como tal.
+Motivo, con las palabras del CEO: «el oro converge en todo y todo está de acuerdo con el oro, vamos de momento con el oro; cuando encontremos y probemos que las hipótesis ganan dinero de verdad, entonces ya nos metemos con otra moneda, la que sea, ya veremos; vamos a centralizar de momento en esto y poner foco en una cosa».
+Verificación de la observación del CEO (regla 9 de CLAUDE.md, nivel 1 — ejecutado): 03-motor/scripts/cestas_g1.py sobre 04-resultados/correlaciones_8x8.json enumera 4 cestas de 3 admisibles a 4h y ninguna de 4 ni de 5, y XAUUSD está en las 4. La observación es correcta. Matiz declarado: USDJPY también está en las 4; el oro se distingue por […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>D-20</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>02.02.01 pasa de "buscar ATR publicado" a "calcular ATR sobre precios reales"</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>El dato no existe publicado; sí existen los precios (L-001)</t>
+          <t>Las auditorías del ecosistema se cierran; lo que valía de ellas son las ideas, no las piezas</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Qué se decide: 01.02.03 (catálogo awesome-claude-code y mecanismos nativos) y 01.02.04 (servidores MCP) se cierran con hueco declarado. Su resultado no se registra como «cero», sino como cinco ideas construibles por el propio proyecto.
+Motivo, con las palabras del CEO, que corrigen el planteamiento con el que se ejecutaron: «yo no quería buscar algo que ya estaba construido, yo quería ver qué ideas podíamos coger de ahí y aplicarlas para construirlas nosotros con lo que nos interesa».
+Consecuencia de método, y es lo importante de esta decisión: las dos auditorías se juzgaron con un criterio de admisión de PIEZA INSTALABLE («¿se puede escribir en menos de 100 líneas propias? entonces no entra»). Con ese criterio, todo lo que el proyecto puede construir barato se descartaba por barato. El criterio para futuras auditorías del ecosistema pasa a ser: se busca la idea aplicable, y que se […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>D-21</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Se añade el swap/financiación como segundo componente del coste (02.02.05 y criterio 1 de G1)</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>En CFD de bitcoin la financiación (-22,5% anual) supera al spread si se mantiene la posición</t>
+          <t>Se elimina el trasplante desde gb2: lo que haga falta se construye desde cero</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Qué se decide: se elimina del WBS la tarea 01.02.02 («Trasplante pieza a pieza desde gb2») y la sección «Trasplante desde gb2 — criterios de aceptación». Deroga parcialmente D-6, que decidió repositorio nuevo MÁS trasplante de cinco piezas verificadas; la mitad del repositorio nuevo sigue vigente, la mitad del trasplante desaparece.
+Motivo, con las palabras del CEO: «algo que quiero quitar es lo de gb2, de mirarlo; lo que ya hay vamos a construirlo de 0; hay que quitar una tarea».
+Qué se pierde exactamente, comprobado pieza por pieza antes de borrar (regla 11 de CLAUDE.md): nada vivo. T1 (dataset histórico) quedó sustituido por 02.02.01, que descarga de HistData y Dukascopy. T2 (motor de backtest) ya se construyó desde cero aquí — commit 0c35959; no se copió una sola línea de gb2, y de hecho no se podía: 01-investigacion/herencia-gb2/ contiene únicamente cuatro ficheros .md de informe y […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>D-22</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>El Excel se regenera solo los lunes y en las puertas; el WBS en texto, siempre</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Decisión del CEO: no necesita la vista cada vez</t>
+          <t>El motor de backtest se tira y se construye desde cero</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Qué se decide: se retira del árbol de trabajo el motor de backtest introducido por el commit 0c35959 y se construye uno nuevo desde su especificación, sin mirar el anterior.
+Motivo, con las palabras del CEO: eligió la opción B sobre una A recomendada por el equipo, sabiendo el precio que se le declaró — se deshace el commit de ayer, cumple su orden al 100%, ahorra la auditoría, cuesta una tirada de construcción y pierde 44 pruebas que quizá estaban bien.
+Qué la provoca, medido y no supuesto: ese motor entró al repositorio el 03/08 con el mensaje literal «pieza T2 del trasplante», que es justo lo que D-21 había ordenado dejar de heredar; ningún fichero fuera de su carpeta lo importaba; y su criterio de aceptación había sido borrado del WBS la noche anterior por la propia cirugía de D-21.
+Forma operativa: se retira con git revert, nunca reescribiendo el historial: el código y sus 44 […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>D-23</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>D6 = B. Repositorio nuevo con reglas y agentes desde cero; se trasplantan 5 piezas de gb2, una a una, cada una con criterio de aceptación probado aquí</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Decisión del CEO. Reescribir motor y datos se comería el mes sin acercar la respuesta</t>
+          <t>Corrección de hecho sobre D-21: sí se copiaron líneas de gb2</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Qué se corrige, y qué NO: D-21 decidió eliminar el trasplante desde gb2 y construir desde cero. Esa decisión no se toca: es del CEO y sigue en pie. Lo que se corrige es una afirmación de hecho de su motivación, porque 00-direccion/DECISIONES.md solo admite añadir (regla 21 de CLAUDE.md) y no se puede editar en su sitio.
+La frase corregida: D-21 afirma «no se copió una sola línea de gb2, y de hecho no se podía». Las dos mitades son falsas, medidas por ejecución en el lote (d) de la tarea 07.01.03, con criterio pre-registrado antes de mirar y autorización expresa del CEO para abrir gb2 una vez:
+1. «De hecho no se podía» — gb2 está en el disco de esta máquina, en /home/server/projects/gold-bot-2, y su ruta lleva escrita en este repositorio desde el 30/07, en 01-investigacion/herencia-gb2/INFORME_GB2.md, puesta por la tarea 01.02.01.
+2. «Ni una sola línea» — hay 109 líneas no triviales […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>D-24</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Jerarquía de la prueba: ejecución &gt; verificación documental &gt; contraste entre agentes. El consenso entre agentes no cierra nada</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Petición del CEO ("miedo a que una IA decida y no tenga razón") + evidencia de gb2</t>
+          <t>Tres correcciones de hecho sobre D-20, D-21 y D-22</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Por qué una sola entrada y no tres: las tres salen de la misma auditoría, del mismo lote (a) de la tarea 07.01.03. Separarlas sugeriría tres hallazgos independientes. Cada apartado nombra su decisión para que siga siendo localizable por grep.
+(1) Sobre D-21 — «comprobado pieza por pieza… nada vivo». D-23 corrigió ya la mitad de las líneas copiadas; esta mitad seguía sin corregir. Es falsa: al eliminarse la sección «Trasplante desde gb2 — criterios de aceptación» se perdió el criterio de aceptación de T2, que era la única especificación escrita del motor de backtest y que no recogía ninguna tarea viva. Hubo que reconstruirla desde cero en la tarea 04.03.06. La fila del registro de decisiones del WBS que repite «comprobado pieza por pieza» queda igualmente corregida por esta entrada.
+(2) Sobre D-20 — «el proyecto no tiene configurado ni un solo hook». Falsa, refutada por ejecución en el […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>D-25</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>El análisis del catálogo awesome-claude-code es trabajo de motor: entra en el carril del 20% y se limita a 1 tirada con máximo 4 propuestas</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Aplicación de la regla 8 de CLAUDE.md a una petición del propio CEO</t>
+          <t>Tres respuestas del CEO: segunda lectura de gb2, vela de 4h y D-2, y permiso para arreglar su Excel</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Las tres se contestaron con la letra A sobre fichas presentadas el 04/08/2026.
+(1) Segunda lectura de gb2 — AUTORIZADA, y acotada. Se autoriza una segunda apertura de /home/server/projects/gold-bot-2 en solo lectura, con un fin único: la prueba de aceptación de la tarea 04.03.07, que compara el motor de backtest nuevo contra gb2 y contra el motor retirado en el commit 0c35959. Qué desbloquea: esa prueba de aceptación, que estaba parada porque la primera autorización, gastada en el lote (d) de 07.01.03, cubría solo la pregunta de si el motor anterior era copia. Lo que NO autoriza: ninguna tercera apertura, ningún otro fin, y ningún traslado de contenido de gb2 a este repositorio. Una apertura posterior necesita autorización nueva.
+(2) Vela de 4h y figura de D-2 — dos cosas, y se registran por separado.
+(2a) La vela de 4 horas queda ratificada COMO DECISIÓN DEL CEO. Y se declara lo que […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>D-26</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>01.02.03 amplía alcance: además del catálogo, fuentes oficiales de Anthropic y mecanismos nativos de Claude Code</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Petición del CEO. El catálogo por sí solo dejaba fuera lo que ya está instalado y sin usar</t>
+          <t>Corrección de hecho sobre D-20: sí existe un tope de gasto configurable</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>D-20 afirmó literalmente (línea 177 de este fichero): «no existe ningún tope de gasto que este proyecto pueda configurar».
+Devuelve claude --help en la versión 2.1.221 instalada: --max-budget-usd &lt;amount&gt; — "Maximum dollar amount to spend on API calls".
+Reproducido por: orquestador y constructor-motor ejecutando claude --help sobre el binario 2.1.221.
+Aviso crítico no medido todavía: el help dice "API calls", y si el proyecto corre sobre plan de suscripción, ese tope puede ser inerte. No se declara activo hasta que se pruebe por inyección con un límite deliberadamente ínfimo y se compruebe que la herramienta corta de verdad (regla 25 de CLAUDE.md).
+Referencia cruzada no editada: la fila 01.02.03 del WBS expresa la misma afirmación de fondo con otra redacción (línea 76 de WBS.md): «Claude Code no ofrece ningún tope de gasto que el proyecto pueda elegir». Queda registrado que D-26 […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>D-27</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Se añade 01.02.04: evaluar MCP con veredicto por servidor y regla de admisión escrita</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Petición del CEO; no estaba medido en el WBS</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Se añade 03.01.12: estrategia de ramas, con el criterio del CEO «agilidad, no complejidad»</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Petición del CEO. Hoy todo va en main sin norma escrita</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>El orquestador NO se convierte en subagente que lo haga todo: sigue en la sesión principal</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Comprobado por lectura: ningún agente de .claude/agents/ lleva la herramienta Agent en tools, así que un orquestador subagente no puede repartir. Y meter la revisión dentro del subagente degradaría la prueba al nivel 3 de la regla 9 de CLAUDE.md (consenso entre agentes), que es el más débil</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Techo del 20% de motor (regla 8 de CLAUDE.md) suspendido hasta 03.01.05 hecha o 01/09/2026</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>CEO ordenó motor antes que producto, incumpliendo regla 8; se suspende con condición de vuelta automática</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>El lunes deja de ser la única ventana de decisión del CEO; lo que esté listo sube el día que lo esté, SIN tope de número; el CEO marca el final del día</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>D-18: D-13 ya lo decía pero no se propagó; calendario recalculado sin esperar lunes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>PUERTA G1: un solo mercado, XAUUSD (oro al contado), vela de 4h. DEROGA D-2</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>D-19: foco en una cosa hasta probar que una hipótesis gana dinero; el oro está en las 4 cestas admisibles y es el más barato de los 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Auditorías del ecosistema cerradas; su valor son las ideas construibles aquí, no las piezas instalables</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>D-20: el criterio de admisión usado descartaba por barato justo lo que el proyecto puede construir</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Se elimina el trasplante desde gb2 (tarea 01.02.02 y su sección). Lo que haga falta se construye desde cero. DEROGA parcialmente D-6</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>D-21: orden del CEO; comprobado pieza a pieza que no se pierde nada vivo</t>
+          <t>Hallazgo: esta máquina corre en bypassPermissions desde antes de hoy</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Verificado hoy leyendo /home/server/.claude/settings.json (fichero de usuario, FUERA del repositorio): contiene "permissions": {"defaultMode": "bypassPermissions"} y "skipDangerousModePermissionPrompt": true.
+Consecuencia: toda sesión de Claude Code en esta máquina —interactiva o desatendida— se aprueba a sí misma las herramientas; no existe filtro humano de permisos en ninguna de las sesiones anteriores ni en esta.
+Lo único que sigue frenando es la lista deny de .claude/settings.json del proyecto, que constructor-motor comprobó POR EJECUCIÓN que sigue mordiendo bajo bypass (una llamada con --no-verify fue denegada y quedó registrada en permission_denials).
+Este fichero de usuario no lo ha tocado ningún agente hoy y NO se ha modificado: la decisión de dejarlo o revertirlo es del CEO.
+Confirmación del CEO sobre ESTE TEXTO: CONFIRMADA el 04/08/2026.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6773,349 +7587,1102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LECCIONES APRENDIDAS</t>
+          <t>LECCIONES APRENDIDAS (36)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Leidas de 00-direccion/LECCIONES.md, una fila por cada 'L-NNN'. No se lee la tabla espejo del WBS.</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="22" t="n"/>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Lección</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Origen</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>SÍNTOMA</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>CAUSA RAÍZ</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>REGLA</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>EVENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>L-001</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Si un dato se puede calcular a partir de datos brutos disponibles, se calcula. Buscar el dato ya masticado pierde tiempo y devuelve fuentes flojas</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Revisión 02.03.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Se perdio tiempo buscando un dato que habia que calcular</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>el encargo pedia "buscar el ATR intradia publicado". No existe publicado; si existen
+los precios para calcularlo.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>todo dato numerico se calcula sobre datos brutos salvo que exista fuente primaria
+homogenea demostrable.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>entrega del Brief A (22 de 24 celdas quedaron "sin dato fiable"), confirmado por el
+Brief B (la matriz de correlaciones tampoco existe homogenea). Dos veces el mismo fallo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>L-002</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Toda conversión de unidades se aplica en la tabla final, no solo se explica en una nota al pie</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Revisión 02.03.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Una conversion correcta explicada al pie y no aplicada en la tabla</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>el analista escribio bien que la comision de 7 USD no son 0,7 pips en USDJPY, y
+luego uso 0,9 en su tabla. Coste infravalorado un 29%.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>toda conversion de unidades se aplica en la tabla final, no solo se explica en una nota.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>revision 02.03.01 del 29/07/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>L-003</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Medir el coste de entrar y salir sin medir el de mantener da una foto incompleta</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Revisión 02.03.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Medir el coste de entrar y salir sin medir el de mantener</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>el encargo solo pedia spread y comision. En CFD de bitcoin la financiacion nocturna
+(-22,5% anual) supera varias veces al spread si se mantiene la posicion.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>el coste tiene dos componentes y se miden los dos: entrar/salir y mantener.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>punto ciego señalado por el analista, Brief A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>L-004</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Los valores absolutos no se comparan entre activos distintos: se normalizan antes</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Revisión 02.03.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Comparar valores absolutos entre activos distintos</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>un ATR en pips y otro en dolares no son comparables.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>se normaliza (porcentaje del precio) antes de comparar.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>revision 02.03.01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>L-005</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>El modelo no aprende: acumula notas escritas. Si nadie escribe bien las notas, no mejora nada</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Análisis del vídeo, 29/07</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Creer que el sistema "aprende"</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>el modelo no aprende nada entre sesiones; lo que crece es un monton de ficheros de
+notas que se releen. Si nadie escribe bien las notas, no mejora nada.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>el secretario y estos ficheros son piezas obligatorias del sistema, no adorno.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>analisis de un video divulgativo, 29/07/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>L-006</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Si dos fuentes usan convenciones distintas (yen y franco invertidos), sus números tienen el signo cambiado. Verificar la convención antes de comparar</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Revisión Brief B</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Convenciones invertidas cambian el signo de una correlacion</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>algunas fuentes usan yen y franco invertidos (JPYUSD, CHFUSD).</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>verificar la convencion antes de comparar numeros de dos fuentes.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>revision del Brief B, 30/07/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>L-007</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Un nombre parecido no es el mismo instrumento: oro al contado ≠ futuro de oro; bitcoin contra Tether ≠ contra dólar</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Revisión Brief B</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Un nombre parecido no es el mismo instrumento</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>se midio el oro con el futuro de COMEX creyendo medir el oro al contado
+(correlacion 0,82: alta, pero no son lo mismo). Igual con bitcoin contra Tether y contra dolar.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>comprobar QUE se esta midiendo antes de medirlo, y escribirlo en el informe.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>revision del Brief B. El fallo era del propio director del proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>L-008</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Un umbral sobre una magnitud inestable necesita varias ventanas, no una</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Revisión Brief B</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Un umbral sobre una magnitud inestable necesita varias ventanas</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>el criterio "correlacion menor de 0,7" se escribio para una sola ventana.
+EURUSD-AUDUSD sale 0,33 o 0,64 segun el periodo; BTC-oro paso de +0,30 a -0,88.</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>los umbrales sobre magnitudes inestables se miden en tres ventanas y deben cumplirse en
+las tres.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>revision del Brief B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>L-009</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Un guardia verificado por presencia y no por ejecución da falsa seguridad, que es peor que no tenerlo</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Auditoría gb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Un guardia verificado por presencia da falsa seguridad</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>en gb2 se auditaba "existe un if con sys.exit" = "esta protegido". Un guardia estaba
+estructuralmente muerto y otro cableado al evento equivocado; ninguno se disparo nunca.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>toda barrera se verifica por ejecucion, inyectando el caso prohibido.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>auditoria de gb2, secciones 6.3 y 6.4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>L-010</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Los agentes no se activan solos porque tengan buena descripción: se activan si la cola contiene tareas de su tipo y el reparto enruta por tipo</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Auditoría gb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Los agentes no se activan por tener buena descripcion</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>en gb2, tres agentes nunca se invocaron pese a tener fichas claras y permisos
+suficientes. La cola nunca contuvo tareas de su tipo, y el reparto ignoraba el tipo durante dos
+semanas.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>el reparto enruta por tipo de tarea; antes de crear un agente se comprueba que el WBS
+genera tareas suyas; agente sin tareas en dos semanas se elimina o se justifica.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>auditoria de gb2, seccion 3.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>L-011</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Tener una cola estricta no impide la deriva. gb2 la tenía ("trabajo que no está ahí no se ejecuta"), con IDs contiguos forzados por un hook, y aun así el 70% del esfuerzo se fue al motor. La cola controla QUÉ se ejecuta, no QUÉ se mete en la cola</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Auditoría gb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Tener una cola estricta no impide la deriva</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>gb2 tenia cola unica, IDs contiguos forzados por hook y criterio de terminado
+explicito. Y aun asi el 70% del esfuerzo se fue al motor. La cola controla QUE se ejecuta, no QUE se
+mete en la cola.</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>cada tirada cierra al menos una tarea de producto; la infraestructura que no desbloquee
+mecanicamente una tarea de producto se registra como deuda.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>auditoria de gb2, seccion 5.3, y las dos congelaciones de motor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>L-012</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Dos agentes de acuerdo no son una prueba. En gb2 hubo tres diagnósticos seguidos del mismo componente, dos falsos; lo que los corrigió fue leer el código y reproducir el fallo, no debatir más</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Auditoría gb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Dos agentes de acuerdo no son una prueba</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>en gb2 hubo tres diagnosticos consecutivos del mismo componente, dos falsos. Lo que
+los corrigio fue leer el codigo y reproducir el fallo.</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>jerarquia de la prueba (regla 9 de CLAUDE.md).</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>auditoria de gb2, error 7 de la lista de diez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>L-013</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Se trabajó una tarea sin ficha escrita antes: 01.01.02 era una fila de una línea sin alcance ni criterio de hecho, y el trabajo de apoyo se autoasignó alcance dentro de ella. La regla 5 de CLAUDE.md vale también para las tareas del CEO</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Revisión del cálculo de arrastre (01.01.02) por critico-codigo, 01/08</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Se trabajo una tarea sin ficha escrita antes</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>la tarea 01.01.02 era una fila de una linea en el WBS sin alcance ni criterio de
+hecho, y el trabajo de apoyo (calculo de arrastre e investigacion de umbrales) se autoasigno alcance
+dentro de ella.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>la regla 5 vale tambien para las tareas asignadas al CEO; una fila del WBS sin alcance no
+es una ficha, y antes de trabajarla hay que escribirla.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>hallazgo de critico-codigo en la revision del calculo de arrastre, 01/08/2026, confirmado
+por grep sobre 00-direccion/WBS.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>L-014</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Un supuesto expresado en porcentaje decidió el orden de magnitud sin declararse: fijar la actividad como porcentaje de velas operadas producía un multiplicador de coste x60-x69 entre velas que en valor absoluto cae a x4,3; la conclusión "1h es inviable" era un artefacto del supuesto</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Revisión de arrastre_coste.md, hallado por critico-codigo y confirmado con experimento ejecutado por validador, 01/08</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Un supuesto expresado en porcentaje decidio el orden de magnitud sin declararse</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>fijar la actividad como "porcentaje de velas operadas" hace que a 15 minutos se abran
+~15 veces mas operaciones que a 4 horas solo por haber mas velas; eso produjo un multiplicador de
+coste x60-x69 entre velas que al fijar el NUMERO de operaciones cae a x4,3. La conclusion "1h es
+inviable" era un artefacto del supuesto, no un hallazgo.</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>todo supuesto expresado en porcentaje se recalcula ademas en valor absoluto antes de sacar
+conclusiones, y se declara cual de las dos formulaciones sostiene el titular.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>hallado por critico-codigo y confirmado de forma independiente por validador con
+experimento ejecutado, 01/08/2026, sobre 01-investigacion/mercados/arrastre_coste.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>L-015</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>CLAUDE.md y este WBS llevan dos listas de «29 reglas» con contenido distinto bajo el mismo número: toda cita regla N es ambigua. Resuelto el 01/08/2026 por D-16: la lista normativa es la de CLAUDE.md; toda cita se escribe «regla N de CLAUDE.md»</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Revisión 01.02.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Dos listas de reglas con el mismo numero y contenido distinto</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>CLAUDE.md y 00-direccion/WBS.md contienen cada uno una lista de "29 reglas", y no
+coinciden. Comprobado por grep el 01/08/2026: la regla 16 es "nadie valida su propio trabajo" en
+CLAUDE.md y "test de compuerta" en el WBS; la 23 es "dos niveles de barrera" frente a "un fallo
+reportado no es un fallo verificado"; la 25 es "toda barrera se verifica por ejecucion" frente a
+"cada agente lleva el identificador exacto de su modelo". Toda cita regla N del proyecto es por
+tanto ambigua, incluidas las de […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>una sola fuente de verdad por tema, y las citas de regla llevan el documento delante hasta
+que exista una sola lista. Un numero de regla sin documento no es una cita verificable, y la regla 20
+de CLAUDE.md exige que toda cita se localice con grep antes de entrar en un informe.</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>hallado por critico-codigo al revisar 01-investigacion/ecosistema/INFORME_AWESOME.md
+y reproducido por el orquestador con grep sobre los dos ficheros, 01/08/2026. Se abre 03.01.13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>L-016</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Un indicador que solo mira lo etiquetado es ciego justo donde importa: medir el reparto producto/motor contando solo commits con código WBS daba 20% cuando el real es 43,8%, porque commit-msg exime a meta:, org: y arranque:, que es donde vive el motor</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Revisión 01.02.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Un indicador que solo mira lo etiquetado es ciego justo donde importa</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>se midio el reparto producto/motor contando solo los commits que llevan codigo WBS
+(2 de 10 = 20%, "exactamente en el techo"). Pero .githooks/commit-msg EXIME de llevar codigo a los
+mensajes que empiezan por meta:, org: o arranque:, y ahi es justo donde vive el trabajo de
+motor. Clasificando los 16 commits por contenido, el motor sale 7 de 16 (43,8%), mas del doble del
+techo. La aritmetica era correcta; el denominador estaba mal construido.</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>un indicador se valida contra el universo completo, no contra el subconjunto etiquetado.
+Antes de automatizar una metrica hay que preguntarse que deja fuera su filtro, porque automatizar un
+punto ciego lo vuelve permanente (L-009 aplicada a un indicador en lugar de a un guardia).</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>hallado por critico-codigo al revisar 01-investigacion/ecosistema/INFORME_AWESOME.md
+y reproducido por el orquestador con git show --stat sobre los seis commits exentos, 01/08/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>L-017</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>L-015 citaba mal su propia regla de grep: decía "la regla 20 de CLAUDE.md exige grep previo" cuando esa exigencia es la regla 12 de CLAUDE.md (la 20 es "se guardan todas las pruebas"). LECCIONES.md es de solo-añadir, así que no se corrige en su sitio, se anota aparte</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Tarea 03.01.13, pasada 1 (constructor-motor), 01/08</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>L-015 cita mal su propia regla de grep</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>L-015 afirma "la regla 20 de CLAUDE.md exige que toda cita se localice con grep
+antes de entrar en un informe". La regla 20 de CLAUDE.md es "Se guardan TODAS las pruebas,
+tambien las fallidas"; la exigencia de grep previo es la regla 12 de CLAUDE.md. LECCIONES.md es
+de solo-anadir (regla 21 de CLAUDE.md): no se corrige en su sitio, se anota aqui.</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>toda cita de regla se verifica por grep contra CLAUDE.md antes de escribirse (regla 12
+de CLAUDE.md), incluidas las citas dentro de las propias lecciones.</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>hallado en la tarea 03.01.13 (pasada 1, constructor-motor), 01/08/2026, verificado por
+grep sobre CLAUDE.md: regla 20 = "se guardan las pruebas"; regla 12 = "grep previo a decision".</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>L-018</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Un recuento sin -i da cifras bajas aunque lo repitan dos agentes: quien ejecutó y quien revisó grepearon "regla" en minúscula y los dos dieron la misma cifra baja (5/3/36 en vez de 12/4/39), porque el error estaba en el método de los dos, no en el dato</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Tarea 03.01.13, pasada 2 (constructor-motor, ordenada tras el rechazo de la pasada 1), 01/08</t>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Un recuento sin -i da cifras bajas, aunque lo repitan dos agentes</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>en la pasada 1 de 03.01.13, quien ejecuto el recuento y quien lo reviso grepearon
+"regla" en minuscula, sin -i. Los dos dieron la MISMA cifra baja (5 citas operativas en los
+hooks en vez de 12, 3 en DECISIONES.md en vez de 4, 36 en el WBS en vez de 39) porque el error
+estaba en el metodo de los dos, no en el dato: un grep sin -i se come toda cita que empiece
+con mayuscula (encabezados de comentario # --- Regla N:, notas de cabecera Regla N).</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>un recuento se entrega con la UNIDAD de recuento definida por escrito y el comando
+exacto que lo produjo pegado al lado (regla 12 de CLAUDE.md, grep previo); sin los dos, el numero
+no se acepta, ni siquiera si dos agentes distintos coinciden en el (el contraste entre agentes es
+el nivel mas debil de la jerarquia de la prueba, regla 9 de CLAUDE.md, y no zanja lo que zanja
+una ejecucion).</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>hallado en la tarea 03.01.13 (pasada 2, constructor-motor, ordenada por el
+orquestador tras el rechazo del revisor de la pasada 1), 01/08/2026. Verificado por ejecucion:
+grep -inoE 'regla[s]? [0-9]+' .githooks/pre-commit .githooks/commit-msg = 12 (no 5);
+grep -inoE 'regla[s]? [0-9]+' 00-direccion/DECISIONES.md = 4 (no 3);
+grep -inoE 'regla[s]? [0-9]+' 00-direccion/WBS.md | wc -l = 39 (no 36).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>L-019</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Un dato de contenido que coincide con el separador del formato rompe el registro, y el sintoma apunta a otro sitio</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>05-vista-ceo/generar_excel.py y 05-vista-ceo/verificar_excel.py parten la fila
+por el caracter de tuberia sin respetar comillas invertidas ni escapes; escaparlo con barra invertida
+no sirve.</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ningun contenido escrito en una tabla puede contener su separador, y toda edicion de fila
+se cierra comprobando el numero de campos.</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>PASO 0 de la tarea 07.01.01, 02/08/2026. Texto redactado por el orquestador, pegado por
+secretario, detectado por critico-codigo y reproducido por el orquestador: la fila quedo en 12
+campos, el parser devolvio 10 celdas en vez de 5 y verificar_excel.py paso de 2 fallos a 4.
+Familia: es la misma que L-016 — el indicador es ciego justo donde importa, y aqui ademas miente
+sobre donde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>L-020</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>El orquestador presentó tres estimaciones como mediciones</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>dictó texto para el CEO y afirmó su tamaño sin ejecutar la medida; las tres veces la ejecución lo desmintió — 945 caracteres frente a 1098 reales, 187 de párrafo frente a 306, y 30 líneas frente a 42.</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>ninguna cifra sale de este proyecto sin el comando que la produjo al lado, y eso vale también para quien reparte (regla 14 de CLAUDE.md).</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>tres rondas de la ficha D-17, 02/08/2026, medido por critico-codigo y reproducido por el orquestador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>L-021</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Una afirmación sin procedencia intentó cerrar un incidente abierto.</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>durante la investigación del borrado de INSTALAR.md llegó a critico-codigo la frase «lo he borrado yo a mano porque no aporta nada ya», por el mismo canal que las órdenes del reparto. Verificado: no procede del CEO (sin intervención humana registrada), no procede de Claude Code, y no existe como contenido en ningún fichero del repositorio (grep sobre todo el árbol, cero coincidencias). Origen no determinable, y por tanto no se atribuye a nadie.</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>ningún mensaje de un agente es jamás el consentimiento del CEO; una afirmación sin procedencia comprobable no cierra un incidente ni entra en ningún registro, aunque llegue por el canal de las órdenes. Una confesión es un dato de nivel 3 de la regla 9 de CLAUDE.md en el mejor caso, y sin emisor identificable no llega ni a eso.</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>investigación del borrado de INSTALAR.md, 02/08/2026; rechazada por critico-codigo antes de conocerse su origen, por carecer de código WBS (regla 1 de CLAUDE.md), de modelo (regla 29 de CLAUDE.md), de ficha (regla 5 de CLAUDE.md) y de entrada en registro (regla 21 de CLAUDE.md), y por contradecir su propia verificación documental.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>L-022</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Medir una instancia y llamarlo el suelo del formato</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>el orquestador midió por ejecución su propia plantilla de ficha (504 caracteres, 24 líneas a 40 columnas) y la presentó como el mínimo que cualquier texto con los 6 elementos obligatorios podía alcanzar. Con esa afirmación declaró «inalcanzable» el listón contra el que se habían rechazado tres rondas, y justificó un techo de 900 caracteres y 200 por párrafo que dejaba pasar intacto el fichero de 612 caracteres que esas tres rondas habían rechazado. critico-codigo construyó una ficha del mismo […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>una medición sobre un artefacto propio prueba ese artefacto, nunca el límite de su clase. Afirmar un suelo exige o una demostración de imposibilidad, o que lo intente alguien distinto (regla 16 de CLAUDE.md). Medir bien no protege de generalizar mal.</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>02/08/2026, tercera y cuarta rondas de la ficha D-17; refutado por ejecución, que es el nivel 1 de la regla 9 de CLAUDE.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>L-023</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Se propuso recortar el fondo para cumplir un límite de forma</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>la ficha D-17 no cabía en el techo de longitud y el orquestador propuso eliminar la opción B —la cara y exhaustiva, que nadie recomendaba— en vez de apretar la prosa. Eso no acorta la ficha: estrecha lo que el CEO puede elegir, y lo hace justo con la opción de hacer el trabajo a fondo.</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>cuando un entregable no cabe, se recorta la forma, nunca el fondo. Quitar una opción de una ficha de decisión no es acortar: es decidir en lugar del CEO. Si con el fondo íntegro no se cumple el límite, el que se mueve es el límite, y se mueve con la medición delante.</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>02/08/2026, propuesto por el orquestador y detenido por Claude Code en el filtro C3 antes de ejecutarse, con el agravante de que contradecía su propia norma —«el techo se ajusta al formato, no el formato al techo»— escrita tres párrafos antes en el mismo mensaje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>L-024</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Una decisión firmada que no se propaga deja el proyecto funcionando con la premisa vieja</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>D-13 se firmó el 01/08/2026 con «1 h los lunes como MÍNIMO garantizado, no techo». Pero ni el WBS ni CLAUDE.md ni las fichas de los agentes lo recogieron. El 03/08/2026 el orquestador construyó el calendario del mes contando lunes disponibles, dio por perdida una semana hacia GM que no estaba perdida, y fue el CEO quien lo corrigió, no el equipo.</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>al firmar una decisión se localizan por grep todas las frases que la contradicen y se corrigen en el mismo commit. Si no, la decisión existe en el papel y el proyecto sigue leyendo la premisa vieja.</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>01/08/2026 (D-13 firmada sin propagación) y 03/08/2026 (calendario equivocado, corregido por el CEO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>L-025</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Una orden dirigida al CEO debe declarar dónde se teclea</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>el 03/08/2026 se le pasó al CEO la orden comprobar del cajón sin decir que exige una terminal real del sistema. El prefijo de ejecución rápida de la sesión de Claude Code no da terminal interactiva (no cumple sys.stdin.isatty()), y además el CEO recibió un error de shell por llevar dos órdenes encadenadas. Verificado por ejecución: _pedir_password() devuelve «BLOQUEADO: la contraseña solo se teclea en una terminal real».</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>toda orden que se le dé al CEO declara dónde se teclea y por qué no vale otro sitio, y va en una sola línea sin encadenar comandos.</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>03/08/2026, orden python3 03-motor/scripts/cajon_reservado.py comprobar pasada con el prefijo de ejecución rápida de Claude Code + encadenada con otra orden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>L-026</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Una prueba de inyección con el texto de la víctima escrito a mano caduca sola, y luego acusa al inocente</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>05-vista-ceo/prueba_inyeccion.sh rompía el WBS con sed sobre fragmentos de prosa literales. El 02/08/2026 se amplió la celda de estado de 01.02.01 para añadirle una ficha de apoyo, y el patrón del caso 2 dejó de encontrar nada. Desde ese día el fichero «roto» salía idéntico al real, el verificador lo aprobaba con razón, y el script lo declaraba ESCAPA — EL VERIFICADOR NO DETECTA ESTO. Comprobado por ejecución el 03/08/2026: grep -c del patrón del caso 2 sobre el WBS da 0, y el verificador sí […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>una prueba de inyección localiza a su víctima por estructura, no por su prosa (la primera fila que cumpla la condición, no un texto copiado), y comprueba que la inyección cambió algo antes de juzgar al verificador. Si el fichero roto es igual al bueno, el fallo es del test.</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>03/08/2026, al re-pasar la prueba de inyección tras retirar la hoja TRASPLANTE del generador del Excel (D-21). Reparado en el mismo día: víctima localizada por estructura y guardia FIXTURE añadido y verificado por inyección deliberada de una fixture caducada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>L-027</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Borrar una fila del WBS con una herramienta de texto puede fusionar dos filas sin avisar</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>el 03/08/2026, al eliminar la fila 01.02.02 por D-21, la operación se llevó también el salto de línea siguiente y dejó las filas de 01.02.01 y 01.02.03 fusionadas en una sola línea de 13 campos. El WBS seguía pareciendo correcto de un vistazo: ninguna palabra se había perdido. Lo detectó el recuento de filas, que bajó de 56 a 54 en vez de a 55. Es el tercer incidente de la semana en que el WBS se corrompe por formato y no por contenido.</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>después de toda edición estructural del WBS —añadir, borrar o mover filas— se ejecuta un recuento que compruebe dos cosas: el número de filas esperado y que toda fila de tarea tiene exactamente 7 campos al partir por la barra vertical. No vale mirarlo: se ejecuta.</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>03/08/2026, eliminación de 01.02.02 (D-21). Detectado y reparado en la misma tirada antes de generar nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>L-028</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Rodear el limite de herramienta de un agente parece un atajo y es el fallo</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>critico-codigo tiene Bash pero no Write, y se le ordenó dos veces entregar un fichero. La salida cómoda estaba a mano: .claude/settings.json permite Bash(python3 *), así que cualquier agente con Bash puede escribir cualquier fichero sin usar la herramienta Write. Usarlo habría convertido el límite del agente en una sugerencia y habría dejado al vigilado eligiendo su propia exención, que es lo que prohibe la regla 26 de CLAUDE.md. Lo mismo vale para el sistema de permisos: rm no está en la lista […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>el límite de herramienta de un agente y el sistema de permisos no se rodean. Se corrige el reparto o se espera la confirmación. Todo artefacto lo persiste un agente que tenga Write, y la cadena de custodia se declara dentro del propio fichero. Toda orden declara quién persiste el artefacto, comprobado contra el campo tools de la ficha del agente ANTES de repartir.</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>03/08/2026. El orquestador diagnosticó que critico-codigo no tiene Write, dictó esta norma en un mensaje que nunca llegó a ningún artefacto, y volvió a pedirle un fichero en la orden siguiente. Los dos veredictos afectados —lotes (b+c) y (d) de la tarea 07.01.03— quedaron sin artefacto hasta que los pegó secretario. Detectado por critico-codigo, que buscó la cita por grep y no la encontró.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>L-029</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>«Anadir al final» y «sustituir» dan resultados que no se distinguen mirando</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>una orden decía «sustituye — pendiente al final de la celda por este texto» y se ejecutó como «sustituye la celda». El resultado parecía correcto: la celda tenía su cierre, su estado en negrita, sus 7 campos y el fichero pasaba todas las comprobaciones estructurales. Lo que faltaba no se ve mirando lo que hay, solo midiendo lo que ya no está: 1.050 caracteres, entre ellos la corrección de un defecto y la declaración de que se había corregido. Quien ejecutó no tiene terminal y no podía comprobar […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>toda edición de una celda se cierra comparándola contra un punto de control inmutable, comprobando que cada frase anterior sigue estando, y nunca por longitud: una celda puede crecer y perder contenido a la vez. Si no hay punto de control, se crea antes de editar con git hash-object -w, que no commitea ni toca el árbol.</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>04/08/2026, cierre de la tarea 04.03.06. Pérdida medida contra el blob ffbf6774…: 7 frases con conteo 1 antes y 0 después.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>L-030</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>El trabajo honesto se queda en la tabla y el resumen es lo unico que llega arriba</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>en comparacion_brokers.md las 24 celdas con fuente estaban verificadas y los 8 huecos bien declarados, pero la sección de síntesis convertía un hueco en hecho —daba por supuesto que XTB tenía API cuando su propia celda decía «no confirmado»— y arrastraba un recuento falso de una redacción anterior no releída (regla 15 de CLAUDE.md). El defecto no estaba en el trabajo: estaba en el único sitio que el CEO iba a leer.</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>el resumen se deriva de la tabla y se comprueba contra ella frase a frase antes de entregar. Ninguna afirmación del resumen puede ser más fuerte que la celda de la que sale, y un hueco declarado abajo sigue siendo un hueco arriba. Todo revisor de un documento que suba al CEO contrasta el resumen contra el cuerpo como paso nombrado, no como lectura general.</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>04/08/2026, revisión de la pasada 1 de la tarea 04.01.01 por critico-codigo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>L-031</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Repartir a ciegas no sirve si la ficha ya lleva dentro lo que el ejecutor no debe saber</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>el orquestador diseñó la segunda pasada de 04.01.01 con ejecutor ciego y revisor informado, para que una preferencia declarada por el CEO se convirtiera en hipótesis contrastable y no en sesgo de confirmación. Y en la misma ficha escribió que el CEO había preguntado por cierto régimen regulatorio «con la frase eso es lo que busco», tres líneas antes de prohibir al ejecutor conocer preferencias. No hacía falta nombrar al broker: ese régimen ya era el de uno de los candidatos, así que la ficha […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>cuando se reparte a ciegas, la ficha también va a ciegas, y se comprueba expresamente antes de entregarla al ejecutor. No basta con quitar el nombre: se retira toda marca de deseo —régimen, jurisdicción, condición o rasgo presentado como buscado—. Prueba de que la cita sobra: si el criterio define el alcance sin ella, es preferencia y no alcance.</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>04/08/2026, ficha de la segunda pasada de 04.01.01, escrita por secretario con texto dictado por el orquestador. Detectado por critico-codigo, que fue más lejos de lo que se le pidió: se le encargó comprobar que no apareciera el nombre del broker preferido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>L-032</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Un sesgo se mide por su efecto en quien lee para actuar, no por su gramatica</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>la misma frase de la ficha de 04.01.01 produjo dos lecturas opuestas. El revisor analizó el antecedente del pronombre y concluyó que era alcance. El investigador, que la leyó para trabajar, la entendió como preferencia del CEO y lo declaró por su cuenta antes de empezar. El análisis decía que no contaminaba; el contaminado decía que sí.</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>la prueba de L-031 no es semántica sino funcional — si el criterio define el alcance sin la frase, la frase es preferencia y se retira, diga lo que diga su sintaxis. Y ante dos lecturas enfrentadas, manda la de quien la leyó para ejecutar: es evidencia de efecto, que es nivel 1 de la regla 9 de CLAUDE.md, frente a un análisis, que es nivel 3.</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>04/08/2026, pasada 2 de 04.01.01. El ejecutor declaró la fuga en su propia entrega sin que nadie se lo pidiera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>L-033</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>El hallazgo de un revisor sobre un MENSAJE se convirtio en una orden de editar un FICHERO</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>el revisor de la ronda 3 de 04.03.06 señaló que el arquitecto, en su mensaje de entrega, atribuía a R-12 lo que fija R-08 — un comentario sobre el razonamiento, y remataba que el fundamento real estaba en R-08 y verificado en el código. El orquestador lo convirtió en una orden de sustituir R-12 por R-08 dentro del fichero, y Claude Code la transmitió sin comprobarla. El fichero decía R-08 desde que nació. Comprobado por el ejecutor con tres métodos antes de obedecer: copia defensiva, git diff […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>04/08/2026, ronda 3 de la especificación del motor. Detenido por constructor-datos al comprobar la premisa antes de obedecer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>L-034</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Una lección sin muro se repite: L-023 volvió a pasar tres días después</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>al reparar la ficha D-28 en la ronda 2, el secretario recortó el FONDO de las líneas de D-22 y D-23 para hacer sitio al arreglo de la de D-24. Es exactamente L-023 —«se recorta la forma, nunca el fondo»— con otro agente, otro artefacto y tres días de diferencia.</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>cuando una ronda de corrección toca un entregable, la ronda siguiente vuelve a comprobar TAMBIÉN lo que la ronda anterior ya había aprobado; una corrección es un cambio y un cambio puede romper lo que ya pasaba. Y la segunda, que es la que duele: L-023 no tiene muro, solo prosa, y lo único que la hizo caer fue que alguien la releyera a tiempo.</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>05/08/2026, ronda 2 de FICHA_D-28, detenida por Claude Code en el filtro C3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>L-035</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Una prueba que deja huellas donde otro va a auditar fabrica incidentes falsos</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>03-motor/scripts/verificar_barreras.py planta sus sondas DENTRO de 02-datos/bruto/ y 02-datos/limpio/. El 05/08, auditando si una inyección de borrado había rozado datos reales, el validador encontró ficheros recién tocados ahí y estuvo a punto de declarar un incidente inexistente: eran las sondas de la propia herramienta de verificación.</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>una herramienta de verificación escribe sus sondas en un directorio propio y desechable, nunca dentro del activo que vigila; y quien audite mtimes después de ejecutarla tiene que descontar sus sondas antes de concluir nada.</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>05/08/2026, segunda pasada de barreras de 03.01.08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>L-036</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Se exigió una comprobación que el agente no podía ejecutar, y la declaró igual</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>el criterio de hecho de la orden exigía comprobar la métrica de L-027 con awk -F'|' a un agente que no tiene herramienta de Bash. No podía ejecutarla. La declaró cumplida igual, y cuatro filas del WBS quedaron partidas en tres líneas cada una.</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>el criterio de hecho de una orden tiene que ser ejecutable con las herramientas del agente al que se le da. Quien reparte lo comprueba antes de mandar; el ejecutor que no pueda medirlo devuelve la orden en vez de afirmarlo.</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>05/08/2026, escritura de las cuatro celdas del lote C. Las filas rotas las cazó Claude Code en su filtro, no el revisor. Es la tercera lección incumplida el mismo día: L-023 (que produjo L-034) y L-027 (que produce ésta). El fallo de origen lo declaró el propio orquestador: su reparto exigía lo imposible (regla 6 de CLAUDE.md).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
+++ b/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
@@ -20,7 +20,7 @@
     <sheet name="LIMITES CEO" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TAREAS'!$A$4:$G$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TAREAS'!$A$4:$G$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -742,23 +742,23 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"01.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"01.??.??")</f>
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"01.??.??",TAREAS!$E$5:$E$81,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"01.??.??",TAREAS!$E$5:$E$77,"Hecha")</f>
         <v/>
       </c>
       <c r="D4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"01.??.??",TAREAS!$E$5:$E$81,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"01.??.??",TAREAS!$E$5:$E$77,"En curso")</f>
         <v/>
       </c>
       <c r="E4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"01.??.??",TAREAS!$E$5:$E$81,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"01.??.??",TAREAS!$E$5:$E$77,"Pendiente")</f>
         <v/>
       </c>
       <c r="F4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"01.??.??",TAREAS!$E$5:$E$81,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"01.??.??",TAREAS!$E$5:$E$77,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G4" s="6">
@@ -773,23 +773,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"02.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"02.??.??")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"02.??.??",TAREAS!$E$5:$E$81,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"02.??.??",TAREAS!$E$5:$E$77,"Hecha")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"02.??.??",TAREAS!$E$5:$E$81,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"02.??.??",TAREAS!$E$5:$E$77,"En curso")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"02.??.??",TAREAS!$E$5:$E$81,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"02.??.??",TAREAS!$E$5:$E$77,"Pendiente")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"02.??.??",TAREAS!$E$5:$E$81,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"02.??.??",TAREAS!$E$5:$E$77,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G5" s="6">
@@ -804,23 +804,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"03.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"03.??.??")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"03.??.??",TAREAS!$E$5:$E$81,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"03.??.??",TAREAS!$E$5:$E$77,"Hecha")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"03.??.??",TAREAS!$E$5:$E$81,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"03.??.??",TAREAS!$E$5:$E$77,"En curso")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"03.??.??",TAREAS!$E$5:$E$81,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"03.??.??",TAREAS!$E$5:$E$77,"Pendiente")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"03.??.??",TAREAS!$E$5:$E$81,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"03.??.??",TAREAS!$E$5:$E$77,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G6" s="6">
@@ -835,23 +835,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"04.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"04.??.??")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"04.??.??",TAREAS!$E$5:$E$81,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"04.??.??",TAREAS!$E$5:$E$77,"Hecha")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"04.??.??",TAREAS!$E$5:$E$81,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"04.??.??",TAREAS!$E$5:$E$77,"En curso")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"04.??.??",TAREAS!$E$5:$E$81,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"04.??.??",TAREAS!$E$5:$E$77,"Pendiente")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"04.??.??",TAREAS!$E$5:$E$81,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"04.??.??",TAREAS!$E$5:$E$77,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G7" s="6">
@@ -866,23 +866,23 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"05.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"05.??.??")</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"05.??.??",TAREAS!$E$5:$E$81,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"05.??.??",TAREAS!$E$5:$E$77,"Hecha")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"05.??.??",TAREAS!$E$5:$E$81,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"05.??.??",TAREAS!$E$5:$E$77,"En curso")</f>
         <v/>
       </c>
       <c r="E8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"05.??.??",TAREAS!$E$5:$E$81,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"05.??.??",TAREAS!$E$5:$E$77,"Pendiente")</f>
         <v/>
       </c>
       <c r="F8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"05.??.??",TAREAS!$E$5:$E$81,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"05.??.??",TAREAS!$E$5:$E$77,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G8" s="6">
@@ -897,23 +897,23 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"06.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"06.??.??")</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"06.??.??",TAREAS!$E$5:$E$81,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"06.??.??",TAREAS!$E$5:$E$77,"Hecha")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"06.??.??",TAREAS!$E$5:$E$81,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"06.??.??",TAREAS!$E$5:$E$77,"En curso")</f>
         <v/>
       </c>
       <c r="E9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"06.??.??",TAREAS!$E$5:$E$81,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"06.??.??",TAREAS!$E$5:$E$77,"Pendiente")</f>
         <v/>
       </c>
       <c r="F9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"06.??.??",TAREAS!$E$5:$E$81,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"06.??.??",TAREAS!$E$5:$E$77,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G9" s="6">
@@ -928,23 +928,23 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"07.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"07.??.??")</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"07.??.??",TAREAS!$E$5:$E$81,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"07.??.??",TAREAS!$E$5:$E$77,"Hecha")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"07.??.??",TAREAS!$E$5:$E$81,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"07.??.??",TAREAS!$E$5:$E$77,"En curso")</f>
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"07.??.??",TAREAS!$E$5:$E$81,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"07.??.??",TAREAS!$E$5:$E$77,"Pendiente")</f>
         <v/>
       </c>
       <c r="F10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$81,"07.??.??",TAREAS!$E$5:$E$81,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$77,"07.??.??",TAREAS!$E$5:$E$77,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G10" s="6">
@@ -1077,12 +1077,12 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>07.01.03</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
+          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
         </is>
       </c>
       <c r="C18" s="4" t="n"/>
@@ -1095,86 +1095,130 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>04.01.04</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 09/08 (subtarea dentro del alcance de 04.01.01, creada por el orquestador, regla 2 de CLAUDE.md): re-derivar POR CÁLCULO el tamaño mínimo operable de XAUUSD en 4h y el requisito real de lote que 04.01.01 debe exigir al bróker</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>PROXIMA PUERTA</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>G1 — elegir mercado y tamaño de vela (criterios en la hoja PUERTAS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>OBJETIVO DEL MES</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Llegar al 1 de septiembre con respuesta a: ¿existe alguna estrategia que merezca pasar a demo?</t>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>07.01.03</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
+          <t>PROXIMA PUERTA</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>G1 — elegir mercado y tamaño de vela (criterios en la hoja PUERTAS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>OBJETIVO DEL MES</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Llegar al 1 de septiembre con respuesta a: ¿existe alguna estrategia que merezca pasar a demo?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
           <t>FUENTE DE VERDAD</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>00-direccion/WBS.md — este Excel se genera de ahi. Si discrepan, manda el texto.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>LEYENDA</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Hecha</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>En curso</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Bloqueada</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B20:G20"/>
+  <mergeCells count="11">
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B19:F19"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B21:G21"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
   </mergeCells>
@@ -1384,7 +1428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1437,7 +1481,7 @@
       <c r="B4" s="24" t="n"/>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t>03.01.08 — Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
+          <t>04.01.04 — NUEVA 09/08 (subtarea dentro del alcance de 04.01.01, creada por el orquestador, regla 2 de CLAUDE.md): re-derivar POR CÁLCULO el tamaño mínimo operable de XAUUSD en 4h y el requisito real de lote que 04.01.01 debe exigir al bróker</t>
         </is>
       </c>
       <c r="D4" s="24" t="n"/>
@@ -1447,7 +1491,7 @@
       <c r="H4" s="24" t="n"/>
       <c r="I4" s="25" t="inlineStr">
         <is>
-          <t>Crítico</t>
+          <t>Constructor de datos</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1527,7 @@
       <c r="B6" s="30" t="n"/>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>04.02.01 — Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente. Detras de ella esperan 16 de las 42 tareas vivas.</t>
+          <t>04.02.01 — Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente. Detras de ella esperan 16 de las 37 tareas vivas.</t>
         </is>
       </c>
       <c r="D6" s="30" t="n"/>
@@ -1547,7 +1591,7 @@
     <row r="9">
       <c r="A9" s="32" t="inlineStr">
         <is>
-          <t>SE PUEDE TRABAJAR YA — 20 tareas, en este orden</t>
+          <t>SE PUEDE TRABAJAR YA — 16 tareas, en este orden</t>
         </is>
       </c>
       <c r="B9" s="32" t="n"/>
@@ -1565,22 +1609,22 @@
       </c>
       <c r="B10" s="33" t="inlineStr">
         <is>
-          <t>03.01.08</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Crítico</t>
-        </is>
-      </c>
-      <c r="E10" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
+          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -1592,7 +1636,7 @@
         <v>2</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
@@ -1606,22 +1650,22 @@
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
-          <t>03.01.23</t>
+          <t>04.01.04</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Encadenador de trabajo desatendido: una conversación por tarea</t>
+          <t>NUEVA 09/08 (subtarea dentro del alcance de 04.01.01, creada por el orquestador, regla 2 de CLAUDE.md): re-derivar POR CÁLCULO el tamaño mínimo operable de XAUUSD en 4h y el requisito real de lote que 04.01.01 debe exigir al bróker</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Constructor de motor</t>
-        </is>
-      </c>
-      <c r="E11" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
+          <t>Constructor de datos</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
@@ -1643,17 +1687,17 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>07.01.03</t>
+          <t>03.01.08</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
+          <t>Prueba de fuego de las barreras (regla 25 de CLAUDE.md): inyectar cada caso prohibido —leer el cajón reservado, escribir fuera del proyecto, borrar datos, gastar dinero— y comprobar que se bloquea de verdad. Lo que no se bloquee se marca "no verificada"</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Crítico</t>
         </is>
       </c>
       <c r="E12" s="34" t="inlineStr">
@@ -1666,8 +1710,12 @@
           <t>En curso</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -1680,35 +1728,31 @@
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>03.01.23</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
-        </is>
-      </c>
-      <c r="D13" s="28" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>15</v>
-      </c>
+          <t>Encadenador de trabajo desatendido: una conversación por tarea</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Constructor de motor</t>
+        </is>
+      </c>
+      <c r="E13" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -1721,35 +1765,31 @@
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>04.02.01</t>
+          <t>07.01.03</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
+          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>16</v>
-      </c>
+          <t>Orquestador</t>
+        </is>
+      </c>
+      <c r="E14" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -1762,22 +1802,22 @@
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>03.01.03</t>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Ejecución desatendida: arranques programados, permisos AMPLIOS por defecto (git como red de seguridad) y topes de gasto</t>
+          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E15" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
+          <t>Investigador</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1789,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -1803,12 +1843,12 @@
       </c>
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>03.01.04</t>
+          <t>03.01.03</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Plan de respaldo de modelos: si un modelo no está disponible o rechaza, el agente sigue con su respaldo y lo anota</t>
+          <t>Ejecución desatendida: arranques programados, permisos AMPLIOS por defecto (git como red de seguridad) y topes de gasto</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1844,17 +1884,17 @@
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>03.01.06</t>
+          <t>03.01.04</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Plantilla y automatismo de fichas de decisión: el secretario prepara cada decisión del CEO en el formato obligatorio y la adjunta al informe semanal</t>
+          <t>Plan de respaldo de modelos: si un modelo no está disponible o rechaza, el agente sigue con su respaldo y lo anota</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E17" s="34" t="inlineStr">
@@ -1885,17 +1925,17 @@
       </c>
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>03.01.09</t>
+          <t>03.01.06</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Enrutado por tipo de tarea y comprobación de que el WBS genera tareas de cada tipo de agente (ver L-010 de LECCIONES.md; sin número propio en CLAUDE.md)</t>
+          <t>Plantilla y automatismo de fichas de decisión: el secretario prepara cada decisión del CEO en el formato obligatorio y la adjunta al informe semanal</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E18" s="34" t="inlineStr">
@@ -1908,8 +1948,12 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>nada: se puede empezar ya</t>
@@ -1922,12 +1966,12 @@
       </c>
       <c r="B19" s="33" t="inlineStr">
         <is>
-          <t>03.01.10</t>
+          <t>03.01.09</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Testbed sintético de invarianza: resultado de referencia fijo que debe reproducirse tras cualquier cambio del motor</t>
+          <t>Enrutado por tipo de tarea y comprobación de que el WBS genera tareas de cada tipo de agente (ver L-010 de LECCIONES.md; sin número propio en CLAUDE.md)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1959,12 +2003,12 @@
       </c>
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>03.01.12</t>
+          <t>03.01.10</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 01/08 (petición del CEO): fijar la estrategia de ramas de git. Criterio del CEO, literal: que dé agilidad, no complejidad</t>
+          <t>Testbed sintético de invarianza: resultado de referencia fijo que debe reproducirse tras cualquier cambio del motor</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -2033,17 +2077,17 @@
       </c>
       <c r="B22" s="33" t="inlineStr">
         <is>
-          <t>03.01.15</t>
+          <t>03.01.17</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Herramientas del secretario: puede escribir los registros que solo admiten añadir pero no puede verificarlos</t>
+          <t>Reparar la prueba 7 de verificar_excel.py (entregables de las tareas hechas)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Constructor de motor</t>
         </is>
       </c>
       <c r="E22" s="34" t="inlineStr">
@@ -2070,17 +2114,17 @@
       </c>
       <c r="B23" s="33" t="inlineStr">
         <is>
-          <t>03.01.17</t>
+          <t>03.01.18</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Reparar la prueba 7 de verificar_excel.py (entregables de las tareas hechas)</t>
+          <t>NUEVA 03/08 (D-20, idea 1 de las auditorías): contador mecánico del reparto producto/motor, inyectado en el contexto al arrancar cada tirada</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Constructor de motor</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E23" s="34" t="inlineStr">
@@ -2107,12 +2151,12 @@
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>03.01.18</t>
+          <t>07.01.01</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (D-20, idea 1 de las auditorías): contador mecánico del reparto producto/motor, inyectado en el contexto al arrancar cada tirada</t>
+          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -2144,12 +2188,12 @@
       </c>
       <c r="B25" s="33" t="inlineStr">
         <is>
-          <t>03.01.19</t>
+          <t>07.01.02</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (D-20, idea 2 de las auditorías): registro mecánico de autoría, para que «nadie valida su propio trabajo» deje de ser solo prosa</t>
+          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2176,59 +2220,39 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t>03.01.20</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>NUEVA 04/08 (incidente del 03/08): muro para que una sesión no siga trabajando sola después de un /compact</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E26" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>nada: se puede empezar ya</t>
-        </is>
-      </c>
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>ESPERANDO A OTRA TAREA — 21 tareas, en orden de codigo WBS</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="n"/>
+      <c r="C26" s="32" t="n"/>
+      <c r="D26" s="32" t="n"/>
+      <c r="E26" s="32" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="32" t="n"/>
+      <c r="H26" s="32" t="n"/>
+      <c r="I26" s="32" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
-        <v>18</v>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="B27" s="33" t="inlineStr">
         <is>
-          <t>03.01.25</t>
+          <t>03.01.05</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 05/08 (nace del incidente de este mismo día): guardia en .githooks/pre-commit que ejecuta la métrica de L-027 de 00-direccion/LECCIONES.md sobre 00-direccion/WBS.md y rechaza el commit si alguna fila de tarea no da 7 campos al partirla por la barra vertical. Motivo: hoy la métrica existe, está escrita como normativa en este WBS, y no la ejecuta nadie automáticamente; 05-vista-ceo/verificar_excel.py no la cubre. Es el muro que le falta a la única fuente de verdad del proyecto. Regla 24 de CLAUDE.md: nace de un incidente real y medido — el 05/08 cuatro filas quedaron partidas y ningún guardia se enteró. Regla 25 de CLAUDE.md: se verifica por inyección de una fila rota ANTES de documentarse como activo. AVISO PARA QUIEN LA EJECUTE, medido el mismo día: el propio texto de esta fila no puede contener el comando literal, porque la barra vertical que lleva dentro rompe la fila que describe; el guardia tiene que tolerar esa cita cuando aparezca en prosa fuera de una tabla.</t>
+          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Constructor de motor</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="E27" s="34" t="inlineStr">
@@ -2245,27 +2269,29 @@
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>nada: se puede empezar ya</t>
+          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
-        <v>19</v>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>07.01.01</t>
+          <t>03.01.07</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
+          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E28" s="34" t="inlineStr">
@@ -2282,22 +2308,24 @@
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>nada: se puede empezar ya</t>
+          <t>03.01.06 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>20</v>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>07.01.02</t>
+          <t>03.01.11</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2310,33 +2338,57 @@
           <t>MOTOR</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>nada: se puede empezar ya</t>
+          <t>03.01.08 (en curso, Crítico)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="inlineStr">
-        <is>
-          <t>ESPERANDO A OTRA TAREA — 22 tareas, en orden de codigo WBS</t>
-        </is>
-      </c>
-      <c r="B30" s="32" t="n"/>
-      <c r="C30" s="32" t="n"/>
-      <c r="D30" s="32" t="n"/>
-      <c r="E30" s="32" t="n"/>
-      <c r="F30" s="32" t="n"/>
-      <c r="G30" s="32" t="n"/>
-      <c r="H30" s="32" t="n"/>
-      <c r="I30" s="32" t="n"/>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>04.01.02</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02) REQUISITO AÑADIDO 04/08: al recalcular con precios reales se comprueba que la entidad que publica la tarifa es la misma con la que se opera. Si no coinciden, la cifra vieja no se hereda: se vuelve a medir.</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Constructor datos</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>04.01.01 (en curso, CEO + Orquestador)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -2346,22 +2398,22 @@
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>03.01.05</t>
+          <t>04.01.03</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
+          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
-        </is>
-      </c>
-      <c r="E31" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
+          <t>Constructor datos</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2369,11 +2421,15 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
+          <t>04.01.01 (en curso, CEO + Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2385,22 +2441,22 @@
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>03.01.07</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
+          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
-        </is>
-      </c>
-      <c r="E32" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
+          <t>Investigador</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2408,11 +2464,15 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>03.01.06 (pendiente, Secretario)</t>
+          <t>04.02.01 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -2424,34 +2484,38 @@
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>03.01.11</t>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
+          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E33" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr"/>
+          <t>Validador</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>14</v>
+      </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>03.01.08 (en curso, Crítico)</t>
+          <t>04.02.02 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -2463,22 +2527,22 @@
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>03.01.24</t>
+          <t>04.02.04</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 05/08 (nace de los huecos medidos por ejecución en 03.01.08): las tres barreras que hoy NO existen. (a) El patrón Bash( 02-datos/reservado) de .claude/settings.json exige un espacio literal y no cubre la ruta pegada a una comilla, así que una línea de python lo esquiva: sustituirlo por un patrón que cubra cualquier verbo y cualquier forma de escribir la ruta, y probarlo con las TRES formas. (b) Nada impide rm -rf dentro de 02-datos/, y los datos no están en git (regla 27 de CLAUDE.md): no se rehacen deshaciendo un commit, se rehacen volviendo a descargarlos. (c) No hay ninguna barrera de gasto, ni en código ni en configuración; D-26 de 00-direccion/DECISIONES.md deja escrito que --max-budget-usd existe. Regla 24 de CLAUDE.md: las tres nacen de una inyección ejecutada con su salida guardada, no de una sospecha, y ninguna causó daño. Regla 25 de CLAUDE.md: cada barrera nueva se verifica por inyección ANTES de documentarse como activa.</t>
+          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
+          <t>Validador</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2486,11 +2550,15 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>03.01.08 (en curso, Crítico)</t>
+          <t>04.02.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2502,17 +2570,17 @@
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>04.01.02</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02) REQUISITO AÑADIDO 04/08: al recalcular con precios reales se comprueba que la entidad que publica la tarifa es la misma con la que se opera. Si no coinciden, la cifra vieja no se hereda: se vuelve a medir.</t>
+          <t>Backtest con costes reales sobre el cajón de construir</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2525,11 +2593,15 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
+          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2541,17 +2613,17 @@
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>04.01.03</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
+          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2568,11 +2640,11 @@
         <v>1</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>04.01.01 (pendiente, CEO + Orquestador)</t>
+          <t>04.03.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2584,17 +2656,17 @@
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
+          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2611,11 +2683,11 @@
         <v>1</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>04.02.01 (pendiente, Investigador)</t>
+          <t>04.03.02 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2699,12 @@
       </c>
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
+          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2654,11 +2726,11 @@
         <v>1</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>04.02.02 (pendiente, Investigador)</t>
+          <t>04.03.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2742,12 @@
       </c>
       <c r="B39" s="33" t="inlineStr">
         <is>
-          <t>04.02.04</t>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
+          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2697,11 +2769,11 @@
         <v>1</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>04.02.03 (pendiente, Validador)</t>
+          <t>04.03.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2713,17 +2785,17 @@
       </c>
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Backtest con costes reales sobre el cajón de construir</t>
+          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2737,14 +2809,14 @@
         </is>
       </c>
       <c r="G40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
+          <t>04.03.05 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2756,17 +2828,17 @@
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.04.02</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
+          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -2779,15 +2851,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>11</v>
-      </c>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>04.03.01 (pendiente, Constructores)</t>
+          <t>04.04.01 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -2799,17 +2867,17 @@
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.04.03</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Validador</t>
+          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
+        </is>
+      </c>
+      <c r="D42" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -2826,11 +2894,11 @@
         <v>1</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>04.03.02 (pendiente, Constructores)</t>
+          <t>04.04.01 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -2842,17 +2910,17 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+          <t>Bot en demo, solo y con guardias automáticos</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -2869,11 +2937,11 @@
         <v>1</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>04.03.03 (pendiente, Validador)</t>
+          <t>04.04.03 (pendiente, CEO)</t>
         </is>
       </c>
     </row>
@@ -2885,17 +2953,17 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>04.03.05</t>
+          <t>05.01.02</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
+          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -2912,11 +2980,11 @@
         <v>1</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>04.03.04 (pendiente, Validador)</t>
+          <t>05.01.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2928,17 +2996,17 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>05.01.03</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>Secretario</t>
+          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
+        </is>
+      </c>
+      <c r="D45" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -2952,14 +3020,14 @@
         </is>
       </c>
       <c r="G45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H45" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>04.03.05 (pendiente, Validador)</t>
+          <t>05.01.02 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -2971,17 +3039,17 @@
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>04.04.02</t>
+          <t>06.01.01</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
+          <t>Dinero pequeño respetando los límites de 01.01.03</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -2994,11 +3062,15 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>04.04.01 (pendiente, Secretario)</t>
+          <t>05.01.03 (pendiente, CEO)</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3082,12 @@
       </c>
       <c r="B47" s="33" t="inlineStr">
         <is>
-          <t>04.04.03</t>
+          <t>06.01.02</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
+          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
         </is>
       </c>
       <c r="D47" s="28" t="inlineStr">
@@ -3033,249 +3105,34 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>5</v>
-      </c>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>04.04.01 (pendiente, Secretario)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B48" s="33" t="inlineStr">
-        <is>
-          <t>05.01.01</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Bot en demo, solo y con guardias automáticos</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>04.04.03 (pendiente, CEO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B49" s="33" t="inlineStr">
-        <is>
-          <t>05.01.02</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Secretario</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>05.01.01 (pendiente, Constructores)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B50" s="33" t="inlineStr">
-        <is>
-          <t>05.01.03</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
-        </is>
-      </c>
-      <c r="D50" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>05.01.02 (pendiente, Secretario)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B51" s="33" t="inlineStr">
-        <is>
-          <t>06.01.01</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Dinero pequeño respetando los límites de 01.01.03</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>05.01.03 (pendiente, CEO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B52" s="33" t="inlineStr">
-        <is>
-          <t>06.01.02</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
-        </is>
-      </c>
-      <c r="D52" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
           <t>06.01.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="46" customHeight="1">
-      <c r="A54" s="35" t="inlineStr">
-        <is>
-          <t>Aviso de la regla 8 (CLAUDE.md): si la cola de arriba solo tuviera tareas de MOTOR, hay que parar y avisar al CEO; significa que la cola esta mal llena. Ahora mismo la cola tiene 2 de producto y 18 de motor.</t>
+    <row r="49" ht="46" customHeight="1">
+      <c r="A49" s="35" t="inlineStr">
+        <is>
+          <t>Aviso de la regla 8 (CLAUDE.md): si la cola de arriba solo tuviera tareas de MOTOR, hay que parar y avisar al CEO; significa que la cola esta mal llena. Ahora mismo la cola tiene 3 de producto y 13 de motor.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A26:I26"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A49:I49"/>
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="C4:H4"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3287,7 +3144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4204,7 +4061,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>ejecutada la primera pasada 31/07 con verificar_barreras.py: 4 barreras de 5 VERIFICADAS por ejecucion (hooks instalados, datos rechazados en commit, .gitignore ignora 02-datos, mensaje exige codigo WBS). 1 NO VERIFICADA: el cajon reservado era un filtro de texto sobre el comando. CORRECCIÓN DE DEPENDENCIA (03/08/2026): la dependencia de 03.01.03 fue falsa desde el inicio — verificar_barreras.py ejecutada el 31/07 sin que 03.01.03 existiera ya. Las barreras probadas (hooks, .gitignore, commit-msg, cifrado) dependen de 03.01.01 (repo con WBS y reglas) y 03.01.02 (ocho agentes creados). Se remedia en 03.01.11 (D-10). No se cierra hasta repetir la pasada con 03.01.11 terminada SEGUNDA PASADA […] texto completo en 00-direccion/WBS.md</t>
+          <t>* — ejecutada la primera pasada 31/07 con verificar_barreras.py: 4 barreras de 5 VERIFICADAS por ejecucion (hooks instalados, datos rechazados en commit, .gitignore ignora 02-datos, mensaje exige codigo WBS). 1 NO VERIFICADA: el cajon reservado era un filtro de texto sobre el comando. CORRECCIÓN DE DEPENDENCIA (03/08/2026): la dependencia de 03.01.03 fue falsa desde el inicio — verificar_barreras.py ejecutada el 31/07 sin que 03.01.03 existiera ya. Las barreras probadas (hooks, .gitignore, commit-msg, cifrado) dependen de 03.01.01 (repo con WBS y reglas) y 03.01.02 (ocho agentes creados). Se remedia en 03.01.11 (D-10). No se cierra hasta repetir la pasada con 03.01.11 terminada SEGUNDA […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
@@ -4303,12 +4160,12 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>03.01.12</t>
+          <t>03.01.11</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 01/08 (petición del CEO): fijar la estrategia de ramas de git. Criterio del CEO, literal: que dé agilidad, no complejidad</t>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -4318,30 +4175,30 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>03.01.01</t>
+          <t>03.01.08</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (01/08): Estado de partida, comprobado por ejecución el 01/08: git branch -a → una sola rama, main · git remote -v → vacío, no hay remoto · 16 commits · un solo humano. Alcance: decidir y dejar escrito (a) cuándo se trabaja en main y cuándo no, (b) si se usan worktrees y para qué, (c) qué NO se hace. Lo que ya se sabe y no hay que volver a investigar: Claude Code 2.1.220 trae worktrees nativos (claude --worktree &lt;nombre&gt;, y isolation: worktree en la ficha de un subagente) · los worktrees […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>script escrito y probado por ejecucion 31/07: 6 de 6 casos prohibidos bloqueados (contraseña por tuberia, abrir sin declarar variante, lectura a pelo del fichero cifrado, contraseña incorrecta, y ninguna orden de terminal vuelca datos en claro). VERIFICADO POR EJECUCION (03/08/2026): 04-resultados/registro-cajon.md registra una entrada SELLAR del 31/07 a las 18:31:29 UTC con resultado sellado. La funcion sellar() en cajon_reservado.py aborta con mensaje «El cajon ya esta sellado» si se intenta llamar una segunda vez. El CEO confirmo el 03/08/2026 que la contraseña la tecleo en una terminal real del sistema (nunca mediante el prefijo de ejecucion rapida de la sesion de Claude Code), porque […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>03.01.11</t>
+          <t>03.01.14</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
+          <t>NUEVA 01/08 (deuda detectada al cerrar 03.01.13): la hoja REGLAS del Excel del CEO la construye 05-vista-ceo/generar_excel.py leyendo las líneas numeradas de la sección de reglas del WBS, que tras D-16 ya no existen: la hoja saldría vacía bajo el título «LAS 29 REGLAS», y verificar_excel.py no comprueba esa hoja, así que sus 8 pruebas pasarían igual (L-016). Hay que leer las reglas de CLAUDE.md y añadir una prueba que falle si la hoja sale vacía. Deuda de motor: no se ejecuta sin permiso del CEO.</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -4351,17 +4208,17 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>03.01.08</t>
+          <t>03.01.13</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>script escrito y probado por ejecucion 31/07: 6 de 6 casos prohibidos bloqueados (contraseña por tuberia, abrir sin declarar variante, lectura a pelo del fichero cifrado, contraseña incorrecta, y ninguna orden de terminal vuelca datos en claro). VERIFICADO POR EJECUCION (03/08/2026): 04-resultados/registro-cajon.md registra una entrada SELLAR del 31/07 a las 18:31:29 UTC con resultado sellado. La funcion sellar() en cajon_reservado.py aborta con mensaje «El cajon ya esta sellado» si se intenta llamar una segunda vez. El CEO confirmo el 03/08/2026 que la contraseña la tecleo en una terminal real del sistema (nunca mediante el prefijo de ejecucion rapida de la sesion de Claude Code), porque […] texto completo en 00-direccion/WBS.md</t>
+          <t>**</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr"/>
@@ -4369,12 +4226,12 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>03.01.14</t>
+          <t>03.01.15</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 01/08 (deuda detectada al cerrar 03.01.13): la hoja REGLAS del Excel del CEO la construye 05-vista-ceo/generar_excel.py leyendo las líneas numeradas de la sección de reglas del WBS, que tras D-16 ya no existen: la hoja saldría vacía bajo el título «LAS 29 REGLAS», y verificar_excel.py no comprueba esa hoja, así que sus 8 pruebas pasarían igual (L-016). Hay que leer las reglas de CLAUDE.md y añadir una prueba que falle si la hoja sale vacía. Deuda de motor: no se ejecuta sin permiso del CEO.</t>
+          <t>Herramientas del secretario: puede escribir los registros que solo admiten añadir pero no puede verificarlos</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -4384,30 +4241,34 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>03.01.13</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecha</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>**</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr"/>
+          <t>10/08</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 02/08 (tres incidentes reales el 02/08): secretario mantiene los tres registros que solo admiten añadir y todas las fichas del CEO, y no tiene Bash: no puede comprobar por ejecución ninguna de las reglas que gobiernan su trabajo. El 02/08 falló tres veces por lo mismo — no pudo verificar el pegado en tabla, ni el append-only, ni el ancho de su ficha — y las tres las descubrió otro agente, que es la regla 15 de CLAUDE.md rota por diseño, no por descuido. Decidir entre dos salidas, y NO se […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>03.01.15</t>
+          <t>03.01.16</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Herramientas del secretario: puede escribir los registros que solo admiten añadir pero no puede verificarlos</t>
+          <t>Las hojas del Excel se construyen de sus fuentes primarias, no de copias</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -4417,77 +4278,77 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>03.01.02</t>
+          <t>03.01.13, 03.01.14</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr"/>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>el 03/08», que llevaba la marca sin guion delante) que se detectó y reparó antes de terminar. Las dos demostradas por inyección en 05-vista-ceo/prueba_inyeccion.sh, casos 6 y 7 nuevos (función probar_argv, con el mismo guardia FIXTURE de L-026): el caso 6 añade una lección a una copia de LECCIONES.md sin tocar el Excel y hace caer la prueba de recuento; el caso 7 inserta una marca pendiente sin guion delante 40 caracteres antes del cierre real de una celda y hace caer solo la prueba de posición, sin falsear el ESTADO leído (igual que describe el mecanismo del bug). bash 05-vista-ceo/prueba_inyeccion.sh caza los 7 casos salvo el 3, que ya fallaba ANTES de esta tarea: usa el código 07.01.03 […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 02/08 (tres incidentes reales el 02/08): secretario mantiene los tres registros que solo admiten añadir y todas las fichas del CEO, y no tiene Bash: no puede comprobar por ejecución ninguna de las reglas que gobiernan su trabajo. El 02/08 falló tres veces por lo mismo — no pudo verificar el pegado en tabla, ni el append-only, ni el ancho de su ficha — y las tres las descubrió otro agente, que es la regla 15 de CLAUDE.md rota por diseño, no por descuido. Decidir entre dos salidas, y NO se […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (03/08): Problema verificado hoy: 05-vista-ceo/generar_excel.py construye las hojas REGLAS, LECCIONES y DECISIONES, pero lo hace leyendo tablas espejo en el WBS, no de las fuentes primarias. Consecuencia, medida el 03/08 y ya caducada en sus cifras concretas —de ahí la reescritura del 04/08 más abajo, la fuente sigue viva y crece cada día—: (1) hoja REGLAS sale vacía tras D-16 (las reglas ya no están numeradas en el WBS); (2) hoja LECCIONES muestra 18 cuando 00-direccion/LECCIONES.md […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>03.01.16</t>
+          <t>03.01.17</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Las hojas del Excel se construyen de sus fuentes primarias, no de copias</t>
+          <t>Reparar la prueba 7 de verificar_excel.py (entregables de las tareas hechas)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Constructor de motor</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>03.01.13, 03.01.14</t>
+          <t>03.01.13</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Hecha</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>el 03/08», que llevaba la marca sin guion delante) que se detectó y reparó antes de terminar. Las dos demostradas por inyección en 05-vista-ceo/prueba_inyeccion.sh, casos 6 y 7 nuevos (función probar_argv, con el mismo guardia FIXTURE de L-026): el caso 6 añade una lección a una copia de LECCIONES.md sin tocar el Excel y hace caer la prueba de recuento; el caso 7 inserta una marca pendiente sin guion delante 40 caracteres antes del cierre real de una celda y hace caer solo la prueba de posición, sin falsear el ESTADO leído (igual que describe el mecanismo del bug). bash 05-vista-ceo/prueba_inyeccion.sh caza los 7 casos salvo el 3, que ya fallaba ANTES de esta tarea: usa el código 07.01.03 […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>FICHA (03/08): Problema verificado hoy: 05-vista-ceo/generar_excel.py construye las hojas REGLAS, LECCIONES y DECISIONES, pero lo hace leyendo tablas espejo en el WBS, no de las fuentes primarias. Consecuencia, medida el 03/08 y ya caducada en sus cifras concretas —de ahí la reescritura del 04/08 más abajo, la fuente sigue viva y crece cada día—: (1) hoja REGLAS sale vacía tras D-16 (las reglas ya no están numeradas en el WBS); (2) hoja LECCIONES muestra 18 cuando 00-direccion/LECCIONES.md […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (03/08): Problema reproducido hoy: la prueba 7 localiza entregables citados en las celdas de tarea, pero corta cada celda por el primer hecha y solo examina lo que va después. En 03.01.13 ese marcador es el último carácter de la celda, así que examina cero ficheros y no caza que esa tarea, marcada hecha, cita 00-direccion/PENDIENTE-03.01.13-lista-de-reglas.md, que no existe en disco ni ha existido nunca en git. Dos defectos más: busca por nombre de fichero en CUALQUIER parte del […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>03.01.17</t>
+          <t>03.01.18</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Reparar la prueba 7 de verificar_excel.py (entregables de las tareas hechas)</t>
+          <t>NUEVA 03/08 (D-20, idea 1 de las auditorías): contador mecánico del reparto producto/motor, inyectado en el contexto al arrancar cada tirada</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Constructor de motor</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>03.01.13</t>
+          <t>03.01.01</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -4498,24 +4359,24 @@
       <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>FICHA (03/08): Problema reproducido hoy: la prueba 7 localiza entregables citados en las celdas de tarea, pero corta cada celda por el primer hecha y solo examina lo que va después. En 03.01.13 ese marcador es el último carácter de la celda, así que examina cero ficheros y no caza que esa tarea, marcada hecha, cita 00-direccion/PENDIENTE-03.01.13-lista-de-reglas.md, que no existe en disco ni ha existido nunca en git. Dos defectos más: busca por nombre de fichero en CUALQUIER parte del […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (03/08): Problema, medido y no supuesto: el techo del 20% de motor de la regla 8 de CLAUDE.md es prosa y nadie lo mide. La primera vez que se midió, el 01/08, el reparto real era 7 de 16 commits, 43,8%, más del doble del techo, y el proyecto llevaba desde el arranque sin saberlo. Qué se construye: un hook SessionStart que calcula el reparto desde git log y lo inyecta en el contexto con hookSpecificOutput.additionalContext, de forma que cada tirada empiece con el número delante en vez de […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>03.01.18</t>
+          <t>03.01.21</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (D-20, idea 1 de las auditorías): contador mecánico del reparto producto/motor, inyectado en el contexto al arrancar cada tirada</t>
+          <t>Diagnóstico medido del consumo de tokens del motor de agentes</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -4525,63 +4386,63 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (03/08): Problema, medido y no supuesto: el techo del 20% de motor de la regla 8 de CLAUDE.md es prosa y nadie lo mide. La primera vez que se midió, el 01/08, el reparto real era 7 de 16 commits, 43,8%, más del doble del techo, y el proyecto llevaba desde el arranque sin saberlo. Qué se construye: un hook SessionStart que calcula el reparto desde git log y lo inyecta en el contexto con hookSpecificOutput.additionalContext, de forma que cada tirada empiece con el número delante en vez de […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>04/08 — medición sobre el transcript en disco de la sesión del 03-04/08 (/home/server/.claude/projects/-home-server-projects-bot-trading/1d064480-a2c4-42fd-a199-5fd72ce78fd9.jsonl y su carpeta subagents/). Hilo principal: 207 peticiones, 94,9 M de tokens leídos de cache, contexto pico 794.459, contexto medio ~452.000. 75 subagentes: 1.293 peticiones, 114,8 M leídos, 11,5 M escritos. Total ~209,7 M en una sola sesión. Causa identificada: el coste crece con el cuadrado de los pasos dados dentro de una misma conversación, sobre un suelo fijo de ~85.000 tokens por conversación. Correcciones aplicadas al propio diagnóstico tras revisión de critico-codigo: el ahorro estimado bajó de "5x" y de un […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>03.01.19</t>
+          <t>03.01.22</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (D-20, idea 2 de las auditorías): registro mecánico de autoría, para que «nadie valida su propio trabajo» deje de ser solo prosa</t>
+          <t>Inventario por ejecución de los mecanismos de trabajo desatendido en esta máquina</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Constructor de motor</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>03.01.02</t>
+          <t>03.01.01</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (03/08): Problema: la regla 16 de CLAUDE.md y C2 no tienen muro. Hoy dependen de que el orquestador reparta bien y de que nadie se equivoque; no hay forma de comprobar a posteriori quién escribió qué. Nivel 1, que es lo que ESTA tarea entrega: un hook PostToolUse con matcher de escritura anota en 04-resultados/autoria.jsonl qué fichero se tocó y qué tipo de agente lo tocó. El campo del tipo de agente viaja en la entrada JSON de todo hook que corre dentro de un subagente. Con eso la regla […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>04/08 — ejecutado por constructor-motor, revisado por critico-codigo. Probado por ejecución: tmux 3.4 presente · cron corriendo (PID 156, activo bajo systemd, persiste tras reinicio) · systemd real en esta WSL2 · flock y jq presentes · screen, at, notify-send, mail y sendmail NO instalados · claude 2.1.221. Hallazgos: --max-budget-usd existe (solo con --print) · --max-turns existe pero oculto, no sale en claude --help · --fallback-model existe · en modo -p un permiso no se queda colgado: se resuelve solo. HUECOS:** no hay forma de avisar al CEO fuera de la máquina sin webhook, porque no hay notify-send ni correo. Pendiente de decisión del CEO. Que --max-budget-usd corte de verdad no está […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>03.01.20</t>
+          <t>03.01.23</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 04/08 (incidente del 03/08): muro para que una sesión no siga trabajando sola después de un /compact</t>
+          <t>Encadenador de trabajo desatendido: una conversación por tarea</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Constructor de motor</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4591,101 +4452,73 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr"/>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>. No se enciende: depende de una tirada real supervisada y de 03.01.08. CRITERIO DE HECHO (no cambia): una tirada que arranque sola sin nadie delante, y la tabla muro/prosa con cada línea "muro" disparada por inyección. (Tabla muro/prosa en 03-motor/desatendido/LEEME.md, líneas 62-81; 13 mecanismos: 12 MURO verificados por ejecución, 1 NO verificado.)</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>FICHA (04/08, dictada por el orquestador): Incidente que la origina, verificado (regla 24 de CLAUDE.md): el 03/08/2026, tras un /compact a las 21:29, la sesión recibió una orden del CEO a las 21:44 y trabajó sin invocar a un solo subagente hasta las 21:58 — escribió tres decisiones y cuatro lecciones en registros de solo-añadir, hizo cirugía estructural sobre el WBS y tocó dos scripts del Excel del CEO. Nadie lo revisó. El detalle está en la tarea 07.01.03. NO ES EL «Nivel 2» DE 03.01.19 y no […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>03.01.21</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Diagnóstico medido del consumo de tokens del motor de agentes</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Secretario</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>03.01.01</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Hecha</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>04/08 — medición sobre el transcript en disco de la sesión del 03-04/08 (/home/server/.claude/projects/-home-server-projects-bot-trading/1d064480-a2c4-42fd-a199-5fd72ce78fd9.jsonl y su carpeta subagents/). Hilo principal: 207 peticiones, 94,9 M de tokens leídos de cache, contexto pico 794.459, contexto medio ~452.000. 75 subagentes: 1.293 peticiones, 114,8 M leídos, 11,5 M escritos. Total ~209,7 M en una sola sesión. Causa identificada: el coste crece con el cuadrado de los pasos dados dentro de una misma conversación, sobre un suelo fijo de ~85.000 tokens por conversación. Correcciones aplicadas al propio diagnóstico tras revisión de critico-codigo: el ahorro estimado bajó de "5x" y de un […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr"/>
+          <t>REDUCCIÓN ORDENADA POR EL CEO (04/08): la pieza se había crecido con gobernanza que él nunca pidió. Se borraron: lista-verde.txt (y toda su barrera de autorización) · los topes en dólares (MAX_BUDGET_USD_SESION, MAX_BUDGET_USD_DIARIO, gasto-.tsv) · crontab.propuesto.txt (arranques programados) · hook-notificacion.ejemplo.json (aviso al móvil) · cola.txt, progreso.tsv y --disallowedTools. Petición literal del CEO: "en vez de enlazar tantas tareas seguidas se parará antes para no consumir tokens […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="36" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B44" s="37" t="inlineStr">
+        <is>
+          <t>HIPÓTESIS Y VALIDACIÓN (PUERTA G2)</t>
+        </is>
+      </c>
+      <c r="C44" s="37" t="n"/>
+      <c r="D44" s="37" t="n"/>
+      <c r="E44" s="37" t="n"/>
+      <c r="F44" s="37" t="n"/>
+      <c r="G44" s="37" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="inlineStr">
-        <is>
-          <t>03.01.22</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Inventario por ejecución de los mecanismos de trabajo desatendido en esta máquina</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Constructor de motor</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>03.01.01</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Hecha</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>04/08 — ejecutado por constructor-motor, revisado por critico-codigo. Probado por ejecución: tmux 3.4 presente · cron corriendo (PID 156, activo bajo systemd, persiste tras reinicio) · systemd real en esta WSL2 · flock y jq presentes · screen, at, notify-send, mail y sendmail NO instalados · claude 2.1.221. Hallazgos: --max-budget-usd existe (solo con --print) · --max-turns existe pero oculto, no sale en claude --help · --fallback-model existe · en modo -p un permiso no se queda colgado: se resuelve solo. HUECOS:** no hay forma de avisar al CEO fuera de la máquina sin webhook, porque no hay notify-send ni correo. Pendiente de decisión del CEO. Que --max-budget-usd corte de verdad no está […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr"/>
+      <c r="A45" s="38" t="inlineStr">
+        <is>
+          <t>04.01</t>
+        </is>
+      </c>
+      <c r="B45" s="39" t="inlineStr">
+        <is>
+          <t>Broker y cajones de datos</t>
+        </is>
+      </c>
+      <c r="C45" s="39" t="n"/>
+      <c r="D45" s="39" t="n"/>
+      <c r="E45" s="39" t="n"/>
+      <c r="F45" s="39" t="n"/>
+      <c r="G45" s="39" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>03.01.23</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Encadenador de trabajo desatendido: una conversación por tarea</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Constructor de motor</t>
+          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>03.01.02</t>
+          <t>02.03.03</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -4695,34 +4528,34 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>. No se enciende: depende de una tirada real supervisada y de 03.01.08. CRITERIO DE HECHO (no cambia): una tirada que arranque sola sin nadie delante, y la tabla muro/prosa con cada línea "muro" disparada por inyección. (Tabla muro/prosa en 03-motor/desatendido/LEEME.md, líneas 62-81; 13 mecanismos: 12 MURO verificados por ejecución, 1 NO verificado.)</t>
+          <t>RONDA 2 CERRADA EN FALSO 06/08. Revisión del validador (revision_04.01.01.md): RECHAZA con 7 motivos. Auditoría de critico-codigo: RECHAZA la revisión. Seis motivos confirmados por método propio, entre ellos una CITA LITERAL FALSA —la celda del criterio 12 de IC Markets atribuía a su fichero de FAQs una condición del «90%» que solo existe en la de Pepperstone— y 11 celdas de 84 con dato sin fuente. P8 ANULADO: la orden que lo pidió añadió como eliminatorios los criterios 5 y 6, que esta ficha no declara; la palabra no aparecía más que una vez en el WBS, pegada al criterio 1, y eso se comprueba contra el commit da93597, no contra el fichero de hoy: este mismo párrafo añade dos apariciones […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>REDUCCIÓN ORDENADA POR EL CEO (04/08): la pieza se había crecido con gobernanza que él nunca pidió. Se borraron: lista-verde.txt (y toda su barrera de autorización) · los topes en dólares (MAX_BUDGET_USD_SESION, MAX_BUDGET_USD_DIARIO, gasto-.tsv) · crontab.propuesto.txt (arranques programados) · hook-notificacion.ejemplo.json (aviso al móvil) · cola.txt, progreso.tsv y --disallowedTools. Petición literal del CEO: "en vez de enlazar tantas tareas seguidas se parará antes para no consumir tokens […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (04/08, dictada por el orquestador): Por qué ahora: 02.03.03 cerró el 03/08 con D-19 y esta tarea quedó desbloqueada; es la única con plazo duro —10/08, sin retorno— y quedan 6 días. Alcance: comparar 3 o 4 brokers que ofrezcan XAUUSD al contado y entregar la tabla para que el CEO firme. PROHIBIDO ELEGIR: la elección es del CEO. Criterios obligatorios, uno por columna: (1) lote mínimo, y si admite fraccionado de 0,1 onzas —es eliminatorio de hecho: el lote entero son unos 1.962 € contra […] texto completo en 00-direccion/WBS.md</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>03.01.24</t>
+          <t>04.01.02</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 05/08 (nace de los huecos medidos por ejecución en 03.01.08): las tres barreras que hoy NO existen. (a) El patrón Bash( 02-datos/reservado) de .claude/settings.json exige un espacio literal y no cubre la ruta pegada a una comilla, así que una línea de python lo esquiva: sustituirlo por un patrón que cubra cualquier verbo y cualquier forma de escribir la ruta, y probarlo con las TRES formas. (b) Nada impide rm -rf dentro de 02-datos/, y los datos no están en git (regla 27 de CLAUDE.md): no se rehacen deshaciendo un commit, se rehacen volviendo a descargarlos. (c) No hay ninguna barrera de gasto, ni en código ni en configuración; D-26 de 00-direccion/DECISIONES.md deja escrito que --max-budget-usd existe. Regla 24 de CLAUDE.md: las tres nacen de una inyección ejecutada con su salida guardada, no de una sospecha, y ninguna causó daño. Regla 25 de CLAUDE.md: cada barrera nueva se verifica por inyección ANTES de documentarse como activa.</t>
+          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02) REQUISITO AÑADIDO 04/08: al recalcular con precios reales se comprueba que la entidad que publica la tarifa es la misma con la que se opera. Si no coinciden, la cifra vieja no se hereda: se vuelve a medir.</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>03.01.08</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4730,32 +4563,28 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>** — DEUDA DE MOTOR: no se ejecuta sin permiso expreso del CEO (regla 7 de CLAUDE.md). Ficha de decisión preparada para el 06/08</t>
-        </is>
-      </c>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>03.01.25</t>
+          <t>04.01.03</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 05/08 (nace del incidente de este mismo día): guardia en .githooks/pre-commit que ejecuta la métrica de L-027 de 00-direccion/LECCIONES.md sobre 00-direccion/WBS.md y rechaza el commit si alguna fila de tarea no da 7 campos al partirla por la barra vertical. Motivo: hoy la métrica existe, está escrita como normativa en este WBS, y no la ejecuta nadie automáticamente; 05-vista-ceo/verificar_excel.py no la cubre. Es el muro que le falta a la única fuente de verdad del proyecto. Regla 24 de CLAUDE.md: nace de un incidente real y medido — el 05/08 cuatro filas quedaron partidas y ningún guardia se enteró. Regla 25 de CLAUDE.md: se verifica por inyección de una fila rota ANTES de documentarse como activo. AVISO PARA QUIEN LA EJECUTE, medido el mismo día: el propio texto de esta fila no puede contener el comando literal, porque la barra vertical que lleva dentro rompe la fila que describe; el guardia tiene que tolerar esa cita cuando aparezca en prosa fuera de una tabla.</t>
+          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Constructor de motor</t>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>03.01.01</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -4763,39 +4592,51 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>** — DEUDA DE MOTOR: no se ejecuta sin permiso expreso del CEO (regla 7 de CLAUDE.md). Entra como cuarto punto de la ficha D-29 del 06/08</t>
-        </is>
-      </c>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="inlineStr"/>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="36" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="B49" s="37" t="inlineStr">
-        <is>
-          <t>HIPÓTESIS Y VALIDACIÓN (PUERTA G2)</t>
-        </is>
-      </c>
-      <c r="C49" s="37" t="n"/>
-      <c r="D49" s="37" t="n"/>
-      <c r="E49" s="37" t="n"/>
-      <c r="F49" s="37" t="n"/>
-      <c r="G49" s="37" t="n"/>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>04.01.04</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 09/08 (subtarea dentro del alcance de 04.01.01, creada por el orquestador, regla 2 de CLAUDE.md): re-derivar POR CÁLCULO el tamaño mínimo operable de XAUUSD en 4h y el requisito real de lote que 04.01.01 debe exigir al bróker</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Constructor de datos</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>02.02.01, 02.03.03</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>FICHA ESCRITA TARDE Y POR ESO ANOTADA (regla 5 de CLAUDE.md incumplida): el orquestador dictó esta subtarea en el reparto del 09/08 con código, motivo y criterio de hecho, pero ordenó ejecutarla sin mandar que se escribiera antes en este WBS; el trabajo se hizo el mismo día y la fila se añade después. Lo detectó validador al revisar la entrega, con grep -rn "04.01.04" 00-direccion/ devolviendo cero. Es el defecto de L-013 de LECCIONES.md, ya anotado en las celdas de 01.02.03 y 01.02.04, y el origen es el reparto, no el ejecutor. MOTIVO: la ficha de 04.01.01 declara eliminatorio su criterio 1 justificándolo con «el lote entero son unos 1.962 € contra un techo de cuenta de 2.000 €» y de ahí […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="38" t="inlineStr">
         <is>
-          <t>04.01</t>
+          <t>04.02</t>
         </is>
       </c>
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>Broker y cajones de datos</t>
+          <t>Investigación de hipótesis</t>
         </is>
       </c>
       <c r="C50" s="39" t="n"/>
@@ -4807,22 +4648,22 @@
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
-        </is>
-      </c>
-      <c r="C51" s="28" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
+          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>02.03.03</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -4831,31 +4672,27 @@
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr"/>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (04/08, dictada por el orquestador): Por qué ahora: 02.03.03 cerró el 03/08 con D-19 y esta tarea quedó desbloqueada; es la única con plazo duro —10/08, sin retorno— y quedan 6 días. Alcance: comparar 3 o 4 brokers que ofrezcan XAUUSD al contado y entregar la tabla para que el CEO firme. PROHIBIDO ELEGIR: la elección es del CEO. Criterios obligatorios, uno por columna: (1) lote mínimo, y si admite fraccionado de 0,1 onzas —es eliminatorio de hecho: el lote entero son unos 1.962 € contra […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
+      <c r="G51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>04.01.02</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02) REQUISITO AÑADIDO 04/08: al recalcular con precios reales se comprueba que la entidad que publica la tarifa es la misma con la que se opera. Si no coinciden, la cifra vieja no se hereda: se vuelve a medir.</t>
+          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -4869,22 +4706,22 @@
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>04.01.03</t>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
+          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -4896,70 +4733,70 @@
       <c r="G53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="38" t="inlineStr">
-        <is>
-          <t>04.02</t>
-        </is>
-      </c>
-      <c r="B54" s="39" t="inlineStr">
-        <is>
-          <t>Investigación de hipótesis</t>
-        </is>
-      </c>
-      <c r="C54" s="39" t="n"/>
-      <c r="D54" s="39" t="n"/>
-      <c r="E54" s="39" t="n"/>
-      <c r="F54" s="39" t="n"/>
-      <c r="G54" s="39" t="n"/>
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>04.02.04</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Validador</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>04.02.03</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>04.02.01</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>03.01.02</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr"/>
-      <c r="G55" s="4" t="inlineStr"/>
+      <c r="A55" s="38" t="inlineStr">
+        <is>
+          <t>04.03</t>
+        </is>
+      </c>
+      <c r="B55" s="39" t="inlineStr">
+        <is>
+          <t>Laboratorio de pruebas (por hipótesis y variante)</t>
+        </is>
+      </c>
+      <c r="C55" s="39" t="n"/>
+      <c r="D55" s="39" t="n"/>
+      <c r="E55" s="39" t="n"/>
+      <c r="F55" s="39" t="n"/>
+      <c r="G55" s="39" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
+          <t>Backtest con costes reales sobre el cajón de construir</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>04.02.01</t>
+          <t>04.01.03, 04.02.04, 04.03.07</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -4973,22 +4810,22 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
+          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -5002,12 +4839,12 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>04.02.04</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
+          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -5017,7 +4854,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -5029,41 +4866,53 @@
       <c r="G58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="38" t="inlineStr">
-        <is>
-          <t>04.03</t>
-        </is>
-      </c>
-      <c r="B59" s="39" t="inlineStr">
-        <is>
-          <t>Laboratorio de pruebas (por hipótesis y variante)</t>
-        </is>
-      </c>
-      <c r="C59" s="39" t="n"/>
-      <c r="D59" s="39" t="n"/>
-      <c r="E59" s="39" t="n"/>
-      <c r="F59" s="39" t="n"/>
-      <c r="G59" s="39" t="n"/>
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>04.03.04</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Validador</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>04.03.03</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Backtest con costes reales sobre el cajón de construir</t>
+          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>04.01.03, 04.02.04, 04.03.07</t>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -5077,109 +4926,113 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.03.06</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
+          <t>NUEVA 03/08 (decisión del CEO, opción B): especificación del motor de backtest propio, escrita para una construcción desde cero y no para un trasplante</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Arquitecto</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>02.03.03</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr"/>
-      <c r="G61" s="4" t="inlineStr"/>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>04/08 — 03-motor/ESPECIFICACION_MOTOR_BACKTEST.md. 16 requisitos, cada uno con su prueba de aceptación ejecutable; 8 casos calculados a mano; 8 exclusiones motivadas y 7 huecos declarados. RECORRIDO: escrita por arquitecto a ciegas —declara no haber abierto 03-motor/backtester/, ni el commit 0c35959, ni /home/server/projects/gold-bot-2, y la prohibición se comprobó pidiéndole la lista de ficheros leídos—; RECHAZADA en ronda 1 por constructor-datos porque R-06(c) era una revisión a ojo y no una prueba ejecutable, más una atribución de fuente desajustada en R-13(b); el orquestador añadió un tercer defecto que la revisión no cazó: tres citas por número de línea en la sección 10, ya caducadas […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (03/08, dictada por el orquestador): Por qué se rehace y no se rescata: el criterio de aceptación anterior vivía en la sección «Trasplante desde gb2 — criterios de aceptación», que la cirugía de D-21 borró y hoy solo existe en el historial de git. Nació describiendo qué se traía y qué se descartaba de otro proyecto, y se escribió el 30/07, antes de D-19 y antes de las mediciones de la Fase 02, así que no dice nada del oro, ni de la vela de 4h, ni del lote mínimo. Insumos obligatorios: los […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.03.07</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
+          <t>NUEVA 03/08 (decisión del CEO, opción B): construir el motor de backtest desde cero contra la especificación de 04.03.06, tras retirar el anterior</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructor de motor</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.03.06, 07.01.03</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr"/>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>04/08 — 03-motor/backtester/. Motor de backtest construido desde cero contra la especificación de 04.03.06. PROCEDENCIA, que era la pregunta que originó esta tarea: INDEPENDIENTE de las dos fuentes. Medido con el procedimiento pre-registrado del lote (d) de 07.01.03, bajo la segunda lectura de gb2 que autorizó el CEO en D-25: 0% de intersección de símbolos contra gb2 y contra el commit retirado 0c35959, con coincidencias de línea de 5,2-12,9% que son boilerplate (import pandas as pd, @dataclass, else:) y ninguna constante de calibración heredada. Contraste: 0c35959 disparaba 66,7% y 100% en ese mismo criterio. Reproducido de forma independiente por el orquestador. ADAPTACIÓN DEL […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (03/08, dictada por el orquestador): PASO 0, que se ejecuta antes que nada: retirar del árbol de trabajo el motor anterior con git revert, sin reescribir historia, para que quien construya no lo tenga delante. El código sigue existiendo en el commit 0c35959 para siempre, y con él sus 44 funciones de prueba —13 en test_costs.py, 20 en test_execution.py y 11 en test_sizing.py, contadas sobre el commit— que la regla 20 de CLAUDE.md obliga a conservar aunque no se usen. Verificado antes de […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="13" t="inlineStr">
-        <is>
-          <t>04.03.04</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Validador</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>04.03.03</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr"/>
+      <c r="A63" s="38" t="inlineStr">
+        <is>
+          <t>04.04</t>
+        </is>
+      </c>
+      <c r="B63" s="39" t="inlineStr">
+        <is>
+          <t>Decisión y bucle</t>
+        </is>
+      </c>
+      <c r="C63" s="39" t="n"/>
+      <c r="D63" s="39" t="n"/>
+      <c r="E63" s="39" t="n"/>
+      <c r="F63" s="39" t="n"/>
+      <c r="G63" s="39" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
+          <t>04.04.01</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Secretario</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
           <t>04.03.05</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>Validador</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>04.03.04</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -5193,113 +5046,97 @@
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>04.03.06</t>
+          <t>04.04.02</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (decisión del CEO, opción B): especificación del motor de backtest propio, escrita para una construcción desde cero y no para un trasplante</t>
+          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Arquitecto</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>02.03.03</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Hecha</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>04/08 — 03-motor/ESPECIFICACION_MOTOR_BACKTEST.md. 16 requisitos, cada uno con su prueba de aceptación ejecutable; 8 casos calculados a mano; 8 exclusiones motivadas y 7 huecos declarados. RECORRIDO: escrita por arquitecto a ciegas —declara no haber abierto 03-motor/backtester/, ni el commit 0c35959, ni /home/server/projects/gold-bot-2, y la prohibición se comprobó pidiéndole la lista de ficheros leídos—; RECHAZADA en ronda 1 por constructor-datos porque R-06(c) era una revisión a ojo y no una prueba ejecutable, más una atribución de fuente desajustada en R-13(b); el orquestador añadió un tercer defecto que la revisión no cazó: tres citas por número de línea en la sección 10, ya caducadas […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (03/08, dictada por el orquestador): Por qué se rehace y no se rescata: el criterio de aceptación anterior vivía en la sección «Trasplante desde gb2 — criterios de aceptación», que la cirugía de D-21 borró y hoy solo existe en el historial de git. Nació describiendo qué se traía y qué se descartaba de otro proyecto, y se escribió el 30/07, antes de D-19 y antes de las mediciones de la Fase 02, así que no dice nada del oro, ni de la vela de 4h, ni del lote mínimo. Insumos obligatorios: los […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>04.03.07</t>
+          <t>04.04.03</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (decisión del CEO, opción B): construir el motor de backtest desde cero contra la especificación de 04.03.06, tras retirar el anterior</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>Constructor de motor</t>
+          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
+        </is>
+      </c>
+      <c r="C66" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>04.03.06, 07.01.03</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Hecha</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>04/08 — 03-motor/backtester/. Motor de backtest construido desde cero contra la especificación de 04.03.06. PROCEDENCIA, que era la pregunta que originó esta tarea: INDEPENDIENTE de las dos fuentes. Medido con el procedimiento pre-registrado del lote (d) de 07.01.03, bajo la segunda lectura de gb2 que autorizó el CEO en D-25: 0% de intersección de símbolos contra gb2 y contra el commit retirado 0c35959, con coincidencias de línea de 5,2-12,9% que son boilerplate (import pandas as pd, @dataclass, else:) y ninguna constante de calibración heredada. Contraste: 0c35959 disparaba 66,7% y 100% en ese mismo criterio. Reproducido de forma independiente por el orquestador. ADAPTACIÓN DEL […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (03/08, dictada por el orquestador): PASO 0, que se ejecuta antes que nada: retirar del árbol de trabajo el motor anterior con git revert, sin reescribir historia, para que quien construya no lo tenga delante. El código sigue existiendo en el commit 0c35959 para siempre, y con él sus 44 funciones de prueba —13 en test_costs.py, 20 en test_execution.py y 11 en test_sizing.py, contadas sobre el commit— que la regla 20 de CLAUDE.md obliga a conservar aunque no se usen. Verificado antes de […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="38" t="inlineStr">
-        <is>
-          <t>04.04</t>
-        </is>
-      </c>
-      <c r="B67" s="39" t="inlineStr">
-        <is>
-          <t>Decisión y bucle</t>
-        </is>
-      </c>
-      <c r="C67" s="39" t="n"/>
-      <c r="D67" s="39" t="n"/>
-      <c r="E67" s="39" t="n"/>
-      <c r="F67" s="39" t="n"/>
-      <c r="G67" s="39" t="n"/>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="36" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B67" s="37" t="inlineStr">
+        <is>
+          <t>DEMO (PUERTA G3) — SE DETALLA AL CERRAR G2</t>
+        </is>
+      </c>
+      <c r="C67" s="37" t="n"/>
+      <c r="D67" s="37" t="n"/>
+      <c r="E67" s="37" t="n"/>
+      <c r="F67" s="37" t="n"/>
+      <c r="G67" s="37" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
+          <t>Bot en demo, solo y con guardias automáticos</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>04.03.05</t>
+          <t>04.04.03</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -5307,28 +5144,32 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>REQUISITO AÑADIDO POR D-14 (01/08): el guardia de parada dura (-30% del capital inicial) lo aplica el BOT de forma CONTINUA, no una revision periodica; comprobado solo una vez al mes, un -30% puede ser un -45% cuando alguien mire. Se verifica por inyeccion antes de declararlo activo (regla 25 de CLAUDE.md).</t>
+        </is>
+      </c>
       <c r="G68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>04.04.02</t>
+          <t>05.01.02</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
+          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -5342,12 +5183,12 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>04.04.03</t>
+          <t>05.01.03</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
+          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
         </is>
       </c>
       <c r="C70" s="28" t="inlineStr">
@@ -5357,7 +5198,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>05.01.02</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -5371,12 +5212,12 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="36" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="B71" s="37" t="inlineStr">
         <is>
-          <t>DEMO (PUERTA G3) — SE DETALLA AL CERRAR G2</t>
+          <t>REAL (PUERTA G4) — SE DETALLA AL CERRAR G3</t>
         </is>
       </c>
       <c r="C71" s="37" t="n"/>
@@ -5388,12 +5229,12 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>06.01.01</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Bot en demo, solo y con guardias automáticos</t>
+          <t>Dinero pequeño respetando los límites de 01.01.03</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -5403,7 +5244,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>04.04.03</t>
+          <t>05.01.03</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -5413,7 +5254,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>REQUISITO AÑADIDO POR D-14 (01/08): el guardia de parada dura (-30% del capital inicial) lo aplica el BOT de forma CONTINUA, no una revision periodica; comprobado solo una vez al mes, un -30% puede ser un -45% cuando alguien mire. Se verifica por inyeccion antes de declararlo activo (regla 25 de CLAUDE.md).</t>
+          <t>limites ya escritos y firmados (D-14, 01/08): capital 1.000-2.000 €, AVISO a -25% del capital inicial que no para nada, PARADA DURA AUTOMATICA a -30% aplicada por el bot de forma continua y sin exencion activable desde dentro (regla 26 de CLAUDE.md).</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr"/>
@@ -5421,22 +5262,22 @@
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>05.01.02</t>
+          <t>06.01.02</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>Secretario</t>
+          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
+        </is>
+      </c>
+      <c r="C73" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>06.01.01</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -5447,104 +5288,112 @@
       <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="inlineStr"/>
     </row>
-    <row r="74">
-      <c r="A74" s="13" t="inlineStr">
-        <is>
-          <t>05.01.03</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
-        </is>
-      </c>
-      <c r="C74" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>05.01.02</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="36" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B74" s="37" t="inlineStr">
+        <is>
+          <t>MOTOR Y ORDEN (PARALELA; MÁX. 20% DEL ESFUERZO SEMANAL)</t>
+        </is>
+      </c>
+      <c r="C74" s="37" t="n"/>
+      <c r="D74" s="37" t="n"/>
+      <c r="E74" s="37" t="n"/>
+      <c r="F74" s="37" t="n"/>
+      <c r="G74" s="37" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>07.01.01</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>03.01.01</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr"/>
-      <c r="G74" s="4" t="inlineStr"/>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="36" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="B75" s="37" t="inlineStr">
-        <is>
-          <t>REAL (PUERTA G4) — SE DETALLA AL CERRAR G3</t>
-        </is>
-      </c>
-      <c r="C75" s="37" t="n"/>
-      <c r="D75" s="37" t="n"/>
-      <c r="E75" s="37" t="n"/>
-      <c r="F75" s="37" t="n"/>
-      <c r="G75" s="37" t="n"/>
+      <c r="F75" s="4" t="inlineStr"/>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (02/08): ALCANCE — cuatro arreglos de documento, NINGUNO toca código: (a) Las celdas ESTADO de 01.02.04 y 03.01.12 declaran en negrita un estado del vocabulario pendiente / en_curso / hecha / bloqueada, como exige la sección «Estados y cadencia de este WBS». Valores ya decididos por el orquestador, no se deducen: 01.02.04 pasa a en_curso (entregado INFORME_MCP_2.md, RECHAZADO por critico-codigo, sin reparar); 03.01.12 pasa a pendiente (nadie la ha trabajado). En 01.02.04 la marca actual […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>06.01.01</t>
+          <t>07.01.03</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Dinero pequeño respetando los límites de 01.01.03</t>
+          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>05.01.03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>limites ya escritos y firmados (D-14, 01/08): capital 1.000-2.000 €, AVISO a -25% del capital inicial que no para nada, PARADA DURA AUTOMATICA a -30% aplicada por el bot de forma continua y sin exencion activable desde dentro (regla 26 de CLAUDE.md).</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr"/>
+          <t>2ª AMPLIACIÓN 03/08, decisión del CEO — opción B: el motor de backtest se tira y se construye de cero. Consecuencias sobre esta tarea: los lotes (e1) y (e2) de aptitud QUEDAN CANCELADOS — juzgar si sirve un código que se borra es gastar la verificación en un cadáver. No se pierde su contenido: su eje A3, que no juzgaba al motor viejo sino que describía qué debe hacer cualquier motor para servir a D-19, migra íntegro a la especificación nueva (tarea 04.03.06). El lote (d) SE MANTIENE, recortado a la medición mecánica, por tres motivos: D-21 afirma en un registro de solo-añadir que no se copió una sola línea de gb2 y esa mitad sigue sin comprobar; la autorización de una sola apertura que dio […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (03/08, dictada por el orquestador): Qué pasó, medido y no supuesto: tras un /compact a las 21:29, la sesión recibió una orden del CEO a las 21:44 y trabajó sola hasta las 21:58 sin invocar a un solo subagente. Escribió D-19, D-20 y D-21 en un registro de solo-añadir, L-024 a L-027, cirugía estructural sobre el WBS, y dos scripts del Excel del CEO. Nadie lo revisó (regla 16 de CLAUDE.md y C2 rotas). Alcance: tres lotes con veredicto propio — (d) procedencia del motor de backtest, (b y c) […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>06.01.02</t>
+          <t>07.01.02</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
-        </is>
-      </c>
-      <c r="C77" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>06.01.01</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -5555,129 +5404,13 @@
       <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="inlineStr"/>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="36" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="B78" s="37" t="inlineStr">
-        <is>
-          <t>MOTOR Y ORDEN (PARALELA; MÁX. 20% DEL ESFUERZO SEMANAL)</t>
-        </is>
-      </c>
-      <c r="C78" s="37" t="n"/>
-      <c r="D78" s="37" t="n"/>
-      <c r="E78" s="37" t="n"/>
-      <c r="F78" s="37" t="n"/>
-      <c r="G78" s="37" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="13" t="inlineStr">
-        <is>
-          <t>07.01.01</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>03.01.01</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr"/>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (02/08): ALCANCE — cuatro arreglos de documento, NINGUNO toca código: (a) Las celdas ESTADO de 01.02.04 y 03.01.12 declaran en negrita un estado del vocabulario pendiente / en_curso / hecha / bloqueada, como exige la sección «Estados y cadencia de este WBS». Valores ya decididos por el orquestador, no se deducen: 01.02.04 pasa a en_curso (entregado INFORME_MCP_2.md, RECHAZADO por critico-codigo, sin reparar); 03.01.12 pasa a pendiente (nadie la ha trabajado). En 01.02.04 la marca actual […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="13" t="inlineStr">
-        <is>
-          <t>07.01.03</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Orquestador</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>2ª AMPLIACIÓN 03/08, decisión del CEO — opción B: el motor de backtest se tira y se construye de cero. Consecuencias sobre esta tarea: los lotes (e1) y (e2) de aptitud QUEDAN CANCELADOS — juzgar si sirve un código que se borra es gastar la verificación en un cadáver. No se pierde su contenido: su eje A3, que no juzgaba al motor viejo sino que describía qué debe hacer cualquier motor para servir a D-19, migra íntegro a la especificación nueva (tarea 04.03.06). El lote (d) SE MANTIENE, recortado a la medición mecánica, por tres motivos: D-21 afirma en un registro de solo-añadir que no se copió una sola línea de gb2 y esa mitad sigue sin comprobar; la autorización de una sola apertura que dio […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (03/08, dictada por el orquestador): Qué pasó, medido y no supuesto: tras un /compact a las 21:29, la sesión recibió una orden del CEO a las 21:44 y trabajó sola hasta las 21:58 sin invocar a un solo subagente. Escribió D-19, D-20 y D-21 en un registro de solo-añadir, L-024 a L-027, cirugía estructural sobre el WBS, y dos scripts del Excel del CEO. Nadie lo revisó (regla 16 de CLAUDE.md y C2 rotas). Alcance: tres lotes con veredicto propio — (d) procedencia del motor de backtest, (b y c) […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="13" t="inlineStr">
-        <is>
-          <t>07.01.02</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>03.01.02</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr"/>
-      <c r="G81" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:G81"/>
+  <autoFilter ref="A4:G77"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E81">
+  <conditionalFormatting sqref="E5:E77">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecha"</formula>
     </cfRule>
@@ -5689,7 +5422,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,Hecha,Bloqueada"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6506,7 +6239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6516,7 +6249,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LAS 29 REGLAS — mandan sobre cualquier otra instruccion</t>
+          <t>LAS 30 REGLAS — mandan sobre cualquier otra instruccion</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6603,229 +6336,239 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cada tirada autónoma cierra al menos una tarea que avanza el PRODUCTO. La infraestructura que no desbloquee mecánicamente una tarea de producto se registra como deuda y no se ejecuta sin permiso del CEO.</t>
+          <t>Ningún criterio de hecho exige una herramienta que el ejecutor no tiene. Antes de escribirlo, se localiza por grep la línea tools: del agente que va a ejecutarlo. Si la prueba exige algo que no aparece ahí, la prueba se traslada al revisor. Un agente al que se le pide lo imposible no falla: fabrica, y el fallo se le acaba imputando a él en vez de a quien repartió. (D-34, 10/08/2026.)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>El trabajo de motor y orden tiene un techo del 20% del esfuerzo semanal. Si en una tirada solo hay tareas de motor disponibles, para y avisa: es señal de que la cola está mal llena.</t>
+          <t>Cada tirada autónoma cierra al menos una tarea que avanza el PRODUCTO. La infraestructura que no desbloquee mecánicamente una tarea de producto se registra como deuda y no se ejecuta sin permiso del CEO.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Jerarquía de la prueba. Ninguna afirmación se acepta por consenso entre agentes:</t>
+          <t>El trabajo de motor y orden tiene un techo del 20% del esfuerzo semanal. Si en una tirada solo hay tareas de motor disponibles, para y avisa: es señal de que la cola está mal llena.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Quien discrepa aporta el experimento que zanjaría la discusión, no otro argumento. Si no hay experimento posible, sube al CEO marcado como no probado.</t>
+          <t>Jerarquía de la prueba. Ninguna afirmación se acepta por consenso entre agentes:</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Un fallo reportado por un agente no es un fallo verificado. Antes de encolar o reparar: lee el componente y reproduce el fallo.</t>
+          <t>Quien discrepa aporta el experimento que zanjaría la discusión, no otro argumento. Si no hay experimento posible, sube al CEO marcado como no probado.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Ninguna referencia a una decisión entra en código o informe sin un grep previo que la localice por fichero y línea. Solo se cita lo firmado y guardado, nunca en pasado ni antes de existir.</t>
+          <t>Un fallo reportado por un agente no es un fallo verificado. Antes de encolar o reparar: lee el componente y reproduce el fallo.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Se referencia por nombre de símbolo, nunca por número de línea.</t>
+          <t>Ninguna referencia a una decisión entra en código o informe sin un grep previo que la localice por fichero y línea. Solo se cita lo firmado y guardado, nunca en pasado ni antes de existir.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Todo dato numérico se calcula sobre datos brutos, salvo que exista una fuente primaria homogénea demostrable.</t>
+          <t>Se referencia por nombre de símbolo, nunca por número de línea.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Quien implementa ejecuta y lee su artefacto completo antes de entregar. Las puertas confirman, no descubren.</t>
+          <t>Todo dato numérico se calcula sobre datos brutos, salvo que exista una fuente primaria homogénea demostrable.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Nadie valida su propio trabajo. Quien construye no revisa; quien produce las métricas no firma el veredicto.</t>
+          <t>Quien implementa ejecuta y lee su artefacto completo antes de entregar. Las puertas confirman, no descubren.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Éxito = código fiel a la especificación, NO estrategia rentable. Un backtest con mal resultado y código correcto es un éxito registrable.</t>
+          <t>Nadie valida su propio trabajo. Quien construye no revisa; quien produce las métricas no firma el veredicto.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Test de compuerta: si la justificación de un cambio no se sostiene sin citar métricas de resultado, se deniega.</t>
+          <t>Éxito = código fiel a la especificación, NO estrategia rentable. Un backtest con mal resultado y código correcto es un éxito registrable.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Pre-registro: ninguna variante se prueba sin estar registrada antes (máx. 5-7 por hipótesis). Lo no registrado no se prueba.</t>
+          <t>Test de compuerta: si la justificación de un cambio no se sostiene sin citar métricas de resultado, se deniega.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Se guardan TODAS las pruebas, también las fallidas. Saber cuántas cosas se probaron es lo que permite juzgar si la ganadora es real o casualidad.</t>
+          <t>Pre-registro: ninguna variante se prueba sin estar registrada antes (máx. 5-7 por hipótesis). Lo no registrado no se prueba.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Registros que solo permiten añadir: 04-resultados/registro-pruebas.md y 00-direccion/DECISIONES.md nunca se reescriben. Una corrección es una entrada nueva.</t>
+          <t>Se guardan TODAS las pruebas, también las fallidas. Saber cuántas cosas se probaron es lo que permite juzgar si la ganadora es real o casualidad.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>El cajón 02-datos/reservado/ no se abre. Solo el CEO puede autorizar su uso, una vez por variante. Ningún agente, ningún debate, ninguna urgencia.</t>
+          <t>Registros que solo permiten añadir: 04-resultados/registro-pruebas.md y 00-direccion/DECISIONES.md nunca se reescriben. Una corrección es una entrada nueva.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Dos niveles. Lo REVERSIBLE (archivos, código, pruebas) tiene permisos amplios: git lo deshace. Lo IRREVERSIBLE (dinero real, órdenes al broker, borrar el cajón reservado, gastar dinero nuevo) lleva barrera desde el minuto uno.</t>
+          <t>El cajón 02-datos/reservado/ no se abre. Solo el CEO puede autorizar su uso, una vez por variante. Ningún agente, ningún debate, ninguna urgencia.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Una restricción solo se añade tras un incidente real, anotada junto al incidente, y se revisa cada mes. La que no tenga incidente vivo detrás, se quita.</t>
+          <t>Dos niveles. Lo REVERSIBLE (archivos, código, pruebas) tiene permisos amplios: git lo deshace. Lo IRREVERSIBLE (dinero real, órdenes al broker, borrar el cajón reservado, gastar dinero nuevo) lleva barrera desde el minuto uno.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Toda barrera se verifica por ejecución —inyectando el caso prohibido— antes de documentarla como activa. Sin prueba: "no verificada". Un guardia presente en el código no es un guardia probado.</t>
+          <t>Una restricción solo se añade tras un incidente real, anotada junto al incidente, y se revisa cada mes. La que no tenga incidente vivo detrás, se quita.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Los guardias bloquean por defecto. La condición que activa una exención debe ser un hecho impuesto por el sistema, nunca un dato que elija el vigilado.</t>
+          <t>Toda barrera se verifica por ejecución —inyectando el caso prohibido— antes de documentarla como activa. Sin prueba: "no verificada". Un guardia presente en el código no es un guardia probado.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Los datos nunca entran en git. Se descargan con script. Comprobar el día 1 que .gitignore funciona de verdad.</t>
+          <t>Los guardias bloquean por defecto. La condición que activa una exención debe ser un hecho impuesto por el sistema, nunca un dato que elija el vigilado.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Una sola fuente de verdad por tema. Documento que se sustituye, se borra: git guarda el historial.</t>
+          <t>Los datos nunca entran en git. Se descargan con script. Comprobar el día 1 que .gitignore funciona de verdad.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Una sola fuente de verdad por tema. Documento que se sustituye, se borra: git guarda el historial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Cada agente lleva el identificador exacto de su modelo, nunca un alias, y ningún agente sin modelo.</t>
         </is>
@@ -6846,7 +6589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6858,7 +6601,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REGISTRO DE DECISIONES (27) — solo se añade, nunca se reescribe (regla 21 de CLAUDE.md)</t>
+          <t>REGISTRO DE DECISIONES (30) — solo se añade, nunca se reescribe (regla 21 de CLAUDE.md)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7568,7 +7311,86 @@
 Consecuencia: toda sesión de Claude Code en esta máquina —interactiva o desatendida— se aprueba a sí misma las herramientas; no existe filtro humano de permisos en ninguna de las sesiones anteriores ni en esta.
 Lo único que sigue frenando es la lista deny de .claude/settings.json del proyecto, que constructor-motor comprobó POR EJECUCIÓN que sigue mordiendo bajo bypass (una llamada con --no-verify fue denegada y quedó registrada en permission_denials).
 Este fichero de usuario no lo ha tocado ningún agente hoy y NO se ha modificado: la decisión de dejarlo o revertirlo es del CEO.
-Confirmación del CEO sobre ESTE TEXTO: CONFIRMADA el 04/08/2026.</t>
+Confirmación del CEO sobre ESTE TEXTO: CONFIRMADA el 04/08/2026.
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>D-28</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Confirmadas las tres correcciones de hecho (D-22, D-23, D-24)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Qué se confirma. Ninguna de las tres cambia nada de lo ya hecho: solo ponen el registro de acuerdo con lo medido.
+1. D-22: la decisión del CEO del 03/08 — tirar el motor de backtest anterior y construir uno nuevo desde cero.
+2. D-23: el motor retirado sí copiaba 109 líneas del proyecto anterior (gb2); antes se había escrito que ninguna.
+3. D-24, sobre D-21: el criterio de aceptación del motor se perdió al eliminar la sección de trasplante; hubo que reconstruirlo en la tarea 04.03.06.
+4. D-24, sobre D-20: los muros mecánicos del proyecto sí existen, desde el 31/07/2026.
+5. D-24, sobre D-22: la cronología de D-22 estaba invertida — el motor entró antes de que existiera la orden que supuestamente contradecía.
+Decide: CEO, 09/08/2026, opción A de 00-direccion/informes/FICHA_D-28.md (confirma las tres tal como están). Palabras literales del CEO: «a la 28 y 29 respondo A a las dos».
+Qué […] texto completo en 00-direccion/DECISIONES.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>D-29</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Se autorizan las CUATRO barreras de seguridad (a, b, c, d)</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Las cuatro nacen de una inyección ejecutada con su salida guardada, no de una sospecha, y ninguna causó daño (regla 24 de CLAUDE.md). Cada una se verifica por inyección ANTES de documentarse como activa (regla 25 de CLAUDE.md).
+(a) El patrón que protege el cajón reservado tiene un agujero. Bash( 02-datos/reservado) de .claude/settings.json exige un espacio literal y no cubre la ruta pegada a una comilla: una línea de python lo esquiva. Ese intento lo paró otra capa, no determinista, con la que no se puede contar. Y desde el 04/08 esa lista deny es lo único que frena, porque D-27 de este mismo fichero dejó registrado que la máquina corre en bypassPermissions y ninguna sesión pide permiso. El contenido sigue cifrado y la clave solo la tiene el CEO. Comprobado el 05/08 leyendo el fichero de configuración, no por reporte de agente.
+(b) Los datos descargados se pueden borrar sin […] texto completo en 00-direccion/DECISIONES.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>D-34</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Herramientas de los agentes: la prueba que el ejecutor no puede hacer se traslada al revisor</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Qué se decide. Opción B de 00-direccion/informes/FICHA_D-34.md. Palabras literales del CEO, 10/08/2026: «continua, para la 34 marca la b».
+Qué significa. Ningún criterio de hecho puede exigir una comprobación que las herramientas declaradas en la línea tools: del agente que lo ejecuta no le permitan hacer. Antes de escribir un criterio de hecho se localiza esa línea por grep; si la prueba exige algo que no aparece en ella, la prueba se traslada al revisor, que sí la tiene. Queda escrito como regla 30 de CLAUDE.md.
+Qué NO hace. No cambia la línea tools: de ningún agente. En particular, secretario sigue sin Bash.
+Por qué ésta y no repartir herramientas. Del diagnóstico de 03.01.15 en 04-resultados/diagnostico_03.01.15_herramientas_agentes.md, con los ocho agentes barridos: los fallos medidos son de dos clases y solo una la arregla una herramienta. Un agente sin Bash declaró una cifra […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>
@@ -7587,7 +7409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7600,7 +7422,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LECCIONES APRENDIDAS (36)</t>
+          <t>LECCIONES APRENDIDAS (41)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8676,6 +8498,165 @@
       <c r="E40" s="4" t="inlineStr">
         <is>
           <t>05/08/2026, escritura de las cuatro celdas del lote C. Las filas rotas las cazó Claude Code en su filtro, no el revisor. Es la tercera lección incumplida el mismo día: L-023 (que produjo L-034) y L-027 (que produce ésta). El fallo de origen lo declaró el propio orquestador: su reparto exigía lo imposible (regla 6 de CLAUDE.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>L-037</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Quien reparte dictó para el CEO una frase más fuerte que su celda, el mismo día que ordenaba cazar eso mismo</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>el orquestador dictó el fondo de la ficha D-29 y escribió «el cajón reservado se puede leer esquivando el permiso… comprobado por ejecución». Lo comprobado el 05/08 en 03.01.08 es otra cosa: el patrón Bash( 02-datos/reservado) exige un espacio literal y no cubre la ruta pegada a una comilla, y ese intento «la paró una capa distinta y no determinista»; el contenido además sigue cifrado (D-10). Hueco de diseño probado, lectura no lograda. En la misma tirada, ese mismo orquestador ordenaba a un […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>L-030 se aplica también —y sobre todo— a la ficha de decisión del CEO, que es el resumen que llega más arriba, y también cuando el texto lo dicta quien reparte. Toda afirmación de hecho de una ficha se localiza en su celda de origen antes de entregarla, y quien la dicta no queda exento por dictarla. Añadido: un estado de tarea citado en una ficha se lee del WBS, no del informe de estado que lo […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>06/08/2026, ronda 1 de FICHA_D-29. H2 lo detectó critico-codigo localizando la celda de 03.01.08; el estado falso lo detectó el orquestador al juzgar, con awk sobre el WBS. En la misma ronda el revisor atribuyó al secretario una frase que había dictado el orquestador, sin localizarla en su origen: L-033 otra vez, ahora dentro del hallazgo que sí era bueno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>L-038</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Se declaró no comprobable el origen de un texto dictado, buscándolo donde no estaba</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>en la ronda 2 de la ficha D-29, critico-codigo intentó averiguar quién había
+escrito «cuatro arreglos pequeños», buscó con grep -rn sobre 00-direccion/ y concluyó, con
+razón para ese ámbito, que la autoría no era comprobable a nivel 1 ni 2. El orquestador había
+afirmado que era suya, lo que sin prueba es nivel 3. El texto sí estaba en disco: las órdenes
+de reparto viven en los transcripts de sesión, ficheros .jsonl bajo el directorio de proyectos de
+Claude Code —la misma clase de fuente que la […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>un texto dictado por un agente no es prueba perdida. Antes de declarar una autoría o una
+procedencia «no comprobable», se busca también en los transcripts de sesión y se distingue el rol de
+la entrada: un assistant es producción y un user puede ser la misma frase volviendo. Y la que
+duele: quien afirma su propia autoría está dando nivel 3 sobre sí mismo; si hay fichero, se cita
+el fichero.</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>06/08/2026, ronda 2 de FICHA_D-29. Reparo levantado por critico-codigo, localización
+aportada por Claude Code y verificada por el orquestador: entrada 48 de
+agent-abddab6a788baa2d2.jsonl, role: assistant, model: claude-opus-5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>L-039</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Una orden de reparto añadió filtros que la ficha no tenía, y el ejecutor eliminó por el CEO sin saberlo</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>la instrucción P8 de la orden del 06/08 pidió juzgar la tabla de brokers por «los criterios eliminatorios — 1, 10, 5 (demo) y 6 (API)». La ficha de 04.01.01 no declara eliminatorios ni el 5 ni el 6: grep -on "eliminatori[a-z]*" 00-direccion/WBS.md devuelve UNA aparición, línea 129, pegada al criterio 1, y de la API la ficha solo dice que hará falta en 03.01.03 y 05.01.01, tareas futuras y no condición para firmar. Con el 6 como filtro, el veredicto declaró eliminado al único bróker con fuente […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>quien reparte no añade criterios de exclusión que no estén en la ficha. Todo filtro que se pase a un ejecutor lleva pegada su localización por grep en la ficha o en la decisión que lo creó; filtro sin localización no se pasa. Y todo veredicto que EXCLUYA candidatos se comprueba contra el criterio con el que los excluye antes de aceptarlo: un ejecutor obediente convierte un filtro inventado en […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>06/08/2026, ronda 2 de 04.01.01. Detectado por critico-codigo auditando el veredicto del validador, que lo había firmado obedeciendo la orden. El auditor lo atribuyó al validador; la comprobación por el método de L-038 lo devolvió a su origen — entrada 48 de agent-abddab6a788baa2d2.jsonl, role: assistant, model: claude-opus-5: lo dictó el orquestador. Segunda vez el mismo día que un hallazgo […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>L-040</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Un texto que cita un grep sobre el fichero donde se escribe rompe su propia prueba al guardarse</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>el cierre de 04.01.01 y la lección L-039 afirman que la palabra «eliminatorio»
+«aparece una sola vez en el WBS». Era cierto al repartir la orden y falso en el instante de
+guardarse: el propio párrafo que lo afirma introduce dos apariciones más. Medido —
+grep -on "eliminatori[a-z]*" 00-direccion/WBS.md da 1 sobre el commit da93597 y 3 sobre
+el fichero después de la pasada, las tres en la línea 129. El fondo del hallazgo no cambia: que
+la instrucción P8 añadió como eliminatorios los criterios 5 y […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>toda cifra de recuento se ancla al objeto inmutable sobre el que se midió —un commit o un
+blob de git hash-object—, nunca al fichero vivo en el que se está escribiendo. Y todo recuento que
+vaya a vivir dentro del mismo fichero que cuenta se vuelve a ejecutar DESPUÉS de escribirlo: si
+el número cambió, lo cambió el texto. Heredar una cifra correcta del momento en que otro la calculó
+es justo lo […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>06/08/2026, auditoría del cierre de 04.01.01 por critico-codigo, que ejecutó el mismo
+grep sobre el punto de control y sobre el fichero posterior y obtuvo 1 frente a 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>L-041</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>El mensaje de reparto no es el registro. Lo que no está en el fichero que manda, no existe.</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>una orden de reparto no crea nada. Antes de mandar ejecutar: la fila de la tarea está
+en el WBS o no se manda · la línea tools: del agente que ejecuta se localiza por grep y ningún
+criterio de hecho exige una herramienta que no aparezca en ella, y si la exige **la prueba se
+traslada al revisor** · todo L-NN o D-NN citado se localiza por grep antes de pasarlo · y
+ninguna cifra de recuento se dicta […] texto completo en 00-direccion/LECCIONES.md</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>09/08/2026. Casos 1 y 2 detectados por critico-codigo; caso 3 por validador; caso 4
+por critico-codigo sobre la propia frase escrita para confesar el caso 1. Los cuatro reproducidos
+por el orquestador antes de juzgar.
+Anclaje de la cifra (añadido el 09/08/2026 por el orquestador al ordenar el pegado; no forma parte del texto dictado en el parte y por eso va firmado aparte). La frase del punto […] texto completo en 00-direccion/LECCIONES.md</t>
         </is>
       </c>
     </row>

--- a/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
+++ b/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
@@ -1428,7 +1428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1527,7 +1527,7 @@
       <c r="B6" s="30" t="n"/>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>04.02.01 — Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente. Detras de ella esperan 16 de las 37 tareas vivas.</t>
+          <t>04.02.01 — Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente. Detras de ella esperan 16 de las 36 tareas vivas.</t>
         </is>
       </c>
       <c r="D6" s="30" t="n"/>
@@ -1591,7 +1591,7 @@
     <row r="9">
       <c r="A9" s="32" t="inlineStr">
         <is>
-          <t>SE PUEDE TRABAJAR YA — 16 tareas, en este orden</t>
+          <t>SE PUEDE TRABAJAR YA — 15 tareas, en este orden</t>
         </is>
       </c>
       <c r="B9" s="32" t="n"/>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B23" s="33" t="inlineStr">
         <is>
-          <t>03.01.18</t>
+          <t>07.01.01</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (D-20, idea 1 de las auditorías): contador mecánico del reparto producto/motor, inyectado en el contexto al arrancar cada tirada</t>
+          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>07.01.01</t>
+          <t>07.01.02</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
+          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -2183,56 +2183,58 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>07.01.02</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E25" s="34" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>ESPERANDO A OTRA TAREA — 21 tareas, en orden de codigo WBS</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="32" t="n"/>
+      <c r="E25" s="32" t="n"/>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="32" t="n"/>
+      <c r="H25" s="32" t="n"/>
+      <c r="I25" s="32" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="inlineStr">
+        <is>
+          <t>03.01.05</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
+        </is>
+      </c>
+      <c r="E26" s="34" t="inlineStr">
         <is>
           <t>MOTOR</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>nada: se puede empezar ya</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="32" t="inlineStr">
-        <is>
-          <t>ESPERANDO A OTRA TAREA — 21 tareas, en orden de codigo WBS</t>
-        </is>
-      </c>
-      <c r="B26" s="32" t="n"/>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="32" t="n"/>
-      <c r="E26" s="32" t="n"/>
-      <c r="F26" s="32" t="n"/>
-      <c r="G26" s="32" t="n"/>
-      <c r="H26" s="32" t="n"/>
-      <c r="I26" s="32" t="n"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2242,17 +2244,17 @@
       </c>
       <c r="B27" s="33" t="inlineStr">
         <is>
-          <t>03.01.05</t>
+          <t>03.01.07</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
+          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E27" s="34" t="inlineStr">
@@ -2269,7 +2271,7 @@
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
+          <t>03.01.06 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -2281,17 +2283,17 @@
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>03.01.07</t>
+          <t>03.01.11</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E28" s="34" t="inlineStr">
@@ -2299,16 +2301,16 @@
           <t>MOTOR</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>03.01.06 (pendiente, Secretario)</t>
+          <t>03.01.08 (en curso, Crítico)</t>
         </is>
       </c>
     </row>
@@ -2320,34 +2322,34 @@
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>03.01.11</t>
+          <t>04.01.02</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
+          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02) REQUISITO AÑADIDO 04/08: al recalcular con precios reales se comprueba que la entidad que publica la tarifa es la misma con la que se opera. Si no coinciden, la cifra vieja no se hereda: se vuelve a medir.</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="E29" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>En curso</t>
+          <t>Constructor datos</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>03.01.08 (en curso, Crítico)</t>
+          <t>04.01.01 (en curso, CEO + Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2359,12 +2361,12 @@
       </c>
       <c r="B30" s="33" t="inlineStr">
         <is>
-          <t>04.01.02</t>
+          <t>04.01.03</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02) REQUISITO AÑADIDO 04/08: al recalcular con precios reales se comprueba que la entidad que publica la tarifa es la misma con la que se opera. Si no coinciden, la cifra vieja no se hereda: se vuelve a medir.</t>
+          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2382,8 +2384,12 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
           <t>04.01.01 (en curso, CEO + Orquestador)</t>
@@ -2398,17 +2404,17 @@
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>04.01.03</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
+          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2425,11 +2431,11 @@
         <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>04.01.01 (en curso, CEO + Orquestador)</t>
+          <t>04.02.01 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -2441,17 +2447,17 @@
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
+          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2468,11 +2474,11 @@
         <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>04.02.01 (pendiente, Investigador)</t>
+          <t>04.02.02 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2490,12 @@
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.02.04</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
+          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2511,11 +2517,11 @@
         <v>1</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>04.02.02 (pendiente, Investigador)</t>
+          <t>04.02.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2527,17 +2533,17 @@
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>04.02.04</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
+          <t>Backtest con costes reales sobre el cajón de construir</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2554,11 +2560,11 @@
         <v>1</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>04.02.03 (pendiente, Validador)</t>
+          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2570,12 +2576,12 @@
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Backtest con costes reales sobre el cajón de construir</t>
+          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2597,11 +2603,11 @@
         <v>1</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
+          <t>04.03.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2613,17 +2619,17 @@
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
+          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2640,11 +2646,11 @@
         <v>1</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>04.03.01 (pendiente, Constructores)</t>
+          <t>04.03.02 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2656,12 +2662,12 @@
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
+          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2683,11 +2689,11 @@
         <v>1</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>04.03.02 (pendiente, Constructores)</t>
+          <t>04.03.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2699,12 +2705,12 @@
       </c>
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2726,11 +2732,11 @@
         <v>1</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>04.03.03 (pendiente, Validador)</t>
+          <t>04.03.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2742,17 +2748,17 @@
       </c>
       <c r="B39" s="33" t="inlineStr">
         <is>
-          <t>04.03.05</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
+          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2766,14 +2772,14 @@
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>04.03.04 (pendiente, Validador)</t>
+          <t>04.03.05 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2785,17 +2791,17 @@
       </c>
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.04.02</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
+          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2808,15 +2814,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>7</v>
-      </c>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>04.03.05 (pendiente, Validador)</t>
+          <t>04.04.01 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -2828,17 +2830,17 @@
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>04.04.02</t>
+          <t>04.04.03</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Orquestador</t>
+          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
+        </is>
+      </c>
+      <c r="D41" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -2851,8 +2853,12 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
           <t>04.04.01 (pendiente, Secretario)</t>
@@ -2867,17 +2873,17 @@
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>04.04.03</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
-        </is>
-      </c>
-      <c r="D42" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Bot en demo, solo y con guardias automáticos</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -2894,11 +2900,11 @@
         <v>1</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>04.04.01 (pendiente, Secretario)</t>
+          <t>04.04.03 (pendiente, CEO)</t>
         </is>
       </c>
     </row>
@@ -2910,17 +2916,17 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>05.01.02</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Bot en demo, solo y con guardias automáticos</t>
+          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -2937,11 +2943,11 @@
         <v>1</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>04.04.03 (pendiente, CEO)</t>
+          <t>05.01.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2959,17 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>05.01.02</t>
+          <t>05.01.03</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Secretario</t>
+          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
+        </is>
+      </c>
+      <c r="D44" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -2980,11 +2986,11 @@
         <v>1</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>05.01.01 (pendiente, Constructores)</t>
+          <t>05.01.02 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -2996,17 +3002,17 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>05.01.03</t>
+          <t>06.01.01</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
-        </is>
-      </c>
-      <c r="D45" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Dinero pequeño respetando los límites de 01.01.03</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3023,11 +3029,11 @@
         <v>1</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>05.01.02 (pendiente, Secretario)</t>
+          <t>05.01.03 (pendiente, CEO)</t>
         </is>
       </c>
     </row>
@@ -3039,17 +3045,17 @@
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>06.01.01</t>
+          <t>06.01.02</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Dinero pequeño respetando los límites de 01.01.03</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
+          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
+        </is>
+      </c>
+      <c r="D46" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3062,76 +3068,33 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>05.01.03 (pendiente, CEO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B47" s="33" t="inlineStr">
-        <is>
-          <t>06.01.02</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
-        </is>
-      </c>
-      <c r="D47" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
           <t>06.01.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="46" customHeight="1">
-      <c r="A49" s="35" t="inlineStr">
-        <is>
-          <t>Aviso de la regla 8 (CLAUDE.md): si la cola de arriba solo tuviera tareas de MOTOR, hay que parar y avisar al CEO; significa que la cola esta mal llena. Ahora mismo la cola tiene 3 de producto y 13 de motor.</t>
+    <row r="48" ht="46" customHeight="1">
+      <c r="A48" s="35" t="inlineStr">
+        <is>
+          <t>Aviso de la regla 8 (CLAUDE.md): si la cola de arriba solo tuviera tareas de MOTOR, hay que parar y avisar al CEO; significa que la cola esta mal llena. Ahora mismo la cola tiene 3 de producto y 12 de motor.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A26:I26"/>
     <mergeCell ref="C6:H6"/>
+    <mergeCell ref="A25:I25"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A49:I49"/>
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A48:I48"/>
     <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4353,15 +4316,15 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (03/08): Problema, medido y no supuesto: el techo del 20% de motor de la regla 8 de CLAUDE.md es prosa y nadie lo mide. La primera vez que se midió, el 01/08, el reparto real era 7 de 16 commits, 43,8%, más del doble del techo, y el proyecto llevaba desde el arranque sin saberlo. Qué se construye: un hook SessionStart que calcula el reparto desde git log y lo inyecta en el contexto con hookSpecificOutput.additionalContext, de forma que cada tirada empiece con el número delante en vez de […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>12/08 — contador .claude/hooks/contador_producto_motor.py, hook SessionStart montado; reproduce 43,8% sobre los 16 commits del 01/08 FICHA (03/08): Problema, medido y no supuesto: el techo del 20% de motor de la regla 8 de CLAUDE.md es prosa y nadie lo mide. La primera vez que se midió, el 01/08, el reparto real era 7 de 16 commits, 43,8%, más del doble del techo, y el proyecto llevaba desde el arranque sin saberlo. Qué se construye: un hook SessionStart que calcula el reparto desde git log y lo inyecta en el contexto con hookSpecificOutput.additionalContext, de forma que cada tirada empiece con el número delante en vez de con la buena intención. Regla de clasificación obligatoria, ya […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">

--- a/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
+++ b/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
@@ -3293,10 +3293,14 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>01/08 — los tres limites firmados como D-12, D-13 y D-14** y escritos en la seccion «Limites del CEO» de este WBS. (1) FECHA TOPE 01/12/2026 + revision de avance el dia 1 de cada mes con poder de parar; GM gana una cuarta salida (parar). (2) 1 h los lunes como MINIMO garantizado, no techo, con tope de 5 fichas por revision. (3) DINERO REAL: aviso a -25% que no para nada, parada dura automatica a -30% del capital inicial ingresado, aplicada por el bot de forma continua (regla 26 de CLAUDE.md); genera requisito nuevo en 05.01.01 y 06.01.01. Resuelta la contradiccion que este WBS arrastraba (-25% propuesto frente a tolerancia declarada del 50-60%). No se reabrio el capital: los 1.000-2.000 € […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
+          <t>** 01/08 — los tres limites del CEO firmados: D-12 fecha tope, D-13 horas, D-14 perdida maxima → 00-direccion/expedientes/01.01.03.md</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>hecha 01/08 — los tres limites firmados como D-12, D-13 y D-14 y escritos en la seccion «Limites del CEO» de este WBS. (1) FECHA TOPE 01/12/2026 + revision de avance el dia 1 de cada mes con poder de parar; GM gana una cuarta salida (parar). (2) 1 h los lunes como MINIMO garantizado, no techo, con tope de 5 fichas por revision. (3) DINERO REAL: aviso a -25% que no para nada, parada dura automatica a -30% del capital inicial ingresado, aplicada por el bot de forma continua (regla 26 de […] texto completo en 00-direccion/expedientes/01.01.03.md</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -3357,10 +3361,14 @@
           <t>Hecha</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>** 03/08 — auditoria del ecosistema: las cuatro propuestas nativas repartidas a 03.01.18, 03.01.19, 03.01.04 y 03.01.03 → 00-direccion/expedientes/01.02.03.md</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>FICHA (01/08): Aviso de proceso, dicho sin adornos: la ficha se escribe DESPUÉS del barrido, no antes, incumpliendo la regla 5 de CLAUDE.md. Motivo: el CEO pidió la investigación y la ampliación de alcance en la misma orden, en sesión. Queda anotado en vez de disimulado. Alcance ampliado: además del catálogo, fuentes oficiales de Anthropic (anthropics/, documentación de code.claude.com) y mecanismos nativos ya instalados y sin usar (hooks, reglas con ámbito de ruta, worktrees, subagentes […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (01/08): Aviso de proceso, dicho sin adornos: la ficha se escribe DESPUÉS del barrido, no antes, incumpliendo la regla 5 de CLAUDE.md. Motivo: el CEO pidió la investigación y la ampliación de alcance en la misma orden, en sesión. Queda anotado en vez de disimulado. Alcance ampliado: además del catálogo, fuentes oficiales de Anthropic (anthropics/, documentación de code.claude.com) y mecanismos nativos ya instalados y sin usar (hooks, reglas con ámbito de ruta, worktrees, subagentes […] texto completo en 00-direccion/expedientes/01.02.03.md</t>
         </is>
       </c>
     </row>
@@ -3390,10 +3398,14 @@
           <t>Hecha</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>** 03/08 — veredicto sobre MCP: cero servidores; las reglas deny no alcanzan al espacio de nombres mcp__ → 00-direccion/expedientes/01.02.04.md</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>FICHA (01/08): Motivo de la tarea: el CEO pregunta si los MCP salen a cuenta aquí; no estaba medido en el WBS. Alcance: veredicto uno por uno sobre los servidores de referencia oficiales (filesystem, git, memory, sequential-thinking, fetch, time, everything, y sqlite, que está archivado upstream), sobre github, sobre los de datos de mercado (yfinance, TradingView, QuantConnect, ccxt), sobre los de broker (Kraken, Alpaca, IBKR) y sobre los de navegador (Playwright, Chrome DevTools). Filtros […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (01/08): Motivo de la tarea: el CEO pregunta si los MCP salen a cuenta aquí; no estaba medido en el WBS. Alcance: veredicto uno por uno sobre los servidores de referencia oficiales (filesystem, git, memory, sequential-thinking, fetch, time, everything, y sqlite, que está archivado upstream), sobre github, sobre los de datos de mercado (yfinance, TradingView, QuantConnect, ccxt), sobre los de broker (Kraken, Alpaca, IBKR) y sobre los de navegador (Playwright, Chrome DevTools). Filtros […] texto completo en 00-direccion/expedientes/01.02.04.md</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3487,12 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>31/07 — coste_operar.md. Tabla final de coste de entrar y salir, 8 instrumentos, ida y vuelta, con tipo de cuenta declarado (raw/ECN vs spread-only, que no son comparables entre si). CORRECCIONES DE L-002 APLICADAS EN LA TABLA y no en nota al pie: USDJPY 1,16 pips (no 0,90) y USDCHF 0,73 pips (no 0,80). VERIFICADO por el orquestador: aritmetica de las 8 filas recalculada (spread + comision = total, cuadran las 6 con comision); las cifras citadas existen en el origen, localizadas por grep. RECORRIDO: primera entrega DEVUELTA por incumplir la regla 13 de CLAUDE.md (seis citas por numero de linea, que se rompen solas al editar el origen); corregida a referencias por seccion y fila de tabla, […] texto completo en 00-direccion/WBS.md</t>
+          <t>** 31/07 — coste de entrar y salir de 8 instrumentos, ida y vuelta, con el tipo de cuenta declarado → 00-direccion/expedientes/02.01.02.md</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>FICHA (31/07): Alcance: tabla FINAL de coste de entrar y salir (spread + comision) para los 8 instrumentos, en la unidad natural de cada uno, ida y vuelta. Base ya existente: la Entrega 1 del Brief A (entrega_brief_A.md), ACEPTADA por el revisor con fuentes primarias (PDF oficiales de Pepperstone e IC Markets). No se rehace la investigacion: se consolida. Correcciones OBLIGATORIAS, aplicadas EN LA TABLA y no en nota al pie (L-002): USDJPY = 1,16 pips (no 0,90) y USDCHF = 0,73 pips (no 0,80); […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (31/07): Alcance: tabla FINAL de coste de entrar y salir (spread + comision) para los 8 instrumentos, en la unidad natural de cada uno, ida y vuelta. Base ya existente: la Entrega 1 del Brief A (entrega_brief_A.md), ACEPTADA por el revisor con fuentes primarias (PDF oficiales de Pepperstone e IC Markets). No se rehace la investigacion: se consolida. Correcciones OBLIGATORIAS, aplicadas EN LA TABLA y no en nota al pie (L-002): USDJPY = 1,16 pips (no 0,90) y USDCHF = 0,73 pips (no 0,80); […] texto completo en 00-direccion/expedientes/02.01.02.md</t>
         </is>
       </c>
     </row>
@@ -3512,12 +3524,12 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>31/07 — precios_mercado.py, atr_15m_1h_4h.json, atr_real_15m_1h_4h.md. Tabla de 8 instrumentos x 3 velas, 24/24 celdas calculadas sobre precios descargados, 0 estimadas, 0 duplicados, 0 velas invalidas. Cordura del oro OK: 3.596,64 USD/oz, en miles. RECORRIDO: entregada, RECHAZADA por critico-codigo (bin incompleto contado como completo, en el filtro de ventana y en el primer bin de 4h de los 8 instrumentos), reparada en ronda 1, re-revisada y ACEPTADA. El critico recalculo el ATR desde los datos brutos con su propio codigo y coincide digito a digito con el script (XAUUSD 1h = 14.464676282400184, n=11824); verifico ademas que el descarte de bins de borde NO se come huecos legitimos (801 […] texto completo en 00-direccion/WBS.md</t>
+          <t>** 31/07 — ATR real de 8 instrumentos en 15m, 1h y 4h: 24 de 24 celdas calculadas sobre precios descargados → 00-direccion/expedientes/02.02.01.md</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>FICHA (31/07): Fuente fijada: HistData para EURUSD, GBPUSD, USDJPY, AUDUSD y USDCHF · Dukascopy para XAUUSD al contado (NO el futuro GC=F, ver L-007) · Kraken para BTCUSD y ETHUSD contra dolar real, no contra Tether (L-007). Se jubila Yahoo/yfinance. Alcance: descargar historico suficiente para 2 años completos y calcular ATR(14) en velas de 15m, 1h y 4h para los 8 instrumentos. Corte: 22:00 UTC, unico para todos. Artefacto: un solo script que sirva tambien a 02.02.03 (T2 avisa: en gb2 la […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (31/07): Fuente fijada: HistData para EURUSD, GBPUSD, USDJPY, AUDUSD y USDCHF · Dukascopy para XAUUSD al contado (NO el futuro GC=F, ver L-007) · Kraken para BTCUSD y ETHUSD contra dolar real, no contra Tether (L-007). Se jubila Yahoo/yfinance. Alcance: descargar historico suficiente para 2 años completos y calcular ATR(14) en velas de 15m, 1h y 4h para los 8 instrumentos. Corte: 22:00 UTC, unico para todos. Artefacto: un solo script que sirva tambien a 02.02.03 (T2 avisa: en gb2 la […] texto completo en 00-direccion/expedientes/02.02.01.md</t>
         </is>
       </c>
     </row>
@@ -3549,12 +3561,12 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>31/07 — coste_relativo.py, coste_relativo_15m_1h_4h.json, coste_relativo.md. ES EL CRITERIO 1 DE G1. Coste de ida y vuelta ÷ ATR x 100, 8 instrumentos x 3 velas, en CUATRO escenarios: vela media, mediana, tranquila (p10) y agitada (p90). RECORRIDO: entregada, RECHAZADA por critico-codigo (no por error de calculo —reejecuto el script y salio bit-identico— sino por un sesgo de metodo sin declarar), corregida y ACEPTADA. EL SESGO, hallado por el revisor y reproducido por el orquestador: el ATR medio de XAUUSD esta inflado respecto a su mediana (1,28-1,30) mas que el de ningun otro instrumento (0,985-1,144), porque su pausa diaria de 21:00-22:00 UTC genera un salto de rango UNA VEZ AL DIA […] texto completo en 00-direccion/WBS.md</t>
+          <t>** 31/07 — coste relativo, el criterio 1 de G1: coste entre ATR en cuatro escenarios de vela → 00-direccion/expedientes/02.02.02.md</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>FICHA (31/07): Alcance: coste relativo = coste de ida y vuelta ÷ ATR medio de la vela x 100, para los 8 instrumentos x 3 velas (15m, 1h, 4h). Es el criterio 1 de la puerta G1: se exige ≤10-15%. Insumos, ambos ya cerrados y verificados: costes de coste_operar.md (02.01.02) y ATR de 04-resultados/atr_15m_1h_4h.json (02.02.01). No se recalcula ninguno de los dos. TRAMPA PRINCIPAL, declarada de antemano (L-002 y L-004): el JSON guarda el ATR en unidad CRUDA de precio, no en pips. El divisor de pip […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (31/07): Alcance: coste relativo = coste de ida y vuelta ÷ ATR medio de la vela x 100, para los 8 instrumentos x 3 velas (15m, 1h, 4h). Es el criterio 1 de la puerta G1: se exige ≤10-15%. Insumos, ambos ya cerrados y verificados: costes de coste_operar.md (02.01.02) y ATR de 04-resultados/atr_15m_1h_4h.json (02.02.01). No se recalcula ninguno de los dos. TRAMPA PRINCIPAL, declarada de antemano (L-002 y L-004): el JSON guarda el ATR en unidad CRUDA de precio, no en pips. El divisor de pip […] texto completo en 00-direccion/expedientes/02.02.02.md</t>
         </is>
       </c>
     </row>
@@ -3586,12 +3598,12 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>31/07 — correlaciones_mercado.py, correlaciones_8x8.json, correlaciones_8x8.md. 12 matrices 8x8 (3 ventanas x 4 velas, incluida la diaria) sobre RENDIMIENTOS logaritmicos, corte unico 22:00 UTC. ACEPTADA por critico-codigo sin ronda de reparacion. VERIFICADO POR EJECUCION por el revisor: recalculo 4 celdas con codigo propio y coinciden a 15 decimales; confirmo que correlaciona rendimientos y no precios (XAUUSD/USDJPY da +0,586 en precios frente a -0,060 en rendimientos); demostro que pandas ignora el offset con "1D" y que el codigo usa "24h", con el 100% de las velas diarias ancladas a las 22:00; y SIN REGRESION en precios_mercado.py, cuyo ATR regenerado sale identico digito a digito al […] texto completo en 00-direccion/WBS.md</t>
+          <t>** 31/07 — 12 matrices de correlaciones 8x8 sobre rendimientos logaritmicos, corte unico 22:00 UTC → 00-direccion/expedientes/02.02.03.md</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>FICHA (31/07): Alcance: matriz de correlaciones 8x8 sobre RENDIMIENTOS logaritmicos (nunca sobre precios), en 3 ventanas (3 meses, 1 año, 2 años) y en LAS TRES VELAS (15m, 1h, 4h), mas la diaria como comprobacion. Por que las tres velas: la ficha original decia "en la vela elegida", pero la vela se elige en G1, que es despues; calcular las tres evita adivinar (regla 6 de CLAUDE.md) y deja a la puerta el dato elija la que elija. Corte: 22:00 UTC unico, imprescindible o los rendimientos no […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (31/07): Alcance: matriz de correlaciones 8x8 sobre RENDIMIENTOS logaritmicos (nunca sobre precios), en 3 ventanas (3 meses, 1 año, 2 años) y en LAS TRES VELAS (15m, 1h, 4h), mas la diaria como comprobacion. Por que las tres velas: la ficha original decia "en la vela elegida", pero la vela se elige en G1, que es despues; calcular las tres evita adivinar (regla 6 de CLAUDE.md) y deja a la puerta el dato elija la que elija. Corte: 22:00 UTC unico, imprescindible o los rendimientos no […] texto completo en 00-direccion/expedientes/02.02.03.md</t>
         </is>
       </c>
     </row>
@@ -3689,10 +3701,14 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>02/08 — 04-resultados/veredictos/veredicto_fase_02.md y 03-motor/scripts/deriva_oro.py. Segunda pasada del RECHAZA del 31/07. ACEPTA CON HUECOS DECLARADOS, válido SOLO si el defecto del motivo 5 llega declarado al CEO en la ficha de G1; si se omite, decae y rige el RECHAZA. Balance: 4 cerrados (1, 3, 6, 7), 3 abiertos (2, 4, 5), el 5 escalado. Motivo 3 zanjado por ejecución: XAUUSD a 4h pasa de 2,32% a 4,22% y 5,43%, bajo el umbral del 10%, así que la deriva del coste del oro NO cambia el veredicto a 4h; sí lo rompe a 1h (11,01%) y a 15m (19,80-25,46%). Motivo 5 confirmado uno a uno: 7 de 8 instrumentos** mezclan broker o tipo de cuenta; solo BTCUSD comparte fuente. RECORRIDO: validador […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr"/>
+          <t>** 02/08 — revision transversal de la Fase 02: ACEPTA CON HUECOS DECLARADOS, con el motivo 5 al CEO → 00-direccion/expedientes/02.03.01.md</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>hecha 02/08 — 04-resultados/veredictos/veredicto_fase_02.md y 03-motor/scripts/deriva_oro.py. Segunda pasada del RECHAZA del 31/07. ACEPTA CON HUECOS DECLARADOS, válido SOLO si el defecto del motivo 5 llega declarado al CEO en la ficha de G1; si se omite, decae y rige el RECHAZA. Balance: 4 cerrados (1, 3, 6, 7), 3 abiertos (2, 4, 5), el 5 escalado. Motivo 3 zanjado por ejecución: XAUUSD a 4h pasa de 2,32% a 4,22% y 5,43%, bajo el umbral del 10%, así que la deriva del coste del oro NO cambia el […] texto completo en 00-direccion/expedientes/02.03.01.md</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
@@ -3869,10 +3885,14 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>** 04/08 — ficha escrita: arranque por cron, aviso fuera de sesion y topes de gasto. Sin ejecutar → 00-direccion/expedientes/03.01.03.md</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>FICHA (03/08, D-20): Cómo se arranca: claude -p en modo no interactivo lanzado desde el cron del sistema. Los arranques programados son dos líneas de crontab y no requieren ninguna pieza externa. Cómo se avisa al humano sin instalar nada, idea 5 de las auditorías: hook nativo de tipo http, que hace el POST él mismo sin script intermedio, con los eventos StopFailure (admite matcher por tipo de error), Notification con matchers idle_prompt y permission_prompt —que detectan la tirada parada […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (03/08, D-20): Cómo se arranca: claude -p en modo no interactivo lanzado desde el cron del sistema. Los arranques programados son dos líneas de crontab y no requieren ninguna pieza externa. Cómo se avisa al humano sin instalar nada, idea 5 de las auditorías: hook nativo de tipo http, que hace el POST él mismo sin script intermedio, con los eventos StopFailure (admite matcher por tipo de error), Notification con matchers idle_prompt y permission_prompt —que detectan la tirada parada […] texto completo en 00-direccion/expedientes/03.01.03.md</t>
         </is>
       </c>
     </row>
@@ -3902,10 +3922,14 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>** 04/08 — ficha escrita: respaldo de modelo probado inyectando un fallo. Sin ejecutar → 00-direccion/expedientes/03.01.04.md</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>FICHA (03/08, D-20) — CORRECCIÓN DE ALCANCE, dicha sin adornos: esta tarea prometía que el agente «sigue con su respaldo», y eso no se puede automatizar entero: un hook no puede cambiar el modelo (CORRECCIÓN DE ALCANCE (04/08, reproducida por el orquestador): cierto que un hook no cambia de modelo, pero existe --fallback-model &lt;model&gt; — "Enable automatic fallback to specified model(s) when the default model is overloaded or not available. Accepts a comma-separated list to try each in order. […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (03/08, D-20) — CORRECCIÓN DE ALCANCE, dicha sin adornos: esta tarea prometía que el agente «sigue con su respaldo», y eso no se puede automatizar entero: un hook no puede cambiar el modelo (CORRECCIÓN DE ALCANCE (04/08, reproducida por el orquestador): cierto que un hook no cambia de modelo, pero existe --fallback-model &lt;model&gt; — "Enable automatic fallback to specified model(s) when the default model is overloaded or not available. Accepts a comma-separated list to try each in order. […] texto completo en 00-direccion/expedientes/03.01.04.md</t>
         </is>
       </c>
     </row>
@@ -4024,10 +4048,14 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>* — ejecutada la primera pasada 31/07 con verificar_barreras.py: 4 barreras de 5 VERIFICADAS por ejecucion (hooks instalados, datos rechazados en commit, .gitignore ignora 02-datos, mensaje exige codigo WBS). 1 NO VERIFICADA: el cajon reservado era un filtro de texto sobre el comando. CORRECCIÓN DE DEPENDENCIA (03/08/2026): la dependencia de 03.01.03 fue falsa desde el inicio — verificar_barreras.py ejecutada el 31/07 sin que 03.01.03 existiera ya. Las barreras probadas (hooks, .gitignore, commit-msg, cifrado) dependen de 03.01.01 (repo con WBS y reglas) y 03.01.02 (ocho agentes creados). Se remedia en 03.01.11 (D-10). No se cierra hasta repetir la pasada con 03.01.11 terminada SEGUNDA […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr"/>
+          <t>** 31/07 — primera pasada: 4 barreras de 5 verificadas por ejecucion; el cajon reservado sigue sin verificar → 00-direccion/expedientes/03.01.08.md</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>en_curso — ejecutada la primera pasada 31/07 con verificar_barreras.py: 4 barreras de 5 VERIFICADAS por ejecucion (hooks instalados, datos rechazados en commit, .gitignore ignora 02-datos, mensaje exige codigo WBS). 1 NO VERIFICADA: el cajon reservado era un filtro de texto sobre el comando. CORRECCIÓN DE DEPENDENCIA (03/08/2026): la dependencia de 03.01.03 fue falsa desde el inicio — verificar_barreras.py ejecutada el 31/07 sin que 03.01.03 existiera ya. Las barreras probadas (hooks, […] texto completo en 00-direccion/expedientes/03.01.08.md</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -4113,10 +4141,14 @@
           <t>Hecha</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>** 03/08 — una sola lista de reglas normativa, la de CLAUDE.md (D-16); la del WBS queda derogada → 00-direccion/expedientes/03.01.13.md</t>
+        </is>
+      </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>FICHA (01/08): Hallazgo, comprobado por grep sobre los dos ficheros el 01/08: regla 16 = «nadie valida su propio trabajo» (CLAUDE.md) frente a «test de compuerta» (WBS) · regla 23 = «dos niveles de barrera» frente a «un fallo reportado no es un fallo verificado» · regla 25 = «toda barrera se verifica por ejecución» frente a «cada agente lleva el identificador exacto de su modelo». Por qué importa: la regla 12 de CLAUDE.md exige que toda cita se localice con grep antes de entrar en un informe; […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (01/08): Hallazgo, comprobado por grep sobre los dos ficheros el 01/08: regla 16 = «nadie valida su propio trabajo» (CLAUDE.md) frente a «test de compuerta» (WBS) · regla 23 = «dos niveles de barrera» frente a «un fallo reportado no es un fallo verificado» · regla 25 = «toda barrera se verifica por ejecución» frente a «cada agente lleva el identificador exacto de su modelo». Por qué importa: la regla 12 de CLAUDE.md exige que toda cita se localice con grep antes de entrar en un informe; […] texto completo en 00-direccion/expedientes/03.01.13.md</t>
         </is>
       </c>
     </row>
@@ -4148,10 +4180,14 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>script escrito y probado por ejecucion 31/07: 6 de 6 casos prohibidos bloqueados (contraseña por tuberia, abrir sin declarar variante, lectura a pelo del fichero cifrado, contraseña incorrecta, y ninguna orden de terminal vuelca datos en claro). VERIFICADO POR EJECUCION (03/08/2026): 04-resultados/registro-cajon.md registra una entrada SELLAR del 31/07 a las 18:31:29 UTC con resultado sellado. La funcion sellar() en cajon_reservado.py aborta con mensaje «El cajon ya esta sellado» si se intenta llamar una segunda vez. El CEO confirmo el 03/08/2026 que la contraseña la tecleo en una terminal real del sistema (nunca mediante el prefijo de ejecucion rapida de la sesion de Claude Code), porque […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr"/>
+          <t>** 31/07 — cajon_reservado.py probado: 6 de 6 casos prohibidos bloqueados; falta el hueco de settings.json → 00-direccion/expedientes/03.01.11.md</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>en_curso — script escrito y probado por ejecucion 31/07: 6 de 6 casos prohibidos bloqueados (contraseña por tuberia, abrir sin declarar variante, lectura a pelo del fichero cifrado, contraseña incorrecta, y ninguna orden de terminal vuelca datos en claro). VERIFICADO POR EJECUCION (03/08/2026): 04-resultados/registro-cajon.md registra una entrada SELLAR del 31/07 a las 18:31:29 UTC con resultado sellado. La funcion sellar() en cajon_reservado.py aborta con mensaje «El cajon ya esta sellado» si […] texto completo en 00-direccion/expedientes/03.01.11.md</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
@@ -4214,12 +4250,12 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>10/08</t>
+          <t>** 10/08 — diagnostico de las herramientas de los ocho agentes; de ahi salieron D-34 y la regla 30 → 00-direccion/expedientes/03.01.15.md</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 02/08 (tres incidentes reales el 02/08): secretario mantiene los tres registros que solo admiten añadir y todas las fichas del CEO, y no tiene Bash: no puede comprobar por ejecución ninguna de las reglas que gobiernan su trabajo. El 02/08 falló tres veces por lo mismo — no pudo verificar el pegado en tabla, ni el append-only, ni el ancho de su ficha — y las tres las descubrió otro agente, que es la regla 15 de CLAUDE.md rota por diseño, no por descuido. Decidir entre dos salidas, y NO se […] texto completo en 00-direccion/WBS.md</t>
+          <t>NUEVA 02/08 (tres incidentes reales el 02/08): secretario mantiene los tres registros que solo admiten añadir y todas las fichas del CEO, y no tiene Bash: no puede comprobar por ejecución ninguna de las reglas que gobiernan su trabajo. El 02/08 falló tres veces por lo mismo — no pudo verificar el pegado en tabla, ni el append-only, ni el ancho de su ficha — y las tres las descubrió otro agente, que es la regla 15 de CLAUDE.md rota por diseño, no por descuido. Decidir entre dos salidas, y NO se […] texto completo en 00-direccion/expedientes/03.01.15.md</t>
         </is>
       </c>
     </row>
@@ -4251,12 +4287,12 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>el 03/08», que llevaba la marca sin guion delante) que se detectó y reparó antes de terminar. Las dos demostradas por inyección en 05-vista-ceo/prueba_inyeccion.sh, casos 6 y 7 nuevos (función probar_argv, con el mismo guardia FIXTURE de L-026): el caso 6 añade una lección a una copia de LECCIONES.md sin tocar el Excel y hace caer la prueba de recuento; el caso 7 inserta una marca pendiente sin guion delante 40 caracteres antes del cierre real de una celda y hace caer solo la prueba de posición, sin falsear el ESTADO leído (igual que describe el mecanismo del bug). bash 05-vista-ceo/prueba_inyeccion.sh caza los 7 casos salvo el 3, que ya fallaba ANTES de esta tarea: usa el código 07.01.03 […] texto completo en 00-direccion/WBS.md</t>
+          <t>** 05/08 — las hojas del Excel se construyen de sus fuentes primarias; dos inyecciones nuevas, casos 6 y 7 → 00-direccion/expedientes/03.01.16.md</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>FICHA (03/08): Problema verificado hoy: 05-vista-ceo/generar_excel.py construye las hojas REGLAS, LECCIONES y DECISIONES, pero lo hace leyendo tablas espejo en el WBS, no de las fuentes primarias. Consecuencia, medida el 03/08 y ya caducada en sus cifras concretas —de ahí la reescritura del 04/08 más abajo, la fuente sigue viva y crece cada día—: (1) hoja REGLAS sale vacía tras D-16 (las reglas ya no están numeradas en el WBS); (2) hoja LECCIONES muestra 18 cuando 00-direccion/LECCIONES.md […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (03/08): Problema verificado hoy: 05-vista-ceo/generar_excel.py construye las hojas REGLAS, LECCIONES y DECISIONES, pero lo hace leyendo tablas espejo en el WBS, no de las fuentes primarias. Consecuencia, medida el 03/08 y ya caducada en sus cifras concretas —de ahí la reescritura del 04/08 más abajo, la fuente sigue viva y crece cada día—: (1) hoja REGLAS sale vacía tras D-16 (las reglas ya no están numeradas en el WBS); (2) hoja LECCIONES muestra 18 cuando 00-direccion/LECCIONES.md […] texto completo en 00-direccion/expedientes/03.01.16.md</t>
         </is>
       </c>
     </row>
@@ -4286,10 +4322,14 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>** 03/08 — ficha escrita: reparar la prueba 7 del verificador para que examine celdas completas. Sin ejecutar → 00-direccion/expedientes/03.01.17.md</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>FICHA (03/08): Problema reproducido hoy: la prueba 7 localiza entregables citados en las celdas de tarea, pero corta cada celda por el primer hecha y solo examina lo que va después. En 03.01.13 ese marcador es el último carácter de la celda, así que examina cero ficheros y no caza que esa tarea, marcada hecha, cita 00-direccion/PENDIENTE-03.01.13-lista-de-reglas.md, que no existe en disco ni ha existido nunca en git. Dos defectos más: busca por nombre de fichero en CUALQUIER parte del […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (03/08): Problema reproducido hoy: la prueba 7 localiza entregables citados en las celdas de tarea, pero corta cada celda por el primer hecha y solo examina lo que va después. En 03.01.13 ese marcador es el último carácter de la celda, así que examina cero ficheros y no caza que esa tarea, marcada hecha, cita 00-direccion/PENDIENTE-03.01.13-lista-de-reglas.md, que no existe en disco ni ha existido nunca en git. Dos defectos más: busca por nombre de fichero en CUALQUIER parte del […] texto completo en 00-direccion/expedientes/03.01.17.md</t>
         </is>
       </c>
     </row>
@@ -4321,10 +4361,14 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>12/08 — contador .claude/hooks/contador_producto_motor.py, hook SessionStart montado; reproduce 43,8% sobre los 16 commits del 01/08 FICHA (03/08): Problema, medido y no supuesto: el techo del 20% de motor de la regla 8 de CLAUDE.md es prosa y nadie lo mide. La primera vez que se midió, el 01/08, el reparto real era 7 de 16 commits, 43,8%, más del doble del techo, y el proyecto llevaba desde el arranque sin saberlo. Qué se construye: un hook SessionStart que calcula el reparto desde git log y lo inyecta en el contexto con hookSpecificOutput.additionalContext, de forma que cada tirada empiece con el número delante en vez de con la buena intención. Regla de clasificación obligatoria, ya […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr"/>
+          <t>** 12/08 — contador producto/motor y hook SessionStart; reproduce 43,8% sobre los 16 commits del 01/08 → 00-direccion/expedientes/03.01.18.md</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>hecha 12/08 — contador .claude/hooks/contador_producto_motor.py, hook SessionStart montado; reproduce 43,8% sobre los 16 commits del 01/08 FICHA (03/08): Problema, medido y no supuesto: el techo del 20% de motor de la regla 8 de CLAUDE.md es prosa y nadie lo mide. La primera vez que se midió, el 01/08, el reparto real era 7 de 16 commits, 43,8%, más del doble del techo, y el proyecto llevaba desde el arranque sin saberlo. Qué se construye: un hook SessionStart que calcula el reparto desde git […] texto completo en 00-direccion/expedientes/03.01.18.md</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
@@ -4354,10 +4398,14 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>04/08 — medición sobre el transcript en disco de la sesión del 03-04/08 (/home/server/.claude/projects/-home-server-projects-bot-trading/1d064480-a2c4-42fd-a199-5fd72ce78fd9.jsonl y su carpeta subagents/). Hilo principal: 207 peticiones, 94,9 M de tokens leídos de cache, contexto pico 794.459, contexto medio ~452.000. 75 subagentes: 1.293 peticiones, 114,8 M leídos, 11,5 M escritos. Total ~209,7 M en una sola sesión. Causa identificada: el coste crece con el cuadrado de los pasos dados dentro de una misma conversación, sobre un suelo fijo de ~85.000 tokens por conversación. Correcciones aplicadas al propio diagnóstico tras revisión de critico-codigo: el ahorro estimado bajó de "5x" y de un […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr"/>
+          <t>** 04/08 — consumo de tokens medido sobre el transcript en disco: 207 peticiones del hilo principal → 00-direccion/expedientes/03.01.21.md</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>hecha 04/08 — medición sobre el transcript en disco de la sesión del 03-04/08 (/home/server/.claude/projects/-home-server-projects-bot-trading/1d064480-a2c4-42fd-a199-5fd72ce78fd9.jsonl y su carpeta subagents/). Hilo principal: 207 peticiones, 94,9 M de tokens leídos de cache, contexto pico 794.459, contexto medio ~452.000. 75 subagentes: 1.293 peticiones, 114,8 M leídos, 11,5 M escritos. Total ~209,7 M en una sola sesión. Causa identificada: el coste crece con el cuadrado de los pasos dados […] texto completo en 00-direccion/expedientes/03.01.21.md</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
@@ -4420,12 +4468,12 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>. No se enciende: depende de una tirada real supervisada y de 03.01.08. CRITERIO DE HECHO (no cambia): una tirada que arranque sola sin nadie delante, y la tabla muro/prosa con cada línea "muro" disparada por inyección. (Tabla muro/prosa en 03-motor/desatendido/LEEME.md, líneas 62-81; 13 mecanismos: 12 MURO verificados por ejecución, 1 NO verificado.)</t>
+          <t>** 04/08 — encadenador desatendido: no se enciende hasta una tirada real supervisada y hasta 03.01.08 → 00-direccion/expedientes/03.01.23.md</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>REDUCCIÓN ORDENADA POR EL CEO (04/08): la pieza se había crecido con gobernanza que él nunca pidió. Se borraron: lista-verde.txt (y toda su barrera de autorización) · los topes en dólares (MAX_BUDGET_USD_SESION, MAX_BUDGET_USD_DIARIO, gasto-.tsv) · crontab.propuesto.txt (arranques programados) · hook-notificacion.ejemplo.json (aviso al móvil) · cola.txt, progreso.tsv y --disallowedTools. Petición literal del CEO: "en vez de enlazar tantas tareas seguidas se parará antes para no consumir tokens […] texto completo en 00-direccion/WBS.md</t>
+          <t>REDUCCIÓN ORDENADA POR EL CEO (04/08): la pieza se había crecido con gobernanza que él nunca pidió. Se borraron: lista-verde.txt (y toda su barrera de autorización) · los topes en dólares (MAX_BUDGET_USD_SESION, MAX_BUDGET_USD_DIARIO, gasto-.tsv) · crontab.propuesto.txt (arranques programados) · hook-notificacion.ejemplo.json (aviso al móvil) · cola.txt, progreso.tsv y --disallowedTools. Petición literal del CEO: "en vez de enlazar tantas tareas seguidas se parará antes para no consumir tokens […] texto completo en 00-direccion/expedientes/03.01.23.md</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4539,12 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>RONDA 2 CERRADA EN FALSO 06/08. Revisión del validador (revision_04.01.01.md): RECHAZA con 7 motivos. Auditoría de critico-codigo: RECHAZA la revisión. Seis motivos confirmados por método propio, entre ellos una CITA LITERAL FALSA —la celda del criterio 12 de IC Markets atribuía a su fichero de FAQs una condición del «90%» que solo existe en la de Pepperstone— y 11 celdas de 84 con dato sin fuente. P8 ANULADO: la orden que lo pidió añadió como eliminatorios los criterios 5 y 6, que esta ficha no declara; la palabra no aparecía más que una vez en el WBS, pegada al criterio 1, y eso se comprueba contra el commit da93597, no contra el fichero de hoy: este mismo párrafo añade dos apariciones […] texto completo en 00-direccion/WBS.md</t>
+          <t>** 06/08 — comparacion de brokers: ronda 2 cerrada en falso, con una cita literal falsa cazada → 00-direccion/expedientes/04.01.01.md</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>FICHA (04/08, dictada por el orquestador): Por qué ahora: 02.03.03 cerró el 03/08 con D-19 y esta tarea quedó desbloqueada; es la única con plazo duro —10/08, sin retorno— y quedan 6 días. Alcance: comparar 3 o 4 brokers que ofrezcan XAUUSD al contado y entregar la tabla para que el CEO firme. PROHIBIDO ELEGIR: la elección es del CEO. Criterios obligatorios, uno por columna: (1) lote mínimo, y si admite fraccionado de 0,1 onzas —es eliminatorio de hecho: el lote entero son unos 1.962 € contra […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (04/08, dictada por el orquestador): Por qué ahora: 02.03.03 cerró el 03/08 con D-19 y esta tarea quedó desbloqueada; es la única con plazo duro —10/08, sin retorno— y quedan 6 días. Alcance: comparar 3 o 4 brokers que ofrezcan XAUUSD al contado y entregar la tabla para que el CEO firme. PROHIBIDO ELEGIR: la elección es del CEO. Criterios obligatorios, uno por columna: (1) lote mínimo, y si admite fraccionado de 0,1 onzas —es eliminatorio de hecho: el lote entero son unos 1.962 € contra […] texto completo en 00-direccion/expedientes/04.01.01.md</t>
         </is>
       </c>
     </row>
@@ -4586,10 +4634,14 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>FICHA ESCRITA TARDE Y POR ESO ANOTADA (regla 5 de CLAUDE.md incumplida): el orquestador dictó esta subtarea en el reparto del 09/08 con código, motivo y criterio de hecho, pero ordenó ejecutarla sin mandar que se escribiera antes en este WBS; el trabajo se hizo el mismo día y la fila se añade después. Lo detectó validador al revisar la entrega, con grep -rn "04.01.04" 00-direccion/ devolviendo cero. Es el defecto de L-013 de LECCIONES.md, ya anotado en las celdas de 01.02.03 y 01.02.04, y el origen es el reparto, no el ejecutor. MOTIVO: la ficha de 04.01.01 declara eliminatorio su criterio 1 justificándolo con «el lote entero son unos 1.962 € contra un techo de cuenta de 2.000 €» y de ahí […] texto completo en 00-direccion/WBS.md</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr"/>
+          <t>** 09/08 — re-derivacion de la comparacion de brokers; ficha escrita tarde y anotada como incumplimiento → 00-direccion/expedientes/04.01.04.md</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>en_curso — FICHA ESCRITA TARDE Y POR ESO ANOTADA (regla 5 de CLAUDE.md incumplida): el orquestador dictó esta subtarea en el reparto del 09/08 con código, motivo y criterio de hecho, pero ordenó ejecutarla sin mandar que se escribiera antes en este WBS; el trabajo se hizo el mismo día y la fila se añade después. Lo detectó validador al revisar la entrega, con grep -rn "04.01.04" 00-direccion/ devolviendo cero. Es el defecto de L-013 de LECCIONES.md, ya anotado en las celdas de 01.02.03 y […] texto completo en 00-direccion/expedientes/04.01.04.md</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="38" t="inlineStr">
@@ -4914,12 +4966,12 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>04/08 — 03-motor/ESPECIFICACION_MOTOR_BACKTEST.md. 16 requisitos, cada uno con su prueba de aceptación ejecutable; 8 casos calculados a mano; 8 exclusiones motivadas y 7 huecos declarados. RECORRIDO: escrita por arquitecto a ciegas —declara no haber abierto 03-motor/backtester/, ni el commit 0c35959, ni /home/server/projects/gold-bot-2, y la prohibición se comprobó pidiéndole la lista de ficheros leídos—; RECHAZADA en ronda 1 por constructor-datos porque R-06(c) era una revisión a ojo y no una prueba ejecutable, más una atribución de fuente desajustada en R-13(b); el orquestador añadió un tercer defecto que la revisión no cazó: tres citas por número de línea en la sección 10, ya caducadas […] texto completo en 00-direccion/WBS.md</t>
+          <t>** 04/08 — especificacion del motor de backtest: 16 requisitos con prueba ejecutable y 8 casos a mano → 00-direccion/expedientes/04.03.06.md</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>FICHA (03/08, dictada por el orquestador): Por qué se rehace y no se rescata: el criterio de aceptación anterior vivía en la sección «Trasplante desde gb2 — criterios de aceptación», que la cirugía de D-21 borró y hoy solo existe en el historial de git. Nació describiendo qué se traía y qué se descartaba de otro proyecto, y se escribió el 30/07, antes de D-19 y antes de las mediciones de la Fase 02, así que no dice nada del oro, ni de la vela de 4h, ni del lote mínimo. Insumos obligatorios: los […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (03/08, dictada por el orquestador): Por qué se rehace y no se rescata: el criterio de aceptación anterior vivía en la sección «Trasplante desde gb2 — criterios de aceptación», que la cirugía de D-21 borró y hoy solo existe en el historial de git. Nació describiendo qué se traía y qué se descartaba de otro proyecto, y se escribió el 30/07, antes de D-19 y antes de las mediciones de la Fase 02, así que no dice nada del oro, ni de la vela de 4h, ni del lote mínimo. Insumos obligatorios: los […] texto completo en 00-direccion/expedientes/04.03.06.md</t>
         </is>
       </c>
     </row>
@@ -4951,12 +5003,12 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>04/08 — 03-motor/backtester/. Motor de backtest construido desde cero contra la especificación de 04.03.06. PROCEDENCIA, que era la pregunta que originó esta tarea: INDEPENDIENTE de las dos fuentes. Medido con el procedimiento pre-registrado del lote (d) de 07.01.03, bajo la segunda lectura de gb2 que autorizó el CEO en D-25: 0% de intersección de símbolos contra gb2 y contra el commit retirado 0c35959, con coincidencias de línea de 5,2-12,9% que son boilerplate (import pandas as pd, @dataclass, else:) y ninguna constante de calibración heredada. Contraste: 0c35959 disparaba 66,7% y 100% en ese mismo criterio. Reproducido de forma independiente por el orquestador. ADAPTACIÓN DEL […] texto completo en 00-direccion/WBS.md</t>
+          <t>** 04/08 — motor de backtest construido desde cero; procedencia independiente de las dos fuentes → 00-direccion/expedientes/04.03.07.md</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>FICHA (03/08, dictada por el orquestador): PASO 0, que se ejecuta antes que nada: retirar del árbol de trabajo el motor anterior con git revert, sin reescribir historia, para que quien construya no lo tenga delante. El código sigue existiendo en el commit 0c35959 para siempre, y con él sus 44 funciones de prueba —13 en test_costs.py, 20 en test_execution.py y 11 en test_sizing.py, contadas sobre el commit— que la regla 20 de CLAUDE.md obliga a conservar aunque no se usen. Verificado antes de […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (03/08, dictada por el orquestador): PASO 0, que se ejecuta antes que nada: retirar del árbol de trabajo el motor anterior con git revert, sin reescribir historia, para que quien construya no lo tenga delante. El código sigue existiendo en el commit 0c35959 para siempre, y con él sus 44 funciones de prueba —13 en test_costs.py, 20 en test_execution.py y 11 en test_sizing.py, contadas sobre el commit— que la regla 20 de CLAUDE.md obliga a conservar aunque no se usen. Verificado antes de […] texto completo en 00-direccion/expedientes/04.03.07.md</t>
         </is>
       </c>
     </row>
@@ -5294,10 +5346,14 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>** 02/08 — orden de carpetas y documentos: la cifra 246/105 retirada por no reproducirse. Sin cerrar → 00-direccion/expedientes/07.01.01.md</t>
+        </is>
+      </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>FICHA (02/08): ALCANCE — cuatro arreglos de documento, NINGUNO toca código: (a) Las celdas ESTADO de 01.02.04 y 03.01.12 declaran en negrita un estado del vocabulario pendiente / en_curso / hecha / bloqueada, como exige la sección «Estados y cadencia de este WBS». Valores ya decididos por el orquestador, no se deducen: 01.02.04 pasa a en_curso (entregado INFORME_MCP_2.md, RECHAZADO por critico-codigo, sin reparar); 03.01.12 pasa a pendiente (nadie la ha trabajado). En 01.02.04 la marca actual […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (02/08): ALCANCE — cuatro arreglos de documento, NINGUNO toca código: (a) Las celdas ESTADO de 01.02.04 y 03.01.12 declaran en negrita un estado del vocabulario pendiente / en_curso / hecha / bloqueada, como exige la sección «Estados y cadencia de este WBS». Valores ya decididos por el orquestador, no se deducen: 01.02.04 pasa a en_curso (entregado INFORME_MCP_2.md, RECHAZADO por critico-codigo, sin reparar); 03.01.12 pasa a pendiente (nadie la ha trabajado). En 01.02.04 la marca actual […] texto completo en 00-direccion/expedientes/07.01.01.md</t>
         </is>
       </c>
     </row>
@@ -5329,12 +5385,12 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>2ª AMPLIACIÓN 03/08, decisión del CEO — opción B: el motor de backtest se tira y se construye de cero. Consecuencias sobre esta tarea: los lotes (e1) y (e2) de aptitud QUEDAN CANCELADOS — juzgar si sirve un código que se borra es gastar la verificación en un cadáver. No se pierde su contenido: su eje A3, que no juzgaba al motor viejo sino que describía qué debe hacer cualquier motor para servir a D-19, migra íntegro a la especificación nueva (tarea 04.03.06). El lote (d) SE MANTIENE, recortado a la medición mecánica, por tres motivos: D-21 afirma en un registro de solo-añadir que no se copió una sola línea de gb2 y esa mitad sigue sin comprobar; la autorización de una sola apertura que dio […] texto completo en 00-direccion/WBS.md</t>
+          <t>** 09/08 — auditoria de lo escrito sin flujo el 03/08; los lotes de aptitud cancelados por el CEO → 00-direccion/expedientes/07.01.03.md</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>FICHA (03/08, dictada por el orquestador): Qué pasó, medido y no supuesto: tras un /compact a las 21:29, la sesión recibió una orden del CEO a las 21:44 y trabajó sola hasta las 21:58 sin invocar a un solo subagente. Escribió D-19, D-20 y D-21 en un registro de solo-añadir, L-024 a L-027, cirugía estructural sobre el WBS, y dos scripts del Excel del CEO. Nadie lo revisó (regla 16 de CLAUDE.md y C2 rotas). Alcance: tres lotes con veredicto propio — (d) procedencia del motor de backtest, (b y c) […] texto completo en 00-direccion/WBS.md</t>
+          <t>FICHA (03/08, dictada por el orquestador): Qué pasó, medido y no supuesto: tras un /compact a las 21:29, la sesión recibió una orden del CEO a las 21:44 y trabajó sola hasta las 21:58 sin invocar a un solo subagente. Escribió D-19, D-20 y D-21 en un registro de solo-añadir, L-024 a L-027, cirugía estructural sobre el WBS, y dos scripts del Excel del CEO. Nadie lo revisó (regla 16 de CLAUDE.md y C2 rotas). Alcance: tres lotes con veredicto propio — (d) procedencia del motor de backtest, (b y c) […] texto completo en 00-direccion/expedientes/07.01.03.md</t>
         </is>
       </c>
     </row>

--- a/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
+++ b/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
@@ -1309,7 +1309,7 @@
           <t>gasto nuevo (datos de pago, VPS, broker, créditos extra)
 · cualquier cosa con dinero real
 · bloqueo de más de 24 h
-· 3 vueltas del bucle de hipótesis sin éxito.</t>
+· 2 vueltas sin éxito.</t>
         </is>
       </c>
     </row>

--- a/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
+++ b/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
@@ -1328,7 +1328,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>FORMATO OBLIGATORIO DE FICHA DE DECISION (regla 10)</t>
+          <t>FORMATO OBLIGATORIO DE FICHA DE DECISION (seccion 'Que llega al CEO' de CLAUDE.md)</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6268,7 +6268,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LAS 30 REGLAS — mandan sobre cualquier otra instruccion</t>
+          <t>LAS 28 REGLAS — mandan sobre cualquier otra instruccion</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Los códigos son estables: una tarea empezada no se renumera jamás.</t>
+          <t>Se va en orden salvo las marcadas paralelas. Una tarea no se cierra sin cumplir su criterio de "hecho".</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Se va en orden salvo las marcadas paralelas. Una tarea no se cierra sin cumplir su criterio de "hecho".</t>
+          <t>La ficha de una tarea se escribe en la cola ANTES de trabajarla, nunca al cerrarla. Sin ficha, no hay tarea.</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>La ficha de una tarea se escribe en la cola ANTES de trabajarla, nunca al cerrarla. Sin ficha, no hay tarea.</t>
+          <t>Regla de no-ambigüedad: toda tarea debe poder ejecutarse sin adivinar nada. Si tienes que suponer algo, devuelve la tarea al orquestador para que la reescriba. No supongas.</t>
         </is>
       </c>
     </row>
@@ -6349,245 +6349,225 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Regla de no-ambigüedad: toda tarea debe poder ejecutarse sin adivinar nada. Si tienes que suponer algo, devuelve la tarea al orquestador para que la reescriba. No supongas.</t>
+          <t>Ningún criterio de hecho exige una herramienta que el ejecutor no tiene. Antes de escribirlo, se localiza por grep la línea tools: del agente que va a ejecutarlo. Si la prueba exige algo que no aparece ahí, la prueba se traslada al revisor. Un agente al que se le pide lo imposible no falla: fabrica, y el fallo se le acaba imputando a él en vez de a quien repartió. (D-34, 10/08/2026.)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ningún criterio de hecho exige una herramienta que el ejecutor no tiene. Antes de escribirlo, se localiza por grep la línea tools: del agente que va a ejecutarlo. Si la prueba exige algo que no aparece ahí, la prueba se traslada al revisor. Un agente al que se le pide lo imposible no falla: fabrica, y el fallo se le acaba imputando a él en vez de a quien repartió. (D-34, 10/08/2026.)</t>
+          <t>Cada tirada autónoma cierra al menos una tarea que avanza el PRODUCTO. La infraestructura que no desbloquee mecánicamente una tarea de producto se registra como deuda y no se ejecuta sin permiso del CEO.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Cada tirada autónoma cierra al menos una tarea que avanza el PRODUCTO. La infraestructura que no desbloquee mecánicamente una tarea de producto se registra como deuda y no se ejecuta sin permiso del CEO.</t>
+          <t>El trabajo de motor y orden tiene un techo del 20% del esfuerzo semanal. Si en una tirada solo hay tareas de motor disponibles, para y avisa: es señal de que la cola está mal llena.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>El trabajo de motor y orden tiene un techo del 20% del esfuerzo semanal. Si en una tirada solo hay tareas de motor disponibles, para y avisa: es señal de que la cola está mal llena.</t>
+          <t>Jerarquía de la prueba. Ninguna afirmación se acepta por consenso entre agentes:</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Jerarquía de la prueba. Ninguna afirmación se acepta por consenso entre agentes:</t>
+          <t>Un fallo reportado por un agente no es un fallo verificado. Antes de encolar o reparar: lee el componente y reproduce el fallo.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Quien discrepa aporta el experimento que zanjaría la discusión, no otro argumento. Si no hay experimento posible, sube al CEO marcado como no probado.</t>
+          <t>Ninguna referencia a una decisión entra en código o informe sin un grep previo que la localice por fichero y línea. Solo se cita lo firmado y guardado, nunca en pasado ni antes de existir.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Un fallo reportado por un agente no es un fallo verificado. Antes de encolar o reparar: lee el componente y reproduce el fallo.</t>
+          <t>Se referencia por nombre de símbolo, nunca por número de línea.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ninguna referencia a una decisión entra en código o informe sin un grep previo que la localice por fichero y línea. Solo se cita lo firmado y guardado, nunca en pasado ni antes de existir.</t>
+          <t>Todo dato numérico se calcula sobre datos brutos, salvo que exista una fuente primaria homogénea demostrable.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Se referencia por nombre de símbolo, nunca por número de línea.</t>
+          <t>Quien implementa ejecuta y lee su artefacto completo antes de entregar. Las puertas confirman, no descubren.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Todo dato numérico se calcula sobre datos brutos, salvo que exista una fuente primaria homogénea demostrable.</t>
+          <t>Nadie valida su propio trabajo. Quien construye no revisa; quien produce las métricas no firma el veredicto.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Quien implementa ejecuta y lee su artefacto completo antes de entregar. Las puertas confirman, no descubren.</t>
+          <t>Éxito = código fiel a la especificación, NO estrategia rentable. Un backtest con mal resultado y código correcto es un éxito registrable.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Nadie valida su propio trabajo. Quien construye no revisa; quien produce las métricas no firma el veredicto.</t>
+          <t>Test de compuerta: si la justificación de un cambio no se sostiene sin citar métricas de resultado, se deniega.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Éxito = código fiel a la especificación, NO estrategia rentable. Un backtest con mal resultado y código correcto es un éxito registrable.</t>
+          <t>Pre-registro: ninguna variante se prueba sin estar registrada antes (máx. 5-7 por hipótesis). Lo no registrado no se prueba.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Test de compuerta: si la justificación de un cambio no se sostiene sin citar métricas de resultado, se deniega.</t>
+          <t>Se guardan TODAS las pruebas, también las fallidas. Saber cuántas cosas se probaron es lo que permite juzgar si la ganadora es real o casualidad.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Pre-registro: ninguna variante se prueba sin estar registrada antes (máx. 5-7 por hipótesis). Lo no registrado no se prueba.</t>
+          <t>Registros que solo permiten añadir: 04-resultados/registro-pruebas.md y 00-direccion/DECISIONES.md nunca se reescriben. Una corrección es una entrada nueva.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Se guardan TODAS las pruebas, también las fallidas. Saber cuántas cosas se probaron es lo que permite juzgar si la ganadora es real o casualidad.</t>
+          <t>El cajón 02-datos/reservado/ no se abre. Solo el CEO puede autorizar su uso, una vez por variante. Ningún agente, ningún debate, ninguna urgencia.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Registros que solo permiten añadir: 04-resultados/registro-pruebas.md y 00-direccion/DECISIONES.md nunca se reescriben. Una corrección es una entrada nueva.</t>
+          <t>Dos niveles. Lo REVERSIBLE (archivos, código, pruebas) tiene permisos amplios: git lo deshace. Lo IRREVERSIBLE (dinero real, órdenes al broker, borrar el cajón reservado, gastar dinero nuevo) lleva barrera desde el minuto uno.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>El cajón 02-datos/reservado/ no se abre. Solo el CEO puede autorizar su uso, una vez por variante. Ningún agente, ningún debate, ninguna urgencia.</t>
+          <t>Una restricción solo se añade tras un incidente real, anotada junto al incidente, y se revisa cada mes. La que no tenga incidente vivo detrás, se quita.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Dos niveles. Lo REVERSIBLE (archivos, código, pruebas) tiene permisos amplios: git lo deshace. Lo IRREVERSIBLE (dinero real, órdenes al broker, borrar el cajón reservado, gastar dinero nuevo) lleva barrera desde el minuto uno.</t>
+          <t>Toda barrera se verifica por ejecución —inyectando el caso prohibido— antes de documentarla como activa. Sin prueba: "no verificada". Un guardia presente en el código no es un guardia probado.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Una restricción solo se añade tras un incidente real, anotada junto al incidente, y se revisa cada mes. La que no tenga incidente vivo detrás, se quita.</t>
+          <t>Los guardias bloquean por defecto. La condición que activa una exención debe ser un hecho impuesto por el sistema, nunca un dato que elija el vigilado.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Toda barrera se verifica por ejecución —inyectando el caso prohibido— antes de documentarla como activa. Sin prueba: "no verificada". Un guardia presente en el código no es un guardia probado.</t>
+          <t>Los datos nunca entran en git. Se descargan con script. Comprobar el día 1 que .gitignore funciona de verdad.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Los guardias bloquean por defecto. La condición que activa una exención debe ser un hecho impuesto por el sistema, nunca un dato que elija el vigilado.</t>
+          <t>Una sola fuente de verdad por tema. Documento que se sustituye, se borra: git guarda el historial.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Los datos nunca entran en git. Se descargan con script. Comprobar el día 1 que .gitignore funciona de verdad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Una sola fuente de verdad por tema. Documento que se sustituye, se borra: git guarda el historial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Cada agente lleva el identificador exacto de su modelo, nunca un alias, y ningún agente sin modelo.</t>
         </is>
@@ -6608,7 +6588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6620,7 +6600,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REGISTRO DE DECISIONES (30) — solo se añade, nunca se reescribe (regla 21 de CLAUDE.md)</t>
+          <t>REGISTRO DE DECISIONES (32) — solo se añade, nunca se reescribe (regla 21 de CLAUDE.md)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7410,6 +7390,56 @@
 Qué significa. Ningún criterio de hecho puede exigir una comprobación que las herramientas declaradas en la línea tools: del agente que lo ejecuta no le permitan hacer. Antes de escribir un criterio de hecho se localiza esa línea por grep; si la prueba exige algo que no aparece en ella, la prueba se traslada al revisor, que sí la tiene. Queda escrito como regla 30 de CLAUDE.md.
 Qué NO hace. No cambia la línea tools: de ningún agente. En particular, secretario sigue sin Bash.
 Por qué ésta y no repartir herramientas. Del diagnóstico de 03.01.15 en 04-resultados/diagnostico_03.01.15_herramientas_agentes.md, con los ocho agentes barridos: los fallos medidos son de dos clases y solo una la arregla una herramienta. Un agente sin Bash declaró una cifra […] texto completo en 00-direccion/DECISIONES.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>D-35</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Las reglas sin incidente detrás: se retira la 3, la 10 se fusiona en la 9, quedan 28</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Qué se decide. Opción A de la ficha del apartado 3 de 00-direccion/INFORME-CIRUGIA-MOTOR.md. Palabras literales del CEO, 12/08/2026: «Retirar la regla 3. Fusionar la 10 con la 9. Dejar la 17, la 18, la 19 y la 20.»
+Motivo que el CEO ordena escribir, literal: las cuatro reglas de estrategia no tienen incidente detrás porque la fase 04 nunca ha empezado. Eso no es peso muerto: es la prueba de que el producto no ha arrancado. Retirarlas sería quitar el airbag por no haber chocado.
+Qué cambia en el disco.
+1. Vieja regla 3 («los códigos son estables: una tarea empezada no se renumera jamás») — RETIRADA. No tenía incidente detrás ni en este proyecto ni en el anterior.
+2. Vieja regla 10 («quien discrepa aporta el experimento que zanjaría la discusión») — FUSIONADA dentro de la 9, la jerarquía de la prueba, cuyo nivel 1 ya decía lo mismo. El texto no se pierde: sigue entero dentro de la regla […] texto completo en 00-direccion/DECISIONES.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>D-36</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Se aplican las barreras (a), (b) y (d) de D-29; la (c), la de gasto, se cierra por imposible</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Qué se decide. Palabras literales del CEO, 12/08/2026: «se autorizan (a), (b) y (d). El punto (c) se cierra por imposible.» Los cuatro puntos son los de 00-direccion/informes/FICHA_D-29.md.
+POR QUÉ ESTA ENTRADA EXISTE SI D-29 YA ESTABA FIRMADA, y conviene que quede claro. D-29 de este mismo fichero ya firmó las cuatro barreras el 09/08/2026 (opción A). Lo que dejó sin firmar fue el cómo: su propio texto dice que aplicar el parche de (a) y (b) a .claude/settings.json «necesita una letra aparte del CEO, porque bajo bypassPermissions (D-27) escribir ese fichero no dispara ninguna aprobación y el sistema no le preguntaría». D-36 es esa letra aparte. No repite D-29: la ejecuta.
+(a) El agujero del cajón reservado — SE AUTORIZA APLICAR. El patrón Bash( 02-datos/reservado) de .claude/settings.json exige un espacio literal y no cubre la ruta pegada a una comilla. Medido el 05/08. Se sustituye […] texto completo en 00-direccion/DECISIONES.md</t>
         </is>
       </c>
     </row>

--- a/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
+++ b/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
@@ -20,7 +20,7 @@
     <sheet name="LIMITES CEO" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TAREAS'!$A$4:$G$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TAREAS'!$A$4:$G$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -742,23 +742,23 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"01.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"01.??.??")</f>
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"01.??.??",TAREAS!$E$5:$E$77,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"01.??.??",TAREAS!$E$5:$E$79,"Hecha")</f>
         <v/>
       </c>
       <c r="D4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"01.??.??",TAREAS!$E$5:$E$77,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"01.??.??",TAREAS!$E$5:$E$79,"En curso")</f>
         <v/>
       </c>
       <c r="E4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"01.??.??",TAREAS!$E$5:$E$77,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"01.??.??",TAREAS!$E$5:$E$79,"Pendiente")</f>
         <v/>
       </c>
       <c r="F4" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"01.??.??",TAREAS!$E$5:$E$77,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"01.??.??",TAREAS!$E$5:$E$79,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G4" s="6">
@@ -773,23 +773,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"02.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"02.??.??")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"02.??.??",TAREAS!$E$5:$E$77,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"02.??.??",TAREAS!$E$5:$E$79,"Hecha")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"02.??.??",TAREAS!$E$5:$E$77,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"02.??.??",TAREAS!$E$5:$E$79,"En curso")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"02.??.??",TAREAS!$E$5:$E$77,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"02.??.??",TAREAS!$E$5:$E$79,"Pendiente")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"02.??.??",TAREAS!$E$5:$E$77,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"02.??.??",TAREAS!$E$5:$E$79,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G5" s="6">
@@ -804,23 +804,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"03.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"03.??.??")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"03.??.??",TAREAS!$E$5:$E$77,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"03.??.??",TAREAS!$E$5:$E$79,"Hecha")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"03.??.??",TAREAS!$E$5:$E$77,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"03.??.??",TAREAS!$E$5:$E$79,"En curso")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"03.??.??",TAREAS!$E$5:$E$77,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"03.??.??",TAREAS!$E$5:$E$79,"Pendiente")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"03.??.??",TAREAS!$E$5:$E$77,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"03.??.??",TAREAS!$E$5:$E$79,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G6" s="6">
@@ -835,23 +835,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"04.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"04.??.??")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"04.??.??",TAREAS!$E$5:$E$77,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"04.??.??",TAREAS!$E$5:$E$79,"Hecha")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"04.??.??",TAREAS!$E$5:$E$77,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"04.??.??",TAREAS!$E$5:$E$79,"En curso")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"04.??.??",TAREAS!$E$5:$E$77,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"04.??.??",TAREAS!$E$5:$E$79,"Pendiente")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"04.??.??",TAREAS!$E$5:$E$77,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"04.??.??",TAREAS!$E$5:$E$79,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G7" s="6">
@@ -866,23 +866,23 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"05.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"05.??.??")</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"05.??.??",TAREAS!$E$5:$E$77,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"05.??.??",TAREAS!$E$5:$E$79,"Hecha")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"05.??.??",TAREAS!$E$5:$E$77,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"05.??.??",TAREAS!$E$5:$E$79,"En curso")</f>
         <v/>
       </c>
       <c r="E8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"05.??.??",TAREAS!$E$5:$E$77,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"05.??.??",TAREAS!$E$5:$E$79,"Pendiente")</f>
         <v/>
       </c>
       <c r="F8" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"05.??.??",TAREAS!$E$5:$E$77,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"05.??.??",TAREAS!$E$5:$E$79,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G8" s="6">
@@ -897,23 +897,23 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"06.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"06.??.??")</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"06.??.??",TAREAS!$E$5:$E$77,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"06.??.??",TAREAS!$E$5:$E$79,"Hecha")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"06.??.??",TAREAS!$E$5:$E$77,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"06.??.??",TAREAS!$E$5:$E$79,"En curso")</f>
         <v/>
       </c>
       <c r="E9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"06.??.??",TAREAS!$E$5:$E$77,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"06.??.??",TAREAS!$E$5:$E$79,"Pendiente")</f>
         <v/>
       </c>
       <c r="F9" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"06.??.??",TAREAS!$E$5:$E$77,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"06.??.??",TAREAS!$E$5:$E$79,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G9" s="6">
@@ -928,23 +928,23 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"07.??.??")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"07.??.??")</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"07.??.??",TAREAS!$E$5:$E$77,"Hecha")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"07.??.??",TAREAS!$E$5:$E$79,"Hecha")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"07.??.??",TAREAS!$E$5:$E$77,"En curso")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"07.??.??",TAREAS!$E$5:$E$79,"En curso")</f>
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"07.??.??",TAREAS!$E$5:$E$77,"Pendiente")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"07.??.??",TAREAS!$E$5:$E$79,"Pendiente")</f>
         <v/>
       </c>
       <c r="F10" s="5">
-        <f>COUNTIFS(TAREAS!$A$5:$A$77,"07.??.??",TAREAS!$E$5:$E$77,"Bloqueada")</f>
+        <f>COUNTIFS(TAREAS!$A$5:$A$79,"07.??.??",TAREAS!$E$5:$E$79,"Bloqueada")</f>
         <v/>
       </c>
       <c r="G10" s="6">
@@ -1428,7 +1428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1527,7 +1527,7 @@
       <c r="B6" s="30" t="n"/>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>04.02.01 — Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente. Detras de ella esperan 16 de las 36 tareas vivas.</t>
+          <t>04.02.01 — Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente. Detras de ella esperan 16 de las 38 tareas vivas.</t>
         </is>
       </c>
       <c r="D6" s="30" t="n"/>
@@ -1591,7 +1591,7 @@
     <row r="9">
       <c r="A9" s="32" t="inlineStr">
         <is>
-          <t>SE PUEDE TRABAJAR YA — 15 tareas, en este orden</t>
+          <t>SE PUEDE TRABAJAR YA — 16 tareas, en este orden</t>
         </is>
       </c>
       <c r="B9" s="32" t="n"/>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -2114,17 +2114,17 @@
       </c>
       <c r="B23" s="33" t="inlineStr">
         <is>
-          <t>07.01.01</t>
+          <t>03.01.25</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
+          <t>NUEVA 05/08 (nace del incidente de este mismo día): guardia en .githooks/pre-commit que ejecuta la métrica de L-027 de 00-direccion/LECCIONES.md sobre 00-direccion/WBS.md y rechaza el commit si alguna fila de tarea no da 7 campos al partirla por la barra vertical. Motivo: hoy la métrica existe, está escrita como normativa en este WBS, y no la ejecuta nadie automáticamente; 05-vista-ceo/verificar_excel.py no la cubre. Es el muro que le falta a la única fuente de verdad del proyecto. Regla 24 de CLAUDE.md: nace de un incidente real y medido — el 05/08 cuatro filas quedaron partidas y ningún guardia se enteró. Regla 25 de CLAUDE.md: se verifica por inyección de una fila rota ANTES de documentarse como activo. AVISO PARA QUIEN LA EJECUTE, medido el mismo día: el propio texto de esta fila no puede contener el comando literal, porque la barra vertical que lleva dentro rompe la fila que describe; el guardia tiene que tolerar esa cita cuando aparezca en prosa fuera de una tabla.</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Constructor de motor</t>
         </is>
       </c>
       <c r="E23" s="34" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>07.01.02</t>
+          <t>07.01.01</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
+          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -2183,58 +2183,56 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="inlineStr">
-        <is>
-          <t>ESPERANDO A OTRA TAREA — 21 tareas, en orden de codigo WBS</t>
-        </is>
-      </c>
-      <c r="B25" s="32" t="n"/>
-      <c r="C25" s="32" t="n"/>
-      <c r="D25" s="32" t="n"/>
-      <c r="E25" s="32" t="n"/>
-      <c r="F25" s="32" t="n"/>
-      <c r="G25" s="32" t="n"/>
-      <c r="H25" s="32" t="n"/>
-      <c r="I25" s="32" t="n"/>
+      <c r="A25" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>07.01.02</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>nada: se puede empezar ya</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t>03.01.05</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Orquestador</t>
-        </is>
-      </c>
-      <c r="E26" s="34" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
-        </is>
-      </c>
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>ESPERANDO A OTRA TAREA — 22 tareas, en orden de codigo WBS</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="n"/>
+      <c r="C26" s="32" t="n"/>
+      <c r="D26" s="32" t="n"/>
+      <c r="E26" s="32" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="32" t="n"/>
+      <c r="H26" s="32" t="n"/>
+      <c r="I26" s="32" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2244,17 +2242,17 @@
       </c>
       <c r="B27" s="33" t="inlineStr">
         <is>
-          <t>03.01.07</t>
+          <t>03.01.05</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
+          <t>PRUEBA REAL DEL MOTOR: un día entero de trabajo desatendido de verdad antes de dar la fase por buena</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="E27" s="34" t="inlineStr">
@@ -2271,7 +2269,7 @@
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>03.01.06 (pendiente, Secretario)</t>
+          <t>03.01.03 (pendiente, Constructores), 03.01.04 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2283,17 +2281,17 @@
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>03.01.11</t>
+          <t>03.01.07</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
+          <t>Cola de aprobación del CEO: tabla con desplegable Aprobado / Saltar / Corregir y columna de corrección. Lo aprobado se ejecuta solo; lo corregido se rehace Y la corrección se guarda en LECCIONES.md</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E28" s="34" t="inlineStr">
@@ -2301,16 +2299,16 @@
           <t>MOTOR</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>En curso</t>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>03.01.08 (en curso, Crítico)</t>
+          <t>03.01.06 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -2322,34 +2320,34 @@
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>04.01.02</t>
+          <t>03.01.11</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02) REQUISITO AÑADIDO 04/08: al recalcular con precios reales se comprueba que la entidad que publica la tarifa es la misma con la que se opera. Si no coinciden, la cifra vieja no se hereda: se vuelve a medir.</t>
+          <t>NUEVA 31/07 (D-10): guardia del cajon reservado por cifrado. Script cajon_reservado.py: la contraseña solo la tiene el CEO, no se guarda, se pide en cada operacion y nada se descifra a disco</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E29" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>En curso</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>04.01.01 (en curso, CEO + Orquestador)</t>
+          <t>03.01.08 (en curso, Crítico)</t>
         </is>
       </c>
     </row>
@@ -2361,22 +2359,22 @@
       </c>
       <c r="B30" s="33" t="inlineStr">
         <is>
-          <t>04.01.03</t>
+          <t>03.01.24</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
+          <t>NUEVA 05/08 (nace de los huecos medidos por ejecución en 03.01.08): las tres barreras que hoy NO existen. (a) El patrón Bash( 02-datos/reservado) de .claude/settings.json exige un espacio literal y no cubre la ruta pegada a una comilla, así que una línea de python lo esquiva: sustituirlo por un patrón que cubra cualquier verbo y cualquier forma de escribir la ruta, y probarlo con las TRES formas. (b) Nada impide rm -rf dentro de 02-datos/, y los datos no están en git (regla 27 de CLAUDE.md): no se rehacen deshaciendo un commit, se rehacen volviendo a descargarlos. (c) No hay ninguna barrera de gasto, ni en código ni en configuración; D-26 de 00-direccion/DECISIONES.md deja escrito que --max-budget-usd existe. Regla 24 de CLAUDE.md: las tres nacen de una inyección ejecutada con su salida guardada, no de una sospecha, y ninguna causó daño. Regla 25 de CLAUDE.md: cada barrera nueva se verifica por inyección ANTES de documentarse como activa.</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Constructor datos</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E30" s="34" t="inlineStr">
+        <is>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2384,15 +2382,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>13</v>
-      </c>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>04.01.01 (en curso, CEO + Orquestador)</t>
+          <t>03.01.08 (en curso, Crítico)</t>
         </is>
       </c>
     </row>
@@ -2404,17 +2398,17 @@
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>04.01.02</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
+          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02) REQUISITO AÑADIDO 04/08: al recalcular con precios reales se comprueba que la entidad que publica la tarifa es la misma con la que se opera. Si no coinciden, la cifra vieja no se hereda: se vuelve a medir.</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2427,15 +2421,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>15</v>
-      </c>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>04.02.01 (pendiente, Investigador)</t>
+          <t>04.01.01 (en curso, CEO + Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2447,17 +2437,17 @@
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.01.03</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
+          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2474,11 +2464,11 @@
         <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>04.02.02 (pendiente, Investigador)</t>
+          <t>04.01.01 (en curso, CEO + Orquestador)</t>
         </is>
       </c>
     </row>
@@ -2490,17 +2480,17 @@
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>04.02.04</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
+          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2517,11 +2507,11 @@
         <v>1</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>04.02.03 (pendiente, Validador)</t>
+          <t>04.02.01 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2523,17 @@
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Backtest con costes reales sobre el cajón de construir</t>
+          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2560,11 +2550,11 @@
         <v>1</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
+          <t>04.02.02 (pendiente, Investigador)</t>
         </is>
       </c>
     </row>
@@ -2576,17 +2566,17 @@
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.02.04</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
+          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2603,11 +2593,11 @@
         <v>1</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>04.03.01 (pendiente, Constructores)</t>
+          <t>04.02.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2619,17 +2609,17 @@
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
+          <t>Backtest con costes reales sobre el cajón de construir</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2646,11 +2636,11 @@
         <v>1</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>04.03.02 (pendiente, Constructores)</t>
+          <t>04.01.03 (pendiente, Constructor datos), 04.02.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2662,17 +2652,17 @@
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2689,11 +2679,11 @@
         <v>1</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>04.03.03 (pendiente, Validador)</t>
+          <t>04.03.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2705,12 +2695,12 @@
       </c>
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>04.03.05</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
+          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2732,11 +2722,11 @@
         <v>1</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>04.03.04 (pendiente, Validador)</t>
+          <t>04.03.02 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -2748,17 +2738,17 @@
       </c>
       <c r="B39" s="33" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
+          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2772,14 +2762,14 @@
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>04.03.05 (pendiente, Validador)</t>
+          <t>04.03.03 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2791,17 +2781,17 @@
       </c>
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>04.04.02</t>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
+          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Orquestador</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2814,11 +2804,15 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>8</v>
+      </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>04.04.01 (pendiente, Secretario)</t>
+          <t>04.03.04 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2830,17 +2824,17 @@
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>04.04.03</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
-        </is>
-      </c>
-      <c r="D41" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -2854,14 +2848,14 @@
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>04.04.01 (pendiente, Secretario)</t>
+          <t>04.03.05 (pendiente, Validador)</t>
         </is>
       </c>
     </row>
@@ -2873,17 +2867,17 @@
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>04.04.02</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Bot en demo, solo y con guardias automáticos</t>
+          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Orquestador</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -2896,15 +2890,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>4</v>
-      </c>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>04.04.03 (pendiente, CEO)</t>
+          <t>04.04.01 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -2916,17 +2906,17 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>05.01.02</t>
+          <t>04.04.03</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Secretario</t>
+          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
+        </is>
+      </c>
+      <c r="D43" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -2943,11 +2933,11 @@
         <v>1</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>05.01.01 (pendiente, Constructores)</t>
+          <t>04.04.01 (pendiente, Secretario)</t>
         </is>
       </c>
     </row>
@@ -2959,17 +2949,17 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>05.01.03</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
-        </is>
-      </c>
-      <c r="D44" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Bot en demo, solo y con guardias automáticos</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -2986,11 +2976,11 @@
         <v>1</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>05.01.02 (pendiente, Secretario)</t>
+          <t>04.04.03 (pendiente, CEO)</t>
         </is>
       </c>
     </row>
@@ -3002,17 +2992,17 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>06.01.01</t>
+          <t>05.01.02</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Dinero pequeño respetando los límites de 01.01.03</t>
+          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3029,11 +3019,11 @@
         <v>1</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>05.01.03 (pendiente, CEO)</t>
+          <t>05.01.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
@@ -3045,56 +3035,142 @@
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
+          <t>05.01.03</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
+        </is>
+      </c>
+      <c r="D46" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>05.01.02 (pendiente, Secretario)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B47" s="33" t="inlineStr">
+        <is>
+          <t>06.01.01</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Dinero pequeño respetando los límites de 01.01.03</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>05.01.03 (pendiente, CEO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B48" s="33" t="inlineStr">
+        <is>
           <t>06.01.02</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
         </is>
       </c>
-      <c r="D46" s="28" t="inlineStr">
+      <c r="D48" s="28" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>PRODUCTO</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>06.01.01 (pendiente, Constructores)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="46" customHeight="1">
-      <c r="A48" s="35" t="inlineStr">
-        <is>
-          <t>Aviso de la regla 8 (CLAUDE.md): si la cola de arriba solo tuviera tareas de MOTOR, hay que parar y avisar al CEO; significa que la cola esta mal llena. Ahora mismo la cola tiene 3 de producto y 12 de motor.</t>
+    <row r="50" ht="46" customHeight="1">
+      <c r="A50" s="35" t="inlineStr">
+        <is>
+          <t>Aviso de la regla 8 (CLAUDE.md): si la cola de arriba solo tuviera tareas de MOTOR, hay que parar y avisar al CEO; significa que la cola esta mal llena. Ahora mismo la cola tiene 3 de producto y 13 de motor.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A26:I26"/>
     <mergeCell ref="C6:H6"/>
-    <mergeCell ref="A25:I25"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A50:I50"/>
     <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3107,7 +3183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4477,266 +4553,274 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="36" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>03.01.24</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 05/08 (nace de los huecos medidos por ejecución en 03.01.08): las tres barreras que hoy NO existen. (a) El patrón Bash( 02-datos/reservado) de .claude/settings.json exige un espacio literal y no cubre la ruta pegada a una comilla, así que una línea de python lo esquiva: sustituirlo por un patrón que cubra cualquier verbo y cualquier forma de escribir la ruta, y probarlo con las TRES formas. (b) Nada impide rm -rf dentro de 02-datos/, y los datos no están en git (regla 27 de CLAUDE.md): no se rehacen deshaciendo un commit, se rehacen volviendo a descargarlos. (c) No hay ninguna barrera de gasto, ni en código ni en configuración; D-26 de 00-direccion/DECISIONES.md deja escrito que --max-budget-usd existe. Regla 24 de CLAUDE.md: las tres nacen de una inyección ejecutada con su salida guardada, no de una sospecha, y ninguna causó daño. Regla 25 de CLAUDE.md: cada barrera nueva se verifica por inyección ANTES de documentarse como activa.</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>03.01.08</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>DESCONGELADA 12/08/2026 por D-36 de 00-direccion/DECISIONES.md, que da la letra aparte que D-29 exigia para aplicar el parche. Ficha de decisión preparada para el 06/08 FICHA ESCRITA Y ENTREGADA 06/08: 00-direccion/informes/FICHA_D-29.md, dos rondas, ACEPTA CON REPAROS de critico-codigo en la ronda 2, con sus dos reparos resueltos antes de cerrar. Los puntos (a), (b) y (c) de esta tarea son los puntos (a), (b) y (c) de la ficha. CORRECCIÓN DE ALCANCE QUE SALIÓ DE LA REVISIÓN, sobre (c): D-26 avisa de que --max-budget-usd puede ser inerte, y la celda de 03.01.23 lo da por medido —no hay clave de API en esta máquina y un tope en dólares no limita nada—, así que (c) puede resultar imposible […] texto completo en 00-direccion/WBS.md</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>03.01.25</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 05/08 (nace del incidente de este mismo día): guardia en .githooks/pre-commit que ejecuta la métrica de L-027 de 00-direccion/LECCIONES.md sobre 00-direccion/WBS.md y rechaza el commit si alguna fila de tarea no da 7 campos al partirla por la barra vertical. Motivo: hoy la métrica existe, está escrita como normativa en este WBS, y no la ejecuta nadie automáticamente; 05-vista-ceo/verificar_excel.py no la cubre. Es el muro que le falta a la única fuente de verdad del proyecto. Regla 24 de CLAUDE.md: nace de un incidente real y medido — el 05/08 cuatro filas quedaron partidas y ningún guardia se enteró. Regla 25 de CLAUDE.md: se verifica por inyección de una fila rota ANTES de documentarse como activo. AVISO PARA QUIEN LA EJECUTE, medido el mismo día: el propio texto de esta fila no puede contener el comando literal, porque la barra vertical que lleva dentro rompe la fila que describe; el guardia tiene que tolerar esa cita cuando aparezca en prosa fuera de una tabla.</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Constructor de motor</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>03.01.01</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>DESCONGELADA 12/08/2026 por D-36 de 00-direccion/DECISIONES.md, que da la letra aparte que D-29 exigia para aplicar el parche. Entra como cuarto punto de la ficha D-29 del 06/08 CUMPLIDO 06/08: entra como punto (d) de 00-direccion/informes/FICHA_D-29.md, con la cifra restituida —el 05/08 se partieron cuatro filas— después de que un primer intento la perdiera al apretar prosa; la cazó critico-codigo (L-023 y L-034 de LECCIONES.md). SIGUE pendiente: no se ejecuta hasta que el CEO responda la letra.** Misma advertencia de cita que en 03.01.24: la ficha D-29 no está firmada en DECISIONES.md.</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="36" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="B44" s="37" t="inlineStr">
+      <c r="B46" s="37" t="inlineStr">
         <is>
           <t>HIPÓTESIS Y VALIDACIÓN (PUERTA G2)</t>
         </is>
       </c>
-      <c r="C44" s="37" t="n"/>
-      <c r="D44" s="37" t="n"/>
-      <c r="E44" s="37" t="n"/>
-      <c r="F44" s="37" t="n"/>
-      <c r="G44" s="37" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="38" t="inlineStr">
+      <c r="C46" s="37" t="n"/>
+      <c r="D46" s="37" t="n"/>
+      <c r="E46" s="37" t="n"/>
+      <c r="F46" s="37" t="n"/>
+      <c r="G46" s="37" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="38" t="inlineStr">
         <is>
           <t>04.01</t>
         </is>
       </c>
-      <c r="B45" s="39" t="inlineStr">
+      <c r="B47" s="39" t="inlineStr">
         <is>
           <t>Broker y cajones de datos</t>
         </is>
       </c>
-      <c r="C45" s="39" t="n"/>
-      <c r="D45" s="39" t="n"/>
-      <c r="E45" s="39" t="n"/>
-      <c r="F45" s="39" t="n"/>
-      <c r="G45" s="39" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="13" t="inlineStr">
-        <is>
-          <t>04.01.01</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
-        </is>
-      </c>
-      <c r="C46" s="28" t="inlineStr">
-        <is>
-          <t>CEO + Orquestador</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>02.03.03</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>** 06/08 — comparacion de brokers: ronda 2 cerrada en falso, con una cita literal falsa cazada → 00-direccion/expedientes/04.01.01.md</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (04/08, dictada por el orquestador): Por qué ahora: 02.03.03 cerró el 03/08 con D-19 y esta tarea quedó desbloqueada; es la única con plazo duro —10/08, sin retorno— y quedan 6 días. Alcance: comparar 3 o 4 brokers que ofrezcan XAUUSD al contado y entregar la tabla para que el CEO firme. PROHIBIDO ELEGIR: la elección es del CEO. Criterios obligatorios, uno por columna: (1) lote mínimo, y si admite fraccionado de 0,1 onzas —es eliminatorio de hecho: el lote entero son unos 1.962 € contra […] texto completo en 00-direccion/expedientes/04.01.01.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>04.01.02</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02) REQUISITO AÑADIDO 04/08: al recalcular con precios reales se comprueba que la entidad que publica la tarifa es la misma con la que se opera. Si no coinciden, la cifra vieja no se hereda: se vuelve a medir.</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Constructor datos</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>04.01.01</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr"/>
-      <c r="G47" s="4" t="inlineStr"/>
+      <c r="C47" s="39" t="n"/>
+      <c r="D47" s="39" t="n"/>
+      <c r="E47" s="39" t="n"/>
+      <c r="F47" s="39" t="n"/>
+      <c r="G47" s="39" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>04.01.03</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Constructor datos</t>
+          <t>Comparar 3-4 brokers del mercado elegido; elegir uno y abrir demo (CEO firma)</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
+        <is>
+          <t>CEO + Orquestador</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>04.01.01</t>
+          <t>02.03.03</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="4" t="inlineStr"/>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>** 06/08 — comparacion de brokers: ronda 2 cerrada en falso, con una cita literal falsa cazada → 00-direccion/expedientes/04.01.01.md</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (04/08, dictada por el orquestador): Por qué ahora: 02.03.03 cerró el 03/08 con D-19 y esta tarea quedó desbloqueada; es la única con plazo duro —10/08, sin retorno— y quedan 6 días. Alcance: comparar 3 o 4 brokers que ofrezcan XAUUSD al contado y entregar la tabla para que el CEO firme. PROHIBIDO ELEGIR: la elección es del CEO. Criterios obligatorios, uno por columna: (1) lote mínimo, y si admite fraccionado de 0,1 onzas —es eliminatorio de hecho: el lote entero son unos 1.962 € contra […] texto completo en 00-direccion/expedientes/04.01.01.md</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>04.01.04</t>
+          <t>04.01.02</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 09/08 (subtarea dentro del alcance de 04.01.01, creada por el orquestador, regla 2 de CLAUDE.md): re-derivar POR CÁLCULO el tamaño mínimo operable de XAUUSD en 4h y el requisito real de lote que 04.01.01 debe exigir al bróker</t>
+          <t>Recalcular costes con precios reales del broker (sustituye 02.01.02) REQUISITO AÑADIDO 04/08: al recalcular con precios reales se comprueba que la entidad que publica la tarifa es la misma con la que se opera. Si no coinciden, la cifra vieja no se hereda: se vuelve a medir.</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Constructor de datos</t>
+          <t>Constructor datos</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>02.02.01, 02.03.03</t>
+          <t>04.01.01</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>** 09/08 — re-derivacion de la comparacion de brokers; ficha escrita tarde y anotada como incumplimiento → 00-direccion/expedientes/04.01.04.md</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>en_curso — FICHA ESCRITA TARDE Y POR ESO ANOTADA (regla 5 de CLAUDE.md incumplida): el orquestador dictó esta subtarea en el reparto del 09/08 con código, motivo y criterio de hecho, pero ordenó ejecutarla sin mandar que se escribiera antes en este WBS; el trabajo se hizo el mismo día y la fila se añade después. Lo detectó validador al revisar la entrega, con grep -rn "04.01.04" 00-direccion/ devolviendo cero. Es el defecto de L-013 de LECCIONES.md, ya anotado en las celdas de 01.02.03 y […] texto completo en 00-direccion/expedientes/04.01.04.md</t>
-        </is>
-      </c>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="38" t="inlineStr">
-        <is>
-          <t>04.02</t>
-        </is>
-      </c>
-      <c r="B50" s="39" t="inlineStr">
-        <is>
-          <t>Investigación de hipótesis</t>
-        </is>
-      </c>
-      <c r="C50" s="39" t="n"/>
-      <c r="D50" s="39" t="n"/>
-      <c r="E50" s="39" t="n"/>
-      <c r="F50" s="39" t="n"/>
-      <c r="G50" s="39" t="n"/>
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>04.01.03</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Histórico limpio partido en 3 cajones: construir (train), ajustar (validación) y RESERVADO bajo llave (OOS, se abre una sola vez por variante). Ningún agente toca el reservado</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Constructor datos</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>04.01.01</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>04.02.01</t>
+          <t>04.01.04</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
+          <t>NUEVA 09/08 (subtarea dentro del alcance de 04.01.01, creada por el orquestador, regla 2 de CLAUDE.md): re-derivar POR CÁLCULO el tamaño mínimo operable de XAUUSD en 4h y el requisito real de lote que 04.01.01 debe exigir al bróker</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Investigador</t>
+          <t>Constructor de datos</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>03.01.02</t>
+          <t>02.02.01, 02.03.03</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr"/>
-      <c r="G51" s="4" t="inlineStr"/>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>** 09/08 — re-derivacion de la comparacion de brokers; ficha escrita tarde y anotada como incumplimiento → 00-direccion/expedientes/04.01.04.md</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>en_curso — FICHA ESCRITA TARDE Y POR ESO ANOTADA (regla 5 de CLAUDE.md incumplida): el orquestador dictó esta subtarea en el reparto del 09/08 con código, motivo y criterio de hecho, pero ordenó ejecutarla sin mandar que se escribiera antes en este WBS; el trabajo se hizo el mismo día y la fila se añade después. Lo detectó validador al revisar la entrega, con grep -rn "04.01.04" 00-direccion/ devolviendo cero. Es el defecto de L-013 de LECCIONES.md, ya anotado en las celdas de 01.02.03 y […] texto completo en 00-direccion/expedientes/04.01.04.md</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>04.02.02</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Investigador</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>04.02.01</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="4" t="inlineStr"/>
+      <c r="A52" s="38" t="inlineStr">
+        <is>
+          <t>04.02</t>
+        </is>
+      </c>
+      <c r="B52" s="39" t="inlineStr">
+        <is>
+          <t>Investigación de hipótesis</t>
+        </is>
+      </c>
+      <c r="C52" s="39" t="n"/>
+      <c r="D52" s="39" t="n"/>
+      <c r="E52" s="39" t="n"/>
+      <c r="F52" s="39" t="n"/>
+      <c r="G52" s="39" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
+          <t>Barrido de fuentes: papers, libros, foros, GitHub, X. Regla: mínimo 2 fuentes independientes verificables por idea; vendedores de cursos/señales no son fuente</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>04.02.02</t>
+          <t>03.01.02</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -4750,22 +4834,22 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>04.02.04</t>
+          <t>04.02.02</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
+          <t>Ficha por hipótesis: por qué existiría la ventaja, reglas de entrada/salida, mercado y vela. Sin lógica de por qué gana, no entra (nada de probar por probar)</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Investigador</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>04.02.03</t>
+          <t>04.02.01</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -4777,41 +4861,53 @@
       <c r="G54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="38" t="inlineStr">
-        <is>
-          <t>04.03</t>
-        </is>
-      </c>
-      <c r="B55" s="39" t="inlineStr">
-        <is>
-          <t>Laboratorio de pruebas (por hipótesis y variante)</t>
-        </is>
-      </c>
-      <c r="C55" s="39" t="n"/>
-      <c r="D55" s="39" t="n"/>
-      <c r="E55" s="39" t="n"/>
-      <c r="F55" s="39" t="n"/>
-      <c r="G55" s="39" t="n"/>
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>04.02.03</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Filtro de sentido: el Validador puntúa y se eligen las 3-5 mejores</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Validador</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>04.02.02</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>04.03.01</t>
+          <t>04.02.04</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Backtest con costes reales sobre el cajón de construir</t>
+          <t>Pre-registro de variantes: cada hipótesis deja escritas sus variantes ANTES de probar (máx. 5-7 por hipótesis). Lo no registrado no se prueba</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Constructores</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>04.01.03, 04.02.04, 04.03.07</t>
+          <t>04.02.03</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -4823,53 +4919,41 @@
       <c r="G56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="13" t="inlineStr">
-        <is>
-          <t>04.03.02</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>04.03.01</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr"/>
-      <c r="G57" s="4" t="inlineStr"/>
+      <c r="A57" s="38" t="inlineStr">
+        <is>
+          <t>04.03</t>
+        </is>
+      </c>
+      <c r="B57" s="39" t="inlineStr">
+        <is>
+          <t>Laboratorio de pruebas (por hipótesis y variante)</t>
+        </is>
+      </c>
+      <c r="C57" s="39" t="n"/>
+      <c r="D57" s="39" t="n"/>
+      <c r="E57" s="39" t="n"/>
+      <c r="F57" s="39" t="n"/>
+      <c r="G57" s="39" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
+          <t>Backtest con costes reales sobre el cajón de construir</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>04.03.02</t>
+          <t>04.01.03, 04.02.04, 04.03.07</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -4883,22 +4967,22 @@
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
+          <t>Ajuste SOLO con el cajón de validación; lo que no aguanta, muere aquí</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Validador</t>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>04.03.03</t>
+          <t>04.03.01</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -4912,12 +4996,12 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>04.03.05</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
+          <t>Prueba de fuego: UNA sola pasada por variante sobre el cajón reservado (OOS). Repetir sería hacerse trampa</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4927,7 +5011,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>04.03.04</t>
+          <t>04.03.02</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -4941,171 +5025,171 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>04.03.06</t>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (decisión del CEO, opción B): especificación del motor de backtest propio, escrita para una construcción desde cero y no para un trasplante</t>
+          <t>Robustez: Monte Carlo (barajar el orden de operaciones y meter pequeños cambios miles de veces: ¿aguanta o era suerte?) + walk-forward (repetir el ajuste avanzando en el tiempo)</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Arquitecto</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>02.03.03</t>
+          <t>04.03.03</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Hecha</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>** 04/08 — especificacion del motor de backtest: 16 requisitos con prueba ejecutable y 8 casos a mano → 00-direccion/expedientes/04.03.06.md</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (03/08, dictada por el orquestador): Por qué se rehace y no se rescata: el criterio de aceptación anterior vivía en la sección «Trasplante desde gb2 — criterios de aceptación», que la cirugía de D-21 borró y hoy solo existe en el historial de git. Nació describiendo qué se traía y qué se descartaba de otro proyecto, y se escribió el 30/07, antes de D-19 y antes de las mediciones de la Fase 02, así que no dice nada del oro, ni de la vela de 4h, ni del lote mínimo. Insumos obligatorios: los […] texto completo en 00-direccion/expedientes/04.03.06.md</t>
-        </is>
-      </c>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>04.03.07</t>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>NUEVA 03/08 (decisión del CEO, opción B): construir el motor de backtest desde cero contra la especificación de 04.03.06, tras retirar el anterior</t>
+          <t>Veredicto pasa/no pasa por variante, con los criterios de G2. Quien construyó no vota</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Constructor de motor</t>
+          <t>Validador</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>04.03.06, 07.01.03</t>
+          <t>04.03.04</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>04.03.06</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 03/08 (decisión del CEO, opción B): especificación del motor de backtest propio, escrita para una construcción desde cero y no para un trasplante</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Arquitecto</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>02.03.03</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
           <t>Hecha</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>** 04/08 — motor de backtest construido desde cero; procedencia independiente de las dos fuentes → 00-direccion/expedientes/04.03.07.md</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (03/08, dictada por el orquestador): PASO 0, que se ejecuta antes que nada: retirar del árbol de trabajo el motor anterior con git revert, sin reescribir historia, para que quien construya no lo tenga delante. El código sigue existiendo en el commit 0c35959 para siempre, y con él sus 44 funciones de prueba —13 en test_costs.py, 20 en test_execution.py y 11 en test_sizing.py, contadas sobre el commit— que la regla 20 de CLAUDE.md obliga a conservar aunque no se usen. Verificado antes de […] texto completo en 00-direccion/expedientes/04.03.07.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="38" t="inlineStr">
-        <is>
-          <t>04.04</t>
-        </is>
-      </c>
-      <c r="B63" s="39" t="inlineStr">
-        <is>
-          <t>Decisión y bucle</t>
-        </is>
-      </c>
-      <c r="C63" s="39" t="n"/>
-      <c r="D63" s="39" t="n"/>
-      <c r="E63" s="39" t="n"/>
-      <c r="F63" s="39" t="n"/>
-      <c r="G63" s="39" t="n"/>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>** 04/08 — especificacion del motor de backtest: 16 requisitos con prueba ejecutable y 8 casos a mano → 00-direccion/expedientes/04.03.06.md</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (03/08, dictada por el orquestador): Por qué se rehace y no se rescata: el criterio de aceptación anterior vivía en la sección «Trasplante desde gb2 — criterios de aceptación», que la cirugía de D-21 borró y hoy solo existe en el historial de git. Nació describiendo qué se traía y qué se descartaba de otro proyecto, y se escribió el 30/07, antes de D-19 y antes de las mediciones de la Fase 02, así que no dice nada del oro, ni de la vela de 4h, ni del lote mínimo. Insumos obligatorios: los […] texto completo en 00-direccion/expedientes/04.03.06.md</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.03.07</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
+          <t>NUEVA 03/08 (decisión del CEO, opción B): construir el motor de backtest desde cero contra la especificación de 04.03.06, tras retirar el anterior</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Secretario</t>
+          <t>Constructor de motor</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>04.03.05</t>
+          <t>04.03.06, 07.01.03</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr"/>
-      <c r="G64" s="4" t="inlineStr"/>
+          <t>Hecha</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>** 04/08 — motor de backtest construido desde cero; procedencia independiente de las dos fuentes → 00-direccion/expedientes/04.03.07.md</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (03/08, dictada por el orquestador): PASO 0, que se ejecuta antes que nada: retirar del árbol de trabajo el motor anterior con git revert, sin reescribir historia, para que quien construya no lo tenga delante. El código sigue existiendo en el commit 0c35959 para siempre, y con él sus 44 funciones de prueba —13 en test_costs.py, 20 en test_execution.py y 11 en test_sizing.py, contadas sobre el commit— que la regla 20 de CLAUDE.md obliga a conservar aunque no se usen. Verificado antes de […] texto completo en 00-direccion/expedientes/04.03.07.md</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="13" t="inlineStr">
-        <is>
-          <t>04.04.02</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Orquestador</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>04.04.01</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr"/>
-      <c r="G65" s="4" t="inlineStr"/>
+      <c r="A65" s="38" t="inlineStr">
+        <is>
+          <t>04.04</t>
+        </is>
+      </c>
+      <c r="B65" s="39" t="inlineStr">
+        <is>
+          <t>Decisión y bucle</t>
+        </is>
+      </c>
+      <c r="C65" s="39" t="n"/>
+      <c r="D65" s="39" t="n"/>
+      <c r="E65" s="39" t="n"/>
+      <c r="F65" s="39" t="n"/>
+      <c r="G65" s="39" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>04.04.03</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
-        </is>
-      </c>
-      <c r="C66" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Informe de la vuelta: qué pasó, qué murió y por qué. Registro de TODAS las pruebas, también fallidas</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Secretario</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>04.04.01</t>
+          <t>04.03.05</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -5116,42 +5200,54 @@
       <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="inlineStr"/>
     </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="36" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="B67" s="37" t="inlineStr">
-        <is>
-          <t>DEMO (PUERTA G3) — SE DETALLA AL CERRAR G2</t>
-        </is>
-      </c>
-      <c r="C67" s="37" t="n"/>
-      <c r="D67" s="37" t="n"/>
-      <c r="E67" s="37" t="n"/>
-      <c r="F67" s="37" t="n"/>
-      <c r="G67" s="37" t="n"/>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>04.04.02</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Si ninguna pasa: volver a 04.02 con lecciones (vuelta 2, 3…). Tras la 3ª vuelta sin éxito: revisión completa del planteamiento con el CEO</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>04.04.01</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>05.01.01</t>
+          <t>04.04.03</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Bot en demo, solo y con guardias automáticos</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
+          <t>PUERTA G2: el CEO decide qué pasa a demo</t>
+        </is>
+      </c>
+      <c r="C68" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>04.04.03</t>
+          <t>04.04.01</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -5159,186 +5255,186 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>REQUISITO AÑADIDO POR D-14 (01/08): el guardia de parada dura (-30% del capital inicial) lo aplica el BOT de forma CONTINUA, no una revision periodica; comprobado solo una vez al mes, un -30% puede ser un -45% cuando alguien mire. Se verifica por inyeccion antes de declararlo activo (regla 25 de CLAUDE.md).</t>
-        </is>
-      </c>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="inlineStr"/>
     </row>
-    <row r="69">
-      <c r="A69" s="13" t="inlineStr">
-        <is>
-          <t>05.01.02</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>Secretario</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>05.01.01</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr"/>
-      <c r="G69" s="4" t="inlineStr"/>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="36" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B69" s="37" t="inlineStr">
+        <is>
+          <t>DEMO (PUERTA G3) — SE DETALLA AL CERRAR G2</t>
+        </is>
+      </c>
+      <c r="C69" s="37" t="n"/>
+      <c r="D69" s="37" t="n"/>
+      <c r="E69" s="37" t="n"/>
+      <c r="F69" s="37" t="n"/>
+      <c r="G69" s="37" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>05.01.03</t>
+          <t>05.01.01</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
-        </is>
-      </c>
-      <c r="C70" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
+          <t>Bot en demo, solo y con guardias automáticos</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
+          <t>04.04.03</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>REQUISITO AÑADIDO POR D-14 (01/08): el guardia de parada dura (-30% del capital inicial) lo aplica el BOT de forma CONTINUA, no una revision periodica; comprobado solo una vez al mes, un -30% puede ser un -45% cuando alguien mire. Se verifica por inyeccion antes de declararlo activo (regla 25 de CLAUDE.md).</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
           <t>05.01.02</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Seguimiento semanal real vs. prometido (8-12 semanas)</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Secretario</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>05.01.01</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr"/>
-      <c r="G70" s="4" t="inlineStr"/>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="36" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="B71" s="37" t="inlineStr">
-        <is>
-          <t>REAL (PUERTA G4) — SE DETALLA AL CERRAR G3</t>
-        </is>
-      </c>
-      <c r="C71" s="37" t="n"/>
-      <c r="D71" s="37" t="n"/>
-      <c r="E71" s="37" t="n"/>
-      <c r="F71" s="37" t="n"/>
-      <c r="G71" s="37" t="n"/>
+      <c r="F71" s="4" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
+          <t>05.01.03</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>PUERTA G3: CEO decide dinero, cuánto y pérdida máxima</t>
+        </is>
+      </c>
+      <c r="C72" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>05.01.02</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="36" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B73" s="37" t="inlineStr">
+        <is>
+          <t>REAL (PUERTA G4) — SE DETALLA AL CERRAR G3</t>
+        </is>
+      </c>
+      <c r="C73" s="37" t="n"/>
+      <c r="D73" s="37" t="n"/>
+      <c r="E73" s="37" t="n"/>
+      <c r="F73" s="37" t="n"/>
+      <c r="G73" s="37" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
           <t>06.01.01</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>Dinero pequeño respetando los límites de 01.01.03</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>Constructores</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>05.01.03</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>limites ya escritos y firmados (D-14, 01/08): capital 1.000-2.000 €, AVISO a -25% del capital inicial que no para nada, PARADA DURA AUTOMATICA a -30% aplicada por el bot de forma continua y sin exencion activable desde dentro (regla 26 de CLAUDE.md).</t>
         </is>
       </c>
-      <c r="G72" s="4" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="13" t="inlineStr">
-        <is>
-          <t>06.01.02</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
-        </is>
-      </c>
-      <c r="C73" s="28" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>06.01.01</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr"/>
-      <c r="G73" s="4" t="inlineStr"/>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="36" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="B74" s="37" t="inlineStr">
-        <is>
-          <t>MOTOR Y ORDEN (PARALELA; MÁX. 20% DEL ESFUERZO SEMANAL)</t>
-        </is>
-      </c>
-      <c r="C74" s="37" t="n"/>
-      <c r="D74" s="37" t="n"/>
-      <c r="E74" s="37" t="n"/>
-      <c r="F74" s="37" t="n"/>
-      <c r="G74" s="37" t="n"/>
+      <c r="G74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>07.01.01</t>
+          <t>06.01.02</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>Constructores</t>
+          <t>PUERTA G4 mensual: seguir, ampliar o parar. Si pierde más de lo escrito, se para sin discusión</t>
+        </is>
+      </c>
+      <c r="C75" s="28" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>03.01.01</t>
+          <t>06.01.01</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -5346,90 +5442,136 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>** 02/08 — orden de carpetas y documentos: la cifra 246/105 retirada por no reproducirse. Sin cerrar → 00-direccion/expedientes/07.01.01.md</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (02/08): ALCANCE — cuatro arreglos de documento, NINGUNO toca código: (a) Las celdas ESTADO de 01.02.04 y 03.01.12 declaran en negrita un estado del vocabulario pendiente / en_curso / hecha / bloqueada, como exige la sección «Estados y cadencia de este WBS». Valores ya decididos por el orquestador, no se deducen: 01.02.04 pasa a en_curso (entregado INFORME_MCP_2.md, RECHAZADO por critico-codigo, sin reparar); 03.01.12 pasa a pendiente (nadie la ha trabajado). En 01.02.04 la marca actual […] texto completo en 00-direccion/expedientes/07.01.01.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="13" t="inlineStr">
-        <is>
-          <t>07.01.03</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>Orquestador</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>En curso</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>** 09/08 — auditoria de lo escrito sin flujo el 03/08; los lotes de aptitud cancelados por el CEO → 00-direccion/expedientes/07.01.03.md</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (03/08, dictada por el orquestador): Qué pasó, medido y no supuesto: tras un /compact a las 21:29, la sesión recibió una orden del CEO a las 21:44 y trabajó sola hasta las 21:58 sin invocar a un solo subagente. Escribió D-19, D-20 y D-21 en un registro de solo-añadir, L-024 a L-027, cirugía estructural sobre el WBS, y dos scripts del Excel del CEO. Nadie lo revisó (regla 16 de CLAUDE.md y C2 rotas). Alcance: tres lotes con veredicto propio — (d) procedencia del motor de backtest, (b y c) […] texto completo en 00-direccion/expedientes/07.01.03.md</t>
-        </is>
-      </c>
+      <c r="F75" s="4" t="inlineStr"/>
+      <c r="G75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="36" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B76" s="37" t="inlineStr">
+        <is>
+          <t>MOTOR Y ORDEN (PARALELA; MÁX. 20% DEL ESFUERZO SEMANAL)</t>
+        </is>
+      </c>
+      <c r="C76" s="37" t="n"/>
+      <c r="D76" s="37" t="n"/>
+      <c r="E76" s="37" t="n"/>
+      <c r="F76" s="37" t="n"/>
+      <c r="G76" s="37" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
+          <t>07.01.01</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Carpetas y documentos en orden; una fuente de verdad por tema; lo sustituido se borra</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Constructores</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>03.01.01</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>** 02/08 — orden de carpetas y documentos: la cifra 246/105 retirada por no reproducirse. Sin cerrar → 00-direccion/expedientes/07.01.01.md</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (02/08): ALCANCE — cuatro arreglos de documento, NINGUNO toca código: (a) Las celdas ESTADO de 01.02.04 y 03.01.12 declaran en negrita un estado del vocabulario pendiente / en_curso / hecha / bloqueada, como exige la sección «Estados y cadencia de este WBS». Valores ya decididos por el orquestador, no se deducen: 01.02.04 pasa a en_curso (entregado INFORME_MCP_2.md, RECHAZADO por critico-codigo, sin reparar); 03.01.12 pasa a pendiente (nadie la ha trabajado). En 01.02.04 la marca actual […] texto completo en 00-direccion/expedientes/07.01.01.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>07.01.03</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>NUEVA 03/08 (incidente de proceso): auditar todo lo escrito el 03/08/2026 entre las 21:44 y las 21:58 sin flujo de cuatro capas, y el residuo sin commitear del tramo anterior</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Orquestador</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>** 09/08 — auditoria de lo escrito sin flujo el 03/08; los lotes de aptitud cancelados por el CEO → 00-direccion/expedientes/07.01.03.md</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>FICHA (03/08, dictada por el orquestador): Qué pasó, medido y no supuesto: tras un /compact a las 21:29, la sesión recibió una orden del CEO a las 21:44 y trabajó sola hasta las 21:58 sin invocar a un solo subagente. Escribió D-19, D-20 y D-21 en un registro de solo-añadir, L-024 a L-027, cirugía estructural sobre el WBS, y dos scripts del Excel del CEO. Nadie lo revisó (regla 16 de CLAUDE.md y C2 rotas). Alcance: tres lotes con veredicto propio — (d) procedencia del motor de backtest, (b y c) […] texto completo en 00-direccion/expedientes/07.01.03.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
           <t>07.01.02</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>Mejoras del motor: SOLO tareas aprobadas en revisión semanal (el motor no manda)</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>Constructores</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>03.01.02</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr"/>
-      <c r="G77" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G77"/>
+  <autoFilter ref="A4:G79"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E77">
+  <conditionalFormatting sqref="E5:E79">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecha"</formula>
     </cfRule>
@@ -5441,7 +5583,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,Hecha,Bloqueada"</formula1>
     </dataValidation>
   </dataValidations>

--- a/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
+++ b/05-vista-ceo/WBS_Bot_Trading_v0.9.xlsx
@@ -4400,14 +4400,10 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>** 03/08 — ficha escrita: reparar la prueba 7 del verificador para que examine celdas completas. Sin ejecutar → 00-direccion/expedientes/03.01.17.md</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>FICHA (03/08): Problema reproducido hoy: la prueba 7 localiza entregables citados en las celdas de tarea, pero corta cada celda por el primer hecha y solo examina lo que va después. En 03.01.13 ese marcador es el último carácter de la celda, así que examina cero ficheros y no caza que esa tarea, marcada hecha, cita 00-direccion/PENDIENTE-03.01.13-lista-de-reglas.md, que no existe en disco ni ha existido nunca en git. Dos defectos más: busca por nombre de fichero en CUALQUIER parte del […] texto completo en 00-direccion/expedientes/03.01.17.md</t>
-        </is>
-      </c>
+          <t>** 03/08 — ficha escrita: reparar la prueba 7 del verificador para que examine celdas completas. La reparacion de la prueba 7 SIGUE sin ejecutar; el 12/08 se ejecuto solo el bloque recortado por el CEO (comprobacion cero en dos fichas + los 9 avisos clasificados) → 00-direccion/expedientes/03.01.17.md</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
